--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -201,13 +201,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура — разовая закупка, в ежемесячную себестоимость не входит</t>
+          <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
+        <f>Данные!$B$20*Данные!$B$9</f>
         <v/>
       </c>
       <c r="E19" s="30" t="n">
@@ -1530,106 +1530,134 @@
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="31" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Штат УКПФ</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="6">
+        <f>Данные!$C$20*Данные!$B$9</f>
+        <v/>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F20" s="9">
-        <f>SUM(F19:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="F21" s="9">
+        <f>SUM(F19:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>За год</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D25" s="6">
         <f>Данные!$B$54</f>
         <v/>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E25" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="12">
-        <f>D24*E24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="E25" s="31" t="inlineStr">
+      <c r="F25" s="12">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F25" s="9">
-        <f>SUM(F24:F24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
-        </is>
+      <c r="F26" s="9">
+        <f>SUM(F25:F25)</f>
+        <v/>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -1638,8 +1666,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1651,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2258,7 +2286,7 @@
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура — разовая закупка, в ежемесячную себестоимость не входит</t>
+          <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -2267,7 +2295,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <f>(SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30))*Данные!$B$9</f>
+        <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
         <v/>
       </c>
       <c r="E31" s="30" t="n">
@@ -2279,86 +2307,86 @@
       </c>
     </row>
     <row r="32">
-      <c r="E32" s="31" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Штат УКПФ</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="6">
+        <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
+        <v/>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="12">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F32" s="9">
-        <f>SUM(F31:F31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="F33" s="9">
+        <f>SUM(F31:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C35" s="28" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F35" s="28" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>За год</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B36" s="29" t="inlineStr">
-        <is>
-          <t>Айыртау БП</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D36" s="6">
-        <f>Данные!$B$48</f>
-        <v/>
-      </c>
-      <c r="E36" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="F36" s="12">
-        <f>D36*E36</f>
-        <v/>
       </c>
     </row>
     <row r="37">
@@ -2369,7 +2397,7 @@
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Многоэтажки Д и Г</t>
+          <t>Айыртау БП</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -2378,7 +2406,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <f>Данные!$B$49</f>
+        <f>Данные!$B$48</f>
         <v/>
       </c>
       <c r="E37" s="30" t="n">
@@ -2397,7 +2425,7 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Площадки А, Б, Е, Ж, В (РМ), В</t>
+          <t>Многоэтажки Д и Г</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
@@ -2406,7 +2434,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <f>Данные!$B$50</f>
+        <f>Данные!$B$49</f>
         <v/>
       </c>
       <c r="E38" s="30" t="n">
@@ -2418,35 +2446,63 @@
       </c>
     </row>
     <row r="39">
-      <c r="E39" s="31" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>Площадки А, Б, Е, Ж, В (РМ), В</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D39" s="6">
+        <f>Данные!$B$50</f>
+        <v/>
+      </c>
+      <c r="E39" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" s="12">
+        <f>D39*E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F39" s="9">
-        <f>SUM(F36:F38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
-        </is>
+      <c r="F40" s="9">
+        <f>SUM(F37:F39)</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
+          <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
           <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2458,7 +2514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2872,7 +2928,7 @@
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура — разовая закупка, в ежемесячную себестоимость не входит</t>
+          <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -2881,7 +2937,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
+        <f>Данные!$B$21*Данные!$B$9</f>
         <v/>
       </c>
       <c r="E24" s="30" t="n">
@@ -2893,101 +2949,129 @@
       </c>
     </row>
     <row r="25">
-      <c r="E25" s="31" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Штат УКПФ</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="6">
+        <f>Данные!$C$21*Данные!$B$9</f>
+        <v/>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="12">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F25" s="9">
-        <f>SUM(F24:F24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="F26" s="9">
+        <f>SUM(F24:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>За год</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D29" s="6">
+      <c r="D30" s="6">
         <f>Данные!$B$51</f>
         <v/>
       </c>
-      <c r="E29" s="30" t="n">
+      <c r="E30" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F29" s="12">
-        <f>D29*E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="E30" s="31" t="inlineStr">
+      <c r="F30" s="12">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F30" s="9">
-        <f>SUM(F29:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="F31" s="9">
+        <f>SUM(F30:F30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -2996,7 +3080,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3616,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3946,7 +4030,7 @@
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура — разовая закупка, в ежемесячную себестоимость не входит</t>
+          <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -3955,7 +4039,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <f>(Данные!$B$22+Данные!$C$22)*Данные!$B$9</f>
+        <f>Данные!$B$22*Данные!$B$9</f>
         <v/>
       </c>
       <c r="E19" s="30" t="n">
@@ -3967,34 +4051,62 @@
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="31" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Штат УКПФ</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="6">
+        <f>Данные!$C$22*Данные!$B$9</f>
+        <v/>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="12">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F20" s="9">
-        <f>SUM(F19:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
-        </is>
+      <c r="F21" s="9">
+        <f>SUM(F19:F20)</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
+          <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4007,16 +4119,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4124,7 +4238,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ И ЯДЫ РАЗДЕЛЬНО</t>
+          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ, ЗЕРНОЦИД И БРИКЕТЫ РАЗДЕЛЬНО</t>
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
@@ -4133,6 +4247,8 @@
       <c r="E11" s="16" t="n"/>
       <c r="F11" s="16" t="n"/>
       <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
@@ -4157,15 +4273,25 @@
       </c>
       <c r="E12" s="35" t="inlineStr">
         <is>
+          <t>Зерноцид, кг/мес</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
+        <is>
+          <t>Pest Killer, кг/мес</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="I12" s="35" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -4189,16 +4315,24 @@
         <f>B13*Данные!$B$8*Данные!$B$15+C13*Данные!$B$8*Данные!$B$16</f>
         <v/>
       </c>
-      <c r="E13" s="12">
-        <f>Данные!$G$20*Данные!$B$6*Данные!$B$15</f>
+      <c r="E13" s="37">
+        <f>Данные!$G$20</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>Данные!$F$20*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G13" s="17">
-        <f>D13+E13+F13</f>
+        <f>E13*Данные!$B$6*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="G13" s="37">
+        <f>Данные!$F$20</f>
+        <v/>
+      </c>
+      <c r="H13" s="12">
+        <f>G13*Данные!$B$7*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>D13+F13+H13</f>
         <v/>
       </c>
     </row>
@@ -4220,16 +4354,24 @@
         <f>B14*Данные!$B$8*Данные!$B$15+C14*Данные!$B$8*Данные!$B$16</f>
         <v/>
       </c>
-      <c r="E14" s="12">
-        <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6*Данные!$B$15</f>
+      <c r="E14" s="37">
+        <f>SUM(Данные!$G$23:$G$30)</f>
         <v/>
       </c>
       <c r="F14" s="12">
-        <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G14" s="17">
-        <f>D14+E14+F14</f>
+        <f>E14*Данные!$B$6*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="G14" s="37">
+        <f>SUM(Данные!$F$23:$F$30)</f>
+        <v/>
+      </c>
+      <c r="H14" s="12">
+        <f>G14*Данные!$B$7*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="I14" s="17">
+        <f>D14+F14+H14</f>
         <v/>
       </c>
     </row>
@@ -4251,16 +4393,24 @@
         <f>B15*Данные!$B$8*Данные!$B$15+C15*Данные!$B$8*Данные!$B$16</f>
         <v/>
       </c>
-      <c r="E15" s="12">
-        <f>Данные!$G$21*Данные!$B$6*Данные!$B$15</f>
+      <c r="E15" s="37">
+        <f>Данные!$G$21</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>Данные!$F$21*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G15" s="17">
-        <f>D15+E15+F15</f>
+        <f>E15*Данные!$B$6*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="G15" s="37">
+        <f>Данные!$F$21</f>
+        <v/>
+      </c>
+      <c r="H15" s="12">
+        <f>G15*Данные!$B$7*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>D15+F15+H15</f>
         <v/>
       </c>
     </row>
@@ -4282,16 +4432,24 @@
         <f>B16*Данные!$B$8*Данные!$B$15+C16*Данные!$B$8*Данные!$B$16</f>
         <v/>
       </c>
-      <c r="E16" s="12">
-        <f>Данные!$G$22*Данные!$B$6*Данные!$B$15</f>
+      <c r="E16" s="37">
+        <f>Данные!$G$22</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>Данные!$F$22*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G16" s="17">
-        <f>D16+E16+F16</f>
+        <f>E16*Данные!$B$6*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="G16" s="37">
+        <f>Данные!$F$22</f>
+        <v/>
+      </c>
+      <c r="H16" s="12">
+        <f>G16*Данные!$B$7*Данные!$B$15</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>D16+F16+H16</f>
         <v/>
       </c>
     </row>
@@ -4306,7 +4464,9 @@
       <c r="D17" s="11" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="11" t="n"/>
-      <c r="G17" s="17">
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="17">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v/>
       </c>
@@ -4323,7 +4483,7 @@
         <f>SUM(D13:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="38">
         <f>SUM(E13:E17)</f>
         <v/>
       </c>
@@ -4331,20 +4491,30 @@
         <f>SUM(F13:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="38">
         <f>SUM(G13:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="9">
+        <f>SUM(H13:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="9">
+        <f>SUM(I13:I17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>РАЗОВАЯ ЗАКУПКА ПРИМАНОЧНЫХ СТАНЦИЙ 1-го И 2-го КОНТУРА</t>
+          <t>РАЗОВАЯ ЗАКУПКА ПРИМАНОЧНЫХ СТАНЦИЙ</t>
         </is>
       </c>
       <c r="B20" s="16" t="n"/>
       <c r="C20" s="16" t="n"/>
       <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
@@ -4354,15 +4524,25 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>Точек 1-го и 2-го контура, шт</t>
+          <t>1-й контур, шт</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
+          <t>2-й контур, шт</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>Всего, шт</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
           <t>Цена, ₸/шт</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Разово, ₸</t>
         </is>
@@ -4375,15 +4555,23 @@
         </is>
       </c>
       <c r="B22" s="36">
-        <f>Данные!$B$20+Данные!$C$20</f>
-        <v/>
-      </c>
-      <c r="C22" s="6">
+        <f>Данные!$B$20</f>
+        <v/>
+      </c>
+      <c r="C22" s="36">
+        <f>Данные!$C$20</f>
+        <v/>
+      </c>
+      <c r="D22" s="36">
+        <f>B22+C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="6">
         <f>Данные!$B$9</f>
         <v/>
       </c>
-      <c r="D22" s="17">
-        <f>B22*C22</f>
+      <c r="F22" s="17">
+        <f>D22*E22</f>
         <v/>
       </c>
     </row>
@@ -4394,15 +4582,23 @@
         </is>
       </c>
       <c r="B23" s="36">
-        <f>SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30)</f>
-        <v/>
-      </c>
-      <c r="C23" s="6">
+        <f>SUM(Данные!$B$23:$B$30)</f>
+        <v/>
+      </c>
+      <c r="C23" s="36">
+        <f>SUM(Данные!$C$23:$C$30)</f>
+        <v/>
+      </c>
+      <c r="D23" s="36">
+        <f>B23+C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="6">
         <f>Данные!$B$9</f>
         <v/>
       </c>
-      <c r="D23" s="17">
-        <f>B23*C23</f>
+      <c r="F23" s="17">
+        <f>D23*E23</f>
         <v/>
       </c>
     </row>
@@ -4413,15 +4609,23 @@
         </is>
       </c>
       <c r="B24" s="36">
-        <f>Данные!$B$21+Данные!$C$21</f>
-        <v/>
-      </c>
-      <c r="C24" s="6">
+        <f>Данные!$B$21</f>
+        <v/>
+      </c>
+      <c r="C24" s="36">
+        <f>Данные!$C$21</f>
+        <v/>
+      </c>
+      <c r="D24" s="36">
+        <f>B24+C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="6">
         <f>Данные!$B$9</f>
         <v/>
       </c>
-      <c r="D24" s="17">
-        <f>B24*C24</f>
+      <c r="F24" s="17">
+        <f>D24*E24</f>
         <v/>
       </c>
     </row>
@@ -4432,15 +4636,23 @@
         </is>
       </c>
       <c r="B25" s="36">
-        <f>Данные!$B$22+Данные!$C$22</f>
-        <v/>
-      </c>
-      <c r="C25" s="6">
+        <f>Данные!$B$22</f>
+        <v/>
+      </c>
+      <c r="C25" s="36">
+        <f>Данные!$C$22</f>
+        <v/>
+      </c>
+      <c r="D25" s="36">
+        <f>B25+C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
         <f>Данные!$B$9</f>
         <v/>
       </c>
-      <c r="D25" s="17">
-        <f>B25*C25</f>
+      <c r="F25" s="17">
+        <f>D25*E25</f>
         <v/>
       </c>
     </row>
@@ -4450,13 +4662,21 @@
           <t>ИТОГО РАЗОВО</t>
         </is>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="39">
         <f>SUM(B22:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="9">
+      <c r="C26" s="39">
+        <f>SUM(C22:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="39">
         <f>SUM(D22:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="9">
+        <f>SUM(F22:F25)</f>
         <v/>
       </c>
     </row>
@@ -4517,7 +4737,7 @@
         <v/>
       </c>
       <c r="D30" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E30" s="17">
@@ -4542,7 +4762,7 @@
         <v/>
       </c>
       <c r="D31" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E31" s="17">
@@ -4567,7 +4787,7 @@
         <v/>
       </c>
       <c r="D32" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E32" s="17">
@@ -4592,7 +4812,7 @@
         <v/>
       </c>
       <c r="D33" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E33" s="17">
@@ -4617,7 +4837,7 @@
         <v/>
       </c>
       <c r="D34" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E34" s="17">
@@ -4642,7 +4862,7 @@
         <v/>
       </c>
       <c r="D35" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E35" s="17">
@@ -4667,7 +4887,7 @@
         <v/>
       </c>
       <c r="D36" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E36" s="17">
@@ -4692,7 +4912,7 @@
         <v/>
       </c>
       <c r="D37" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E37" s="17">
@@ -4717,7 +4937,7 @@
         <v/>
       </c>
       <c r="D38" s="12">
-        <f>'Штат УКПФ'!$G$18</f>
+        <f>'Штат УКПФ'!$I$18</f>
         <v/>
       </c>
       <c r="E38" s="17">
@@ -4824,7 +5044,7 @@
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
+      <c r="B6" s="40" t="n">
         <v>740</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4844,7 +5064,7 @@
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
+      <c r="B7" s="40" t="n">
         <v>3642.5</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4864,7 +5084,7 @@
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n">
+      <c r="B8" s="40" t="n">
         <v>160</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4884,7 +5104,7 @@
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="38" t="n">
+      <c r="B9" s="40" t="n">
         <v>2160</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4904,7 +5124,7 @@
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n">
+      <c r="B10" s="40" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4924,7 +5144,7 @@
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n">
+      <c r="B11" s="41" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -4944,7 +5164,7 @@
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n">
+      <c r="B12" s="40" t="n">
         <v>258488</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -4964,7 +5184,7 @@
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="38" t="n">
+      <c r="B13" s="40" t="n">
         <v>350000</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4984,7 +5204,7 @@
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="39" t="n">
+      <c r="B14" s="41" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -5004,7 +5224,7 @@
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="39" t="n">
+      <c r="B15" s="41" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -5024,7 +5244,7 @@
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="39" t="n">
+      <c r="B16" s="41" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -5100,23 +5320,23 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="39" t="n">
+      <c r="B20" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="39" t="n">
+      <c r="C20" s="41" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="41" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="32">
         <f>SUM(B20:D20)</f>
         <v/>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="40" t="n">
+      <c r="G20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -5131,23 +5351,23 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="39" t="n">
+      <c r="B21" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="39" t="n">
+      <c r="C21" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D21" s="41" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="32">
         <f>SUM(B21:D21)</f>
         <v/>
       </c>
-      <c r="F21" s="40" t="n">
+      <c r="F21" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="40" t="n">
+      <c r="G21" s="42" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="7" t="inlineStr"/>
@@ -5158,23 +5378,23 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="39" t="n">
+      <c r="B22" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="39" t="n">
+      <c r="C22" s="41" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="41" t="n">
         <v>63</v>
       </c>
       <c r="E22" s="32">
         <f>SUM(B22:D22)</f>
         <v/>
       </c>
-      <c r="F22" s="40" t="n">
+      <c r="F22" s="42" t="n">
         <v>1.3</v>
       </c>
-      <c r="G22" s="40" t="n">
+      <c r="G22" s="42" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -5189,23 +5409,23 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="39" t="n">
+      <c r="B23" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="41" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="32">
         <f>SUM(B23:D23)</f>
         <v/>
       </c>
-      <c r="F23" s="40" t="n">
+      <c r="F23" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="40" t="n">
+      <c r="G23" s="42" t="n">
         <v>2</v>
       </c>
       <c r="H23" s="7" t="inlineStr"/>
@@ -5216,23 +5436,23 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="39" t="n">
+      <c r="B24" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="39" t="n">
+      <c r="C24" s="41" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E24" s="32">
         <f>SUM(B24:D24)</f>
         <v/>
       </c>
-      <c r="F24" s="40" t="n">
+      <c r="F24" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="40" t="n">
+      <c r="G24" s="42" t="n">
         <v>2</v>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
@@ -5243,23 +5463,23 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="39" t="n">
+      <c r="B25" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="39" t="n">
+      <c r="C25" s="41" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D25" s="41" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="32">
         <f>SUM(B25:D25)</f>
         <v/>
       </c>
-      <c r="F25" s="40" t="n">
+      <c r="F25" s="42" t="n">
         <v>3.5</v>
       </c>
-      <c r="G25" s="40" t="n">
+      <c r="G25" s="42" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
@@ -5270,23 +5490,23 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="39" t="n">
+      <c r="B26" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="41" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="41" t="n">
         <v>80</v>
       </c>
       <c r="E26" s="32">
         <f>SUM(B26:D26)</f>
         <v/>
       </c>
-      <c r="F26" s="40" t="n">
+      <c r="F26" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="40" t="n">
+      <c r="G26" s="42" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
@@ -5297,23 +5517,23 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="39" t="n">
+      <c r="B27" s="41" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="39" t="n">
+      <c r="C27" s="41" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D27" s="41" t="n">
         <v>64</v>
       </c>
       <c r="E27" s="32">
         <f>SUM(B27:D27)</f>
         <v/>
       </c>
-      <c r="F27" s="40" t="n">
+      <c r="F27" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="40" t="n">
+      <c r="G27" s="42" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
@@ -5324,23 +5544,23 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="39" t="n">
+      <c r="B28" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="39" t="n">
+      <c r="C28" s="41" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D28" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="32">
         <f>SUM(B28:D28)</f>
         <v/>
       </c>
-      <c r="F28" s="40" t="n">
+      <c r="F28" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="40" t="n">
+      <c r="G28" s="42" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
@@ -5351,23 +5571,23 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="39" t="n">
+      <c r="B29" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="39" t="n">
+      <c r="C29" s="41" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D29" s="41" t="n">
         <v>10</v>
       </c>
       <c r="E29" s="32">
         <f>SUM(B29:D29)</f>
         <v/>
       </c>
-      <c r="F29" s="40" t="n">
+      <c r="F29" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="40" t="n">
+      <c r="G29" s="42" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="7" t="inlineStr"/>
@@ -5378,23 +5598,23 @@
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="39" t="n">
+      <c r="B30" s="41" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="39" t="n">
+      <c r="C30" s="41" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D30" s="41" t="n">
         <v>24</v>
       </c>
       <c r="E30" s="32">
         <f>SUM(B30:D30)</f>
         <v/>
       </c>
-      <c r="F30" s="40" t="n">
+      <c r="F30" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="40" t="n">
+      <c r="G30" s="42" t="n">
         <v>3</v>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
@@ -5409,8 +5629,8 @@
       <c r="C31" s="32" t="n"/>
       <c r="D31" s="32" t="n"/>
       <c r="E31" s="32" t="n"/>
-      <c r="F31" s="41" t="n"/>
-      <c r="G31" s="41" t="n"/>
+      <c r="F31" s="37" t="n"/>
+      <c r="G31" s="37" t="n"/>
       <c r="H31" s="7" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
@@ -5427,8 +5647,8 @@
       <c r="C32" s="32" t="n"/>
       <c r="D32" s="32" t="n"/>
       <c r="E32" s="32" t="n"/>
-      <c r="F32" s="41" t="n"/>
-      <c r="G32" s="41" t="n"/>
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="37" t="n"/>
       <c r="H32" s="7" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
@@ -5441,27 +5661,27 @@
           <t>ИТОГО ПО ФАБРИКЕ</t>
         </is>
       </c>
-      <c r="B33" s="42">
+      <c r="B33" s="43">
         <f>SUM(B20:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="42">
+      <c r="C33" s="43">
         <f>SUM(C20:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="42">
+      <c r="D33" s="43">
         <f>SUM(D20:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="43">
         <f>SUM(E20:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="43">
+      <c r="F33" s="38">
         <f>SUM(F20:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="43">
+      <c r="G33" s="38">
         <f>SUM(G20:G32)</f>
         <v/>
       </c>
@@ -5513,7 +5733,7 @@
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="38" t="n">
+      <c r="B37" s="40" t="n">
         <v>96600</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -5533,7 +5753,7 @@
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="38" t="n">
+      <c r="B38" s="40" t="n">
         <v>618400</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -5553,7 +5773,7 @@
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="38" t="n">
+      <c r="B39" s="40" t="n">
         <v>478400</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -5573,7 +5793,7 @@
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="38" t="n">
+      <c r="B40" s="40" t="n">
         <v>569800</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -5593,7 +5813,7 @@
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="38" t="n">
+      <c r="B41" s="40" t="n">
         <v>440700</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -5613,7 +5833,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="38" t="n">
+      <c r="B42" s="40" t="n">
         <v>2599100</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -5633,7 +5853,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="38" t="n">
+      <c r="B43" s="40" t="n">
         <v>2010300</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -5653,7 +5873,7 @@
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="38" t="n">
+      <c r="B44" s="40" t="n">
         <v>126200</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -5673,7 +5893,7 @@
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="38" t="n">
+      <c r="B45" s="40" t="n">
         <v>106800</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -5693,7 +5913,7 @@
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="38" t="n">
+      <c r="B46" s="40" t="n">
         <v>126200</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -5713,7 +5933,7 @@
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="38" t="n">
+      <c r="B47" s="40" t="n">
         <v>106800</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -5733,7 +5953,7 @@
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="38" t="n">
+      <c r="B48" s="40" t="n">
         <v>720000</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -5753,7 +5973,7 @@
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="38" t="n">
+      <c r="B49" s="40" t="n">
         <v>1080000</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -5773,7 +5993,7 @@
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="38" t="n">
+      <c r="B50" s="40" t="n">
         <v>3000000</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -5793,7 +6013,7 @@
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="38" t="n">
+      <c r="B51" s="40" t="n">
         <v>100800</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -5813,7 +6033,7 @@
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="38" t="n">
+      <c r="B52" s="40" t="n">
         <v>160800</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -5833,7 +6053,7 @@
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="38" t="n">
+      <c r="B53" s="40" t="n">
         <v>75000</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -5853,7 +6073,7 @@
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="38" t="n">
+      <c r="B54" s="40" t="n">
         <v>70000</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -5873,7 +6093,7 @@
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="38" t="n">
+      <c r="B55" s="40" t="n">
         <v>3172000</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -5893,7 +6113,7 @@
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="38" t="n">
+      <c r="B56" s="40" t="n">
         <v>2074000</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -5913,7 +6133,7 @@
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="38" t="n">
+      <c r="B57" s="40" t="n">
         <v>2806000</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -5933,7 +6153,7 @@
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="38" t="n">
+      <c r="B58" s="40" t="n">
         <v>1830000</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -5953,7 +6173,7 @@
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="38" t="n">
+      <c r="B59" s="40" t="n">
         <v>180000</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5973,7 +6193,7 @@
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="38" t="n">
+      <c r="B60" s="40" t="n">
         <v>80000</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -5993,7 +6213,7 @@
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="39" t="n">
+      <c r="B61" s="41" t="n">
         <v>9</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -6013,7 +6233,7 @@
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="39" t="n">
+      <c r="B62" s="41" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -6033,7 +6253,7 @@
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="39" t="n">
+      <c r="B63" s="41" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="5" t="inlineStr">

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сравнение" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ККЗ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Бройлерные площадки" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Инкубаторий" sheetId="4" state="visible" r:id="rId4"/>
@@ -24,13 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="#,##0 &quot;₸&quot;;(#,##0 &quot;₸&quot;);&quot;—&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0 &quot;кг&quot;;;&quot;—&quot;"/>
-    <numFmt numFmtId="167" formatCode="0 %"/>
-    <numFmt numFmtId="168" formatCode="#,##0 &quot;шт&quot;;;&quot;—&quot;"/>
-    <numFmt numFmtId="169" formatCode="0.0&quot;×&quot;"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;×&quot;"/>
+    <numFmt numFmtId="166" formatCode="0 %"/>
+    <numFmt numFmtId="167" formatCode="#,##0;;&quot;—&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;;&quot;—&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -137,36 +136,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,30 +188,26 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,592 +573,1311 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СВОДКА · дератизация за год, ₸</t>
+          <t>СРАВНЕНИЕ КП · дератизация АО «Усть-Каменогорская птицефабрика», 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сравнивается только дератизация. Цены Indigo включают НДС, цены Pest Hunters — без НДС. Дезинсекция у обоих подрядчиков считается отдельно и в этот свод не входит.</t>
-        </is>
-      </c>
-    </row>
+          <t>Все суммы в тенге. Сравнивается только дератизация. Цены Indigo включают НДС, цены Pest Hunters — без НДС. Дезинсекция у обоих подрядчиков считается отдельно и сюда не входит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
+          <t>ККЗ · КОРМОЦЕХ</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>ККЗ</t>
-        </is>
-      </c>
-      <c r="B5" s="6">
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Что входит</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>барьер вокруг периметра кормоцеха и грязный барьер</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D6" s="10">
+        <f>E6/12</f>
+        <v>96600</v>
+      </c>
+      <c r="E6" s="11">
         <f>'ККЗ'!B5</f>
-        <v/>
-      </c>
-      <c r="C5" s="6">
+        <v>1159200</v>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>цены КП включают НДС</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>дератизация</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10">
+        <f>E7/12</f>
+        <v>75000</v>
+      </c>
+      <c r="E7" s="11">
         <f>'ККЗ'!C5</f>
-        <v/>
-      </c>
-      <c r="D5" s="6">
+        <v>900000</v>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>без НДС; дезинсекция ещё 70 000 ₸/мес отдельно</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · материалы</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>29 приманочных станций 2-го контура, 1 кг брикетов Pest Killer</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="10">
+        <f>E8/12</f>
+        <v>2124.791667</v>
+      </c>
+      <c r="E8" s="11">
         <f>'ККЗ'!D5</f>
-        <v/>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>кормоцех</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Бройлерные площадки</t>
-        </is>
-      </c>
-      <c r="B6" s="6">
+        <v>25497.5</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>зарплата в эту строку не входит — она общая на все объекты</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>БРОЙЛЕРНЫЕ ПЛОЩАДКИ</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Что входит</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>три группы: Айыртау БП, Многоэтажки Д и Г, Площадки А‚Б‚Е‚Ж‚В‚В(РМ) — полная замена оборудования</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D12" s="10">
+        <f>E12/12</f>
+        <v>3787300</v>
+      </c>
+      <c r="E12" s="11">
         <f>'Бройлерные площадки'!B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="6">
+        <v>45447600</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>1 139 ед. оборудования; вариант с частичной заменой — на листе «Бройлерные площадки»</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>122 объекта, оборудование подрядчика</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="10">
+        <f>E13/12</f>
+        <v>2897500</v>
+      </c>
+      <c r="E13" s="11">
         <f>'Бройлерные площадки'!C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
+        <v>34770000</v>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>3 172 000 ₸/мес март — ноябрь и 2 074 000 ₸/мес декабрь — февраль</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · материалы</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>8 площадок: 161 / 1 096 / 268 точек по контурам, 17 кг брикетов и 15 кг Зерноцида</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="10">
+        <f>E14/12</f>
+        <v>103343.125</v>
+      </c>
+      <c r="E14" s="11">
         <f>'Бройлерные площадки'!D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>8 площадок; у Indigo три группы, у Pest Hunters 122 объекта</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Инкубаторий</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>'Инкубаторий'!B5</f>
-        <v/>
-      </c>
-      <c r="C7" s="6">
-        <f>'Инкубаторий'!C5</f>
-        <v/>
-      </c>
-      <c r="D7" s="6">
-        <f>'Инкубаторий'!D5</f>
-        <v/>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>у Pest Hunters предложения нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>'ЗПП'!B5</f>
-        <v/>
-      </c>
-      <c r="C8" s="6">
-        <f>'ЗПП'!C5</f>
-        <v/>
-      </c>
-      <c r="D8" s="6">
-        <f>'ЗПП'!D5</f>
-        <v/>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>у Pest Hunters цена включает дезинсекцию; нормы штата не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>'Склад ТМЦ'!B5</f>
-        <v/>
-      </c>
-      <c r="C9" s="6">
-        <f>'Склад ТМЦ'!C5</f>
-        <v/>
-      </c>
-      <c r="D9" s="6">
-        <f>'Склад ТМЦ'!D5</f>
-        <v/>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>только Pest Hunters, апрель — декабрь</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>АБК</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>'АБК'!B5</f>
-        <v/>
-      </c>
-      <c r="C10" s="6">
-        <f>'АБК'!C5</f>
-        <v/>
-      </c>
-      <c r="D10" s="6">
-        <f>'АБК'!D5</f>
-        <v/>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>только штат УКПФ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Материалы и станции, итого</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>SUM(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>SUM(C5:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>SUM(D5:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="10" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Бутылки (штат, по объектам не разносятся)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="12">
-        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="E12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Фонд оплаты труда штата за год</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="12">
-        <f>Данные!$B$14*Данные!$B$12*12</f>
-        <v/>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>при окладе 258 488 ₸; вариант 350 000 ₸ — на листе «Штат УКПФ»</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>ИТОГО ЗА ГОД</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>B11</f>
-        <v/>
-      </c>
-      <c r="C14" s="14">
-        <f>C11</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>D11+D12+D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="10" t="n"/>
-    </row>
+        <v>1240117.5</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>зимой 1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ИНКУБАТОРИЙ</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Indigo Solutions дороже штата на</t>
-        </is>
-      </c>
-      <c r="B17" s="17">
-        <f>B14-D14</f>
-        <v/>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>во сколько раз</t>
-        </is>
-      </c>
-      <c r="D17" s="19">
-        <f>IF(D14=0,0,B14/D14)</f>
-        <v/>
-      </c>
-      <c r="E17" s="11" t="n"/>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Что входит</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Pest Hunters дороже штата на</t>
-        </is>
-      </c>
-      <c r="B18" s="17">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>во сколько раз</t>
-        </is>
-      </c>
-      <c r="D18" s="19">
-        <f>IF(D14=0,0,C14/D14)</f>
-        <v/>
-      </c>
-      <c r="E18" s="11" t="n"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>полная замена оборудования, 48 ед.</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D18" s="10">
+        <f>E18/12</f>
+        <v>126200</v>
+      </c>
+      <c r="E18" s="11">
+        <f>'Инкубаторий'!B5</f>
+        <v>1514400</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>появился в КП от 19.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>предложения нет</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="10">
+        <f>E19/12</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <f>'Инкубаторий'!C5</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>Условие</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Ставка</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>Цена за год, ₸</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>Формулировка из КП</t>
-        </is>
-      </c>
-    </row>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · материалы</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>18 / 34 / 12 точек по контурам, 1 кг брикетов и 1 кг Зерноцида</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="10">
+        <f>E20/12</f>
+        <v>5276.458333</v>
+      </c>
+      <c r="E20" s="11">
+        <f>'Инкубаторий'!D5</f>
+        <v>63317.5</v>
+      </c>
+      <c r="F20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Цена КП без скидок</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="17">
-        <f>B14</f>
-        <v/>
-      </c>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>все цены приведены в тенге и включают НДС</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>ЗПП · ЗАВОД ПО ПЕРЕРАБОТКЕ ПТИЦЫ</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Обслуживание всей территории фабрики</t>
-        </is>
-      </c>
-      <c r="B23" s="21">
-        <f>Данные!$B$64</f>
-        <v/>
-      </c>
-      <c r="C23" s="17">
-        <f>B14*(1-Данные!$B$64)</f>
-        <v/>
-      </c>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>при заключении договора на обслуживание всей территории птицефабрики предоставляется скидка 15 %</t>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Что входит</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Вся территория + 100 % предоплата за год</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="17">
-        <f>B14*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
-        <v/>
-      </c>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>при внесении 100 % предоплаты за год обслуживания предоставляется дополнительная скидка 15 %</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>полная замена оборудования</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D24" s="10">
+        <f>E24/12</f>
+        <v>126200</v>
+      </c>
+      <c r="E24" s="11">
+        <f>'ЗПП'!B5</f>
+        <v>1514400</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>дезинсекция ещё 160 800 ₸/мес отдельно</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Вся территория + предоплата + неплательщик НДС</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="17">
-        <f>B14*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
-        <v/>
-      </c>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>при заключении договора с компанией, не являющейся плательщиком НДС, предоставляется скидка 16 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-    </row>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>договор №88 от 01.01.2026 — дератизация и дезинсекция вместе</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="10">
+        <f>E25/12</f>
+        <v>180000</v>
+      </c>
+      <c r="E25" s="11">
+        <f>'ЗПП'!C5</f>
+        <v>2160000</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>8 309 м², бригада из трёх человек</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · материалы</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>нормы расхода по ЗПП не заданы</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" s="10">
+        <f>E26/12</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="11">
+        <f>'ЗПП'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>дайте нормы — строка встанет в расчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>Что зафиксировано в документах</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>СКЛАД ТМЦ</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Что входит</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>предложения нет</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="10">
+        <f>E30/12</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="11">
+        <f>'Склад ТМЦ'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>договор №921 от 01.04.2026 — дератизация и дезинсекция</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="10">
+        <f>E31/12</f>
+        <v>60000</v>
+      </c>
+      <c r="E31" s="11">
+        <f>'Склад ТМЦ'!C5</f>
+        <v>720000</v>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>действует апрель — декабрь, девять оплачиваемых месяцев</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · материалы</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>нормы расхода по складу не заданы</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="10">
+        <f>E32/12</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="11">
+        <f>'Склад ТМЦ'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="12" t="inlineStr"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>АБК · 11 КОРПУСОВ</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Что входит</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>предложения нет</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="10">
+        <f>E36/12</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="11">
+        <f>'АБК'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>предложения нет</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="10">
+        <f>E37/12</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="11">
+        <f>'АБК'!C5</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · материалы</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>63 клеевые станции и 39 приманочных, 1,3 кг брикетов</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="10">
+        <f>E38/12</f>
+        <v>17042.22917</v>
+      </c>
+      <c r="E38" s="11">
+        <f>'АБК'!D5</f>
+        <v>204506.75</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО ФАБРИКЕ</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr"/>
+      <c r="C41" s="13" t="inlineStr"/>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · все объекты</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="10">
+        <f>E42/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="E42" s="11">
+        <f>E6+E12+E18+E24+E30+E36</f>
+        <v>49635600</v>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>полная замена оборудования; скидки — ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters · все объекты</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n"/>
+      <c r="C43" s="14" t="n"/>
+      <c r="D43" s="10">
+        <f>E43/12</f>
+        <v>3212500</v>
+      </c>
+      <c r="E43" s="11">
+        <f>E7+E13+E19+E25+E31+E37</f>
+        <v>38550000</v>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>оборудование подрядчика; цены без НДС</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · материалы по объектам</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="10">
+        <f>E44/12</f>
+        <v>127786.6042</v>
+      </c>
+      <c r="E44" s="11">
+        <f>E8+E14+E20+E26+E32+E38</f>
+        <v>1533439.25</v>
+      </c>
+      <c r="F44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · бутылки</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="10">
+        <f>E45/12</f>
+        <v>1586.666667</v>
+      </c>
+      <c r="E45" s="11">
+        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
+        <v>19040</v>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>по объектам не разносятся</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · фонд оплаты труда</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="10">
+        <f>E46/12</f>
+        <v>1033952</v>
+      </c>
+      <c r="E46" s="11">
+        <f>Данные!$B$14*Данные!$B$12*12</f>
+        <v>12407424</v>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>при окладе 258 488 ₸ и текущей численности; вариант 350 000 ₸ — на листе «Штат УКПФ»</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ · ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="17">
+        <f>E47/12</f>
+        <v>1163325.271</v>
+      </c>
+      <c r="E47" s="18">
+        <f>E44+E45+E46</f>
+        <v>13959903.25</v>
+      </c>
+      <c r="F47" s="16" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions дороже штата</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n"/>
+      <c r="C50" s="39">
+        <f>IF(E47=0,0,E42/E47)</f>
+        <v>3.555583381</v>
+      </c>
+      <c r="D50" s="10">
+        <f>E50/12</f>
+        <v>2972974.729</v>
+      </c>
+      <c r="E50" s="11">
+        <f>E42-E47</f>
+        <v>35675696.75</v>
+      </c>
+      <c r="F50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Pest Hunters дороже штата</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="n"/>
+      <c r="C51" s="39">
+        <f>IF(E47=0,0,E43/E47)</f>
+        <v>2.761480457</v>
+      </c>
+      <c r="D51" s="10">
+        <f>E51/12</f>
+        <v>2049174.729</v>
+      </c>
+      <c r="E51" s="11">
+        <f>E43-E47</f>
+        <v>24590096.75</v>
+      </c>
+      <c r="F51" s="14" t="n"/>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr"/>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>В среднем в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>Формулировка из КП</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Цена КП без скидок</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="10">
+        <f>E55/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="E55" s="11">
+        <f>E42</f>
+        <v>49635600</v>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>все цены приведены в тенге и включают НДС</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Вся территория фабрики</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n"/>
+      <c r="C56" s="20">
+        <f>Данные!$B$64</f>
+        <v>0.15</v>
+      </c>
+      <c r="D56" s="10">
+        <f>E56/12</f>
+        <v>3515855</v>
+      </c>
+      <c r="E56" s="11">
+        <f>E42*(1-Данные!$B$64)</f>
+        <v>42190260</v>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>при заключении договора на обслуживание всей территории птицефабрики предоставляется скидка 15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Вся территория + 100 % предоплата</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="n"/>
+      <c r="C57" s="14" t="n"/>
+      <c r="D57" s="10">
+        <f>E57/12</f>
+        <v>2988476.75</v>
+      </c>
+      <c r="E57" s="11">
+        <f>E42*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+        <v>35861721</v>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>при внесении 100 % предоплаты за год обслуживания предоставляется дополнительная скидка 15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Вся территория + предоплата + неплательщик НДС</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n"/>
+      <c r="C58" s="14" t="n"/>
+      <c r="D58" s="10">
+        <f>E58/12</f>
+        <v>2510320.47</v>
+      </c>
+      <c r="E58" s="11">
+        <f>E42*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
+        <v>30123845.64</v>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>при заключении договора с компанией, не являющейся плательщиком НДС, предоставляется скидка 16 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr"/>
+      <c r="E61" s="13" t="inlineStr"/>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>Что зафиксировано в документах</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D62" s="14" t="n"/>
+      <c r="E62" s="14" t="n"/>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений, клеевые пластины меняются по мере необходимости</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="C30" s="22" t="n">
+      <c r="C63" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="D63" s="14" t="n"/>
+      <c r="E63" s="14" t="n"/>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>выезд по запросу</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>бройлерные площадки</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="D64" s="14" t="n"/>
+      <c r="E64" s="14" t="n"/>
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>дополнительные визиты по вызову заказчика</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C65" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="D65" s="14" t="n"/>
+      <c r="E65" s="14" t="n"/>
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>по утверждённому графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>склад ТМЦ</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C66" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="D66" s="14" t="n"/>
+      <c r="E66" s="14" t="n"/>
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>выезд по рекламации в течение двух рабочих дней</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C67" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="D67" s="14" t="n"/>
+      <c r="E67" s="14" t="n"/>
+      <c r="F67" s="12" t="inlineStr">
         <is>
           <t>присутствие на фабрике 5/2, реакция в тот же день</t>
         </is>
@@ -1167,7 +1885,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1198,466 +1916,471 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура, 1 кг брикетов Pest Killer на обработку.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="24">
         <f>F9</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
+        <v>1159200</v>
+      </c>
+      <c r="C5" s="24">
         <f>F10</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
+        <v>900000</v>
+      </c>
+      <c r="D5" s="24">
         <f>F11+F12+F13+F14</f>
-        <v/>
-      </c>
-    </row>
+        <v>25497.5</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="27">
         <f>Данные!$B$37</f>
-        <v/>
-      </c>
-      <c r="E9" s="30" t="n">
+        <v>96600</v>
+      </c>
+      <c r="E9" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="11">
         <f>D9*E9</f>
-        <v/>
+        <v>1159200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>дератизация</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="27">
         <f>Данные!$B$53</f>
-        <v/>
-      </c>
-      <c r="E10" s="30" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E10" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="11">
         <f>D10*E10</f>
-        <v/>
+        <v>900000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="27">
         <f>Данные!$D$20*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E11" s="30">
+        <v>0</v>
+      </c>
+      <c r="E11" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F11" s="17">
+        <v>7</v>
+      </c>
+      <c r="F11" s="11">
         <f>D11*E11</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="27">
         <f>Данные!$D$20*2*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E12" s="30">
+        <v>0</v>
+      </c>
+      <c r="E12" s="27">
         <f>Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
+        <v>5</v>
+      </c>
+      <c r="F12" s="11">
         <f>D12*E12</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="27">
         <f>Данные!$G$20*Данные!$B$6</f>
-        <v/>
-      </c>
-      <c r="E13" s="30">
+        <v>0</v>
+      </c>
+      <c r="E13" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F13" s="17">
+        <v>7</v>
+      </c>
+      <c r="F13" s="11">
         <f>D13*E13</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="27">
         <f>Данные!$F$20*Данные!$B$7</f>
-        <v/>
-      </c>
-      <c r="E14" s="30">
+        <v>3642.5</v>
+      </c>
+      <c r="E14" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
+        <v>7</v>
+      </c>
+      <c r="F14" s="11">
         <f>D14*E14</f>
-        <v/>
+        <v>25497.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="29">
         <f>SUM(F9:F14)</f>
-        <v/>
-      </c>
-    </row>
+        <v>2084697.5</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="27">
         <f>Данные!$B$20*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="10">
         <f>D19*E19</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="27">
         <f>Данные!$C$20*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E20" s="30" t="n">
+        <v>62640</v>
+      </c>
+      <c r="E20" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <f>D20*E20</f>
-        <v/>
+        <v>62640</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="29">
         <f>SUM(F19:F20)</f>
-        <v/>
-      </c>
-    </row>
+        <v>62640</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="27">
         <f>Данные!$B$54</f>
-        <v/>
-      </c>
-      <c r="E25" s="30" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E25" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="10">
         <f>D25*E25</f>
-        <v/>
+        <v>840000</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="29">
         <f>SUM(F25:F25)</f>
-        <v/>
-      </c>
-    </row>
+        <v>840000</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -1698,801 +2421,807 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="24">
         <f>F9+F10+F11</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
+        <v>45447600</v>
+      </c>
+      <c r="C5" s="24">
         <f>F12+F13</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
+        <v>34770000</v>
+      </c>
+      <c r="D5" s="24">
         <f>F14+F15+F16+F17</f>
-        <v/>
-      </c>
-    </row>
+        <v>1240117.5</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ОСНОВНОЙ ВАРИАНТ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="27">
         <f>Данные!$B$38</f>
-        <v/>
-      </c>
-      <c r="E9" s="30" t="n">
+        <v>618400</v>
+      </c>
+      <c r="E9" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="11">
         <f>D9*E9</f>
-        <v/>
+        <v>7420800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="27">
         <f>Данные!$B$40</f>
-        <v/>
-      </c>
-      <c r="E10" s="30" t="n">
+        <v>569800</v>
+      </c>
+      <c r="E10" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="11">
         <f>D10*E10</f>
-        <v/>
+        <v>6837600</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="27">
         <f>Данные!$B$42</f>
-        <v/>
-      </c>
-      <c r="E11" s="30" t="n">
+        <v>2599100</v>
+      </c>
+      <c r="E11" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="11">
         <f>D11*E11</f>
-        <v/>
+        <v>31189200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="27">
         <f>Данные!$B$55</f>
-        <v/>
-      </c>
-      <c r="E12" s="30">
+        <v>3172000</v>
+      </c>
+      <c r="E12" s="27">
         <f>Данные!$B$61</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
+        <v>9</v>
+      </c>
+      <c r="F12" s="11">
         <f>D12*E12</f>
-        <v/>
+        <v>28548000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="27">
         <f>Данные!$B$56</f>
-        <v/>
-      </c>
-      <c r="E13" s="30">
+        <v>2074000</v>
+      </c>
+      <c r="E13" s="27">
         <f>Данные!$B$62</f>
-        <v/>
-      </c>
-      <c r="F13" s="17">
+        <v>3</v>
+      </c>
+      <c r="F13" s="11">
         <f>D13*E13</f>
-        <v/>
+        <v>6222000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="27">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E14" s="30">
+        <v>42880</v>
+      </c>
+      <c r="E14" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
+        <v>7</v>
+      </c>
+      <c r="F14" s="11">
         <f>D14*E14</f>
-        <v/>
+        <v>300160</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="27">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E15" s="30">
+        <v>85760</v>
+      </c>
+      <c r="E15" s="27">
         <f>Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="F15" s="17">
+        <v>5</v>
+      </c>
+      <c r="F15" s="11">
         <f>D15*E15</f>
-        <v/>
+        <v>428800</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="27">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
-        <v/>
-      </c>
-      <c r="E16" s="30">
+        <v>11100</v>
+      </c>
+      <c r="E16" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F16" s="17">
+        <v>7</v>
+      </c>
+      <c r="F16" s="11">
         <f>D16*E16</f>
-        <v/>
+        <v>77700</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="27">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
-        <v/>
-      </c>
-      <c r="E17" s="30">
+        <v>61922.5</v>
+      </c>
+      <c r="E17" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F17" s="17">
+        <v>7</v>
+      </c>
+      <c r="F17" s="11">
         <f>D17*E17</f>
-        <v/>
+        <v>433457.5</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="31" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="29">
         <f>SUM(F9:F17)</f>
-        <v/>
-      </c>
-    </row>
+        <v>81457717.5</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="27">
         <f>Данные!$B$39</f>
-        <v/>
-      </c>
-      <c r="E22" s="30" t="n">
+        <v>478400</v>
+      </c>
+      <c r="E22" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="10">
         <f>D22*E22</f>
-        <v/>
+        <v>5740800</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="27">
         <f>Данные!$B$41</f>
-        <v/>
-      </c>
-      <c r="E23" s="30" t="n">
+        <v>440700</v>
+      </c>
+      <c r="E23" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="10">
         <f>D23*E23</f>
-        <v/>
+        <v>5288400</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="27">
         <f>Данные!$B$43</f>
-        <v/>
-      </c>
-      <c r="E24" s="30" t="n">
+        <v>2010300</v>
+      </c>
+      <c r="E24" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="10">
         <f>D24*E24</f>
-        <v/>
+        <v>24123600</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="27">
         <f>Данные!$B$57</f>
-        <v/>
-      </c>
-      <c r="E25" s="30">
+        <v>2806000</v>
+      </c>
+      <c r="E25" s="27">
         <f>Данные!$B$61</f>
-        <v/>
-      </c>
-      <c r="F25" s="12">
+        <v>9</v>
+      </c>
+      <c r="F25" s="10">
         <f>D25*E25</f>
-        <v/>
+        <v>25254000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="27">
         <f>Данные!$B$58</f>
-        <v/>
-      </c>
-      <c r="E26" s="30">
+        <v>1830000</v>
+      </c>
+      <c r="E26" s="27">
         <f>Данные!$B$62</f>
-        <v/>
-      </c>
-      <c r="F26" s="12">
+        <v>3</v>
+      </c>
+      <c r="F26" s="10">
         <f>D26*E26</f>
-        <v/>
+        <v>5490000</v>
       </c>
     </row>
     <row r="27">
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="29">
         <f>SUM(F22:F26)</f>
-        <v/>
-      </c>
-    </row>
+        <v>65896800</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F30" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="27">
         <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E31" s="30" t="n">
+        <v>347760</v>
+      </c>
+      <c r="E31" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="10">
         <f>D31*E31</f>
-        <v/>
+        <v>347760</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="27">
         <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E32" s="30" t="n">
+        <v>2367360</v>
+      </c>
+      <c r="E32" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="10">
         <f>D32*E32</f>
-        <v/>
+        <v>2367360</v>
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="29">
         <f>SUM(F31:F32)</f>
-        <v/>
-      </c>
-    </row>
+        <v>2715120</v>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F36" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F36" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Айыртау БП</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="27">
         <f>Данные!$B$48</f>
-        <v/>
-      </c>
-      <c r="E37" s="30" t="n">
+        <v>720000</v>
+      </c>
+      <c r="E37" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="10">
         <f>D37*E37</f>
-        <v/>
+        <v>8640000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="27">
         <f>Данные!$B$49</f>
-        <v/>
-      </c>
-      <c r="E38" s="30" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="E38" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="10">
         <f>D38*E38</f>
-        <v/>
+        <v>12960000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="27">
         <f>Данные!$B$50</f>
-        <v/>
-      </c>
-      <c r="E39" s="30" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E39" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="10">
         <f>D39*E39</f>
-        <v/>
+        <v>36000000</v>
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="31" t="inlineStr">
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="29">
         <f>SUM(F37:F39)</f>
-        <v/>
-      </c>
-    </row>
+        <v>57600000</v>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
         </is>
@@ -2533,545 +3262,551 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="24">
         <f>F9</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
+        <v>1514400</v>
+      </c>
+      <c r="C5" s="24">
         <f>F10</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24">
         <f>F11+F12+F13+F14</f>
-        <v/>
-      </c>
-    </row>
+        <v>63317.5</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="27">
         <f>Данные!$B$44</f>
-        <v/>
-      </c>
-      <c r="E9" s="30" t="n">
+        <v>126200</v>
+      </c>
+      <c r="E9" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="11">
         <f>D9*E9</f>
-        <v/>
+        <v>1514400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="11">
         <f>D10*E10</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="27">
         <f>Данные!$D$21*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E11" s="30">
+        <v>1920</v>
+      </c>
+      <c r="E11" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F11" s="17">
+        <v>7</v>
+      </c>
+      <c r="F11" s="11">
         <f>D11*E11</f>
-        <v/>
+        <v>13440</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="27">
         <f>Данные!$D$21*2*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E12" s="30">
+        <v>3840</v>
+      </c>
+      <c r="E12" s="27">
         <f>Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
+        <v>5</v>
+      </c>
+      <c r="F12" s="11">
         <f>D12*E12</f>
-        <v/>
+        <v>19200</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="27">
         <f>Данные!$G$21*Данные!$B$6</f>
-        <v/>
-      </c>
-      <c r="E13" s="30">
+        <v>740</v>
+      </c>
+      <c r="E13" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F13" s="17">
+        <v>7</v>
+      </c>
+      <c r="F13" s="11">
         <f>D13*E13</f>
-        <v/>
+        <v>5180</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="27">
         <f>Данные!$F$21*Данные!$B$7</f>
-        <v/>
-      </c>
-      <c r="E14" s="30">
+        <v>3642.5</v>
+      </c>
+      <c r="E14" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
+        <v>7</v>
+      </c>
+      <c r="F14" s="11">
         <f>D14*E14</f>
-        <v/>
+        <v>25497.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="29">
         <f>SUM(F9:F14)</f>
-        <v/>
-      </c>
-    </row>
+        <v>1577717.5</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>частичная замена оборудования</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="27">
         <f>Данные!$B$45</f>
-        <v/>
-      </c>
-      <c r="E19" s="30" t="n">
+        <v>106800</v>
+      </c>
+      <c r="E19" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="10">
         <f>D19*E19</f>
-        <v/>
+        <v>1281600</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="29">
         <f>SUM(F19:F19)</f>
-        <v/>
-      </c>
-    </row>
+        <v>1281600</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="27">
         <f>Данные!$B$21*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E24" s="30" t="n">
+        <v>38880</v>
+      </c>
+      <c r="E24" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="10">
         <f>D24*E24</f>
-        <v/>
+        <v>38880</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="27">
         <f>Данные!$C$21*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E25" s="30" t="n">
+        <v>73440</v>
+      </c>
+      <c r="E25" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="10">
         <f>D25*E25</f>
-        <v/>
+        <v>73440</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="29">
         <f>SUM(F24:F25)</f>
-        <v/>
-      </c>
-    </row>
+        <v>112320</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C29" s="28" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="27">
         <f>Данные!$B$51</f>
-        <v/>
-      </c>
-      <c r="E30" s="30" t="n">
+        <v>100800</v>
+      </c>
+      <c r="E30" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="10">
         <f>D30*E30</f>
-        <v/>
+        <v>1209600</v>
       </c>
     </row>
     <row r="31">
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="29">
         <f>SUM(F30:F30)</f>
-        <v/>
-      </c>
-    </row>
+        <v>1209600</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3111,357 +3846,362 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="24">
         <f>F9</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
+        <v>1514400</v>
+      </c>
+      <c r="C5" s="24">
         <f>F10</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
+        <v>2160000</v>
+      </c>
+      <c r="D5" s="24">
         <f>F11</f>
-        <v/>
-      </c>
-    </row>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>полная замена оборудования</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="27">
         <f>Данные!$B$46</f>
-        <v/>
-      </c>
-      <c r="E9" s="30" t="n">
+        <v>126200</v>
+      </c>
+      <c r="E9" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="11">
         <f>D9*E9</f>
-        <v/>
+        <v>1514400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="27">
         <f>Данные!$B$59</f>
-        <v/>
-      </c>
-      <c r="E10" s="30" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E10" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="11">
         <f>D10*E10</f>
-        <v/>
+        <v>2160000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="11">
         <f>D11*E11</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="31" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="29">
         <f>SUM(F9:F11)</f>
-        <v/>
-      </c>
-    </row>
+        <v>3674400</v>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>частичная замена оборудования</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="27">
         <f>Данные!$B$47</f>
-        <v/>
-      </c>
-      <c r="E16" s="30" t="n">
+        <v>106800</v>
+      </c>
+      <c r="E16" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="10">
         <f>D16*E16</f>
-        <v/>
+        <v>1281600</v>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="31" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="29">
         <f>SUM(F16:F16)</f>
-        <v/>
-      </c>
-    </row>
+        <v>1281600</v>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="27">
         <f>Данные!$B$52</f>
-        <v/>
-      </c>
-      <c r="E21" s="30" t="n">
+        <v>160800</v>
+      </c>
+      <c r="E21" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="10">
         <f>D21*E21</f>
-        <v/>
+        <v>1929600</v>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="31" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="29">
         <f>SUM(F21:F21)</f>
-        <v/>
-      </c>
-    </row>
+        <v>1929600</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3502,184 +4242,187 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="24">
         <f>F9</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
+        <v>0</v>
+      </c>
+      <c r="C5" s="24">
         <f>F10</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
+        <v>720000</v>
+      </c>
+      <c r="D5" s="24">
         <f>F11</f>
-        <v/>
-      </c>
-    </row>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="11">
         <f>D9*E9</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="27">
         <f>Данные!$B$60</f>
-        <v/>
-      </c>
-      <c r="E10" s="30">
+        <v>80000</v>
+      </c>
+      <c r="E10" s="27">
         <f>Данные!$B$63</f>
-        <v/>
-      </c>
-      <c r="F10" s="17">
+        <v>9</v>
+      </c>
+      <c r="F10" s="11">
         <f>D10*E10</f>
-        <v/>
+        <v>720000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="11">
         <f>D11*E11</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="31" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="29">
         <f>SUM(F9:F11)</f>
-        <v/>
-      </c>
-    </row>
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3719,385 +4462,389 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="24">
         <f>F9</f>
-        <v/>
-      </c>
-      <c r="C5" s="26">
+        <v>0</v>
+      </c>
+      <c r="C5" s="24">
         <f>F10</f>
-        <v/>
-      </c>
-      <c r="D5" s="26">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24">
         <f>F11+F12+F13+F14</f>
-        <v/>
-      </c>
-    </row>
+        <v>204506.75</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="11">
         <f>D9*E9</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="11">
         <f>D10*E10</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="27">
         <f>Данные!$D$22*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E11" s="30">
+        <v>10080</v>
+      </c>
+      <c r="E11" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F11" s="17">
+        <v>7</v>
+      </c>
+      <c r="F11" s="11">
         <f>D11*E11</f>
-        <v/>
+        <v>70560</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="27">
         <f>Данные!$D$22*2*Данные!$B$8</f>
-        <v/>
-      </c>
-      <c r="E12" s="30">
+        <v>20160</v>
+      </c>
+      <c r="E12" s="27">
         <f>Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
+        <v>5</v>
+      </c>
+      <c r="F12" s="11">
         <f>D12*E12</f>
-        <v/>
+        <v>100800</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="27">
         <f>Данные!$G$22*Данные!$B$6</f>
-        <v/>
-      </c>
-      <c r="E13" s="30">
+        <v>0</v>
+      </c>
+      <c r="E13" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F13" s="17">
+        <v>7</v>
+      </c>
+      <c r="F13" s="11">
         <f>D13*E13</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="27">
         <f>Данные!$F$22*Данные!$B$7</f>
-        <v/>
-      </c>
-      <c r="E14" s="30">
+        <v>4735.25</v>
+      </c>
+      <c r="E14" s="27">
         <f>Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
+        <v>7</v>
+      </c>
+      <c r="F14" s="11">
         <f>D14*E14</f>
-        <v/>
+        <v>33146.75</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="29">
         <f>SUM(F9:F14)</f>
-        <v/>
-      </c>
-    </row>
+        <v>204506.75</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
-        <is>
-          <t>Цена в месяц</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
-        <is>
-          <t>За год</t>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="27">
         <f>Данные!$B$22*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="10">
         <f>D19*E19</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="27">
         <f>Данные!$C$22*Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="E20" s="30" t="n">
+        <v>84240</v>
+      </c>
+      <c r="E20" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <f>D20*E20</f>
-        <v/>
+        <v>84240</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="29">
         <f>SUM(F19:F20)</f>
-        <v/>
-      </c>
-    </row>
+        <v>84240</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4147,810 +4894,815 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ФОНД ОПЛАТЫ ТРУДА</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Показатель, ₸</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Оклад одного дератизатора, ₸/мес</t>
         </is>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <f>Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C6" s="12">
+        <v>258488</v>
+      </c>
+      <c r="C6" s="10">
         <f>Данные!$B$13</f>
-        <v/>
+        <v>350000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="10">
         <f>Данные!$B$14</f>
-        <v/>
-      </c>
-      <c r="C7" s="32">
+        <v>4</v>
+      </c>
+      <c r="C7" s="10">
         <f>Данные!$B$14</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Зарплата в месяц</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <f>B6*B7</f>
-        <v/>
-      </c>
-      <c r="C8" s="12">
+        <v>1033952</v>
+      </c>
+      <c r="C8" s="10">
         <f>C6*C7</f>
-        <v/>
+        <v>1400000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="11">
         <f>B8*12</f>
-        <v/>
-      </c>
-      <c r="C9" s="17">
+        <v>12407424</v>
+      </c>
+      <c r="C9" s="11">
         <f>C8*12</f>
-        <v/>
-      </c>
-    </row>
+        <v>16800000</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ, ЗЕРНОЦИД И БРИКЕТЫ РАЗДЕЛЬНО</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="31">
         <f>Данные!$D$20</f>
-        <v/>
-      </c>
-      <c r="C13" s="36">
+        <v>0</v>
+      </c>
+      <c r="C13" s="31">
         <f>Данные!$D$20*2</f>
-        <v/>
-      </c>
-      <c r="D13" s="12">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
         <f>B13*Данные!$B$8*Данные!$B$15+C13*Данные!$B$8*Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="E13" s="37">
+        <v>0</v>
+      </c>
+      <c r="E13" s="40">
         <f>Данные!$G$20</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
         <f>E13*Данные!$B$6*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G13" s="37">
+        <v>0</v>
+      </c>
+      <c r="G13" s="40">
         <f>Данные!$F$20</f>
-        <v/>
-      </c>
-      <c r="H13" s="12">
+        <v>1</v>
+      </c>
+      <c r="H13" s="10">
         <f>G13*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
+        <v>25497.5</v>
+      </c>
+      <c r="I13" s="11">
         <f>D13+F13+H13</f>
-        <v/>
+        <v>25497.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="31">
         <f>SUM(Данные!$D$23:$D$30)</f>
-        <v/>
-      </c>
-      <c r="C14" s="36">
+        <v>268</v>
+      </c>
+      <c r="C14" s="31">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
-        <v/>
-      </c>
-      <c r="D14" s="12">
+        <v>536</v>
+      </c>
+      <c r="D14" s="10">
         <f>B14*Данные!$B$8*Данные!$B$15+C14*Данные!$B$8*Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="E14" s="37">
+        <v>728960</v>
+      </c>
+      <c r="E14" s="40">
         <f>SUM(Данные!$G$23:$G$30)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>15</v>
+      </c>
+      <c r="F14" s="10">
         <f>E14*Данные!$B$6*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G14" s="37">
+        <v>77700</v>
+      </c>
+      <c r="G14" s="40">
         <f>SUM(Данные!$F$23:$F$30)</f>
-        <v/>
-      </c>
-      <c r="H14" s="12">
+        <v>17</v>
+      </c>
+      <c r="H14" s="10">
         <f>G14*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
+        <v>433457.5</v>
+      </c>
+      <c r="I14" s="11">
         <f>D14+F14+H14</f>
-        <v/>
+        <v>1240117.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="31">
         <f>Данные!$D$21</f>
-        <v/>
-      </c>
-      <c r="C15" s="36">
+        <v>12</v>
+      </c>
+      <c r="C15" s="31">
         <f>Данные!$D$21*2</f>
-        <v/>
-      </c>
-      <c r="D15" s="12">
+        <v>24</v>
+      </c>
+      <c r="D15" s="10">
         <f>B15*Данные!$B$8*Данные!$B$15+C15*Данные!$B$8*Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="E15" s="37">
+        <v>32640</v>
+      </c>
+      <c r="E15" s="40">
         <f>Данные!$G$21</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>1</v>
+      </c>
+      <c r="F15" s="10">
         <f>E15*Данные!$B$6*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G15" s="37">
+        <v>5180</v>
+      </c>
+      <c r="G15" s="40">
         <f>Данные!$F$21</f>
-        <v/>
-      </c>
-      <c r="H15" s="12">
+        <v>1</v>
+      </c>
+      <c r="H15" s="10">
         <f>G15*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="I15" s="17">
+        <v>25497.5</v>
+      </c>
+      <c r="I15" s="11">
         <f>D15+F15+H15</f>
-        <v/>
+        <v>63317.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="31">
         <f>Данные!$D$22</f>
-        <v/>
-      </c>
-      <c r="C16" s="36">
+        <v>63</v>
+      </c>
+      <c r="C16" s="31">
         <f>Данные!$D$22*2</f>
-        <v/>
-      </c>
-      <c r="D16" s="12">
+        <v>126</v>
+      </c>
+      <c r="D16" s="10">
         <f>B16*Данные!$B$8*Данные!$B$15+C16*Данные!$B$8*Данные!$B$16</f>
-        <v/>
-      </c>
-      <c r="E16" s="37">
+        <v>171360</v>
+      </c>
+      <c r="E16" s="40">
         <f>Данные!$G$22</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
         <f>E16*Данные!$B$6*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="G16" s="37">
+        <v>0</v>
+      </c>
+      <c r="G16" s="40">
         <f>Данные!$F$22</f>
-        <v/>
-      </c>
-      <c r="H16" s="12">
+        <v>1.3</v>
+      </c>
+      <c r="H16" s="10">
         <f>G16*Данные!$B$7*Данные!$B$15</f>
-        <v/>
-      </c>
-      <c r="I16" s="17">
+        <v>33146.75</v>
+      </c>
+      <c r="I16" s="11">
         <f>D16+F16+H16</f>
-        <v/>
+        <v>204506.75</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Бутылки (по объектам не разносятся)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="17">
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="11">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v/>
+        <v>19040</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ ЗА ГОД, ИТОГО</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="9">
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="29">
         <f>SUM(D13:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="38">
+        <v>932960</v>
+      </c>
+      <c r="E18" s="41">
         <f>SUM(E13:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="9">
+        <v>16</v>
+      </c>
+      <c r="F18" s="29">
         <f>SUM(F13:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="38">
+        <v>82880</v>
+      </c>
+      <c r="G18" s="41">
         <f>SUM(G13:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="9">
+        <v>20.3</v>
+      </c>
+      <c r="H18" s="29">
         <f>SUM(H13:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="9">
+        <v>517599.25</v>
+      </c>
+      <c r="I18" s="29">
         <f>SUM(I13:I17)</f>
-        <v/>
-      </c>
-    </row>
+        <v>1552479.25</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>РАЗОВАЯ ЗАКУПКА ПРИМАНОЧНЫХ СТАНЦИЙ</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>Всего, шт</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>Цена, ₸/шт</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="26" t="inlineStr">
         <is>
           <t>Разово, ₸</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="31">
         <f>Данные!$B$20</f>
-        <v/>
-      </c>
-      <c r="C22" s="36">
+        <v>0</v>
+      </c>
+      <c r="C22" s="31">
         <f>Данные!$C$20</f>
-        <v/>
-      </c>
-      <c r="D22" s="36">
+        <v>29</v>
+      </c>
+      <c r="D22" s="31">
         <f>B22+C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="6">
+        <v>29</v>
+      </c>
+      <c r="E22" s="27">
         <f>Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="F22" s="17">
+        <v>2160</v>
+      </c>
+      <c r="F22" s="11">
         <f>D22*E22</f>
-        <v/>
+        <v>62640</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B23" s="36">
+      <c r="B23" s="31">
         <f>SUM(Данные!$B$23:$B$30)</f>
-        <v/>
-      </c>
-      <c r="C23" s="36">
+        <v>161</v>
+      </c>
+      <c r="C23" s="31">
         <f>SUM(Данные!$C$23:$C$30)</f>
-        <v/>
-      </c>
-      <c r="D23" s="36">
+        <v>1096</v>
+      </c>
+      <c r="D23" s="31">
         <f>B23+C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="6">
+        <v>1257</v>
+      </c>
+      <c r="E23" s="27">
         <f>Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="F23" s="17">
+        <v>2160</v>
+      </c>
+      <c r="F23" s="11">
         <f>D23*E23</f>
-        <v/>
+        <v>2715120</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="31">
         <f>Данные!$B$21</f>
-        <v/>
-      </c>
-      <c r="C24" s="36">
+        <v>18</v>
+      </c>
+      <c r="C24" s="31">
         <f>Данные!$C$21</f>
-        <v/>
-      </c>
-      <c r="D24" s="36">
+        <v>34</v>
+      </c>
+      <c r="D24" s="31">
         <f>B24+C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="6">
+        <v>52</v>
+      </c>
+      <c r="E24" s="27">
         <f>Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="F24" s="17">
+        <v>2160</v>
+      </c>
+      <c r="F24" s="11">
         <f>D24*E24</f>
-        <v/>
+        <v>112320</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B25" s="36">
+      <c r="B25" s="31">
         <f>Данные!$B$22</f>
-        <v/>
-      </c>
-      <c r="C25" s="36">
+        <v>0</v>
+      </c>
+      <c r="C25" s="31">
         <f>Данные!$C$22</f>
-        <v/>
-      </c>
-      <c r="D25" s="36">
+        <v>39</v>
+      </c>
+      <c r="D25" s="31">
         <f>B25+C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="6">
+        <v>39</v>
+      </c>
+      <c r="E25" s="27">
         <f>Данные!$B$9</f>
-        <v/>
-      </c>
-      <c r="F25" s="17">
+        <v>2160</v>
+      </c>
+      <c r="F25" s="11">
         <f>D25*E25</f>
-        <v/>
+        <v>84240</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>ИТОГО РАЗОВО</t>
         </is>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="35">
         <f>SUM(B22:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="39">
+        <v>179</v>
+      </c>
+      <c r="C26" s="35">
         <f>SUM(C22:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="39">
+        <v>1198</v>
+      </c>
+      <c r="D26" s="35">
         <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="9">
+        <v>1377</v>
+      </c>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="29">
         <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-    </row>
+        <v>2974320</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>ЗП в месяц · 258 488 ₸</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>ЗП за год · 258 488 ₸</t>
-        </is>
-      </c>
-      <c r="D29" s="35" t="inlineStr">
-        <is>
-          <t>Материалы за год</t>
-        </is>
-      </c>
-      <c r="E29" s="35" t="inlineStr">
-        <is>
-          <t>Итого за год · 258 488 ₸</t>
-        </is>
-      </c>
-      <c r="F29" s="35" t="inlineStr">
-        <is>
-          <t>Итого за год · 350 000 ₸</t>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>ЗП в месяц, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ЗП за год, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Материалы за год, ₸</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Итого за год, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="n">
+      <c r="A30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="10">
         <f>A30*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C30" s="12">
+        <v>516976</v>
+      </c>
+      <c r="C30" s="10">
         <f>B30*12</f>
-        <v/>
-      </c>
-      <c r="D30" s="12">
+        <v>6203712</v>
+      </c>
+      <c r="D30" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E30" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E30" s="11">
         <f>C30+D30</f>
-        <v/>
-      </c>
-      <c r="F30" s="17">
+        <v>7756191.25</v>
+      </c>
+      <c r="F30" s="11">
         <f>A30*Данные!$B$13*12+D30</f>
-        <v/>
+        <v>9952479.25</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="10">
         <f>A31*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C31" s="12">
+        <v>775464</v>
+      </c>
+      <c r="C31" s="10">
         <f>B31*12</f>
-        <v/>
-      </c>
-      <c r="D31" s="12">
+        <v>9305568</v>
+      </c>
+      <c r="D31" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E31" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E31" s="11">
         <f>C31+D31</f>
-        <v/>
-      </c>
-      <c r="F31" s="17">
+        <v>10858047.25</v>
+      </c>
+      <c r="F31" s="11">
         <f>A31*Данные!$B$13*12+D31</f>
-        <v/>
+        <v>14152479.25</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="n">
+      <c r="A32" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="10">
         <f>A32*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C32" s="12">
+        <v>1033952</v>
+      </c>
+      <c r="C32" s="10">
         <f>B32*12</f>
-        <v/>
-      </c>
-      <c r="D32" s="12">
+        <v>12407424</v>
+      </c>
+      <c r="D32" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E32" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E32" s="11">
         <f>C32+D32</f>
-        <v/>
-      </c>
-      <c r="F32" s="17">
+        <v>13959903.25</v>
+      </c>
+      <c r="F32" s="11">
         <f>A32*Данные!$B$13*12+D32</f>
-        <v/>
+        <v>18352479.25</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="10">
         <f>A33*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C33" s="12">
+        <v>1292440</v>
+      </c>
+      <c r="C33" s="10">
         <f>B33*12</f>
-        <v/>
-      </c>
-      <c r="D33" s="12">
+        <v>15509280</v>
+      </c>
+      <c r="D33" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E33" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E33" s="11">
         <f>C33+D33</f>
-        <v/>
-      </c>
-      <c r="F33" s="17">
+        <v>17061759.25</v>
+      </c>
+      <c r="F33" s="11">
         <f>A33*Данные!$B$13*12+D33</f>
-        <v/>
+        <v>22552479.25</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="n">
+      <c r="A34" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="10">
         <f>A34*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C34" s="12">
+        <v>1550928</v>
+      </c>
+      <c r="C34" s="10">
         <f>B34*12</f>
-        <v/>
-      </c>
-      <c r="D34" s="12">
+        <v>18611136</v>
+      </c>
+      <c r="D34" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E34" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E34" s="11">
         <f>C34+D34</f>
-        <v/>
-      </c>
-      <c r="F34" s="17">
+        <v>20163615.25</v>
+      </c>
+      <c r="F34" s="11">
         <f>A34*Данные!$B$13*12+D34</f>
-        <v/>
+        <v>26752479.25</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="10">
         <f>A35*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C35" s="12">
+        <v>1809416</v>
+      </c>
+      <c r="C35" s="10">
         <f>B35*12</f>
-        <v/>
-      </c>
-      <c r="D35" s="12">
+        <v>21712992</v>
+      </c>
+      <c r="D35" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E35" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E35" s="11">
         <f>C35+D35</f>
-        <v/>
-      </c>
-      <c r="F35" s="17">
+        <v>23265471.25</v>
+      </c>
+      <c r="F35" s="11">
         <f>A35*Данные!$B$13*12+D35</f>
-        <v/>
+        <v>30952479.25</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="n">
+      <c r="A36" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="10">
         <f>A36*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C36" s="12">
+        <v>2067904</v>
+      </c>
+      <c r="C36" s="10">
         <f>B36*12</f>
-        <v/>
-      </c>
-      <c r="D36" s="12">
+        <v>24814848</v>
+      </c>
+      <c r="D36" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E36" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E36" s="11">
         <f>C36+D36</f>
-        <v/>
-      </c>
-      <c r="F36" s="17">
+        <v>26367327.25</v>
+      </c>
+      <c r="F36" s="11">
         <f>A36*Данные!$B$13*12+D36</f>
-        <v/>
+        <v>35152479.25</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="10">
         <f>A37*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C37" s="12">
+        <v>2326392</v>
+      </c>
+      <c r="C37" s="10">
         <f>B37*12</f>
-        <v/>
-      </c>
-      <c r="D37" s="12">
+        <v>27916704</v>
+      </c>
+      <c r="D37" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E37" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E37" s="11">
         <f>C37+D37</f>
-        <v/>
-      </c>
-      <c r="F37" s="17">
+        <v>29469183.25</v>
+      </c>
+      <c r="F37" s="11">
         <f>A37*Данные!$B$13*12+D37</f>
-        <v/>
+        <v>39352479.25</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n">
+      <c r="A38" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="10">
         <f>A38*Данные!$B$12</f>
-        <v/>
-      </c>
-      <c r="C38" s="12">
+        <v>2584880</v>
+      </c>
+      <c r="C38" s="10">
         <f>B38*12</f>
-        <v/>
-      </c>
-      <c r="D38" s="12">
+        <v>31018560</v>
+      </c>
+      <c r="D38" s="10">
         <f>'Штат УКПФ'!$I$18</f>
-        <v/>
-      </c>
-      <c r="E38" s="17">
+        <v>1552479.25</v>
+      </c>
+      <c r="E38" s="11">
         <f>C38+D38</f>
-        <v/>
-      </c>
-      <c r="F38" s="17">
+        <v>32571039.25</v>
+      </c>
+      <c r="F38" s="11">
         <f>A38*Данные!$B$13*12+D38</f>
-        <v/>
-      </c>
-    </row>
+        <v>43552479.25</v>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -4998,340 +5750,342 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ЦЕНЫ И ПАРАМЕТРЫ ШТАТА УКПФ</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="16" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="36" t="n">
         <v>740</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="36" t="n">
         <v>3642.5</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B8" s="36" t="n">
         <v>160</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="36" t="n">
         <v>2160</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>разовая закупка; цена из прежнего расчёта по ККЗ (29 шт = 62 640 ₸)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="36" t="n">
         <v>68</v>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="41" t="n">
+      <c r="B11" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n">
+      <c r="B12" s="36" t="n">
         <v>258488</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="40" t="n">
+      <c r="B13" s="36" t="n">
         <v>350000</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n">
+      <c r="B14" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="41" t="n">
+      <c r="B15" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="41" t="n">
+      <c r="B16" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>ПРИМАНОЧНЫЕ СТАНЦИИ И НОРМЫ ЯДОВ ПО ОБЪЕКТАМ УКПФ</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>1-й контур</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>2-й контур</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>3-й контур</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>Всего точек</t>
-        </is>
-      </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1-й контур, шт</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>2-й контур, шт</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>3-й контур, шт</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Всего точек, шт</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="35" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="41" t="n">
+      <c r="B20" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="41" t="n">
+      <c r="D20" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="10">
         <f>SUM(B20:D20)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
         <v>1</v>
@@ -5339,30 +6093,30 @@
       <c r="G20" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="41" t="n">
+      <c r="B21" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="41" t="n">
+      <c r="D21" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="10">
         <f>SUM(B21:D21)</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="F21" s="42" t="n">
         <v>1</v>
@@ -5370,26 +6124,26 @@
       <c r="G21" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="41" t="n">
+      <c r="B22" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="36" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="41" t="n">
+      <c r="D22" s="36" t="n">
         <v>63</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="10">
         <f>SUM(B22:D22)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F22" s="42" t="n">
         <v>1.3</v>
@@ -5397,30 +6151,30 @@
       <c r="G22" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="41" t="n">
+      <c r="B23" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="36" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="10">
         <f>SUM(B23:D23)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="F23" s="42" t="n">
         <v>2</v>
@@ -5428,26 +6182,26 @@
       <c r="G23" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="41" t="n">
+      <c r="B24" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C24" s="36" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D24" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="10">
         <f>SUM(B24:D24)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="F24" s="42" t="n">
         <v>2</v>
@@ -5455,26 +6209,26 @@
       <c r="G24" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
+      <c r="H24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="41" t="n">
+      <c r="B25" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="41" t="n">
+      <c r="C25" s="36" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="10">
         <f>SUM(B25:D25)</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="F25" s="42" t="n">
         <v>3.5</v>
@@ -5482,26 +6236,26 @@
       <c r="G25" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
+      <c r="H25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="41" t="n">
+      <c r="B26" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="41" t="n">
+      <c r="C26" s="36" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="10">
         <f>SUM(B26:D26)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="F26" s="42" t="n">
         <v>2</v>
@@ -5509,26 +6263,26 @@
       <c r="G26" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="H26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="41" t="n">
+      <c r="B27" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="41" t="n">
+      <c r="C27" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="41" t="n">
+      <c r="D27" s="36" t="n">
         <v>64</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="10">
         <f>SUM(B27:D27)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="F27" s="42" t="n">
         <v>1.5</v>
@@ -5536,26 +6290,26 @@
       <c r="G27" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="7" t="inlineStr"/>
+      <c r="H27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="41" t="n">
+      <c r="B28" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="41" t="n">
+      <c r="C28" s="36" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="41" t="n">
+      <c r="D28" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="10">
         <f>SUM(B28:D28)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="F28" s="42" t="n">
         <v>2</v>
@@ -5563,26 +6317,26 @@
       <c r="G28" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="H28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="41" t="n">
+      <c r="B29" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="41" t="n">
+      <c r="C29" s="36" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="41" t="n">
+      <c r="D29" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="10">
         <f>SUM(B29:D29)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="F29" s="42" t="n">
         <v>1</v>
@@ -5590,26 +6344,26 @@
       <c r="G29" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
+      <c r="H29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n">
+      <c r="B30" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="41" t="n">
+      <c r="C30" s="36" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="41" t="n">
+      <c r="D30" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="10">
         <f>SUM(B30:D30)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="F30" s="42" t="n">
         <v>3</v>
@@ -5617,711 +6371,712 @@
       <c r="G30" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="7" t="inlineStr"/>
+      <c r="H30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>ЗПП · завод по переработке птицы</t>
         </is>
       </c>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="37" t="n"/>
-      <c r="G31" s="37" t="n"/>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Склад лузги</t>
         </is>
       </c>
-      <c r="B32" s="32" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="32" t="n"/>
-      <c r="E32" s="32" t="n"/>
-      <c r="F32" s="37" t="n"/>
-      <c r="G32" s="37" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>ИТОГО ПО ФАБРИКЕ</t>
         </is>
       </c>
-      <c r="B33" s="43">
+      <c r="B33" s="29">
         <f>SUM(B20:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="43">
+        <v>179</v>
+      </c>
+      <c r="C33" s="29">
         <f>SUM(C20:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="43">
+        <v>1198</v>
+      </c>
+      <c r="D33" s="29">
         <f>SUM(D20:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="43">
+        <v>343</v>
+      </c>
+      <c r="E33" s="29">
         <f>SUM(E20:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="38">
+        <v>179</v>
+      </c>
+      <c r="F33" s="41">
         <f>SUM(F20:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="38">
+        <v>20.3</v>
+      </c>
+      <c r="G33" s="41">
         <f>SUM(G20:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="10" t="n"/>
-    </row>
+        <v>16</v>
+      </c>
+      <c r="H33" s="16" t="n"/>
+    </row>
+    <row r="34"/>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>ЦЕНЫ ПОДРЯДЧИКОВ ИЗ КП И ДОГОВОРОВ</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="16" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr"/>
-      <c r="E36" s="20" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr"/>
-      <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr"/>
+      <c r="E36" s="13" t="inlineStr"/>
+      <c r="F36" s="13" t="inlineStr"/>
+      <c r="G36" s="13" t="inlineStr"/>
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="40" t="n">
+      <c r="B37" s="36" t="n">
         <v>96600</v>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="40" t="n">
+      <c r="B38" s="36" t="n">
         <v>618400</v>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="40" t="n">
+      <c r="B39" s="36" t="n">
         <v>478400</v>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="40" t="n">
+      <c r="B40" s="36" t="n">
         <v>569800</v>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="40" t="n">
+      <c r="B41" s="36" t="n">
         <v>440700</v>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="40" t="n">
+      <c r="B42" s="36" t="n">
         <v>2599100</v>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="40" t="n">
+      <c r="B43" s="36" t="n">
         <v>2010300</v>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="40" t="n">
+      <c r="B44" s="36" t="n">
         <v>126200</v>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="40" t="n">
+      <c r="B45" s="36" t="n">
         <v>106800</v>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="40" t="n">
+      <c r="B46" s="36" t="n">
         <v>126200</v>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="40" t="n">
+      <c r="B47" s="36" t="n">
         <v>106800</v>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="40" t="n">
+      <c r="B48" s="36" t="n">
         <v>720000</v>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="40" t="n">
+      <c r="B49" s="36" t="n">
         <v>1080000</v>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="40" t="n">
+      <c r="B50" s="36" t="n">
         <v>3000000</v>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="40" t="n">
+      <c r="B51" s="36" t="n">
         <v>100800</v>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="40" t="n">
+      <c r="B52" s="36" t="n">
         <v>160800</v>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H52" s="12" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="40" t="n">
+      <c r="B53" s="36" t="n">
         <v>75000</v>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="40" t="n">
+      <c r="B54" s="36" t="n">
         <v>70000</v>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="H54" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="40" t="n">
+      <c r="B55" s="36" t="n">
         <v>3172000</v>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="40" t="n">
+      <c r="B56" s="36" t="n">
         <v>2074000</v>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="40" t="n">
+      <c r="B57" s="36" t="n">
         <v>2806000</v>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="40" t="n">
+      <c r="B58" s="36" t="n">
         <v>1830000</v>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="40" t="n">
+      <c r="B59" s="36" t="n">
         <v>180000</v>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="40" t="n">
+      <c r="B60" s="36" t="n">
         <v>80000</v>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="41" t="n">
+      <c r="B61" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H61" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="41" t="n">
+      <c r="B62" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="41" t="n">
+      <c r="B63" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H63" s="12" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B64" s="44" t="n">
+      <c r="B64" s="38" t="n">
         <v>0.15</v>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B65" s="44" t="n">
+      <c r="B65" s="38" t="n">
         <v>0.15</v>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B66" s="44" t="n">
+      <c r="B66" s="38" t="n">
         <v>0.16</v>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -105,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -132,46 +132,127 @@
         <color rgb="0016211F"/>
       </top>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C8C2AE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C8C2AE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C8C2AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C8C2AE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C8C2AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C8C2AE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C8C2AE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C8C2AE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C8C2AE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C8C2AE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -188,23 +269,37 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -573,28 +668,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СРАВНЕНИЕ КП · дератизация АО «Усть-Каменогорская птицефабрика», 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
+          <t>СРАВНЕНИЕ КП · дератизация УКПФ, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Все суммы в тенге. Сравнивается только дератизация. Цены Indigo включают НДС, цены Pest Hunters — без НДС. Дезинсекция у обоих подрядчиков считается отдельно и сюда не входит.</t>
+          <t>Все суммы в тенге. Только дератизация: дезинсекция у подрядчиков идёт отдельно. Цены Indigo включают НДС, цены Pest Hunters — без НДС.</t>
         </is>
       </c>
     </row>
@@ -602,1290 +698,812 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ККЗ · КОРМОЦЕХ</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Штат УКПФ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
+      <c r="A5" s="44" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>барьер вокруг периметра кормоцеха и грязный барьер</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D6" s="10">
-        <f>E6/12</f>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="B6" s="7">
+        <f>C6/12</f>
         <v>96600</v>
       </c>
-      <c r="E6" s="11">
+      <c r="C6" s="8">
         <f>'ККЗ'!B5</f>
         <v>1159200</v>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>цены КП включают НДС</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>дератизация</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="10">
-        <f>E7/12</f>
+      <c r="D6" s="7">
+        <f>E6/12</f>
         <v>75000</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E6" s="8">
         <f>'ККЗ'!C5</f>
         <v>900000</v>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>без НДС; дезинсекция ещё 70 000 ₸/мес отдельно</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>29 приманочных станций 2-го контура, 1 кг брикетов Pest Killer</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="10">
-        <f>E8/12</f>
+      <c r="F6" s="7">
+        <f>G6/12</f>
         <v>2124.791667</v>
       </c>
-      <c r="E8" s="11">
+      <c r="G6" s="8">
         <f>'ККЗ'!D5</f>
         <v>25497.5</v>
       </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>зарплата в эту строку не входит — она общая на все объекты</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>БРОЙЛЕРНЫЕ ПЛОЩАДКИ</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>три группы: Айыртау БП, Многоэтажки Д и Г, Площадки А‚Б‚Е‚Ж‚В‚В(РМ) — полная замена оборудования</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D12" s="10">
-        <f>E12/12</f>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>C7/12</f>
         <v>3787300</v>
       </c>
-      <c r="E12" s="11">
+      <c r="C7" s="8">
         <f>'Бройлерные площадки'!B5</f>
         <v>45447600</v>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>1 139 ед. оборудования; вариант с частичной заменой — на листе «Бройлерные площадки»</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>122 объекта, оборудование подрядчика</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="10">
-        <f>E13/12</f>
+      <c r="D7" s="7">
+        <f>E7/12</f>
         <v>2897500</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E7" s="8">
         <f>'Бройлерные площадки'!C5</f>
         <v>34770000</v>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>3 172 000 ₸/мес март — ноябрь и 2 074 000 ₸/мес декабрь — февраль</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>8 площадок: 161 / 1 096 / 268 точек по контурам, 17 кг брикетов и 15 кг Зерноцида</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="10">
-        <f>E14/12</f>
+      <c r="F7" s="7">
+        <f>G7/12</f>
         <v>103343.125</v>
       </c>
-      <c r="E14" s="11">
+      <c r="G7" s="8">
         <f>'Бройлерные площадки'!D5</f>
         <v>1240117.5</v>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>зимой 1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
-        </is>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Инкубаторий</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>C8/12</f>
+        <v>126200</v>
+      </c>
+      <c r="C8" s="8">
+        <f>'Инкубаторий'!B5</f>
+        <v>1514400</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="E8" s="45" t="n"/>
+      <c r="F8" s="7">
+        <f>G8/12</f>
+        <v>5276.458333</v>
+      </c>
+      <c r="G8" s="8">
+        <f>'Инкубаторий'!D5</f>
+        <v>63317.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>C9/12</f>
+        <v>126200</v>
+      </c>
+      <c r="C9" s="8">
+        <f>'ЗПП'!B5</f>
+        <v>1514400</v>
+      </c>
+      <c r="D9" s="7">
+        <f>E9/12</f>
+        <v>180000</v>
+      </c>
+      <c r="E9" s="8">
+        <f>'ЗПП'!C5</f>
+        <v>2160000</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>нормы не заданы</t>
+        </is>
+      </c>
+      <c r="G9" s="45" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="7">
+        <f>E10/12</f>
+        <v>60000</v>
+      </c>
+      <c r="E10" s="8">
+        <f>'Склад ТМЦ'!C5</f>
+        <v>720000</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>нормы не заданы</t>
+        </is>
+      </c>
+      <c r="G10" s="45" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>АБК · 11 корпусов</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="7">
+        <f>G11/12</f>
+        <v>17042.22917</v>
+      </c>
+      <c r="G11" s="8">
+        <f>'АБК'!D5</f>
+        <v>204506.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Сумма по объектам</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>C12/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C12" s="12">
+        <f>SUM(C6:C11)</f>
+        <v>49635600</v>
+      </c>
+      <c r="D12" s="12">
+        <f>E12/12</f>
+        <v>3212500</v>
+      </c>
+      <c r="E12" s="12">
+        <f>SUM(E6:E11)</f>
+        <v>38550000</v>
+      </c>
+      <c r="F12" s="12">
+        <f>G12/12</f>
+        <v>127786.6042</v>
+      </c>
+      <c r="G12" s="12">
+        <f>SUM(G6:G11)</f>
+        <v>1533439.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Штат УКПФ: зарплата и бутылки</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="7">
+        <f>G13/12</f>
+        <v>1035538.667</v>
+      </c>
+      <c r="G13" s="7">
+        <f>Данные!$B$14*Данные!$B$12*12+Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
+        <v>12426464</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>ВСЕГО ЗА ГОД</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>C14/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C14" s="14">
+        <f>C12</f>
+        <v>49635600</v>
+      </c>
+      <c r="D14" s="14">
+        <f>E14/12</f>
+        <v>3212500</v>
+      </c>
+      <c r="E14" s="14">
+        <f>E12</f>
+        <v>38550000</v>
+      </c>
+      <c r="F14" s="14">
+        <f>G14/12</f>
+        <v>1163325.271</v>
+      </c>
+      <c r="G14" s="14">
+        <f>G12+G13</f>
+        <v>13959903.25</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>ИНКУБАТОРИЙ</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Вариант</t>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Показатель</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>во сколько раз</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>полная замена оборудования, 48 ед.</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D18" s="10">
-        <f>E18/12</f>
-        <v>126200</v>
-      </c>
-      <c r="E18" s="11">
-        <f>'Инкубаторий'!B5</f>
-        <v>1514400</v>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>появился в КП от 19.08.2026</t>
-        </is>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Indigo Solutions дороже штата</t>
+        </is>
+      </c>
+      <c r="B18" s="7">
+        <f>C18/12</f>
+        <v>2972974.729</v>
+      </c>
+      <c r="C18" s="8">
+        <f>C14-G14</f>
+        <v>35675696.75</v>
+      </c>
+      <c r="D18" s="46">
+        <f>IF(G14=0,0,C14/G14)</f>
+        <v>3.555583381</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>предложения нет</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="10">
-        <f>E19/12</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="11">
-        <f>'Инкубаторий'!C5</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>18 / 34 / 12 точек по контурам, 1 кг брикетов и 1 кг Зерноцида</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="10">
-        <f>E20/12</f>
-        <v>5276.458333</v>
-      </c>
-      <c r="E20" s="11">
-        <f>'Инкубаторий'!D5</f>
-        <v>63317.5</v>
-      </c>
-      <c r="F20" s="12" t="inlineStr"/>
-    </row>
-    <row r="21"/>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters дороже штата</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>C19/12</f>
+        <v>2049174.729</v>
+      </c>
+      <c r="C19" s="8">
+        <f>E14-G14</f>
+        <v>24590096.75</v>
+      </c>
+      <c r="D19" s="46">
+        <f>IF(G14=0,0,E14/G14)</f>
+        <v>2.761480457</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ · ИЗ ЧЕГО СКЛАДЫВАЕТСЯ</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>ЗПП · ЗАВОД ПО ПЕРЕРАБОТКЕ ПТИЦЫ</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Фонд оплаты труда</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>C23/12</f>
+        <v>1033952</v>
+      </c>
+      <c r="C23" s="8">
+        <f>Данные!$B$14*Данные!$B$12*12</f>
+        <v>12407424</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>полная замена оборудования</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D24" s="10">
-        <f>E24/12</f>
-        <v>126200</v>
-      </c>
-      <c r="E24" s="11">
-        <f>'ЗПП'!B5</f>
-        <v>1514400</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>дезинсекция ещё 160 800 ₸/мес отдельно</t>
-        </is>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>C24/12</f>
+        <v>77746.66667</v>
+      </c>
+      <c r="C24" s="8">
+        <f>'Штат УКПФ'!D18</f>
+        <v>932960</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>договор №88 от 01.01.2026 — дератизация и дезинсекция вместе</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="10">
-        <f>E25/12</f>
-        <v>180000</v>
-      </c>
-      <c r="E25" s="11">
-        <f>'ЗПП'!C5</f>
-        <v>2160000</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>8 309 м², бригада из трёх человек</t>
-        </is>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Зерноцид</t>
+        </is>
+      </c>
+      <c r="B25" s="7">
+        <f>C25/12</f>
+        <v>6906.666667</v>
+      </c>
+      <c r="C25" s="8">
+        <f>'Штат УКПФ'!F18</f>
+        <v>82880</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>нормы расхода по ЗПП не заданы</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" s="10">
-        <f>E26/12</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="11">
-        <f>'ЗПП'!D5</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>дайте нормы — строка встанет в расчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>СКЛАД ТМЦ</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>предложения нет</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="10">
-        <f>E30/12</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="11">
-        <f>'Склад ТМЦ'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>договор №921 от 01.04.2026 — дератизация и дезинсекция</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="10">
-        <f>E31/12</f>
-        <v>60000</v>
-      </c>
-      <c r="E31" s="11">
-        <f>'Склад ТМЦ'!C5</f>
-        <v>720000</v>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>действует апрель — декабрь, девять оплачиваемых месяцев</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>нормы расхода по складу не заданы</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" s="10">
-        <f>E32/12</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="11">
-        <f>'Склад ТМЦ'!D5</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="12" t="inlineStr"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>АБК · 11 КОРПУСОВ</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>предложения нет</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="10">
-        <f>E36/12</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="11">
-        <f>'АБК'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="12" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>предложения нет</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="10">
-        <f>E37/12</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="11">
-        <f>'АБК'!C5</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="12" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>63 клеевые станции и 39 приманочных, 1,3 кг брикетов</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D38" s="10">
-        <f>E38/12</f>
-        <v>17042.22917</v>
-      </c>
-      <c r="E38" s="11">
-        <f>'АБК'!D5</f>
-        <v>204506.75</v>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>ИТОГО ПО ФАБРИКЕ</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr"/>
-      <c r="C41" s="13" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>Примечание</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions · все объекты</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="n"/>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="10">
-        <f>E42/12</f>
-        <v>4136300</v>
-      </c>
-      <c r="E42" s="11">
-        <f>E6+E12+E18+E24+E30+E36</f>
-        <v>49635600</v>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>полная замена оборудования; скидки — ниже</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters · все объекты</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="n"/>
-      <c r="C43" s="14" t="n"/>
-      <c r="D43" s="10">
-        <f>E43/12</f>
-        <v>3212500</v>
-      </c>
-      <c r="E43" s="11">
-        <f>E7+E13+E19+E25+E31+E37</f>
-        <v>38550000</v>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>оборудование подрядчика; цены без НДС</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · материалы по объектам</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="n"/>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="10">
-        <f>E44/12</f>
-        <v>127786.6042</v>
-      </c>
-      <c r="E44" s="11">
-        <f>E8+E14+E20+E26+E32+E38</f>
-        <v>1533439.25</v>
-      </c>
-      <c r="F44" s="12" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · бутылки</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="n"/>
-      <c r="C45" s="14" t="n"/>
-      <c r="D45" s="10">
-        <f>E45/12</f>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Pest Killer, брикеты</t>
+        </is>
+      </c>
+      <c r="B26" s="7">
+        <f>C26/12</f>
+        <v>43133.27083</v>
+      </c>
+      <c r="C26" s="8">
+        <f>'Штат УКПФ'!H18</f>
+        <v>517599.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Бутылки</t>
+        </is>
+      </c>
+      <c r="B27" s="7">
+        <f>C27/12</f>
         <v>1586.666667</v>
       </c>
-      <c r="E45" s="11">
+      <c r="C27" s="8">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>по объектам не разносятся</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · фонд оплаты труда</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="n"/>
-      <c r="C46" s="14" t="n"/>
-      <c r="D46" s="10">
-        <f>E46/12</f>
-        <v>1033952</v>
-      </c>
-      <c r="E46" s="11">
-        <f>Данные!$B$14*Данные!$B$12*12</f>
-        <v>12407424</v>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>при окладе 258 488 ₸ и текущей численности; вариант 350 000 ₸ — на листе «Штат УКПФ»</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>ШТАТ УКПФ · ВСЕГО</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="17">
-        <f>E47/12</f>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО ШТАТ</t>
+        </is>
+      </c>
+      <c r="B28" s="12">
+        <f>C28/12</f>
         <v>1163325.271</v>
       </c>
-      <c r="E47" s="18">
-        <f>E44+E45+E46</f>
+      <c r="C28" s="12">
+        <f>SUM(C23:C27)</f>
         <v>13959903.25</v>
       </c>
-      <c r="F47" s="16" t="n"/>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Indigo Solutions дороже штата</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="n"/>
-      <c r="C50" s="39">
-        <f>IF(E47=0,0,E42/E47)</f>
-        <v>3.555583381</v>
-      </c>
-      <c r="D50" s="10">
-        <f>E50/12</f>
-        <v>2972974.729</v>
-      </c>
-      <c r="E50" s="11">
-        <f>E42-E47</f>
-        <v>35675696.75</v>
-      </c>
-      <c r="F50" s="14" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>Pest Hunters дороже штата</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="n"/>
-      <c r="C51" s="39">
-        <f>IF(E47=0,0,E43/E47)</f>
-        <v>2.761480457</v>
-      </c>
-      <c r="D51" s="10">
-        <f>E51/12</f>
-        <v>2049174.729</v>
-      </c>
-      <c r="E51" s="11">
-        <f>E43-E47</f>
-        <v>24590096.75</v>
-      </c>
-      <c r="F51" s="14" t="n"/>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Условие</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr"/>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Ставка</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>В среднем в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="inlineStr">
-        <is>
-          <t>Формулировка из КП</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Цена КП без скидок</t>
         </is>
       </c>
-      <c r="B55" s="14" t="n"/>
-      <c r="C55" s="14" t="n"/>
-      <c r="D55" s="10">
-        <f>E55/12</f>
+      <c r="B32" s="7">
+        <f>C32/12</f>
         <v>4136300</v>
       </c>
-      <c r="E55" s="11">
-        <f>E42</f>
+      <c r="C32" s="8">
+        <f>C14</f>
         <v>49635600</v>
       </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>все цены приведены в тенге и включают НДС</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="D32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n"/>
-      <c r="C56" s="20">
+      <c r="B33" s="7">
+        <f>C33/12</f>
+        <v>3515855</v>
+      </c>
+      <c r="C33" s="8">
+        <f>C14*(1-Данные!$B$64)</f>
+        <v>42190260</v>
+      </c>
+      <c r="D33" s="19">
         <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
-      <c r="D56" s="10">
-        <f>E56/12</f>
-        <v>3515855</v>
-      </c>
-      <c r="E56" s="11">
-        <f>E42*(1-Данные!$B$64)</f>
-        <v>42190260</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>при заключении договора на обслуживание всей территории птицефабрики предоставляется скидка 15 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
-      <c r="B57" s="14" t="n"/>
-      <c r="C57" s="14" t="n"/>
-      <c r="D57" s="10">
-        <f>E57/12</f>
+      <c r="B34" s="7">
+        <f>C34/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="E57" s="11">
-        <f>E42*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+      <c r="C34" s="8">
+        <f>C14*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
         <v>35861721</v>
       </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>при внесении 100 % предоплаты за год обслуживания предоставляется дополнительная скидка 15 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="D34" s="19">
+        <f>Данные!$B$65</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
-      <c r="B58" s="14" t="n"/>
-      <c r="C58" s="14" t="n"/>
-      <c r="D58" s="10">
-        <f>E58/12</f>
+      <c r="B35" s="7">
+        <f>C35/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="E58" s="11">
-        <f>E42*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
+      <c r="C35" s="8">
+        <f>C14*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>при заключении договора с компанией, не являющейся плательщиком НДС, предоставляется скидка 16 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="D35" s="19">
+        <f>Данные!$B$66</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr"/>
-      <c r="E61" s="13" t="inlineStr"/>
-      <c r="F61" s="13" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Что зафиксировано в документах</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D62" s="14" t="n"/>
-      <c r="E62" s="14" t="n"/>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений, клеевые пластины меняются по мере необходимости</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+        </is>
+      </c>
+      <c r="E39" s="47" t="n"/>
+      <c r="F39" s="47" t="n"/>
+      <c r="G39" s="45" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="C63" s="9" t="n">
+      <c r="C40" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="14" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="12" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
         <is>
           <t>выезд по запросу</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="E40" s="47" t="n"/>
+      <c r="F40" s="47" t="n"/>
+      <c r="G40" s="45" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>бройлерные площадки</t>
         </is>
       </c>
-      <c r="C64" s="9" t="n">
+      <c r="C41" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="14" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>дополнительные визиты по вызову заказчика</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>дополнительные визиты по вызову</t>
+        </is>
+      </c>
+      <c r="E41" s="47" t="n"/>
+      <c r="F41" s="47" t="n"/>
+      <c r="G41" s="45" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C42" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D65" s="14" t="n"/>
-      <c r="E65" s="14" t="n"/>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>по утверждённому графику на 2026 год, бригада из трёх человек</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
+        </is>
+      </c>
+      <c r="E42" s="47" t="n"/>
+      <c r="F42" s="47" t="n"/>
+      <c r="G42" s="45" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>склад ТМЦ</t>
         </is>
       </c>
-      <c r="C66" s="9" t="n">
+      <c r="C43" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D66" s="14" t="n"/>
-      <c r="E66" s="14" t="n"/>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>выезд по рекламации в течение двух рабочих дней</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>выезд по рекламации за два рабочих дня</t>
+        </is>
+      </c>
+      <c r="E43" s="47" t="n"/>
+      <c r="F43" s="47" t="n"/>
+      <c r="G43" s="45" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C44" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D67" s="14" t="n"/>
-      <c r="E67" s="14" t="n"/>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>присутствие на фабрике 5/2, реакция в тот же день</t>
-        </is>
-      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>присутствие 5/2, реакция в тот же день</t>
+        </is>
+      </c>
+      <c r="E44" s="47" t="n"/>
+      <c r="F44" s="47" t="n"/>
+      <c r="G44" s="45" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="17">
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1916,7 +1534,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура, 1 кг брикетов Pest Killer на обработку.</t>
         </is>
@@ -1924,463 +1542,463 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <f>F9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <f>F10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>F11+F12+F13+F14</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="30">
         <f>Данные!$B$37</f>
         <v>96600</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>D9*E9</f>
         <v>1159200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>дератизация</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="30">
         <f>Данные!$B$53</f>
         <v>75000</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <f>D10*E10</f>
         <v>900000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="30">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <f>D11*E11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="30">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="30">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="8">
         <f>D12*E12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="30">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <f>D13*E13</f>
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="30">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="8">
         <f>D14*E14</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="12">
         <f>SUM(F9:F14)</f>
         <v>2084697.5</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="30">
         <f>Данные!$B$20*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="7">
         <f>D19*E19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="30">
         <f>Данные!$C$20*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="7">
         <f>D20*E20</f>
         <v>62640</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="12">
         <f>SUM(F19:F20)</f>
         <v>62640</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="30">
         <f>Данные!$B$54</f>
         <v>70000</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="7">
         <f>D25*E25</f>
         <v>840000</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="12">
         <f>SUM(F25:F25)</f>
         <v>840000</v>
       </c>
     </row>
     <row r="27"/>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2421,7 +2039,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2429,799 +2047,799 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <f>F9+F10+F11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <f>F12+F13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>F14+F15+F16+F17</f>
         <v>1240117.5</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ОСНОВНОЙ ВАРИАНТ</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="30">
         <f>Данные!$B$38</f>
         <v>618400</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>D9*E9</f>
         <v>7420800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="30">
         <f>Данные!$B$40</f>
         <v>569800</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <f>D10*E10</f>
         <v>6837600</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="30">
         <f>Данные!$B$42</f>
         <v>2599100</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <f>D11*E11</f>
         <v>31189200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="30">
         <f>Данные!$B$55</f>
         <v>3172000</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="30">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="8">
         <f>D12*E12</f>
         <v>28548000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="30">
         <f>Данные!$B$56</f>
         <v>2074000</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="30">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <f>D13*E13</f>
         <v>6222000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="30">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="8">
         <f>D14*E14</f>
         <v>300160</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="30">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="30">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="8">
         <f>D15*E15</f>
         <v>428800</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="30">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="8">
         <f>D16*E16</f>
         <v>77700</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="30">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="8">
         <f>D17*E17</f>
         <v>433457.5</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="12">
         <f>SUM(F9:F17)</f>
         <v>81457717.5</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="30">
         <f>Данные!$B$39</f>
         <v>478400</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="7">
         <f>D22*E22</f>
         <v>5740800</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="30">
         <f>Данные!$B$41</f>
         <v>440700</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="7">
         <f>D23*E23</f>
         <v>5288400</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="30">
         <f>Данные!$B$43</f>
         <v>2010300</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="7">
         <f>D24*E24</f>
         <v>24123600</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="30">
         <f>Данные!$B$57</f>
         <v>2806000</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="30">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="7">
         <f>D25*E25</f>
         <v>25254000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="30">
         <f>Данные!$B$58</f>
         <v>1830000</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="30">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="7">
         <f>D26*E26</f>
         <v>5490000</v>
       </c>
     </row>
     <row r="27">
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="12">
         <f>SUM(F22:F26)</f>
         <v>65896800</v>
       </c>
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="30">
         <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E31" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="7">
         <f>D31*E31</f>
         <v>347760</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="30">
         <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="7">
         <f>D32*E32</f>
         <v>2367360</v>
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="12">
         <f>SUM(F31:F32)</f>
         <v>2715120</v>
       </c>
     </row>
     <row r="34"/>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="F36" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>Айыртау БП</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="30">
         <f>Данные!$B$48</f>
         <v>720000</v>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="7">
         <f>D37*E37</f>
         <v>8640000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="30">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E38" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="7">
         <f>D38*E38</f>
         <v>12960000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="30">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="E39" s="27" t="n">
+      <c r="E39" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="7">
         <f>D39*E39</f>
         <v>36000000</v>
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="12">
         <f>SUM(F37:F39)</f>
         <v>57600000</v>
       </c>
     </row>
     <row r="41"/>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
         </is>
@@ -3262,7 +2880,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
@@ -3270,543 +2888,543 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <f>F9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <f>F10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>F11+F12+F13+F14</f>
         <v>63317.5</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="30">
         <f>Данные!$B$44</f>
         <v>126200</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>D9*E9</f>
         <v>1514400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <f>D10*E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="30">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <f>D11*E11</f>
         <v>13440</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="30">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="30">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="8">
         <f>D12*E12</f>
         <v>19200</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="30">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <f>D13*E13</f>
         <v>5180</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="30">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="8">
         <f>D14*E14</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="12">
         <f>SUM(F9:F14)</f>
         <v>1577717.5</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>частичная замена оборудования</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="30">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="7">
         <f>D19*E19</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="12">
         <f>SUM(F19:F19)</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="30">
         <f>Данные!$B$21*Данные!$B$9</f>
         <v>38880</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="7">
         <f>D24*E24</f>
         <v>38880</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="30">
         <f>Данные!$C$21*Данные!$B$9</f>
         <v>73440</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="7">
         <f>D25*E25</f>
         <v>73440</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="12">
         <f>SUM(F24:F25)</f>
         <v>112320</v>
       </c>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E29" s="26" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="30">
         <f>Данные!$B$51</f>
         <v>100800</v>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="7">
         <f>D30*E30</f>
         <v>1209600</v>
       </c>
     </row>
     <row r="31">
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="12">
         <f>SUM(F30:F30)</f>
         <v>1209600</v>
       </c>
     </row>
     <row r="32"/>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3846,7 +3464,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3854,354 +3472,354 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <f>F9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <f>F10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>F11</f>
         <v>0</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>полная замена оборудования</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="30">
         <f>Данные!$B$46</f>
         <v>126200</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>D9*E9</f>
         <v>1514400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="30">
         <f>Данные!$B$59</f>
         <v>180000</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <f>D10*E10</f>
         <v>2160000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <f>D11*E11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="12">
         <f>SUM(F9:F11)</f>
         <v>3674400</v>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>частичная замена оборудования</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="30">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="7">
         <f>D16*E16</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="12">
         <f>SUM(F16:F16)</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>дезинсекция</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="30">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="7">
         <f>D21*E21</f>
         <v>1929600</v>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="12">
         <f>SUM(F21:F21)</f>
         <v>1929600</v>
       </c>
     </row>
     <row r="23"/>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -4242,7 +3860,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -4250,179 +3868,179 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <f>F9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <f>F10</f>
         <v>720000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>F11</f>
         <v>0</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="30">
         <f>Данные!$B$60</f>
         <v>80000</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="30">
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <f>D10*E10</f>
         <v>720000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <f>D11*E11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="12">
         <f>SUM(F9:F11)</f>
         <v>720000</v>
       </c>
     </row>
     <row r="13"/>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -4462,7 +4080,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -4470,381 +4088,381 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Штат УКПФ · материалы</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24">
+      <c r="B5" s="26">
         <f>F9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="26">
         <f>F10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>F11+F12+F13+F14</f>
         <v>204506.75</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <f>D10*E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="30">
         <f>Данные!$D$22*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <f>D11*E11</f>
         <v>70560</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="30">
         <f>Данные!$D$22*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="30">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="8">
         <f>D12*E12</f>
         <v>100800</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="30">
         <f>Данные!$G$22*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <f>D13*E13</f>
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="30">
         <f>Данные!$F$22*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="30">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="8">
         <f>D14*E14</f>
         <v>33146.75</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="12">
         <f>SUM(F9:F14)</f>
         <v>204506.75</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Что входит</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="30">
         <f>Данные!$B$22*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="7">
         <f>D19*E19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="30">
         <f>Данные!$C$22*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="7">
         <f>D20*E20</f>
         <v>84240</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>Итого блока</t>
         </is>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="12">
         <f>SUM(F19:F20)</f>
         <v>84240</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4896,813 +4514,813 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>ФОНД ОПЛАТЫ ТРУДА</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Оклад одного дератизатора, ₸/мес</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="7">
         <f>Данные!$B$13</f>
         <v>350000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="7">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Зарплата в месяц</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <f>B6*B7</f>
         <v>1033952</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="7">
         <f>C6*C7</f>
         <v>1400000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="8">
         <f>B8*12</f>
         <v>12407424</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <f>C8*12</f>
         <v>16800000</v>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ, ЗЕРНОЦИД И БРИКЕТЫ РАЗДЕЛЬНО</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="34" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="35">
         <f>Данные!$D$20</f>
         <v>0</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="35">
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="7">
         <f>B13*Данные!$B$8*Данные!$B$15+C13*Данные!$B$8*Данные!$B$16</f>
         <v>0</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="48">
         <f>Данные!$G$20</f>
         <v>0</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="7">
         <f>E13*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="48">
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <f>G13*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="8">
         <f>D13+F13+H13</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="35">
         <f>SUM(Данные!$D$23:$D$30)</f>
         <v>268</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="35">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="7">
         <f>B14*Данные!$B$8*Данные!$B$15+C14*Данные!$B$8*Данные!$B$16</f>
         <v>728960</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="48">
         <f>SUM(Данные!$G$23:$G$30)</f>
         <v>15</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="7">
         <f>E14*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="48">
         <f>SUM(Данные!$F$23:$F$30)</f>
         <v>17</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="7">
         <f>G14*Данные!$B$7*Данные!$B$15</f>
         <v>433457.5</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="8">
         <f>D14+F14+H14</f>
         <v>1240117.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="35">
         <f>Данные!$D$21</f>
         <v>12</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="35">
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="7">
         <f>B15*Данные!$B$8*Данные!$B$15+C15*Данные!$B$8*Данные!$B$16</f>
         <v>32640</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="48">
         <f>Данные!$G$21</f>
         <v>1</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="7">
         <f>E15*Данные!$B$6*Данные!$B$15</f>
         <v>5180</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="48">
         <f>Данные!$F$21</f>
         <v>1</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="7">
         <f>G15*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="8">
         <f>D15+F15+H15</f>
         <v>63317.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="35">
         <f>Данные!$D$22</f>
         <v>63</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="35">
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="7">
         <f>B16*Данные!$B$8*Данные!$B$15+C16*Данные!$B$8*Данные!$B$16</f>
         <v>171360</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="48">
         <f>Данные!$G$22</f>
         <v>0</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="7">
         <f>E16*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="48">
         <f>Данные!$F$22</f>
         <v>1.3</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="7">
         <f>G16*Данные!$B$7*Данные!$B$15</f>
         <v>33146.75</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="8">
         <f>D16+F16+H16</f>
         <v>204506.75</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Бутылки (по объектам не разносятся)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="11">
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="8">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ ЗА ГОД, ИТОГО</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="29">
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="12">
         <f>SUM(D13:D17)</f>
         <v>932960</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="49">
         <f>SUM(E13:E17)</f>
         <v>16</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="12">
         <f>SUM(F13:F17)</f>
         <v>82880</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="49">
         <f>SUM(G13:G17)</f>
         <v>20.3</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="12">
         <f>SUM(H13:H17)</f>
         <v>517599.25</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="12">
         <f>SUM(I13:I17)</f>
         <v>1552479.25</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>РАЗОВАЯ ЗАКУПКА ПРИМАНОЧНЫХ СТАНЦИЙ</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>Всего, шт</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Цена, ₸/шт</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Разово, ₸</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="35">
         <f>Данные!$B$20</f>
         <v>0</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="35">
         <f>Данные!$C$20</f>
         <v>29</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="35">
         <f>B22+C22</f>
         <v>29</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="30">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="8">
         <f>D22*E22</f>
         <v>62640</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="35">
         <f>SUM(Данные!$B$23:$B$30)</f>
         <v>161</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="35">
         <f>SUM(Данные!$C$23:$C$30)</f>
         <v>1096</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="35">
         <f>B23+C23</f>
         <v>1257</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="30">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="8">
         <f>D23*E23</f>
         <v>2715120</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="35">
         <f>Данные!$B$21</f>
         <v>18</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="35">
         <f>Данные!$C$21</f>
         <v>34</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="35">
         <f>B24+C24</f>
         <v>52</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="30">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="8">
         <f>D24*E24</f>
         <v>112320</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="35">
         <f>Данные!$B$22</f>
         <v>0</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="35">
         <f>Данные!$C$22</f>
         <v>39</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="35">
         <f>B25+C25</f>
         <v>39</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="30">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="8">
         <f>D25*E25</f>
         <v>84240</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>ИТОГО РАЗОВО</t>
         </is>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="39">
         <f>SUM(B22:B25)</f>
         <v>179</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="39">
         <f>SUM(C22:C25)</f>
         <v>1198</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="39">
         <f>SUM(D22:D25)</f>
         <v>1377</v>
       </c>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="29">
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="12">
         <f>SUM(F22:F25)</f>
         <v>2974320</v>
       </c>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="34" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="34" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="7">
         <f>A30*Данные!$B$12</f>
         <v>516976</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="7">
         <f>B30*12</f>
         <v>6203712</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="8">
         <f>C30+D30</f>
         <v>7756191.25</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="8">
         <f>A30*Данные!$B$13*12+D30</f>
         <v>9952479.25</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="7">
         <f>A31*Данные!$B$12</f>
         <v>775464</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="7">
         <f>B31*12</f>
         <v>9305568</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="8">
         <f>C31+D31</f>
         <v>10858047.25</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="8">
         <f>A31*Данные!$B$13*12+D31</f>
         <v>14152479.25</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="7">
         <f>A32*Данные!$B$12</f>
         <v>1033952</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="7">
         <f>B32*12</f>
         <v>12407424</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="8">
         <f>C32+D32</f>
         <v>13959903.25</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="8">
         <f>A32*Данные!$B$13*12+D32</f>
         <v>18352479.25</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="7">
         <f>A33*Данные!$B$12</f>
         <v>1292440</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="7">
         <f>B33*12</f>
         <v>15509280</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="8">
         <f>C33+D33</f>
         <v>17061759.25</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="8">
         <f>A33*Данные!$B$13*12+D33</f>
         <v>22552479.25</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="7">
         <f>A34*Данные!$B$12</f>
         <v>1550928</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="7">
         <f>B34*12</f>
         <v>18611136</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="8">
         <f>C34+D34</f>
         <v>20163615.25</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="8">
         <f>A34*Данные!$B$13*12+D34</f>
         <v>26752479.25</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="7">
         <f>A35*Данные!$B$12</f>
         <v>1809416</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="7">
         <f>B35*12</f>
         <v>21712992</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="8">
         <f>C35+D35</f>
         <v>23265471.25</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="8">
         <f>A35*Данные!$B$13*12+D35</f>
         <v>30952479.25</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="7">
         <f>A36*Данные!$B$12</f>
         <v>2067904</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="7">
         <f>B36*12</f>
         <v>24814848</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="8">
         <f>C36+D36</f>
         <v>26367327.25</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="8">
         <f>A36*Данные!$B$13*12+D36</f>
         <v>35152479.25</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="7">
         <f>A37*Данные!$B$12</f>
         <v>2326392</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="7">
         <f>B37*12</f>
         <v>27916704</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="8">
         <f>C37+D37</f>
         <v>29469183.25</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="8">
         <f>A37*Данные!$B$13*12+D37</f>
         <v>39352479.25</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="7">
         <f>A38*Данные!$B$12</f>
         <v>2584880</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="7">
         <f>B38*12</f>
         <v>31018560</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="7">
         <f>'Штат УКПФ'!$I$18</f>
         <v>1552479.25</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="8">
         <f>C38+D38</f>
         <v>32571039.25</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="8">
         <f>A38*Данные!$B$13*12+D38</f>
         <v>43552479.25</v>
       </c>
     </row>
     <row r="39"/>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -5752,260 +5370,260 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>ЦЕНЫ И ПАРАМЕТРЫ ШТАТА УКПФ</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr"/>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr"/>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="40" t="n">
         <v>740</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="41" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="40" t="n">
         <v>3642.5</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="41" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="40" t="n">
         <v>160</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="41" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="40" t="n">
         <v>2160</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="41" t="inlineStr">
         <is>
           <t>разовая закупка; цена из прежнего расчёта по ККЗ (29 шт = 62 640 ₸)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="40" t="n">
         <v>68</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="41" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="40" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="41" t="inlineStr">
         <is>
           <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="40" t="n">
         <v>258488</v>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="41" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="40" t="n">
         <v>350000</v>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="41" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="41" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="41" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="41" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
@@ -6013,1070 +5631,1070 @@
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>ПРИМАНОЧНЫЕ СТАНЦИИ И НОРМЫ ЯДОВ ПО ОБЪЕКТАМ УКПФ</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="34" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="34" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="36" t="n">
+      <c r="B20" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="36" t="n">
+      <c r="C20" s="40" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="36" t="n">
+      <c r="D20" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="42" t="n">
+      <c r="F20" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="42" t="n">
+      <c r="G20" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H20" s="41" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="36" t="n">
+      <c r="B21" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="36" t="n">
+      <c r="C21" s="40" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="36" t="n">
+      <c r="D21" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
         <v>18</v>
       </c>
-      <c r="F21" s="42" t="n">
+      <c r="F21" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="42" t="n">
+      <c r="G21" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="12" t="inlineStr"/>
+      <c r="H21" s="41" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="36" t="n">
+      <c r="B22" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="36" t="n">
+      <c r="C22" s="40" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="36" t="n">
+      <c r="D22" s="40" t="n">
         <v>63</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="42" t="n">
+      <c r="F22" s="50" t="n">
         <v>1.3</v>
       </c>
-      <c r="G22" s="42" t="n">
+      <c r="G22" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="H22" s="41" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="36" t="n">
+      <c r="B23" s="40" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="36" t="n">
+      <c r="C23" s="40" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="36" t="n">
+      <c r="D23" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
         <v>13</v>
       </c>
-      <c r="F23" s="42" t="n">
+      <c r="F23" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="42" t="n">
+      <c r="G23" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
+      <c r="H23" s="41" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n">
+      <c r="B24" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="36" t="n">
+      <c r="C24" s="40" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="36" t="n">
+      <c r="D24" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
         <v>17</v>
       </c>
-      <c r="F24" s="42" t="n">
+      <c r="F24" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="42" t="n">
+      <c r="G24" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="12" t="inlineStr"/>
+      <c r="H24" s="41" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n">
+      <c r="B25" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="36" t="n">
+      <c r="C25" s="40" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="36" t="n">
+      <c r="D25" s="40" t="n">
         <v>30</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
         <v>50</v>
       </c>
-      <c r="F25" s="42" t="n">
+      <c r="F25" s="50" t="n">
         <v>3.5</v>
       </c>
-      <c r="G25" s="42" t="n">
+      <c r="G25" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
+      <c r="H25" s="41" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B26" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="36" t="n">
+      <c r="C26" s="40" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="36" t="n">
+      <c r="D26" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
         <v>17</v>
       </c>
-      <c r="F26" s="42" t="n">
+      <c r="F26" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="42" t="n">
+      <c r="G26" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
+      <c r="H26" s="41" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="36" t="n">
+      <c r="B27" s="40" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="40" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="36" t="n">
+      <c r="D27" s="40" t="n">
         <v>64</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
         <v>15</v>
       </c>
-      <c r="F27" s="42" t="n">
+      <c r="F27" s="50" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="42" t="n">
+      <c r="G27" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="12" t="inlineStr"/>
+      <c r="H27" s="41" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="36" t="n">
+      <c r="B28" s="40" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="36" t="n">
+      <c r="C28" s="40" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="36" t="n">
+      <c r="D28" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
         <v>13</v>
       </c>
-      <c r="F28" s="42" t="n">
+      <c r="F28" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="42" t="n">
+      <c r="G28" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="12" t="inlineStr"/>
+      <c r="H28" s="41" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n">
+      <c r="B29" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="36" t="n">
+      <c r="C29" s="40" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="36" t="n">
+      <c r="D29" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
         <v>17</v>
       </c>
-      <c r="F29" s="42" t="n">
+      <c r="F29" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="42" t="n">
+      <c r="G29" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="12" t="inlineStr"/>
+      <c r="H29" s="41" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="36" t="n">
+      <c r="B30" s="40" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="36" t="n">
+      <c r="C30" s="40" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="36" t="n">
+      <c r="D30" s="40" t="n">
         <v>24</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
         <v>19</v>
       </c>
-      <c r="F30" s="42" t="n">
+      <c r="F30" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="42" t="n">
+      <c r="G30" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="12" t="inlineStr"/>
+      <c r="H30" s="41" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>ЗПП · завод по переработке птицы</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="40" t="n"/>
-      <c r="G31" s="40" t="n"/>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="48" t="n"/>
+      <c r="G31" s="48" t="n"/>
+      <c r="H31" s="41" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Склад лузги</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="40" t="n"/>
-      <c r="G32" s="40" t="n"/>
-      <c r="H32" s="12" t="inlineStr">
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="48" t="n"/>
+      <c r="G32" s="48" t="n"/>
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>ИТОГО ПО ФАБРИКЕ</t>
         </is>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="12">
         <f>SUM(B20:B32)</f>
         <v>179</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="12">
         <f>SUM(C20:C32)</f>
         <v>1198</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="12">
         <f>SUM(D20:D32)</f>
         <v>343</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="12">
         <f>SUM(E20:E32)</f>
         <v>179</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="49">
         <f>SUM(F20:F32)</f>
         <v>20.3</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="49">
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
-      <c r="H33" s="16" t="n"/>
+      <c r="H33" s="37" t="n"/>
     </row>
     <row r="34"/>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>ЦЕНЫ ПОДРЯДЧИКОВ ИЗ КП И ДОГОВОРОВ</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr"/>
-      <c r="F36" s="13" t="inlineStr"/>
-      <c r="G36" s="13" t="inlineStr"/>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr"/>
+      <c r="E36" s="20" t="inlineStr"/>
+      <c r="F36" s="20" t="inlineStr"/>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="36" t="n">
+      <c r="B37" s="40" t="n">
         <v>96600</v>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H37" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="36" t="n">
+      <c r="B38" s="40" t="n">
         <v>618400</v>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="36" t="n">
+      <c r="B39" s="40" t="n">
         <v>478400</v>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="36" t="n">
+      <c r="B40" s="40" t="n">
         <v>569800</v>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H40" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="40" t="n">
         <v>440700</v>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H41" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="36" t="n">
+      <c r="B42" s="40" t="n">
         <v>2599100</v>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H42" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="36" t="n">
+      <c r="B43" s="40" t="n">
         <v>2010300</v>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H43" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="36" t="n">
+      <c r="B44" s="40" t="n">
         <v>126200</v>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="H44" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="36" t="n">
+      <c r="B45" s="40" t="n">
         <v>106800</v>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H45" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B46" s="40" t="n">
         <v>126200</v>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H46" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="40" t="n">
         <v>106800</v>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="H47" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="36" t="n">
+      <c r="B48" s="40" t="n">
         <v>720000</v>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="12" t="inlineStr">
+      <c r="H48" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n">
+      <c r="B49" s="40" t="n">
         <v>1080000</v>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H49" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="36" t="n">
+      <c r="B50" s="40" t="n">
         <v>3000000</v>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H50" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="40" t="n">
         <v>100800</v>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H51" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="36" t="n">
+      <c r="B52" s="40" t="n">
         <v>160800</v>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="12" t="inlineStr">
+      <c r="H52" s="41" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="36" t="n">
+      <c r="B53" s="40" t="n">
         <v>75000</v>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="12" t="inlineStr">
+      <c r="H53" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="36" t="n">
+      <c r="B54" s="40" t="n">
         <v>70000</v>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr">
+      <c r="H54" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="36" t="n">
+      <c r="B55" s="40" t="n">
         <v>3172000</v>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="H55" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="40" t="n">
         <v>2074000</v>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H56" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="36" t="n">
+      <c r="B57" s="40" t="n">
         <v>2806000</v>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr">
+      <c r="H57" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="36" t="n">
+      <c r="B58" s="40" t="n">
         <v>1830000</v>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
+      <c r="H58" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="36" t="n">
+      <c r="B59" s="40" t="n">
         <v>180000</v>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="12" t="inlineStr">
+      <c r="H59" s="41" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="36" t="n">
+      <c r="B60" s="40" t="n">
         <v>80000</v>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="H60" s="41" t="inlineStr">
         <is>
           <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="36" t="n">
+      <c r="B61" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr">
+      <c r="H61" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="36" t="n">
+      <c r="B62" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr">
+      <c r="H62" s="41" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="36" t="n">
+      <c r="B63" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
       </c>
-      <c r="H63" s="12" t="inlineStr">
+      <c r="H63" s="41" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B64" s="38" t="n">
+      <c r="B64" s="43" t="n">
         <v>0.15</v>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H64" s="41" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B65" s="38" t="n">
+      <c r="B65" s="43" t="n">
         <v>0.15</v>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr">
+      <c r="H65" s="41" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B66" s="38" t="n">
+      <c r="B66" s="43" t="n">
         <v>0.16</v>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="H66" s="41" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -263,12 +263,6 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -287,6 +281,12 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1515,15 +1515,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1559,21 +1557,21 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Штат УКПФ · материалы</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="26">
-        <f>F9</f>
+        <f>D9</f>
         <v>1159200</v>
       </c>
       <c r="C5" s="26">
-        <f>F10</f>
+        <f>D10</f>
         <v>900000</v>
       </c>
       <c r="D5" s="26">
-        <f>F11+F12+F13+F14</f>
+        <f>D11+D12+D13+D14</f>
         <v>25497.5</v>
       </c>
     </row>
@@ -1587,211 +1585,149 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>барьер вокруг периметра кормоцеха и грязный барьер</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D9" s="30">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
         <f>Данные!$B$37</f>
         <v>96600</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="C9" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="8">
-        <f>D9*E9</f>
+      <c r="D9" s="8">
+        <f>B9*C9</f>
         <v>1159200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>дератизация</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="30">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · дератизация</t>
+        </is>
+      </c>
+      <c r="B10" s="28">
         <f>Данные!$B$53</f>
         <v>75000</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="C10" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="8">
-        <f>D10*E10</f>
+      <c r="D10" s="8">
+        <f>B10*C10</f>
         <v>900000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, тёплый сезон</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="30">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B11" s="28">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="E11" s="30">
+      <c r="C11" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F11" s="8">
-        <f>D11*E11</f>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="30">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
+        </is>
+      </c>
+      <c r="B12" s="28">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="E12" s="30">
+      <c r="C12" s="28">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F12" s="8">
-        <f>D12*E12</f>
+      <c r="D12" s="8">
+        <f>B12*C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>Зерноцид, 2-й контур</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="30">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Зерноцид, 2-й контур</t>
+        </is>
+      </c>
+      <c r="B13" s="28">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30">
+      <c r="C13" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F13" s="8">
-        <f>D13*E13</f>
+      <c r="D13" s="8">
+        <f>B13*C13</f>
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="30">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Pest Killer, брикеты</t>
+        </is>
+      </c>
+      <c r="B14" s="28">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E14" s="30">
+      <c r="C14" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="8">
-        <f>D14*E14</f>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F15" s="12">
-        <f>SUM(F9:F14)</f>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D15" s="12">
+        <f>SUM(D9:D14)</f>
         <v>2084697.5</v>
       </c>
     </row>
@@ -1805,105 +1741,73 @@
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="30">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
         <f>Данные!$B$20*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="C19" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="7">
-        <f>D19*E19</f>
+      <c r="D19" s="7">
+        <f>B19*C19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="30">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B20" s="28">
         <f>Данные!$C$20*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="C20" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="7">
-        <f>D20*E20</f>
+      <c r="D20" s="7">
+        <f>B20*C20</f>
         <v>62640</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F21" s="12">
-        <f>SUM(F19:F20)</f>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D21" s="12">
+        <f>SUM(D19:D20)</f>
         <v>62640</v>
       </c>
     </row>
@@ -1917,87 +1821,67 @@
       <c r="B23" s="16" t="n"/>
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>дезинсекция</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="30">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · дезинсекция</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
         <f>Данные!$B$54</f>
         <v>70000</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="C25" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F25" s="7">
-        <f>D25*E25</f>
+      <c r="D25" s="7">
+        <f>B25*C25</f>
         <v>840000</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F26" s="12">
-        <f>SUM(F25:F25)</f>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D26" s="12">
+        <f>SUM(D25:D25)</f>
         <v>840000</v>
       </c>
     </row>
     <row r="27"/>
-    <row r="28" ht="28" customHeight="1">
+    <row r="28" ht="26" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
@@ -2006,9 +1890,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2020,15 +1904,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2064,21 +1946,21 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Штат УКПФ · материалы</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="26">
-        <f>F9+F10+F11</f>
+        <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
       <c r="C5" s="26">
-        <f>F12+F13</f>
+        <f>D12+D13</f>
         <v>34770000</v>
       </c>
       <c r="D5" s="26">
-        <f>F14+F15+F16+F17</f>
+        <f>D14+D15+D16+D17</f>
         <v>1240117.5</v>
       </c>
     </row>
@@ -2092,295 +1974,205 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D9" s="30">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
         <f>Данные!$B$38</f>
         <v>618400</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="C9" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="8">
-        <f>D9*E9</f>
+      <c r="D9" s="8">
+        <f>B9*C9</f>
         <v>7420800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D10" s="30">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
+        </is>
+      </c>
+      <c r="B10" s="28">
         <f>Данные!$B$40</f>
         <v>569800</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="C10" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="8">
-        <f>D10*E10</f>
+      <c r="D10" s="8">
+        <f>B10*C10</f>
         <v>6837600</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D11" s="30">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
+        </is>
+      </c>
+      <c r="B11" s="28">
         <f>Данные!$B$42</f>
         <v>2599100</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="C11" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="8">
-        <f>D11*E11</f>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
         <v>31189200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>122 объекта, март — ноябрь, оборудование подрядчика</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="30">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
+        </is>
+      </c>
+      <c r="B12" s="28">
         <f>Данные!$B$55</f>
         <v>3172000</v>
       </c>
-      <c r="E12" s="30">
+      <c r="C12" s="28">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="F12" s="8">
-        <f>D12*E12</f>
+      <c r="D12" s="8">
+        <f>B12*C12</f>
         <v>28548000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>122 объекта, декабрь — февраль, оборудование подрядчика</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="30">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
+        </is>
+      </c>
+      <c r="B13" s="28">
         <f>Данные!$B$56</f>
         <v>2074000</v>
       </c>
-      <c r="E13" s="30">
+      <c r="C13" s="28">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="F13" s="8">
-        <f>D13*E13</f>
+      <c r="D13" s="8">
+        <f>B13*C13</f>
         <v>6222000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, тёплый сезон</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="30">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B14" s="28">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="E14" s="30">
+      <c r="C14" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="8">
-        <f>D14*E14</f>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
         <v>300160</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="30">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
+        </is>
+      </c>
+      <c r="B15" s="28">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="E15" s="30">
+      <c r="C15" s="28">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F15" s="8">
-        <f>D15*E15</f>
+      <c r="D15" s="8">
+        <f>B15*C15</f>
         <v>428800</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>Зерноцид, 2-й контур</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" s="30">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Зерноцид, 2-й контур</t>
+        </is>
+      </c>
+      <c r="B16" s="28">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="E16" s="30">
+      <c r="C16" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F16" s="8">
-        <f>D16*E16</f>
+      <c r="D16" s="8">
+        <f>B16*C16</f>
         <v>77700</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="30">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Pest Killer, брикеты</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="E17" s="30">
+      <c r="C17" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F17" s="8">
-        <f>D17*E17</f>
+      <c r="D17" s="8">
+        <f>B17*C17</f>
         <v>433457.5</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F18" s="12">
-        <f>SUM(F9:F17)</f>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D18" s="12">
+        <f>SUM(D9:D17)</f>
         <v>81457717.5</v>
       </c>
     </row>
@@ -2394,187 +2186,129 @@
       <c r="B20" s="16" t="n"/>
       <c r="C20" s="16" t="n"/>
       <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>Айыртау БП — частичная замена</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D22" s="30">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Айыртау БП — частичная замена</t>
+        </is>
+      </c>
+      <c r="B22" s="28">
         <f>Данные!$B$39</f>
         <v>478400</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="C22" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F22" s="7">
-        <f>D22*E22</f>
+      <c r="D22" s="7">
+        <f>B22*C22</f>
         <v>5740800</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>Многоэтажки Д и Г — частичная замена</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D23" s="30">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
+        </is>
+      </c>
+      <c r="B23" s="28">
         <f>Данные!$B$41</f>
         <v>440700</v>
       </c>
-      <c r="E23" s="30" t="n">
+      <c r="C23" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F23" s="7">
-        <f>D23*E23</f>
+      <c r="D23" s="7">
+        <f>B23*C23</f>
         <v>5288400</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B24" s="29" t="inlineStr">
-        <is>
-          <t>Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D24" s="30">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
+        </is>
+      </c>
+      <c r="B24" s="28">
         <f>Данные!$B$43</f>
         <v>2010300</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="C24" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F24" s="7">
-        <f>D24*E24</f>
+      <c r="D24" s="7">
+        <f>B24*C24</f>
         <v>24123600</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>122 объекта, март — ноябрь, оборудование заказчика</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="30">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
         <f>Данные!$B$57</f>
         <v>2806000</v>
       </c>
-      <c r="E25" s="30">
+      <c r="C25" s="28">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="F25" s="7">
-        <f>D25*E25</f>
+      <c r="D25" s="7">
+        <f>B25*C25</f>
         <v>25254000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B26" s="29" t="inlineStr">
-        <is>
-          <t>122 объекта, декабрь — февраль, оборудование заказчика</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="30">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
+        </is>
+      </c>
+      <c r="B26" s="28">
         <f>Данные!$B$58</f>
         <v>1830000</v>
       </c>
-      <c r="E26" s="30">
+      <c r="C26" s="28">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="F26" s="7">
-        <f>D26*E26</f>
+      <c r="D26" s="7">
+        <f>B26*C26</f>
         <v>5490000</v>
       </c>
     </row>
     <row r="27">
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F27" s="12">
-        <f>SUM(F22:F26)</f>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D27" s="12">
+        <f>SUM(D22:D26)</f>
         <v>65896800</v>
       </c>
     </row>
@@ -2588,105 +2322,73 @@
       <c r="B29" s="16" t="n"/>
       <c r="C29" s="16" t="n"/>
       <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C30" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="30">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B31" s="28">
         <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="E31" s="30" t="n">
+      <c r="C31" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="7">
-        <f>D31*E31</f>
+      <c r="D31" s="7">
+        <f>B31*C31</f>
         <v>347760</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B32" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="30">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B32" s="28">
         <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="E32" s="30" t="n">
+      <c r="C32" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="7">
-        <f>D32*E32</f>
+      <c r="D32" s="7">
+        <f>B32*C32</f>
         <v>2367360</v>
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F33" s="12">
-        <f>SUM(F31:F32)</f>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D33" s="12">
+        <f>SUM(D31:D32)</f>
         <v>2715120</v>
       </c>
     </row>
@@ -2700,145 +2402,103 @@
       <c r="B35" s="16" t="n"/>
       <c r="C35" s="16" t="n"/>
       <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F36" s="28" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>Айыртау БП</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D37" s="30">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Айыртау БП</t>
+        </is>
+      </c>
+      <c r="B37" s="28">
         <f>Данные!$B$48</f>
         <v>720000</v>
       </c>
-      <c r="E37" s="30" t="n">
+      <c r="C37" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="7">
-        <f>D37*E37</f>
+      <c r="D37" s="7">
+        <f>B37*C37</f>
         <v>8640000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B38" s="29" t="inlineStr">
-        <is>
-          <t>Многоэтажки Д и Г</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D38" s="30">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Многоэтажки Д и Г</t>
+        </is>
+      </c>
+      <c r="B38" s="28">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="E38" s="30" t="n">
+      <c r="C38" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F38" s="7">
-        <f>D38*E38</f>
+      <c r="D38" s="7">
+        <f>B38*C38</f>
         <v>12960000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B39" s="29" t="inlineStr">
-        <is>
-          <t>Площадки А, Б, Е, Ж, В (РМ), В</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D39" s="30">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
+        </is>
+      </c>
+      <c r="B39" s="28">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="E39" s="30" t="n">
+      <c r="C39" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="7">
-        <f>D39*E39</f>
+      <c r="D39" s="7">
+        <f>B39*C39</f>
         <v>36000000</v>
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F40" s="12">
-        <f>SUM(F37:F39)</f>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D40" s="12">
+        <f>SUM(D37:D39)</f>
         <v>57600000</v>
       </c>
     </row>
     <row r="41"/>
-    <row r="42" ht="28" customHeight="1">
+    <row r="42" ht="26" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="28" customHeight="1">
+    <row r="43" ht="26" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
           <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
@@ -2847,9 +2507,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2861,15 +2521,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2905,21 +2563,21 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Штат УКПФ · материалы</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="26">
-        <f>F9</f>
+        <f>D9</f>
         <v>1514400</v>
       </c>
       <c r="C5" s="26">
-        <f>F10</f>
+        <f>D10</f>
         <v>0</v>
       </c>
       <c r="D5" s="26">
-        <f>F11+F12+F13+F14</f>
+        <f>D11+D12+D13+D14</f>
         <v>63317.5</v>
       </c>
     </row>
@@ -2933,212 +2591,148 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>полная замена оборудования, 48 ед.</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D9" s="30">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
         <f>Данные!$B$44</f>
         <v>126200</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="C9" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="8">
-        <f>D9*E9</f>
+      <c r="D9" s="8">
+        <f>B9*C9</f>
         <v>1514400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n">
+      <c r="B10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="C10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="8">
-        <f>D10*E10</f>
+      <c r="D10" s="8">
+        <f>B10*C10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, тёплый сезон</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="30">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B11" s="28">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="E11" s="30">
+      <c r="C11" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F11" s="8">
-        <f>D11*E11</f>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
         <v>13440</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="30">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
+        </is>
+      </c>
+      <c r="B12" s="28">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="E12" s="30">
+      <c r="C12" s="28">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F12" s="8">
-        <f>D12*E12</f>
+      <c r="D12" s="8">
+        <f>B12*C12</f>
         <v>19200</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>Зерноцид, 2-й контур</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="30">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Зерноцид, 2-й контур</t>
+        </is>
+      </c>
+      <c r="B13" s="28">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="E13" s="30">
+      <c r="C13" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F13" s="8">
-        <f>D13*E13</f>
+      <c r="D13" s="8">
+        <f>B13*C13</f>
         <v>5180</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="30">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Pest Killer, брикеты</t>
+        </is>
+      </c>
+      <c r="B14" s="28">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E14" s="30">
+      <c r="C14" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="8">
-        <f>D14*E14</f>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F15" s="12">
-        <f>SUM(F9:F14)</f>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D15" s="12">
+        <f>SUM(D9:D14)</f>
         <v>1577717.5</v>
       </c>
     </row>
@@ -3152,77 +2746,55 @@
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>частичная замена оборудования</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D19" s="30">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · частичная замена оборудования</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="C19" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="7">
-        <f>D19*E19</f>
+      <c r="D19" s="7">
+        <f>B19*C19</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="20">
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F20" s="12">
-        <f>SUM(F19:F19)</f>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D20" s="12">
+        <f>SUM(D19:D19)</f>
         <v>1281600</v>
       </c>
     </row>
@@ -3236,105 +2808,73 @@
       <c r="B22" s="16" t="n"/>
       <c r="C22" s="16" t="n"/>
       <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B24" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="30">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B24" s="28">
         <f>Данные!$B$21*Данные!$B$9</f>
         <v>38880</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="C24" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="7">
-        <f>D24*E24</f>
+      <c r="D24" s="7">
+        <f>B24*C24</f>
         <v>38880</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="30">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
         <f>Данные!$C$21*Данные!$B$9</f>
         <v>73440</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="C25" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="7">
-        <f>D25*E25</f>
+      <c r="D25" s="7">
+        <f>B25*C25</f>
         <v>73440</v>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F26" s="12">
-        <f>SUM(F24:F25)</f>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D26" s="12">
+        <f>SUM(D24:D25)</f>
         <v>112320</v>
       </c>
     </row>
@@ -3348,82 +2888,60 @@
       <c r="B28" s="16" t="n"/>
       <c r="C28" s="16" t="n"/>
       <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="inlineStr">
-        <is>
-          <t>дезинсекция</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D30" s="30">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · дезинсекция</t>
+        </is>
+      </c>
+      <c r="B30" s="28">
         <f>Данные!$B$51</f>
         <v>100800</v>
       </c>
-      <c r="E30" s="30" t="n">
+      <c r="C30" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="7">
-        <f>D30*E30</f>
+      <c r="D30" s="7">
+        <f>B30*C30</f>
         <v>1209600</v>
       </c>
     </row>
     <row r="31">
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F31" s="12">
-        <f>SUM(F30:F30)</f>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D31" s="12">
+        <f>SUM(D30:D30)</f>
         <v>1209600</v>
       </c>
     </row>
     <row r="32"/>
-    <row r="33" ht="28" customHeight="1">
+    <row r="33" ht="26" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
@@ -3432,8 +2950,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3445,15 +2963,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3489,21 +3005,21 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Штат УКПФ · материалы</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="26">
-        <f>F9</f>
+        <f>D9</f>
         <v>1514400</v>
       </c>
       <c r="C5" s="26">
-        <f>F10</f>
+        <f>D10</f>
         <v>2160000</v>
       </c>
       <c r="D5" s="26">
-        <f>F11</f>
+        <f>D11</f>
         <v>0</v>
       </c>
     </row>
@@ -3517,128 +3033,90 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>полная замена оборудования</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D9" s="30">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · полная замена оборудования</t>
+        </is>
+      </c>
+      <c r="B9" s="28">
         <f>Данные!$B$46</f>
         <v>126200</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="C9" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="8">
-        <f>D9*E9</f>
+      <c r="D9" s="8">
+        <f>B9*C9</f>
         <v>1514400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="30">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
+        </is>
+      </c>
+      <c r="B10" s="28">
         <f>Данные!$B$59</f>
         <v>180000</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="C10" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="8">
-        <f>D10*E10</f>
+      <c r="D10" s="8">
+        <f>B10*C10</f>
         <v>2160000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>нормы расхода по ЗПП не заданы</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="30" t="n">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="C11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="8">
-        <f>D11*E11</f>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F12" s="12">
-        <f>SUM(F9:F11)</f>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D12" s="12">
+        <f>SUM(D9:D11)</f>
         <v>3674400</v>
       </c>
     </row>
@@ -3652,77 +3130,55 @@
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>частичная замена оборудования</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D16" s="30">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · частичная замена оборудования</t>
+        </is>
+      </c>
+      <c r="B16" s="28">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="C16" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F16" s="7">
-        <f>D16*E16</f>
+      <c r="D16" s="7">
+        <f>B16*C16</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F17" s="12">
-        <f>SUM(F16:F16)</f>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D17" s="12">
+        <f>SUM(D16:D16)</f>
         <v>1281600</v>
       </c>
     </row>
@@ -3736,89 +3192,67 @@
       <c r="B19" s="16" t="n"/>
       <c r="C19" s="16" t="n"/>
       <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>дезинсекция</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D21" s="30">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · дезинсекция</t>
+        </is>
+      </c>
+      <c r="B21" s="28">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="C21" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="F21" s="7">
-        <f>D21*E21</f>
+      <c r="D21" s="7">
+        <f>B21*C21</f>
         <v>1929600</v>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F22" s="12">
-        <f>SUM(F21:F21)</f>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D22" s="12">
+        <f>SUM(D21:D21)</f>
         <v>1929600</v>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="28" customHeight="1">
+    <row r="24" ht="26" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
+    <row r="25" ht="26" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
@@ -3827,9 +3261,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3841,15 +3275,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3885,21 +3317,21 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Штат УКПФ · материалы</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="26">
-        <f>F9</f>
+        <f>D9</f>
         <v>0</v>
       </c>
       <c r="C5" s="26">
-        <f>F10</f>
+        <f>D10</f>
         <v>720000</v>
       </c>
       <c r="D5" s="26">
-        <f>F11</f>
+        <f>D11</f>
         <v>0</v>
       </c>
     </row>
@@ -3913,133 +3345,95 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="n">
+      <c r="B9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="C9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="8">
-        <f>D9*E9</f>
+      <c r="D9" s="8">
+        <f>B9*C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="30">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
+        </is>
+      </c>
+      <c r="B10" s="28">
         <f>Данные!$B$60</f>
         <v>80000</v>
       </c>
-      <c r="E10" s="30">
+      <c r="C10" s="28">
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
-      <c r="F10" s="8">
-        <f>D10*E10</f>
+      <c r="D10" s="8">
+        <f>B10*C10</f>
         <v>720000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>нормы расхода по складу не заданы</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="30" t="n">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · нормы расхода по складу не заданы</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="C11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="8">
-        <f>D11*E11</f>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="E12" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F12" s="12">
-        <f>SUM(F9:F11)</f>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D12" s="12">
+        <f>SUM(D9:D11)</f>
         <v>720000</v>
       </c>
     </row>
     <row r="13"/>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
@@ -4048,8 +3442,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4061,15 +3455,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4105,21 +3497,21 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Штат УКПФ · материалы</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="26">
-        <f>F9</f>
+        <f>D9</f>
         <v>0</v>
       </c>
       <c r="C5" s="26">
-        <f>F10</f>
+        <f>D10</f>
         <v>0</v>
       </c>
       <c r="D5" s="26">
-        <f>F11+F12+F13+F14</f>
+        <f>D11+D12+D13+D14</f>
         <v>204506.75</v>
       </c>
     </row>
@@ -4133,211 +3525,147 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="n">
+      <c r="B9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="C9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="8">
-        <f>D9*E9</f>
+      <c r="D9" s="8">
+        <f>B9*C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n">
+      <c r="B10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="C10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="8">
-        <f>D10*E10</f>
+      <c r="D10" s="8">
+        <f>B10*C10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, тёплый сезон</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="30">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B11" s="28">
         <f>Данные!$D$22*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="E11" s="30">
+      <c r="C11" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F11" s="8">
-        <f>D11*E11</f>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
         <v>70560</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="30">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
+        </is>
+      </c>
+      <c r="B12" s="28">
         <f>Данные!$D$22*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="E12" s="30">
+      <c r="C12" s="28">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="F12" s="8">
-        <f>D12*E12</f>
+      <c r="D12" s="8">
+        <f>B12*C12</f>
         <v>100800</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>Зерноцид, 2-й контур</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="30">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Зерноцид, 2-й контур</t>
+        </is>
+      </c>
+      <c r="B13" s="28">
         <f>Данные!$G$22*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30">
+      <c r="C13" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F13" s="8">
-        <f>D13*E13</f>
+      <c r="D13" s="8">
+        <f>B13*C13</f>
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" s="30">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Pest Killer, брикеты</t>
+        </is>
+      </c>
+      <c r="B14" s="28">
         <f>Данные!$F$22*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="E14" s="30">
+      <c r="C14" s="28">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="F14" s="8">
-        <f>D14*E14</f>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
         <v>33146.75</v>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F15" s="12">
-        <f>SUM(F9:F14)</f>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D15" s="12">
+        <f>SUM(D9:D14)</f>
         <v>204506.75</v>
       </c>
     </row>
@@ -4351,117 +3679,85 @@
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="30">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
         <f>Данные!$B$22*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="C19" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="7">
-        <f>D19*E19</f>
+      <c r="D19" s="7">
+        <f>B19*C19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="30">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B20" s="28">
         <f>Данные!$C$22*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="C20" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="7">
-        <f>D20*E20</f>
+      <c r="D20" s="7">
+        <f>B20*C20</f>
         <v>84240</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>Итого блока</t>
-        </is>
-      </c>
-      <c r="F21" s="12">
-        <f>SUM(F19:F20)</f>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="D21" s="12">
+        <f>SUM(D19:D20)</f>
         <v>84240</v>
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="28" customHeight="1">
+    <row r="23" ht="26" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
+    <row r="24" ht="26" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
@@ -4470,9 +3766,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4587,7 +3883,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -4618,47 +3914,47 @@
       <c r="I11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="34" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -4670,11 +3966,11 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="33">
         <f>Данные!$D$20</f>
         <v>0</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="33">
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
@@ -4709,11 +4005,11 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="33">
         <f>SUM(Данные!$D$23:$D$30)</f>
         <v>268</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="33">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
@@ -4748,11 +4044,11 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="33">
         <f>Данные!$D$21</f>
         <v>12</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="33">
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
@@ -4787,11 +4083,11 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="33">
         <f>Данные!$D$22</f>
         <v>63</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="33">
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
@@ -4844,8 +4140,8 @@
           <t>МАТЕРИАЛЫ ЗА ГОД, ИТОГО</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
       <c r="D18" s="12">
         <f>SUM(D13:D17)</f>
         <v>932960</v>
@@ -4885,32 +4181,32 @@
       <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>Всего, шт</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>Цена, ₸/шт</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="38" t="inlineStr">
         <is>
           <t>Разово, ₸</t>
         </is>
@@ -4922,19 +4218,19 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="33">
         <f>Данные!$B$20</f>
         <v>0</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="33">
         <f>Данные!$C$20</f>
         <v>29</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="33">
         <f>B22+C22</f>
         <v>29</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="28">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4949,19 +4245,19 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="33">
         <f>SUM(Данные!$B$23:$B$30)</f>
         <v>161</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="33">
         <f>SUM(Данные!$C$23:$C$30)</f>
         <v>1096</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="33">
         <f>B23+C23</f>
         <v>1257</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="28">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4976,19 +4272,19 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="33">
         <f>Данные!$B$21</f>
         <v>18</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="33">
         <f>Данные!$C$21</f>
         <v>34</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="33">
         <f>B24+C24</f>
         <v>52</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="28">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -5003,19 +4299,19 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="33">
         <f>Данные!$B$22</f>
         <v>0</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="33">
         <f>Данные!$C$22</f>
         <v>39</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="33">
         <f>B25+C25</f>
         <v>39</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="28">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -5042,7 +4338,7 @@
         <f>SUM(D22:D25)</f>
         <v>1377</v>
       </c>
-      <c r="E26" s="37" t="n"/>
+      <c r="E26" s="35" t="n"/>
       <c r="F26" s="12">
         <f>SUM(F22:F25)</f>
         <v>2974320</v>
@@ -5062,32 +4358,32 @@
       <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C29" s="32" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F29" s="34" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
@@ -5645,42 +4941,42 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="34" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="34" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="34" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -6057,7 +5353,7 @@
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
-      <c r="H33" s="37" t="n"/>
+      <c r="H33" s="35" t="n"/>
     </row>
     <row r="34"/>
     <row r="35">

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -245,17 +245,27 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -279,14 +289,7 @@
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -668,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -690,7 +693,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Все суммы в тенге. Только дератизация: дезинсекция у подрядчиков идёт отдельно. Цены Indigo включают НДС, цены Pest Hunters — без НДС.</t>
+          <t>Все суммы в тенге. Только дератизация: дезинсекция у подрядчиков идёт отдельно. Цены Indigo включают НДС, цены Pest Hunters — без НДС. Колонка «Штат УКПФ» — материалы по объектам; фонд оплаты труда идёт отдельной строкой ниже, его величина зависит от численности, заданной на листе «Данные».</t>
         </is>
       </c>
     </row>
@@ -718,7 +721,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="44" t="n"/>
+      <c r="A5" s="45" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>в месяц</t>
@@ -831,7 +834,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E8" s="45" t="n"/>
+      <c r="E8" s="46" t="n"/>
       <c r="F8" s="7">
         <f>G8/12</f>
         <v>5276.458333</v>
@@ -868,7 +871,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G9" s="45" t="n"/>
+      <c r="G9" s="46" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -881,7 +884,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n"/>
+      <c r="C10" s="46" t="n"/>
       <c r="D10" s="7">
         <f>E10/12</f>
         <v>60000</v>
@@ -895,7 +898,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G10" s="45" t="n"/>
+      <c r="G10" s="46" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -908,13 +911,13 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C11" s="45" t="n"/>
+      <c r="C11" s="46" t="n"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E11" s="45" t="n"/>
+      <c r="E11" s="46" t="n"/>
       <c r="F11" s="7">
         <f>G11/12</f>
         <v>17042.22917</v>
@@ -958,7 +961,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Штат УКПФ: зарплата и бутылки</t>
+          <t>Фонд оплаты труда дератизаторов</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -967,543 +970,806 @@
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="7">
         <f>G13/12</f>
-        <v>1035538.667</v>
+        <v>1033952</v>
       </c>
       <c r="G13" s="7">
-        <f>Данные!$B$14*Данные!$B$12*12+Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v>12426464</v>
+        <f>Данные!$B$14*Данные!$B$12*12</f>
+        <v>12407424</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Бутылки</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="7">
+        <f>G14/12</f>
+        <v>1586.666667</v>
+      </c>
+      <c r="G14" s="7">
+        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
+        <v>19040</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>ВСЕГО ЗА ГОД</t>
         </is>
       </c>
-      <c r="B14" s="14">
-        <f>C14/12</f>
+      <c r="B15" s="14">
+        <f>C15/12</f>
         <v>4136300</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C15" s="14">
         <f>C12</f>
         <v>49635600</v>
       </c>
-      <c r="D14" s="14">
-        <f>E14/12</f>
+      <c r="D15" s="14">
+        <f>E15/12</f>
         <v>3212500</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E15" s="14">
         <f>E12</f>
         <v>38550000</v>
       </c>
-      <c r="F14" s="14">
-        <f>G14/12</f>
+      <c r="F15" s="14">
+        <f>G15/12</f>
         <v>1163325.271</v>
       </c>
-      <c r="G14" s="14">
-        <f>G12+G13</f>
+      <c r="G15" s="14">
+        <f>G12+G13+G14</f>
         <v>13959903.25</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="16" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>во сколько раз</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions дороже штата</t>
-        </is>
-      </c>
-      <c r="B18" s="7">
-        <f>C18/12</f>
-        <v>2972974.729</v>
-      </c>
-      <c r="C18" s="8">
-        <f>C14-G14</f>
-        <v>35675696.75</v>
-      </c>
-      <c r="D18" s="46">
-        <f>IF(G14=0,0,C14/G14)</f>
-        <v>3.555583381</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Pest Hunters дороже штата</t>
+          <t>Indigo Solutions дороже штата</t>
         </is>
       </c>
       <c r="B19" s="7">
         <f>C19/12</f>
+        <v>2972974.729</v>
+      </c>
+      <c r="C19" s="8">
+        <f>C15-G15</f>
+        <v>35675696.75</v>
+      </c>
+      <c r="D19" s="47">
+        <f>IF(G15=0,0,C15/G15)</f>
+        <v>3.555583381</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters дороже штата</t>
+        </is>
+      </c>
+      <c r="B20" s="7">
+        <f>C20/12</f>
         <v>2049174.729</v>
       </c>
-      <c r="C19" s="8">
-        <f>E14-G14</f>
+      <c r="C20" s="8">
+        <f>E15-G15</f>
         <v>24590096.75</v>
       </c>
-      <c r="D19" s="46">
-        <f>IF(G14=0,0,E14/G14)</f>
+      <c r="D20" s="47">
+        <f>IF(G15=0,0,E15/G15)</f>
         <v>2.761480457</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>ШТАТ УКПФ · ИЗ ЧЕГО СКЛАДЫВАЕТСЯ</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Цена за ед., ₸</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>за год, ₸</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Численность штата</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>Данные!$B$14</f>
+        <v>4</v>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>чел.</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Оклад одного дератизатора</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>₸/мес</t>
+        </is>
+      </c>
+      <c r="D25" s="7">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Фонд оплаты труда</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>C23/12</f>
+      <c r="B26" s="7">
+        <f>Данные!$B$14</f>
+        <v>4</v>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>чел.</t>
+        </is>
+      </c>
+      <c r="D26" s="7">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+      <c r="E26" s="7">
+        <f>Данные!$B$14*Данные!$B$12</f>
         <v>1033952</v>
       </c>
-      <c r="C23" s="8">
+      <c r="F26" s="8">
         <f>Данные!$B$14*Данные!$B$12*12</f>
         <v>12407424</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура</t>
-        </is>
-      </c>
-      <c r="B24" s="7">
-        <f>C24/12</f>
-        <v>77746.66667</v>
-      </c>
-      <c r="C24" s="8">
-        <f>'Штат УКПФ'!D18</f>
-        <v>932960</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Зерноцид</t>
-        </is>
-      </c>
-      <c r="B25" s="7">
-        <f>C25/12</f>
-        <v>6906.666667</v>
-      </c>
-      <c r="C25" s="8">
-        <f>'Штат УКПФ'!F18</f>
-        <v>82880</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты</t>
-        </is>
-      </c>
-      <c r="B26" s="7">
-        <f>C26/12</f>
-        <v>43133.27083</v>
-      </c>
-      <c r="C26" s="8">
-        <f>'Штат УКПФ'!H18</f>
-        <v>517599.25</v>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Бутылки</t>
+          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
         </is>
       </c>
       <c r="B27" s="7">
-        <f>C27/12</f>
-        <v>1586.666667</v>
-      </c>
-      <c r="C27" s="8">
+        <f>Данные!$D$33</f>
+        <v>343</v>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D27" s="7">
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E27" s="7">
+        <f>Данные!$D$33*Данные!$B$8</f>
+        <v>54880</v>
+      </c>
+      <c r="F27" s="8">
+        <f>Данные!$D$33*Данные!$B$8*Данные!$B$15</f>
+        <v>384160</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
+        </is>
+      </c>
+      <c r="B28" s="7">
+        <f>Данные!$D$33*2</f>
+        <v>686</v>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D28" s="7">
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E28" s="7">
+        <f>Данные!$D$33*2*Данные!$B$8</f>
+        <v>109760</v>
+      </c>
+      <c r="F28" s="8">
+        <f>Данные!$D$33*2*Данные!$B$8*Данные!$B$16</f>
+        <v>548800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Зерноцид · 2-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B29" s="7">
+        <f>Данные!$G$33</f>
+        <v>16</v>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D29" s="7">
+        <f>Данные!$B$6</f>
+        <v>740</v>
+      </c>
+      <c r="E29" s="7">
+        <f>Данные!$G$33*Данные!$B$6</f>
+        <v>11840</v>
+      </c>
+      <c r="F29" s="8">
+        <f>Данные!$G$33*Данные!$B$6*Данные!$B$15</f>
+        <v>82880</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Pest Killer, брикеты · тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B30" s="7">
+        <f>Данные!$F$33</f>
+        <v>20.3</v>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D30" s="7">
+        <f>Данные!$B$7</f>
+        <v>3642.5</v>
+      </c>
+      <c r="E30" s="7">
+        <f>Данные!$F$33*Данные!$B$7</f>
+        <v>73942.75</v>
+      </c>
+      <c r="F30" s="8">
+        <f>Данные!$F$33*Данные!$B$7*Данные!$B$15</f>
+        <v>517599.25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Бутылки · тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B31" s="7">
+        <f>Данные!$B$11</f>
+        <v>40</v>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D31" s="7">
+        <f>Данные!$B$10</f>
+        <v>68</v>
+      </c>
+      <c r="E31" s="7">
+        <f>Данные!$B$11*Данные!$B$10</f>
+        <v>2720</v>
+      </c>
+      <c r="F31" s="8">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО ШТАТ</t>
-        </is>
-      </c>
-      <c r="B28" s="12">
-        <f>C28/12</f>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО ТЕКУЩИЕ РАСХОДЫ ШТАТА</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="14">
+        <f>F32/12</f>
         <v>1163325.271</v>
       </c>
-      <c r="C28" s="12">
-        <f>SUM(C23:C27)</f>
+      <c r="F32" s="14">
+        <f>F26+F27+F28+F29+F30+F31</f>
         <v>13959903.25</v>
       </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="16" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Условие</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Ставка</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Цена КП без скидок</t>
-        </is>
-      </c>
-      <c r="B32" s="7">
-        <f>C32/12</f>
-        <v>4136300</v>
-      </c>
-      <c r="C32" s="8">
-        <f>C14</f>
-        <v>49635600</v>
-      </c>
-      <c r="D32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
+          <t>Приманочные станции 1-го контура · разовая закупка</t>
+        </is>
+      </c>
+      <c r="B33" s="7">
+        <f>Данные!$B$33</f>
+        <v>179</v>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D33" s="7">
+        <f>Данные!$B$9</f>
+        <v>2160</v>
+      </c>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="8">
+        <f>Данные!$B$33*Данные!$B$9</f>
+        <v>386640</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Приманочные станции 2-го контура · разовая закупка</t>
+        </is>
+      </c>
+      <c r="B34" s="7">
+        <f>Данные!$C$33</f>
+        <v>1198</v>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D34" s="7">
+        <f>Данные!$B$9</f>
+        <v>2160</v>
+      </c>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="8">
+        <f>Данные!$C$33*Данные!$B$9</f>
+        <v>2587680</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО РАЗОВАЯ ЗАКУПКА ОБОРУДОВАНИЯ</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>Данные!$B$33+Данные!$C$33</f>
+        <v>1377</v>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="12">
+        <f>F33+F34</f>
+        <v>2974320</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО ПЕРВЫЙ ГОД · с разовой закупкой</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="14">
+        <f>F32+F35</f>
+        <v>16934223.25</v>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Цена КП без скидок</t>
+        </is>
+      </c>
+      <c r="B41" s="7">
+        <f>C41/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C41" s="8">
+        <f>C15</f>
+        <v>49635600</v>
+      </c>
+      <c r="D41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>C33/12</f>
+      <c r="B42" s="7">
+        <f>C42/12</f>
         <v>3515855</v>
       </c>
-      <c r="C33" s="8">
-        <f>C14*(1-Данные!$B$64)</f>
+      <c r="C42" s="8">
+        <f>C15*(1-Данные!$B$64)</f>
         <v>42190260</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D42" s="25">
         <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>C34/12</f>
+      <c r="B43" s="7">
+        <f>C43/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="C34" s="8">
-        <f>C14*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+      <c r="C43" s="8">
+        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
         <v>35861721</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D43" s="25">
         <f>Данные!$B$65</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
-      <c r="B35" s="7">
-        <f>C35/12</f>
+      <c r="B44" s="7">
+        <f>C44/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="C35" s="8">
-        <f>C14*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
+      <c r="C44" s="8">
+        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D44" s="25">
         <f>Данные!$B$66</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="16" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Что зафиксировано в документах</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
         <is>
           <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
         </is>
       </c>
-      <c r="E39" s="47" t="n"/>
-      <c r="F39" s="47" t="n"/>
-      <c r="G39" s="45" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="E48" s="48" t="n"/>
+      <c r="F48" s="48" t="n"/>
+      <c r="G48" s="46" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="C40" s="21" t="n">
+      <c r="C49" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>выезд по запросу</t>
         </is>
       </c>
-      <c r="E40" s="47" t="n"/>
-      <c r="F40" s="47" t="n"/>
-      <c r="G40" s="45" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="E49" s="48" t="n"/>
+      <c r="F49" s="48" t="n"/>
+      <c r="G49" s="46" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>бройлерные площадки</t>
         </is>
       </c>
-      <c r="C41" s="21" t="n">
+      <c r="C50" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>дополнительные визиты по вызову</t>
         </is>
       </c>
-      <c r="E41" s="47" t="n"/>
-      <c r="F41" s="47" t="n"/>
-      <c r="G41" s="45" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="E50" s="48" t="n"/>
+      <c r="F50" s="48" t="n"/>
+      <c r="G50" s="46" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="C42" s="21" t="n">
+      <c r="C51" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D51" s="27" t="inlineStr">
         <is>
           <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
-      <c r="E42" s="47" t="n"/>
-      <c r="F42" s="47" t="n"/>
-      <c r="G42" s="45" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="E51" s="48" t="n"/>
+      <c r="F51" s="48" t="n"/>
+      <c r="G51" s="46" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>склад ТМЦ</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n">
+      <c r="C52" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="22" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
         <is>
           <t>выезд по рекламации за два рабочих дня</t>
         </is>
       </c>
-      <c r="E43" s="47" t="n"/>
-      <c r="F43" s="47" t="n"/>
-      <c r="G43" s="45" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="E52" s="48" t="n"/>
+      <c r="F52" s="48" t="n"/>
+      <c r="G52" s="46" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C44" s="21" t="n">
+      <c r="C53" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="D53" s="27" t="inlineStr">
         <is>
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
-      <c r="E44" s="47" t="n"/>
-      <c r="F44" s="47" t="n"/>
-      <c r="G44" s="45" t="n"/>
+      <c r="E53" s="48" t="n"/>
+      <c r="F53" s="48" t="n"/>
+      <c r="G53" s="46" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D48:G48"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D53:G53"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D52:G52"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D51:G51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1532,7 +1798,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура, 1 кг брикетов Pest Killer на обработку.</t>
         </is>
@@ -1540,37 +1806,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="30">
         <f>D11+D12+D13+D14</f>
         <v>25497.5</v>
       </c>
@@ -1609,16 +1875,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="32">
         <f>Данные!$B$37</f>
         <v>96600</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -1627,16 +1893,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · дератизация</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="32">
         <f>Данные!$B$53</f>
         <v>75000</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -1645,16 +1911,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="32">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1664,16 +1930,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="32">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="32">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -1683,16 +1949,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="32">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1702,16 +1968,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="32">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1721,7 +1987,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -1765,16 +2031,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="32">
         <f>Данные!$B$20*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="7">
@@ -1783,16 +2049,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="32">
         <f>Данные!$C$20*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="7">
@@ -1801,7 +2067,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -1845,16 +2111,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="32">
         <f>Данные!$B$54</f>
         <v>70000</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="7">
@@ -1863,7 +2129,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -1875,14 +2141,14 @@
     </row>
     <row r="27"/>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -1921,7 +2187,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -1929,37 +2195,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="30">
         <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="30">
         <f>D12+D13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="30">
         <f>D14+D15+D16+D17</f>
         <v>1240117.5</v>
       </c>
@@ -1998,16 +2264,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="32">
         <f>Данные!$B$38</f>
         <v>618400</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2016,16 +2282,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="32">
         <f>Данные!$B$40</f>
         <v>569800</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -2034,16 +2300,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="32">
         <f>Данные!$B$42</f>
         <v>2599100</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="8">
@@ -2052,16 +2318,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="32">
         <f>Данные!$B$55</f>
         <v>3172000</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="32">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2071,16 +2337,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="32">
         <f>Данные!$B$56</f>
         <v>2074000</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="32">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2090,16 +2356,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="32">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2109,16 +2375,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="32">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="32">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2128,16 +2394,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="32">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2147,16 +2413,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="32">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2166,7 +2432,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2210,16 +2476,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="32">
         <f>Данные!$B$39</f>
         <v>478400</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D22" s="7">
@@ -2228,16 +2494,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="32">
         <f>Данные!$B$41</f>
         <v>440700</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="7">
@@ -2246,16 +2512,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="32">
         <f>Данные!$B$43</f>
         <v>2010300</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="7">
@@ -2264,16 +2530,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="32">
         <f>Данные!$B$57</f>
         <v>2806000</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="32">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2283,16 +2549,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="32">
         <f>Данные!$B$58</f>
         <v>1830000</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="32">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2302,7 +2568,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2346,16 +2612,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="32">
         <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C31" s="28" t="n">
+      <c r="C31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="7">
@@ -2364,16 +2630,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="32">
         <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="7">
@@ -2382,7 +2648,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="29" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2426,16 +2692,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="32">
         <f>Данные!$B$48</f>
         <v>720000</v>
       </c>
-      <c r="C37" s="28" t="n">
+      <c r="C37" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D37" s="7">
@@ -2444,16 +2710,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="32">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="C38" s="28" t="n">
+      <c r="C38" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D38" s="7">
@@ -2462,16 +2728,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="inlineStr">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="32">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="C39" s="28" t="n">
+      <c r="C39" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D39" s="7">
@@ -2480,7 +2746,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2492,14 +2758,14 @@
     </row>
     <row r="41"/>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="24" t="inlineStr">
         <is>
           <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
         </is>
@@ -2538,7 +2804,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
@@ -2546,37 +2812,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="30">
         <f>D11+D12+D13+D14</f>
         <v>63317.5</v>
       </c>
@@ -2615,16 +2881,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="32">
         <f>Данные!$B$44</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2633,15 +2899,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -2650,16 +2916,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="32">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2669,16 +2935,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="32">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="32">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2688,16 +2954,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="32">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2707,16 +2973,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="32">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2726,7 +2992,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2770,16 +3036,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="32">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -2788,7 +3054,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2832,16 +3098,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="32">
         <f>Данные!$B$21*Данные!$B$9</f>
         <v>38880</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="7">
@@ -2850,16 +3116,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="32">
         <f>Данные!$C$21*Данные!$B$9</f>
         <v>73440</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="7">
@@ -2868,7 +3134,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2912,16 +3178,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="32">
         <f>Данные!$B$51</f>
         <v>100800</v>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C30" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D30" s="7">
@@ -2930,7 +3196,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="29" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2942,7 +3208,7 @@
     </row>
     <row r="32"/>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -2980,7 +3246,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -2988,37 +3254,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="30">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3057,16 +3323,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="32">
         <f>Данные!$B$46</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -3075,16 +3341,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="32">
         <f>Данные!$B$59</f>
         <v>180000</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -3093,15 +3359,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3110,7 +3376,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3154,16 +3420,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="32">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D16" s="7">
@@ -3172,7 +3438,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3216,16 +3482,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="32">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="C21" s="28" t="n">
+      <c r="C21" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D21" s="7">
@@ -3234,7 +3500,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3246,14 +3512,14 @@
     </row>
     <row r="23"/>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3292,7 +3558,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -3300,37 +3566,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>720000</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="30">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3369,15 +3635,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3386,16 +3652,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="32">
         <f>Данные!$B$60</f>
         <v>80000</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="32">
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
@@ -3405,15 +3671,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3422,7 +3688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3434,7 +3700,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3472,7 +3738,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -3480,37 +3746,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="30">
         <f>D11+D12+D13+D14</f>
         <v>204506.75</v>
       </c>
@@ -3549,15 +3815,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3566,15 +3832,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -3583,16 +3849,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="32">
         <f>Данные!$D$22*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3602,16 +3868,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="32">
         <f>Данные!$D$22*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="32">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -3621,16 +3887,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="32">
         <f>Данные!$G$22*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3640,16 +3906,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="32">
         <f>Данные!$F$22*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3659,7 +3925,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3703,16 +3969,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="32">
         <f>Данные!$B$22*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="7">
@@ -3721,16 +3987,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="32">
         <f>Данные!$C$22*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="7">
@@ -3739,7 +4005,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3751,14 +4017,14 @@
     </row>
     <row r="22"/>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -3821,17 +4087,17 @@
       <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
@@ -3883,7 +4149,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -3914,47 +4180,47 @@
       <c r="I11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="32" t="inlineStr">
+      <c r="G12" s="36" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="32" t="inlineStr">
+      <c r="I12" s="36" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -3966,11 +4232,11 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="37">
         <f>Данные!$D$20</f>
         <v>0</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="37">
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
@@ -3978,7 +4244,7 @@
         <f>B13*Данные!$B$8*Данные!$B$15+C13*Данные!$B$8*Данные!$B$16</f>
         <v>0</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="49">
         <f>Данные!$G$20</f>
         <v>0</v>
       </c>
@@ -3986,7 +4252,7 @@
         <f>E13*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="49">
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
@@ -4005,11 +4271,11 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="37">
         <f>SUM(Данные!$D$23:$D$30)</f>
         <v>268</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="37">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
@@ -4017,7 +4283,7 @@
         <f>B14*Данные!$B$8*Данные!$B$15+C14*Данные!$B$8*Данные!$B$16</f>
         <v>728960</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="49">
         <f>SUM(Данные!$G$23:$G$30)</f>
         <v>15</v>
       </c>
@@ -4025,7 +4291,7 @@
         <f>E14*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="49">
         <f>SUM(Данные!$F$23:$F$30)</f>
         <v>17</v>
       </c>
@@ -4044,11 +4310,11 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="37">
         <f>Данные!$D$21</f>
         <v>12</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="37">
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
@@ -4056,7 +4322,7 @@
         <f>B15*Данные!$B$8*Данные!$B$15+C15*Данные!$B$8*Данные!$B$16</f>
         <v>32640</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="49">
         <f>Данные!$G$21</f>
         <v>1</v>
       </c>
@@ -4064,7 +4330,7 @@
         <f>E15*Данные!$B$6*Данные!$B$15</f>
         <v>5180</v>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="49">
         <f>Данные!$F$21</f>
         <v>1</v>
       </c>
@@ -4083,11 +4349,11 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="37">
         <f>Данные!$D$22</f>
         <v>63</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="37">
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
@@ -4095,7 +4361,7 @@
         <f>B16*Данные!$B$8*Данные!$B$15+C16*Данные!$B$8*Данные!$B$16</f>
         <v>171360</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="49">
         <f>Данные!$G$22</f>
         <v>0</v>
       </c>
@@ -4103,7 +4369,7 @@
         <f>E16*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="49">
         <f>Данные!$F$22</f>
         <v>1.3</v>
       </c>
@@ -4140,13 +4406,13 @@
           <t>МАТЕРИАЛЫ ЗА ГОД, ИТОГО</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
       <c r="D18" s="12">
         <f>SUM(D13:D17)</f>
         <v>932960</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="50">
         <f>SUM(E13:E17)</f>
         <v>16</v>
       </c>
@@ -4154,7 +4420,7 @@
         <f>SUM(F13:F17)</f>
         <v>82880</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="50">
         <f>SUM(G13:G17)</f>
         <v>20.3</v>
       </c>
@@ -4181,32 +4447,32 @@
       <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Всего, шт</t>
         </is>
       </c>
-      <c r="E21" s="38" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>Цена, ₸/шт</t>
         </is>
       </c>
-      <c r="F21" s="38" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Разово, ₸</t>
         </is>
@@ -4218,19 +4484,19 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="37">
         <f>Данные!$B$20</f>
         <v>0</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="37">
         <f>Данные!$C$20</f>
         <v>29</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="37">
         <f>B22+C22</f>
         <v>29</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="32">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4245,19 +4511,19 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="37">
         <f>SUM(Данные!$B$23:$B$30)</f>
         <v>161</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="37">
         <f>SUM(Данные!$C$23:$C$30)</f>
         <v>1096</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="37">
         <f>B23+C23</f>
         <v>1257</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="32">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4272,19 +4538,19 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="37">
         <f>Данные!$B$21</f>
         <v>18</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="37">
         <f>Данные!$C$21</f>
         <v>34</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="37">
         <f>B24+C24</f>
         <v>52</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="32">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4299,19 +4565,19 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="37">
         <f>Данные!$B$22</f>
         <v>0</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="37">
         <f>Данные!$C$22</f>
         <v>39</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="37">
         <f>B25+C25</f>
         <v>39</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="32">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4326,19 +4592,19 @@
           <t>ИТОГО РАЗОВО</t>
         </is>
       </c>
-      <c r="B26" s="39">
+      <c r="B26" s="40">
         <f>SUM(B22:B25)</f>
         <v>179</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="40">
         <f>SUM(C22:C25)</f>
         <v>1198</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="40">
         <f>SUM(D22:D25)</f>
         <v>1377</v>
       </c>
-      <c r="E26" s="35" t="n"/>
+      <c r="E26" s="22" t="n"/>
       <c r="F26" s="12">
         <f>SUM(F22:F25)</f>
         <v>2974320</v>
@@ -4358,32 +4624,32 @@
       <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="F29" s="36" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
@@ -4616,7 +4882,7 @@
     </row>
     <row r="39"/>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -4680,26 +4946,26 @@
       <c r="H4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr"/>
+      <c r="E5" s="26" t="inlineStr"/>
+      <c r="F5" s="26" t="inlineStr"/>
+      <c r="G5" s="26" t="inlineStr"/>
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
@@ -4711,7 +4977,7 @@
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="41" t="n">
         <v>740</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4719,7 +4985,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="41" t="inlineStr">
+      <c r="H6" s="42" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -4731,7 +4997,7 @@
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="41" t="n">
         <v>3642.5</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4739,7 +5005,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="41" t="inlineStr">
+      <c r="H7" s="42" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
@@ -4751,7 +5017,7 @@
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B8" s="41" t="n">
         <v>160</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -4759,7 +5025,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="41" t="inlineStr">
+      <c r="H8" s="42" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
@@ -4771,7 +5037,7 @@
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="41" t="n">
         <v>2160</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -4779,7 +5045,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H9" s="41" t="inlineStr">
+      <c r="H9" s="42" t="inlineStr">
         <is>
           <t>разовая закупка; цена из прежнего расчёта по ККЗ (29 шт = 62 640 ₸)</t>
         </is>
@@ -4791,7 +5057,7 @@
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="41" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4799,7 +5065,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="41" t="inlineStr">
+      <c r="H10" s="42" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -4811,7 +5077,7 @@
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n">
+      <c r="B11" s="41" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4819,7 +5085,7 @@
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="H11" s="41" t="inlineStr">
+      <c r="H11" s="42" t="inlineStr">
         <is>
           <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
         </is>
@@ -4831,7 +5097,7 @@
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n">
+      <c r="B12" s="41" t="n">
         <v>258488</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4839,7 +5105,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="41" t="inlineStr">
+      <c r="H12" s="42" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
@@ -4851,7 +5117,7 @@
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="40" t="n">
+      <c r="B13" s="41" t="n">
         <v>350000</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4859,7 +5125,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H13" s="41" t="inlineStr">
+      <c r="H13" s="42" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
@@ -4871,7 +5137,7 @@
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="40" t="n">
+      <c r="B14" s="41" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4879,7 +5145,7 @@
           <t>чел.</t>
         </is>
       </c>
-      <c r="H14" s="41" t="inlineStr">
+      <c r="H14" s="42" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
@@ -4891,7 +5157,7 @@
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="40" t="n">
+      <c r="B15" s="41" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4899,7 +5165,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="41" t="inlineStr">
+      <c r="H15" s="42" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
@@ -4911,7 +5177,7 @@
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="40" t="n">
+      <c r="B16" s="41" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4919,7 +5185,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H16" s="41" t="inlineStr">
+      <c r="H16" s="42" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
@@ -4941,42 +5207,42 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="32" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="32" t="inlineStr">
+      <c r="H19" s="36" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -4988,26 +5254,26 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="40" t="n">
+      <c r="B20" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="40" t="n">
+      <c r="C20" s="41" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="41" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="50" t="n">
+      <c r="F20" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="50" t="n">
+      <c r="G20" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="41" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
@@ -5019,26 +5285,26 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="40" t="n">
+      <c r="B21" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="40" t="n">
+      <c r="C21" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="40" t="n">
+      <c r="D21" s="41" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
         <v>18</v>
       </c>
-      <c r="F21" s="50" t="n">
+      <c r="F21" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="50" t="n">
+      <c r="G21" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="41" t="inlineStr"/>
+      <c r="H21" s="42" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5046,26 +5312,26 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="40" t="n">
+      <c r="B22" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="40" t="n">
+      <c r="C22" s="41" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="40" t="n">
+      <c r="D22" s="41" t="n">
         <v>63</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="50" t="n">
+      <c r="F22" s="51" t="n">
         <v>1.3</v>
       </c>
-      <c r="G22" s="50" t="n">
+      <c r="G22" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="41" t="inlineStr">
+      <c r="H22" s="42" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
@@ -5077,26 +5343,26 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="40" t="n">
+      <c r="B23" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="40" t="n">
+      <c r="C23" s="41" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="40" t="n">
+      <c r="D23" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
         <v>13</v>
       </c>
-      <c r="F23" s="50" t="n">
+      <c r="F23" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="50" t="n">
+      <c r="G23" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="41" t="inlineStr"/>
+      <c r="H23" s="42" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5104,26 +5370,26 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="40" t="n">
+      <c r="B24" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="40" t="n">
+      <c r="C24" s="41" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="40" t="n">
+      <c r="D24" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
         <v>17</v>
       </c>
-      <c r="F24" s="50" t="n">
+      <c r="F24" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="50" t="n">
+      <c r="G24" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="41" t="inlineStr"/>
+      <c r="H24" s="42" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5131,26 +5397,26 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="40" t="n">
+      <c r="B25" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="40" t="n">
+      <c r="C25" s="41" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="40" t="n">
+      <c r="D25" s="41" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
         <v>50</v>
       </c>
-      <c r="F25" s="50" t="n">
+      <c r="F25" s="51" t="n">
         <v>3.5</v>
       </c>
-      <c r="G25" s="50" t="n">
+      <c r="G25" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="41" t="inlineStr"/>
+      <c r="H25" s="42" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5158,26 +5424,26 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="40" t="n">
+      <c r="B26" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="40" t="n">
+      <c r="C26" s="41" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="40" t="n">
+      <c r="D26" s="41" t="n">
         <v>80</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
         <v>17</v>
       </c>
-      <c r="F26" s="50" t="n">
+      <c r="F26" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="50" t="n">
+      <c r="G26" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="41" t="inlineStr"/>
+      <c r="H26" s="42" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5185,26 +5451,26 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="40" t="n">
+      <c r="B27" s="41" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="40" t="n">
+      <c r="C27" s="41" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="40" t="n">
+      <c r="D27" s="41" t="n">
         <v>64</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
         <v>15</v>
       </c>
-      <c r="F27" s="50" t="n">
+      <c r="F27" s="51" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="50" t="n">
+      <c r="G27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="41" t="inlineStr"/>
+      <c r="H27" s="42" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5212,26 +5478,26 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="40" t="n">
+      <c r="B28" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="40" t="n">
+      <c r="C28" s="41" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="40" t="n">
+      <c r="D28" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
         <v>13</v>
       </c>
-      <c r="F28" s="50" t="n">
+      <c r="F28" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="50" t="n">
+      <c r="G28" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="41" t="inlineStr"/>
+      <c r="H28" s="42" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5239,26 +5505,26 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="40" t="n">
+      <c r="B29" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="40" t="n">
+      <c r="C29" s="41" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="40" t="n">
+      <c r="D29" s="41" t="n">
         <v>10</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
         <v>17</v>
       </c>
-      <c r="F29" s="50" t="n">
+      <c r="F29" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="50" t="n">
+      <c r="G29" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="41" t="inlineStr"/>
+      <c r="H29" s="42" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5266,26 +5532,26 @@
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="40" t="n">
+      <c r="B30" s="41" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="40" t="n">
+      <c r="C30" s="41" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="40" t="n">
+      <c r="D30" s="41" t="n">
         <v>24</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
         <v>19</v>
       </c>
-      <c r="F30" s="50" t="n">
+      <c r="F30" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="50" t="n">
+      <c r="G30" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="41" t="inlineStr"/>
+      <c r="H30" s="42" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5297,9 +5563,9 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="48" t="n"/>
-      <c r="G31" s="48" t="n"/>
-      <c r="H31" s="41" t="inlineStr">
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="42" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5315,9 +5581,9 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="48" t="n"/>
-      <c r="G32" s="48" t="n"/>
-      <c r="H32" s="41" t="inlineStr">
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="42" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5345,15 +5611,15 @@
         <f>SUM(E20:E32)</f>
         <v>179</v>
       </c>
-      <c r="F33" s="49">
+      <c r="F33" s="50">
         <f>SUM(F20:F32)</f>
         <v>20.3</v>
       </c>
-      <c r="G33" s="49">
+      <c r="G33" s="50">
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
-      <c r="H33" s="35" t="n"/>
+      <c r="H33" s="22" t="n"/>
     </row>
     <row r="34"/>
     <row r="35">
@@ -5371,26 +5637,26 @@
       <c r="H35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr"/>
-      <c r="E36" s="20" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr"/>
-      <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr"/>
+      <c r="E36" s="26" t="inlineStr"/>
+      <c r="F36" s="26" t="inlineStr"/>
+      <c r="G36" s="26" t="inlineStr"/>
+      <c r="H36" s="26" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
@@ -5402,7 +5668,7 @@
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="40" t="n">
+      <c r="B37" s="41" t="n">
         <v>96600</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5410,7 +5676,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="41" t="inlineStr">
+      <c r="H37" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
@@ -5422,7 +5688,7 @@
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="40" t="n">
+      <c r="B38" s="41" t="n">
         <v>618400</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -5430,7 +5696,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="41" t="inlineStr">
+      <c r="H38" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
@@ -5442,7 +5708,7 @@
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="40" t="n">
+      <c r="B39" s="41" t="n">
         <v>478400</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -5450,7 +5716,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="41" t="inlineStr">
+      <c r="H39" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5462,7 +5728,7 @@
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="40" t="n">
+      <c r="B40" s="41" t="n">
         <v>569800</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -5470,7 +5736,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="41" t="inlineStr">
+      <c r="H40" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
@@ -5482,7 +5748,7 @@
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="40" t="n">
+      <c r="B41" s="41" t="n">
         <v>440700</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -5490,7 +5756,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="41" t="inlineStr">
+      <c r="H41" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5502,7 +5768,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="40" t="n">
+      <c r="B42" s="41" t="n">
         <v>2599100</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -5510,7 +5776,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="41" t="inlineStr">
+      <c r="H42" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
@@ -5522,7 +5788,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="40" t="n">
+      <c r="B43" s="41" t="n">
         <v>2010300</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -5530,7 +5796,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="41" t="inlineStr">
+      <c r="H43" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5542,7 +5808,7 @@
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="40" t="n">
+      <c r="B44" s="41" t="n">
         <v>126200</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5550,7 +5816,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="41" t="inlineStr">
+      <c r="H44" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
@@ -5562,7 +5828,7 @@
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="40" t="n">
+      <c r="B45" s="41" t="n">
         <v>106800</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -5570,7 +5836,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="41" t="inlineStr">
+      <c r="H45" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5582,7 +5848,7 @@
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="40" t="n">
+      <c r="B46" s="41" t="n">
         <v>126200</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -5590,7 +5856,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="41" t="inlineStr">
+      <c r="H46" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5602,7 +5868,7 @@
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="40" t="n">
+      <c r="B47" s="41" t="n">
         <v>106800</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -5610,7 +5876,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="41" t="inlineStr">
+      <c r="H47" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5622,7 +5888,7 @@
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="40" t="n">
+      <c r="B48" s="41" t="n">
         <v>720000</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -5630,7 +5896,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="41" t="inlineStr">
+      <c r="H48" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5642,7 +5908,7 @@
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="40" t="n">
+      <c r="B49" s="41" t="n">
         <v>1080000</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -5650,7 +5916,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="41" t="inlineStr">
+      <c r="H49" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5662,7 +5928,7 @@
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="40" t="n">
+      <c r="B50" s="41" t="n">
         <v>3000000</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -5670,7 +5936,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="41" t="inlineStr">
+      <c r="H50" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5682,7 +5948,7 @@
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="40" t="n">
+      <c r="B51" s="41" t="n">
         <v>100800</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -5690,7 +5956,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="41" t="inlineStr">
+      <c r="H51" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5702,7 +5968,7 @@
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="40" t="n">
+      <c r="B52" s="41" t="n">
         <v>160800</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -5710,7 +5976,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="41" t="inlineStr">
+      <c r="H52" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5722,7 +5988,7 @@
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="40" t="n">
+      <c r="B53" s="41" t="n">
         <v>75000</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -5730,7 +5996,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="41" t="inlineStr">
+      <c r="H53" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5742,7 +6008,7 @@
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="40" t="n">
+      <c r="B54" s="41" t="n">
         <v>70000</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -5750,7 +6016,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="41" t="inlineStr">
+      <c r="H54" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5762,7 +6028,7 @@
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="40" t="n">
+      <c r="B55" s="41" t="n">
         <v>3172000</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -5770,7 +6036,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="41" t="inlineStr">
+      <c r="H55" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -5782,7 +6048,7 @@
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="40" t="n">
+      <c r="B56" s="41" t="n">
         <v>2074000</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -5790,7 +6056,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="41" t="inlineStr">
+      <c r="H56" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -5802,7 +6068,7 @@
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="40" t="n">
+      <c r="B57" s="41" t="n">
         <v>2806000</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -5810,7 +6076,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="41" t="inlineStr">
+      <c r="H57" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -5822,7 +6088,7 @@
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="40" t="n">
+      <c r="B58" s="41" t="n">
         <v>1830000</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -5830,7 +6096,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="41" t="inlineStr">
+      <c r="H58" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -5842,7 +6108,7 @@
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="40" t="n">
+      <c r="B59" s="41" t="n">
         <v>180000</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -5850,7 +6116,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="41" t="inlineStr">
+      <c r="H59" s="42" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
@@ -5862,7 +6128,7 @@
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="40" t="n">
+      <c r="B60" s="41" t="n">
         <v>80000</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -5870,7 +6136,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="41" t="inlineStr">
+      <c r="H60" s="42" t="inlineStr">
         <is>
           <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
@@ -5882,7 +6148,7 @@
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="40" t="n">
+      <c r="B61" s="41" t="n">
         <v>9</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -5890,7 +6156,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H61" s="41" t="inlineStr">
+      <c r="H61" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5902,7 +6168,7 @@
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="40" t="n">
+      <c r="B62" s="41" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -5910,7 +6176,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H62" s="41" t="inlineStr">
+      <c r="H62" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5922,7 +6188,7 @@
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="40" t="n">
+      <c r="B63" s="41" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -5930,7 +6196,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H63" s="41" t="inlineStr">
+      <c r="H63" s="42" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
@@ -5942,7 +6208,7 @@
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B64" s="43" t="n">
+      <c r="B64" s="44" t="n">
         <v>0.15</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -5950,7 +6216,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H64" s="41" t="inlineStr">
+      <c r="H64" s="42" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
@@ -5962,7 +6228,7 @@
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B65" s="43" t="n">
+      <c r="B65" s="44" t="n">
         <v>0.15</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -5970,7 +6236,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="41" t="inlineStr">
+      <c r="H65" s="42" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
@@ -5982,7 +6248,7 @@
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B66" s="43" t="n">
+      <c r="B66" s="44" t="n">
         <v>0.16</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -5990,7 +6256,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H66" s="41" t="inlineStr">
+      <c r="H66" s="42" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -24,12 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;×&quot;"/>
-    <numFmt numFmtId="166" formatCode="0 %"/>
-    <numFmt numFmtId="167" formatCode="#,##0;;&quot;—&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0;;&quot;—&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000;;&quot;—&quot;"/>
+    <numFmt numFmtId="167" formatCode="0 %"/>
+    <numFmt numFmtId="168" formatCode="#,##0;;&quot;—&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;;&quot;—&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -213,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -254,6 +255,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -261,7 +263,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -287,25 +289,32 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -671,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -721,7 +730,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="n"/>
+      <c r="A5" s="46" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>в месяц</t>
@@ -834,7 +843,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n"/>
+      <c r="E8" s="47" t="n"/>
       <c r="F8" s="7">
         <f>G8/12</f>
         <v>5276.458333</v>
@@ -871,7 +880,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G9" s="46" t="n"/>
+      <c r="G9" s="47" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -884,7 +893,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n"/>
+      <c r="C10" s="47" t="n"/>
       <c r="D10" s="7">
         <f>E10/12</f>
         <v>60000</v>
@@ -898,7 +907,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G10" s="46" t="n"/>
+      <c r="G10" s="47" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -911,13 +920,13 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C11" s="46" t="n"/>
+      <c r="C11" s="47" t="n"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E11" s="46" t="n"/>
+      <c r="E11" s="47" t="n"/>
       <c r="F11" s="7">
         <f>G11/12</f>
         <v>17042.22917</v>
@@ -1077,7 +1086,7 @@
         <f>C15-G15</f>
         <v>35675696.75</v>
       </c>
-      <c r="D19" s="47">
+      <c r="D19" s="48">
         <f>IF(G15=0,0,C15/G15)</f>
         <v>3.555583381</v>
       </c>
@@ -1096,7 +1105,7 @@
         <f>E15-G15</f>
         <v>24590096.75</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="48">
         <f>IF(G15=0,0,E15/G15)</f>
         <v>2.761480457</v>
       </c>
@@ -1300,7 +1309,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Pest Killer, брикеты · тёплый сезон</t>
+          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
         </is>
       </c>
       <c r="B30" s="7">
@@ -1328,358 +1337,350 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
+        </is>
+      </c>
+      <c r="B31" s="7">
+        <f>Данные!$C$33</f>
+        <v>1198</v>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
+        </is>
+      </c>
+      <c r="B32" s="49">
+        <f>Данные!$F$33/Данные!$C$33</f>
+        <v>0.01694490818</v>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
           <t>Бутылки · тёплый сезон</t>
         </is>
       </c>
-      <c r="B31" s="7">
+      <c r="B33" s="7">
         <f>Данные!$B$11</f>
         <v>40</v>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D31" s="7">
+      <c r="D33" s="7">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E33" s="7">
         <f>Данные!$B$11*Данные!$B$10</f>
         <v>2720</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F33" s="8">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>ИТОГО ТЕКУЩИЕ РАСХОДЫ ШТАТА</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="14">
-        <f>F32/12</f>
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="14">
+        <f>F34/12</f>
         <v>1163325.271</v>
       </c>
-      <c r="F32" s="14">
-        <f>F26+F27+F28+F29+F30+F31</f>
+      <c r="F34" s="14">
+        <f>F26+F27+F28+F29+F30+F33</f>
         <v>13959903.25</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B33" s="7">
+      <c r="B35" s="7">
         <f>Данные!$B$33</f>
         <v>179</v>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D33" s="7">
+      <c r="D35" s="7">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="8">
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="8">
         <f>Данные!$B$33*Данные!$B$9</f>
         <v>386640</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B34" s="7">
+      <c r="B36" s="7">
         <f>Данные!$C$33</f>
         <v>1198</v>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D34" s="7">
+      <c r="D36" s="7">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="8">
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="8">
         <f>Данные!$C$33*Данные!$B$9</f>
         <v>2587680</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>ИТОГО РАЗОВАЯ ЗАКУПКА ОБОРУДОВАНИЯ</t>
         </is>
       </c>
-      <c r="B35" s="12">
+      <c r="B37" s="12">
         <f>Данные!$B$33+Данные!$C$33</f>
         <v>1377</v>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="12">
-        <f>F33+F34</f>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="12">
+        <f>F35+F36</f>
         <v>2974320</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>ИТОГО ПЕРВЫЙ ГОД · с разовой закупкой</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="14">
-        <f>F32+F35</f>
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="14">
+        <f>F34+F37</f>
         <v>16934223.25</v>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="16" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>Условие</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Ставка</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Цена КП без скидок</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>C41/12</f>
+      <c r="B43" s="7">
+        <f>C43/12</f>
         <v>4136300</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C43" s="8">
         <f>C15</f>
         <v>49635600</v>
       </c>
-      <c r="D41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="D43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>C42/12</f>
+      <c r="B44" s="7">
+        <f>C44/12</f>
         <v>3515855</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C44" s="8">
         <f>C15*(1-Данные!$B$64)</f>
         <v>42190260</v>
       </c>
-      <c r="D42" s="25">
+      <c r="D44" s="50">
         <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
-      <c r="B43" s="7">
-        <f>C43/12</f>
+      <c r="B45" s="7">
+        <f>C45/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C45" s="8">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
         <v>35861721</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D45" s="50">
         <f>Данные!$B$65</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
-      <c r="B44" s="7">
-        <f>C44/12</f>
+      <c r="B46" s="7">
+        <f>C46/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C46" s="8">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D46" s="50">
         <f>Данные!$B$66</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="16" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="16" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>Что зафиксировано в документах</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D48" s="27" t="inlineStr">
-        <is>
-          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
-        </is>
-      </c>
-      <c r="E48" s="48" t="n"/>
-      <c r="F48" s="48" t="n"/>
-      <c r="G48" s="46" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>ККЗ</t>
-        </is>
-      </c>
-      <c r="C49" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="27" t="inlineStr">
-        <is>
-          <t>выезд по запросу</t>
-        </is>
-      </c>
-      <c r="E49" s="48" t="n"/>
-      <c r="F49" s="48" t="n"/>
-      <c r="G49" s="46" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Pest Hunters</t>
+          <t>Indigo Solutions</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>бройлерные площадки</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="27" t="inlineStr">
-        <is>
-          <t>дополнительные визиты по вызову</t>
-        </is>
-      </c>
-      <c r="E50" s="48" t="n"/>
-      <c r="F50" s="48" t="n"/>
-      <c r="G50" s="46" t="n"/>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D50" s="28" t="inlineStr">
+        <is>
+          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+        </is>
+      </c>
+      <c r="E50" s="51" t="n"/>
+      <c r="F50" s="51" t="n"/>
+      <c r="G50" s="47" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -1689,20 +1690,20 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>ЗПП</t>
+          <t>ККЗ</t>
         </is>
       </c>
       <c r="C51" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="27" t="inlineStr">
-        <is>
-          <t>по графику на 2026 год, бригада из трёх человек</t>
-        </is>
-      </c>
-      <c r="E51" s="48" t="n"/>
-      <c r="F51" s="48" t="n"/>
-      <c r="G51" s="46" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>выезд по запросу</t>
+        </is>
+      </c>
+      <c r="E51" s="51" t="n"/>
+      <c r="F51" s="51" t="n"/>
+      <c r="G51" s="47" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -1712,64 +1713,110 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>склад ТМЦ</t>
+          <t>бройлерные площадки</t>
         </is>
       </c>
       <c r="C52" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="27" t="inlineStr">
-        <is>
-          <t>выезд по рекламации за два рабочих дня</t>
-        </is>
-      </c>
-      <c r="E52" s="48" t="n"/>
-      <c r="F52" s="48" t="n"/>
-      <c r="G52" s="46" t="n"/>
+      <c r="D52" s="28" t="inlineStr">
+        <is>
+          <t>дополнительные визиты по вызову</t>
+        </is>
+      </c>
+      <c r="E52" s="51" t="n"/>
+      <c r="F52" s="51" t="n"/>
+      <c r="G52" s="47" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="28" t="inlineStr">
+        <is>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
+        </is>
+      </c>
+      <c r="E53" s="51" t="n"/>
+      <c r="F53" s="51" t="n"/>
+      <c r="G53" s="47" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="28" t="inlineStr">
+        <is>
+          <t>выезд по рекламации за два рабочих дня</t>
+        </is>
+      </c>
+      <c r="E54" s="51" t="n"/>
+      <c r="F54" s="51" t="n"/>
+      <c r="G54" s="47" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C53" s="21" t="n">
+      <c r="C55" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D53" s="27" t="inlineStr">
+      <c r="D55" s="28" t="inlineStr">
         <is>
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
-      <c r="E53" s="48" t="n"/>
-      <c r="F53" s="48" t="n"/>
-      <c r="G53" s="46" t="n"/>
+      <c r="E55" s="51" t="n"/>
+      <c r="F55" s="51" t="n"/>
+      <c r="G55" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D54:G54"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="D50:G50"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="D53:G53"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="D52:G52"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D55:G55"/>
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1798,7 +1845,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура, 1 кг брикетов Pest Killer на обработку.</t>
         </is>
@@ -1806,37 +1853,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>D9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>D10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>D11+D12+D13+D14</f>
         <v>25497.5</v>
       </c>
@@ -1875,16 +1922,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>Данные!$B$37</f>
         <v>96600</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -1893,16 +1940,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · дератизация</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>Данные!$B$53</f>
         <v>75000</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -1911,16 +1958,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1930,16 +1977,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -1949,16 +1996,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1968,16 +2015,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1987,7 +2034,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2031,16 +2078,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="33">
         <f>Данные!$B$20*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="7">
@@ -2049,16 +2096,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="33">
         <f>Данные!$C$20*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="7">
@@ -2067,7 +2114,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="33" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2111,16 +2158,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <f>Данные!$B$54</f>
         <v>70000</v>
       </c>
-      <c r="C25" s="32" t="n">
+      <c r="C25" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="7">
@@ -2129,7 +2176,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2141,14 +2188,14 @@
     </row>
     <row r="27"/>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2187,7 +2234,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2195,37 +2242,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>D12+D13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>D14+D15+D16+D17</f>
         <v>1240117.5</v>
       </c>
@@ -2264,16 +2311,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>Данные!$B$38</f>
         <v>618400</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2282,16 +2329,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>Данные!$B$40</f>
         <v>569800</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -2300,16 +2347,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>Данные!$B$42</f>
         <v>2599100</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="8">
@@ -2318,16 +2365,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>Данные!$B$55</f>
         <v>3172000</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2337,16 +2384,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>Данные!$B$56</f>
         <v>2074000</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2356,16 +2403,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2375,16 +2422,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="33">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2394,16 +2441,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="33">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2413,16 +2460,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="33">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2432,7 +2479,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="33" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2476,16 +2523,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="33">
         <f>Данные!$B$39</f>
         <v>478400</v>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D22" s="7">
@@ -2494,16 +2541,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="33">
         <f>Данные!$B$41</f>
         <v>440700</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="7">
@@ -2512,16 +2559,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="33">
         <f>Данные!$B$43</f>
         <v>2010300</v>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="7">
@@ -2530,16 +2577,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <f>Данные!$B$57</f>
         <v>2806000</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2549,16 +2596,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="33">
         <f>Данные!$B$58</f>
         <v>1830000</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="33">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2568,7 +2615,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2612,16 +2659,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="33">
         <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C31" s="32" t="n">
+      <c r="C31" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="7">
@@ -2630,16 +2677,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C32" s="32" t="n">
+      <c r="C32" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="7">
@@ -2648,7 +2695,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="33" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2692,16 +2739,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="33">
         <f>Данные!$B$48</f>
         <v>720000</v>
       </c>
-      <c r="C37" s="32" t="n">
+      <c r="C37" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D37" s="7">
@@ -2710,16 +2757,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="33">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="C38" s="32" t="n">
+      <c r="C38" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D38" s="7">
@@ -2728,16 +2775,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="33">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="C39" s="32" t="n">
+      <c r="C39" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D39" s="7">
@@ -2746,7 +2793,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="33" t="inlineStr">
+      <c r="C40" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -2758,14 +2805,14 @@
     </row>
     <row r="41"/>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
         </is>
@@ -2804,7 +2851,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
@@ -2812,37 +2859,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>D11+D12+D13+D14</f>
         <v>63317.5</v>
       </c>
@@ -2881,16 +2928,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>Данные!$B$44</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2899,15 +2946,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -2916,16 +2963,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2935,16 +2982,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2954,16 +3001,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2973,16 +3020,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2992,7 +3039,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3036,16 +3083,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="33">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -3054,7 +3101,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3098,16 +3145,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="33">
         <f>Данные!$B$21*Данные!$B$9</f>
         <v>38880</v>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="7">
@@ -3116,16 +3163,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <f>Данные!$C$21*Данные!$B$9</f>
         <v>73440</v>
       </c>
-      <c r="C25" s="32" t="n">
+      <c r="C25" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="7">
@@ -3134,7 +3181,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3178,16 +3225,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="33">
         <f>Данные!$B$51</f>
         <v>100800</v>
       </c>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D30" s="7">
@@ -3196,7 +3243,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="33" t="inlineStr">
+      <c r="C31" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3208,7 +3255,7 @@
     </row>
     <row r="32"/>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3246,7 +3293,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3254,37 +3301,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>D10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3323,16 +3370,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <f>Данные!$B$46</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -3341,16 +3388,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>Данные!$B$59</f>
         <v>180000</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -3359,15 +3406,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3376,7 +3423,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3420,16 +3467,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="33">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D16" s="7">
@@ -3438,7 +3485,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="33" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3482,16 +3529,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="33">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D21" s="7">
@@ -3500,7 +3547,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="33" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3512,14 +3559,14 @@
     </row>
     <row r="23"/>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3558,7 +3605,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -3566,37 +3613,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>D10</f>
         <v>720000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3635,15 +3682,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
+      <c r="B9" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3652,16 +3699,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>Данные!$B$60</f>
         <v>80000</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
@@ -3671,15 +3718,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3688,7 +3735,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3700,7 +3747,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3738,7 +3785,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -3746,37 +3793,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>D11+D12+D13+D14</f>
         <v>204506.75</v>
       </c>
@@ -3815,15 +3862,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
+      <c r="B9" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3832,15 +3879,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -3849,16 +3896,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>Данные!$D$22*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3868,16 +3915,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>Данные!$D$22*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="33">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -3887,16 +3934,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>Данные!$G$22*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3906,16 +3953,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>Данные!$F$22*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3925,7 +3972,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -3969,16 +4016,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="33">
         <f>Данные!$B$22*Данные!$B$9</f>
         <v>0</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="7">
@@ -3987,16 +4034,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="33">
         <f>Данные!$C$22*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="7">
@@ -4005,7 +4052,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="33" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
@@ -4017,14 +4064,14 @@
     </row>
     <row r="22"/>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4087,17 +4134,17 @@
       <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
@@ -4149,7 +4196,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -4180,47 +4227,47 @@
       <c r="I11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="36" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="H12" s="37" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="36" t="inlineStr">
+      <c r="I12" s="37" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -4232,11 +4279,11 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="52">
         <f>Данные!$D$20</f>
         <v>0</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="52">
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
@@ -4244,7 +4291,7 @@
         <f>B13*Данные!$B$8*Данные!$B$15+C13*Данные!$B$8*Данные!$B$16</f>
         <v>0</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="53">
         <f>Данные!$G$20</f>
         <v>0</v>
       </c>
@@ -4252,7 +4299,7 @@
         <f>E13*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="53">
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
@@ -4271,11 +4318,11 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="52">
         <f>SUM(Данные!$D$23:$D$30)</f>
         <v>268</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="52">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
@@ -4283,7 +4330,7 @@
         <f>B14*Данные!$B$8*Данные!$B$15+C14*Данные!$B$8*Данные!$B$16</f>
         <v>728960</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="53">
         <f>SUM(Данные!$G$23:$G$30)</f>
         <v>15</v>
       </c>
@@ -4291,7 +4338,7 @@
         <f>E14*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="53">
         <f>SUM(Данные!$F$23:$F$30)</f>
         <v>17</v>
       </c>
@@ -4310,11 +4357,11 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="52">
         <f>Данные!$D$21</f>
         <v>12</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="52">
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
@@ -4322,7 +4369,7 @@
         <f>B15*Данные!$B$8*Данные!$B$15+C15*Данные!$B$8*Данные!$B$16</f>
         <v>32640</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="53">
         <f>Данные!$G$21</f>
         <v>1</v>
       </c>
@@ -4330,7 +4377,7 @@
         <f>E15*Данные!$B$6*Данные!$B$15</f>
         <v>5180</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="53">
         <f>Данные!$F$21</f>
         <v>1</v>
       </c>
@@ -4349,11 +4396,11 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="52">
         <f>Данные!$D$22</f>
         <v>63</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="52">
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
@@ -4361,7 +4408,7 @@
         <f>B16*Данные!$B$8*Данные!$B$15+C16*Данные!$B$8*Данные!$B$16</f>
         <v>171360</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="53">
         <f>Данные!$G$22</f>
         <v>0</v>
       </c>
@@ -4369,7 +4416,7 @@
         <f>E16*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="53">
         <f>Данные!$F$22</f>
         <v>1.3</v>
       </c>
@@ -4406,13 +4453,13 @@
           <t>МАТЕРИАЛЫ ЗА ГОД, ИТОГО</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
       <c r="D18" s="12">
         <f>SUM(D13:D17)</f>
         <v>932960</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="54">
         <f>SUM(E13:E17)</f>
         <v>16</v>
       </c>
@@ -4420,7 +4467,7 @@
         <f>SUM(F13:F17)</f>
         <v>82880</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="54">
         <f>SUM(G13:G17)</f>
         <v>20.3</v>
       </c>
@@ -4484,19 +4531,19 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="52">
         <f>Данные!$B$20</f>
         <v>0</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="52">
         <f>Данные!$C$20</f>
         <v>29</v>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="52">
         <f>B22+C22</f>
         <v>29</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4511,19 +4558,19 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B23" s="37">
+      <c r="B23" s="52">
         <f>SUM(Данные!$B$23:$B$30)</f>
         <v>161</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="52">
         <f>SUM(Данные!$C$23:$C$30)</f>
         <v>1096</v>
       </c>
-      <c r="D23" s="37">
+      <c r="D23" s="52">
         <f>B23+C23</f>
         <v>1257</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="33">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4538,19 +4585,19 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="52">
         <f>Данные!$B$21</f>
         <v>18</v>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="52">
         <f>Данные!$C$21</f>
         <v>34</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="52">
         <f>B24+C24</f>
         <v>52</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4565,19 +4612,19 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="52">
         <f>Данные!$B$22</f>
         <v>0</v>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="52">
         <f>Данные!$C$22</f>
         <v>39</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="52">
         <f>B25+C25</f>
         <v>39</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
@@ -4592,19 +4639,19 @@
           <t>ИТОГО РАЗОВО</t>
         </is>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="55">
         <f>SUM(B22:B25)</f>
         <v>179</v>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="55">
         <f>SUM(C22:C25)</f>
         <v>1198</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="55">
         <f>SUM(D22:D25)</f>
         <v>1377</v>
       </c>
-      <c r="E26" s="22" t="n"/>
+      <c r="E26" s="23" t="n"/>
       <c r="F26" s="12">
         <f>SUM(F22:F25)</f>
         <v>2974320</v>
@@ -4624,32 +4671,32 @@
       <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C29" s="36" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D29" s="36" t="inlineStr">
+      <c r="D29" s="37" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E29" s="36" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F29" s="36" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
@@ -4882,7 +4929,7 @@
     </row>
     <row r="39"/>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -4946,26 +4993,26 @@
       <c r="H4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr"/>
-      <c r="E5" s="26" t="inlineStr"/>
-      <c r="F5" s="26" t="inlineStr"/>
-      <c r="G5" s="26" t="inlineStr"/>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr"/>
+      <c r="E5" s="27" t="inlineStr"/>
+      <c r="F5" s="27" t="inlineStr"/>
+      <c r="G5" s="27" t="inlineStr"/>
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
@@ -4977,7 +5024,7 @@
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="42" t="n">
         <v>740</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4985,7 +5032,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="42" t="inlineStr">
+      <c r="H6" s="43" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -4997,7 +5044,7 @@
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n">
+      <c r="B7" s="42" t="n">
         <v>3642.5</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -5005,7 +5052,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="42" t="inlineStr">
+      <c r="H7" s="43" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
@@ -5017,7 +5064,7 @@
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="42" t="n">
         <v>160</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -5025,7 +5072,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="42" t="inlineStr">
+      <c r="H8" s="43" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
@@ -5037,7 +5084,7 @@
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="42" t="n">
         <v>2160</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5045,7 +5092,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H9" s="42" t="inlineStr">
+      <c r="H9" s="43" t="inlineStr">
         <is>
           <t>разовая закупка; цена из прежнего расчёта по ККЗ (29 шт = 62 640 ₸)</t>
         </is>
@@ -5057,7 +5104,7 @@
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="42" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5065,7 +5112,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="42" t="inlineStr">
+      <c r="H10" s="43" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -5077,7 +5124,7 @@
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="41" t="n">
+      <c r="B11" s="42" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5085,7 +5132,7 @@
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="H11" s="42" t="inlineStr">
+      <c r="H11" s="43" t="inlineStr">
         <is>
           <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
         </is>
@@ -5097,7 +5144,7 @@
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="41" t="n">
+      <c r="B12" s="42" t="n">
         <v>258488</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -5105,7 +5152,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="42" t="inlineStr">
+      <c r="H12" s="43" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
@@ -5117,7 +5164,7 @@
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="41" t="n">
+      <c r="B13" s="42" t="n">
         <v>350000</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5125,7 +5172,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H13" s="42" t="inlineStr">
+      <c r="H13" s="43" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
@@ -5137,7 +5184,7 @@
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n">
+      <c r="B14" s="42" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -5145,7 +5192,7 @@
           <t>чел.</t>
         </is>
       </c>
-      <c r="H14" s="42" t="inlineStr">
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
@@ -5157,7 +5204,7 @@
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="41" t="n">
+      <c r="B15" s="42" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -5165,7 +5212,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="42" t="inlineStr">
+      <c r="H15" s="43" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
@@ -5177,7 +5224,7 @@
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="41" t="n">
+      <c r="B16" s="42" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5185,7 +5232,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H16" s="42" t="inlineStr">
+      <c r="H16" s="43" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
@@ -5207,42 +5254,42 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="36" t="inlineStr">
+      <c r="G19" s="37" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="36" t="inlineStr">
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -5254,26 +5301,26 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="41" t="n">
+      <c r="B20" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="42" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="41" t="n">
+      <c r="D20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="51" t="n">
+      <c r="F20" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="51" t="n">
+      <c r="G20" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="42" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
@@ -5285,26 +5332,26 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="41" t="n">
+      <c r="B21" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="42" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="41" t="n">
+      <c r="D21" s="42" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
         <v>18</v>
       </c>
-      <c r="F21" s="51" t="n">
+      <c r="F21" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="51" t="n">
+      <c r="G21" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="42" t="inlineStr"/>
+      <c r="H21" s="43" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5312,26 +5359,26 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="41" t="n">
+      <c r="B22" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="42" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="41" t="n">
+      <c r="D22" s="42" t="n">
         <v>63</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="51" t="n">
+      <c r="F22" s="56" t="n">
         <v>1.3</v>
       </c>
-      <c r="G22" s="51" t="n">
+      <c r="G22" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="42" t="inlineStr">
+      <c r="H22" s="43" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
@@ -5343,26 +5390,26 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="41" t="n">
+      <c r="B23" s="42" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="42" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="42" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
         <v>13</v>
       </c>
-      <c r="F23" s="51" t="n">
+      <c r="F23" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="51" t="n">
+      <c r="G23" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="42" t="inlineStr"/>
+      <c r="H23" s="43" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5370,26 +5417,26 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="41" t="n">
+      <c r="B24" s="42" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C24" s="42" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D24" s="42" t="n">
         <v>20</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
         <v>17</v>
       </c>
-      <c r="F24" s="51" t="n">
+      <c r="F24" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="51" t="n">
+      <c r="G24" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="42" t="inlineStr"/>
+      <c r="H24" s="43" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5397,26 +5444,26 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="41" t="n">
+      <c r="B25" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="41" t="n">
+      <c r="C25" s="42" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="42" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
         <v>50</v>
       </c>
-      <c r="F25" s="51" t="n">
+      <c r="F25" s="56" t="n">
         <v>3.5</v>
       </c>
-      <c r="G25" s="51" t="n">
+      <c r="G25" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="42" t="inlineStr"/>
+      <c r="H25" s="43" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5424,26 +5471,26 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="41" t="n">
+      <c r="B26" s="42" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="41" t="n">
+      <c r="C26" s="42" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="42" t="n">
         <v>80</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
         <v>17</v>
       </c>
-      <c r="F26" s="51" t="n">
+      <c r="F26" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="51" t="n">
+      <c r="G26" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="42" t="inlineStr"/>
+      <c r="H26" s="43" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5451,26 +5498,26 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="41" t="n">
+      <c r="B27" s="42" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="41" t="n">
+      <c r="C27" s="42" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="41" t="n">
+      <c r="D27" s="42" t="n">
         <v>64</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
         <v>15</v>
       </c>
-      <c r="F27" s="51" t="n">
+      <c r="F27" s="56" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="51" t="n">
+      <c r="G27" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="42" t="inlineStr"/>
+      <c r="H27" s="43" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5478,26 +5525,26 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="41" t="n">
+      <c r="B28" s="42" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="41" t="n">
+      <c r="C28" s="42" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="41" t="n">
+      <c r="D28" s="42" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
         <v>13</v>
       </c>
-      <c r="F28" s="51" t="n">
+      <c r="F28" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="51" t="n">
+      <c r="G28" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="42" t="inlineStr"/>
+      <c r="H28" s="43" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5505,26 +5552,26 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="41" t="n">
+      <c r="B29" s="42" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="41" t="n">
+      <c r="C29" s="42" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="41" t="n">
+      <c r="D29" s="42" t="n">
         <v>10</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
         <v>17</v>
       </c>
-      <c r="F29" s="51" t="n">
+      <c r="F29" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="51" t="n">
+      <c r="G29" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="42" t="inlineStr"/>
+      <c r="H29" s="43" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5532,26 +5579,26 @@
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n">
+      <c r="B30" s="42" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="41" t="n">
+      <c r="C30" s="42" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="41" t="n">
+      <c r="D30" s="42" t="n">
         <v>24</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
         <v>19</v>
       </c>
-      <c r="F30" s="51" t="n">
+      <c r="F30" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="51" t="n">
+      <c r="G30" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="42" t="inlineStr"/>
+      <c r="H30" s="43" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5563,9 +5610,9 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="49" t="n"/>
-      <c r="G31" s="49" t="n"/>
-      <c r="H31" s="42" t="inlineStr">
+      <c r="F31" s="53" t="n"/>
+      <c r="G31" s="53" t="n"/>
+      <c r="H31" s="43" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5581,9 +5628,9 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="49" t="n"/>
-      <c r="G32" s="49" t="n"/>
-      <c r="H32" s="42" t="inlineStr">
+      <c r="F32" s="53" t="n"/>
+      <c r="G32" s="53" t="n"/>
+      <c r="H32" s="43" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5611,15 +5658,15 @@
         <f>SUM(E20:E32)</f>
         <v>179</v>
       </c>
-      <c r="F33" s="50">
+      <c r="F33" s="54">
         <f>SUM(F20:F32)</f>
         <v>20.3</v>
       </c>
-      <c r="G33" s="50">
+      <c r="G33" s="54">
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
-      <c r="H33" s="22" t="n"/>
+      <c r="H33" s="23" t="n"/>
     </row>
     <row r="34"/>
     <row r="35">
@@ -5637,26 +5684,26 @@
       <c r="H35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr"/>
-      <c r="E36" s="26" t="inlineStr"/>
-      <c r="F36" s="26" t="inlineStr"/>
-      <c r="G36" s="26" t="inlineStr"/>
-      <c r="H36" s="26" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr"/>
+      <c r="E36" s="27" t="inlineStr"/>
+      <c r="F36" s="27" t="inlineStr"/>
+      <c r="G36" s="27" t="inlineStr"/>
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
@@ -5668,7 +5715,7 @@
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="41" t="n">
+      <c r="B37" s="42" t="n">
         <v>96600</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5676,7 +5723,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="42" t="inlineStr">
+      <c r="H37" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
@@ -5688,7 +5735,7 @@
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="41" t="n">
+      <c r="B38" s="42" t="n">
         <v>618400</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -5696,7 +5743,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="42" t="inlineStr">
+      <c r="H38" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
@@ -5708,7 +5755,7 @@
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="41" t="n">
+      <c r="B39" s="42" t="n">
         <v>478400</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -5716,7 +5763,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="42" t="inlineStr">
+      <c r="H39" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5728,7 +5775,7 @@
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="41" t="n">
+      <c r="B40" s="42" t="n">
         <v>569800</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -5736,7 +5783,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="42" t="inlineStr">
+      <c r="H40" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
@@ -5748,7 +5795,7 @@
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="41" t="n">
+      <c r="B41" s="42" t="n">
         <v>440700</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -5756,7 +5803,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="42" t="inlineStr">
+      <c r="H41" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5768,7 +5815,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="41" t="n">
+      <c r="B42" s="42" t="n">
         <v>2599100</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -5776,7 +5823,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="42" t="inlineStr">
+      <c r="H42" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
@@ -5788,7 +5835,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="41" t="n">
+      <c r="B43" s="42" t="n">
         <v>2010300</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -5796,7 +5843,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="42" t="inlineStr">
+      <c r="H43" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5808,7 +5855,7 @@
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="41" t="n">
+      <c r="B44" s="42" t="n">
         <v>126200</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5816,7 +5863,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="42" t="inlineStr">
+      <c r="H44" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
@@ -5828,7 +5875,7 @@
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="41" t="n">
+      <c r="B45" s="42" t="n">
         <v>106800</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -5836,7 +5883,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="42" t="inlineStr">
+      <c r="H45" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5848,7 +5895,7 @@
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="41" t="n">
+      <c r="B46" s="42" t="n">
         <v>126200</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -5856,7 +5903,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="42" t="inlineStr">
+      <c r="H46" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5868,7 +5915,7 @@
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="41" t="n">
+      <c r="B47" s="42" t="n">
         <v>106800</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -5876,7 +5923,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="42" t="inlineStr">
+      <c r="H47" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5888,7 +5935,7 @@
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="41" t="n">
+      <c r="B48" s="42" t="n">
         <v>720000</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -5896,7 +5943,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="42" t="inlineStr">
+      <c r="H48" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5908,7 +5955,7 @@
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="41" t="n">
+      <c r="B49" s="42" t="n">
         <v>1080000</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -5916,7 +5963,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="42" t="inlineStr">
+      <c r="H49" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5928,7 +5975,7 @@
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="41" t="n">
+      <c r="B50" s="42" t="n">
         <v>3000000</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -5936,7 +5983,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="42" t="inlineStr">
+      <c r="H50" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5948,7 +5995,7 @@
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="41" t="n">
+      <c r="B51" s="42" t="n">
         <v>100800</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -5956,7 +6003,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="42" t="inlineStr">
+      <c r="H51" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5968,7 +6015,7 @@
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="41" t="n">
+      <c r="B52" s="42" t="n">
         <v>160800</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -5976,7 +6023,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="42" t="inlineStr">
+      <c r="H52" s="43" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5988,7 +6035,7 @@
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="41" t="n">
+      <c r="B53" s="42" t="n">
         <v>75000</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -5996,7 +6043,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="42" t="inlineStr">
+      <c r="H53" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6008,7 +6055,7 @@
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="41" t="n">
+      <c r="B54" s="42" t="n">
         <v>70000</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -6016,7 +6063,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="42" t="inlineStr">
+      <c r="H54" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6028,7 +6075,7 @@
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="41" t="n">
+      <c r="B55" s="42" t="n">
         <v>3172000</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -6036,7 +6083,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="42" t="inlineStr">
+      <c r="H55" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -6048,7 +6095,7 @@
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="41" t="n">
+      <c r="B56" s="42" t="n">
         <v>2074000</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -6056,7 +6103,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="42" t="inlineStr">
+      <c r="H56" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -6068,7 +6115,7 @@
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="41" t="n">
+      <c r="B57" s="42" t="n">
         <v>2806000</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -6076,7 +6123,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="42" t="inlineStr">
+      <c r="H57" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -6088,7 +6135,7 @@
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="41" t="n">
+      <c r="B58" s="42" t="n">
         <v>1830000</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -6096,7 +6143,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="42" t="inlineStr">
+      <c r="H58" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -6108,7 +6155,7 @@
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="41" t="n">
+      <c r="B59" s="42" t="n">
         <v>180000</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -6116,7 +6163,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="42" t="inlineStr">
+      <c r="H59" s="43" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
@@ -6128,7 +6175,7 @@
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="41" t="n">
+      <c r="B60" s="42" t="n">
         <v>80000</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -6136,7 +6183,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="42" t="inlineStr">
+      <c r="H60" s="43" t="inlineStr">
         <is>
           <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
@@ -6148,7 +6195,7 @@
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="41" t="n">
+      <c r="B61" s="42" t="n">
         <v>9</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -6156,7 +6203,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H61" s="42" t="inlineStr">
+      <c r="H61" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6168,7 +6215,7 @@
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="41" t="n">
+      <c r="B62" s="42" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -6176,7 +6223,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H62" s="42" t="inlineStr">
+      <c r="H62" s="43" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6188,7 +6235,7 @@
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="41" t="n">
+      <c r="B63" s="42" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -6196,7 +6243,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H63" s="42" t="inlineStr">
+      <c r="H63" s="43" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
@@ -6208,7 +6255,7 @@
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B64" s="44" t="n">
+      <c r="B64" s="57" t="n">
         <v>0.15</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -6216,7 +6263,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H64" s="42" t="inlineStr">
+      <c r="H64" s="43" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
@@ -6228,7 +6275,7 @@
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B65" s="44" t="n">
+      <c r="B65" s="57" t="n">
         <v>0.15</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -6236,7 +6283,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="42" t="inlineStr">
+      <c r="H65" s="43" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
@@ -6248,7 +6295,7 @@
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B66" s="44" t="n">
+      <c r="B66" s="57" t="n">
         <v>0.16</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -6256,7 +6303,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H66" s="42" t="inlineStr">
+      <c r="H66" s="43" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -279,9 +279,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -730,7 +727,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="n"/>
+      <c r="A5" s="45" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>в месяц</t>
@@ -843,7 +840,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E8" s="47" t="n"/>
+      <c r="E8" s="46" t="n"/>
       <c r="F8" s="7">
         <f>G8/12</f>
         <v>5276.458333</v>
@@ -880,7 +877,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G9" s="47" t="n"/>
+      <c r="G9" s="46" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -893,7 +890,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="47" t="n"/>
+      <c r="C10" s="46" t="n"/>
       <c r="D10" s="7">
         <f>E10/12</f>
         <v>60000</v>
@@ -907,7 +904,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G10" s="47" t="n"/>
+      <c r="G10" s="46" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -920,13 +917,13 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C11" s="47" t="n"/>
+      <c r="C11" s="46" t="n"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E11" s="47" t="n"/>
+      <c r="E11" s="46" t="n"/>
       <c r="F11" s="7">
         <f>G11/12</f>
         <v>17042.22917</v>
@@ -1086,7 +1083,7 @@
         <f>C15-G15</f>
         <v>35675696.75</v>
       </c>
-      <c r="D19" s="48">
+      <c r="D19" s="47">
         <f>IF(G15=0,0,C15/G15)</f>
         <v>3.555583381</v>
       </c>
@@ -1105,7 +1102,7 @@
         <f>E15-G15</f>
         <v>24590096.75</v>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="47">
         <f>IF(G15=0,0,E15/G15)</f>
         <v>2.761480457</v>
       </c>
@@ -1359,7 +1356,7 @@
           <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
         </is>
       </c>
-      <c r="B32" s="49">
+      <c r="B32" s="48">
         <f>Данные!$F$33/Данные!$C$33</f>
         <v>0.01694490818</v>
       </c>
@@ -1578,7 +1575,7 @@
         <f>C15*(1-Данные!$B$64)</f>
         <v>42190260</v>
       </c>
-      <c r="D44" s="50">
+      <c r="D44" s="49">
         <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
@@ -1597,7 +1594,7 @@
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
         <v>35861721</v>
       </c>
-      <c r="D45" s="50">
+      <c r="D45" s="49">
         <f>Данные!$B$65</f>
         <v>0.15</v>
       </c>
@@ -1616,7 +1613,7 @@
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D46" s="50">
+      <c r="D46" s="49">
         <f>Данные!$B$66</f>
         <v>0.16</v>
       </c>
@@ -1678,9 +1675,9 @@
           <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
         </is>
       </c>
-      <c r="E50" s="51" t="n"/>
-      <c r="F50" s="51" t="n"/>
-      <c r="G50" s="47" t="n"/>
+      <c r="E50" s="50" t="n"/>
+      <c r="F50" s="50" t="n"/>
+      <c r="G50" s="46" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -1701,9 +1698,9 @@
           <t>выезд по запросу</t>
         </is>
       </c>
-      <c r="E51" s="51" t="n"/>
-      <c r="F51" s="51" t="n"/>
-      <c r="G51" s="47" t="n"/>
+      <c r="E51" s="50" t="n"/>
+      <c r="F51" s="50" t="n"/>
+      <c r="G51" s="46" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -1724,9 +1721,9 @@
           <t>дополнительные визиты по вызову</t>
         </is>
       </c>
-      <c r="E52" s="51" t="n"/>
-      <c r="F52" s="51" t="n"/>
-      <c r="G52" s="47" t="n"/>
+      <c r="E52" s="50" t="n"/>
+      <c r="F52" s="50" t="n"/>
+      <c r="G52" s="46" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -1747,9 +1744,9 @@
           <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
-      <c r="E53" s="51" t="n"/>
-      <c r="F53" s="51" t="n"/>
-      <c r="G53" s="47" t="n"/>
+      <c r="E53" s="50" t="n"/>
+      <c r="F53" s="50" t="n"/>
+      <c r="G53" s="46" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -1770,9 +1767,9 @@
           <t>выезд по рекламации за два рабочих дня</t>
         </is>
       </c>
-      <c r="E54" s="51" t="n"/>
-      <c r="F54" s="51" t="n"/>
-      <c r="G54" s="47" t="n"/>
+      <c r="E54" s="50" t="n"/>
+      <c r="F54" s="50" t="n"/>
+      <c r="G54" s="46" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -1793,9 +1790,9 @@
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
-      <c r="E55" s="51" t="n"/>
-      <c r="F55" s="51" t="n"/>
-      <c r="G55" s="47" t="n"/>
+      <c r="E55" s="50" t="n"/>
+      <c r="F55" s="50" t="n"/>
+      <c r="G55" s="46" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -1828,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2033,169 +2030,136 @@
         <v>25497.5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D15" s="12">
-        <f>SUM(D9:D14)</f>
-        <v>2084697.5</v>
-      </c>
-    </row>
-    <row r="16"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B18" s="33">
+        <f>Данные!$B$20*Данные!$B$9</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <f>B18*C18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
       <c r="B19" s="33">
-        <f>Данные!$B$20*Данные!$B$9</f>
-        <v>0</v>
+        <f>Данные!$C$20*Данные!$B$9</f>
+        <v>62640</v>
       </c>
       <c r="C19" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="7">
         <f>B19*C19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B20" s="33">
-        <f>Данные!$C$20*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C20" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7">
-        <f>B20*C20</f>
-        <v>62640</v>
-      </c>
-    </row>
+    </row>
+    <row r="20"/>
     <row r="21">
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D21" s="12">
-        <f>SUM(D19:D20)</f>
-        <v>62640</v>
-      </c>
-    </row>
-    <row r="22"/>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B25" s="33">
+      <c r="B23" s="33">
         <f>Данные!$B$54</f>
         <v>70000</v>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C23" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D25" s="7">
-        <f>B25*C25</f>
+      <c r="D23" s="7">
+        <f>B23*C23</f>
         <v>840000</v>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D26" s="12">
-        <f>SUM(D25:D25)</f>
-        <v>840000</v>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+    <row r="24"/>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2203,8 +2167,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2217,7 +2181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2478,341 +2442,297 @@
         <v>433457.5</v>
       </c>
     </row>
-    <row r="18">
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D18" s="12">
-        <f>SUM(D9:D17)</f>
-        <v>81457717.5</v>
-      </c>
-    </row>
-    <row r="19"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Айыртау БП — частичная замена</t>
+        </is>
+      </c>
+      <c r="B21" s="33">
+        <f>Данные!$B$39</f>
+        <v>478400</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" s="7">
+        <f>B21*C21</f>
+        <v>5740800</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="32" t="inlineStr">
         <is>
-          <t>Indigo Solutions · Айыртау БП — частичная замена</t>
+          <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
       <c r="B22" s="33">
-        <f>Данные!$B$39</f>
-        <v>478400</v>
+        <f>Данные!$B$41</f>
+        <v>440700</v>
       </c>
       <c r="C22" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D22" s="7">
         <f>B22*C22</f>
-        <v>5740800</v>
+        <v>5288400</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
         <is>
-          <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
+          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
       <c r="B23" s="33">
-        <f>Данные!$B$41</f>
-        <v>440700</v>
+        <f>Данные!$B$43</f>
+        <v>2010300</v>
       </c>
       <c r="C23" s="33" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="7">
         <f>B23*C23</f>
-        <v>5288400</v>
+        <v>24123600</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="32" t="inlineStr">
         <is>
-          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
+          <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
       <c r="B24" s="33">
-        <f>Данные!$B$43</f>
-        <v>2010300</v>
-      </c>
-      <c r="C24" s="33" t="n">
-        <v>12</v>
+        <f>Данные!$B$57</f>
+        <v>2806000</v>
+      </c>
+      <c r="C24" s="33">
+        <f>Данные!$B$61</f>
+        <v>9</v>
       </c>
       <c r="D24" s="7">
         <f>B24*C24</f>
-        <v>24123600</v>
+        <v>25254000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="32" t="inlineStr">
         <is>
-          <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
+          <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
       <c r="B25" s="33">
-        <f>Данные!$B$57</f>
-        <v>2806000</v>
+        <f>Данные!$B$58</f>
+        <v>1830000</v>
       </c>
       <c r="C25" s="33">
-        <f>Данные!$B$61</f>
-        <v>9</v>
+        <f>Данные!$B$62</f>
+        <v>3</v>
       </c>
       <c r="D25" s="7">
         <f>B25*C25</f>
-        <v>25254000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
-        </is>
-      </c>
-      <c r="B26" s="33">
-        <f>Данные!$B$58</f>
-        <v>1830000</v>
-      </c>
-      <c r="C26" s="33">
-        <f>Данные!$B$62</f>
-        <v>3</v>
-      </c>
-      <c r="D26" s="7">
-        <f>B26*C26</f>
         <v>5490000</v>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D27" s="12">
-        <f>SUM(D22:D26)</f>
-        <v>65896800</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B31" s="33">
+      <c r="B29" s="33">
         <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C31" s="33" t="n">
+      <c r="C29" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="7">
-        <f>B31*C31</f>
+      <c r="D29" s="7">
+        <f>B29*C29</f>
         <v>347760</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B32" s="33">
+      <c r="B30" s="33">
         <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C32" s="33" t="n">
+      <c r="C30" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="7">
-        <f>B32*C32</f>
+      <c r="D30" s="7">
+        <f>B30*C30</f>
         <v>2367360</v>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+    </row>
     <row r="33">
-      <c r="C33" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D33" s="12">
-        <f>SUM(D31:D32)</f>
-        <v>2715120</v>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
-      <c r="B37" s="33">
+      <c r="B34" s="33">
         <f>Данные!$B$48</f>
         <v>720000</v>
       </c>
-      <c r="C37" s="33" t="n">
+      <c r="C34" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D37" s="7">
-        <f>B37*C37</f>
+      <c r="D34" s="7">
+        <f>B34*C34</f>
         <v>8640000</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B38" s="33">
+      <c r="B35" s="33">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="C38" s="33" t="n">
+      <c r="C35" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D38" s="7">
-        <f>B38*C38</f>
+      <c r="D35" s="7">
+        <f>B35*C35</f>
         <v>12960000</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B39" s="33">
+      <c r="B36" s="33">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="C39" s="33" t="n">
+      <c r="C36" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D39" s="7">
-        <f>B39*C39</f>
+      <c r="D36" s="7">
+        <f>B36*C36</f>
         <v>36000000</v>
       </c>
     </row>
-    <row r="40">
-      <c r="C40" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D40" s="12">
-        <f>SUM(D37:D39)</f>
-        <v>57600000</v>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
+    <row r="37"/>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
         </is>
@@ -2820,9 +2740,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2834,7 +2754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3038,224 +2958,180 @@
         <v>25497.5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D15" s="12">
-        <f>SUM(D9:D14)</f>
-        <v>1577717.5</v>
-      </c>
-    </row>
-    <row r="16"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B18" s="33">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="C19" s="33" t="n">
+      <c r="C18" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="7">
-        <f>B19*C19</f>
+      <c r="D18" s="7">
+        <f>B18*C18</f>
         <v>1281600</v>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
-      <c r="C20" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D20" s="12">
-        <f>SUM(D19:D19)</f>
-        <v>1281600</v>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B24" s="33">
+      <c r="B22" s="33">
         <f>Данные!$B$21*Данные!$B$9</f>
         <v>38880</v>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C22" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="7">
-        <f>B24*C24</f>
+      <c r="D22" s="7">
+        <f>B22*C22</f>
         <v>38880</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
-      <c r="B25" s="33">
+      <c r="B23" s="33">
         <f>Данные!$C$21*Данные!$B$9</f>
         <v>73440</v>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C23" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="7">
-        <f>B25*C25</f>
+      <c r="D23" s="7">
+        <f>B23*C23</f>
         <v>73440</v>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+    </row>
     <row r="26">
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D26" s="12">
-        <f>SUM(D24:D25)</f>
-        <v>112320</v>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B30" s="33">
+      <c r="B27" s="33">
         <f>Данные!$B$51</f>
         <v>100800</v>
       </c>
-      <c r="C30" s="33" t="n">
+      <c r="C27" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D30" s="7">
-        <f>B30*C30</f>
+      <c r="D27" s="7">
+        <f>B27*C27</f>
         <v>1209600</v>
       </c>
     </row>
-    <row r="31">
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D31" s="12">
-        <f>SUM(D30:D30)</f>
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+    <row r="28"/>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3263,7 +3139,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3276,7 +3152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3422,151 +3298,118 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D12" s="12">
-        <f>SUM(D9:D11)</f>
-        <v>3674400</v>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B15" s="33">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C15" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="7">
-        <f>B16*C16</f>
+      <c r="D15" s="7">
+        <f>B15*C15</f>
         <v>1281600</v>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D17" s="12">
-        <f>SUM(D16:D16)</f>
-        <v>1281600</v>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B19" s="33">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C19" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="D21" s="7">
-        <f>B21*C21</f>
+      <c r="D19" s="7">
+        <f>B19*C19</f>
         <v>1929600</v>
       </c>
     </row>
-    <row r="22">
-      <c r="C22" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D22" s="12">
-        <f>SUM(D21:D21)</f>
-        <v>1929600</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="20"/>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3574,8 +3417,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3588,7 +3431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3734,20 +3577,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D12" s="12">
-        <f>SUM(D9:D11)</f>
-        <v>720000</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3755,7 +3587,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3768,7 +3600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3971,107 +3803,85 @@
         <v>33146.75</v>
       </c>
     </row>
-    <row r="15">
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D15" s="12">
-        <f>SUM(D9:D14)</f>
-        <v>204506.75</v>
-      </c>
-    </row>
-    <row r="16"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+        </is>
+      </c>
+      <c r="B18" s="33">
+        <f>Данные!$B$22*Данные!$B$9</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <f>B18*C18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
+          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
         </is>
       </c>
       <c r="B19" s="33">
-        <f>Данные!$B$22*Данные!$B$9</f>
-        <v>0</v>
+        <f>Данные!$C$22*Данные!$B$9</f>
+        <v>84240</v>
       </c>
       <c r="C19" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="7">
         <f>B19*C19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B20" s="33">
-        <f>Данные!$C$22*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C20" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7">
-        <f>B20*C20</f>
-        <v>84240</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="D21" s="12">
-        <f>SUM(D19:D20)</f>
-        <v>84240</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+    </row>
+    <row r="20"/>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4079,8 +3889,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4196,7 +4006,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -4227,47 +4037,47 @@
       <c r="I11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="D12" s="37" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="F12" s="37" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="G12" s="36" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="37" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="37" t="inlineStr">
+      <c r="I12" s="36" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -4279,11 +4089,11 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="52">
+      <c r="B13" s="51">
         <f>Данные!$D$20</f>
         <v>0</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="51">
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
@@ -4291,7 +4101,7 @@
         <f>B13*Данные!$B$8*Данные!$B$15+C13*Данные!$B$8*Данные!$B$16</f>
         <v>0</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="52">
         <f>Данные!$G$20</f>
         <v>0</v>
       </c>
@@ -4299,7 +4109,7 @@
         <f>E13*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G13" s="53">
+      <c r="G13" s="52">
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
@@ -4318,11 +4128,11 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="52">
+      <c r="B14" s="51">
         <f>SUM(Данные!$D$23:$D$30)</f>
         <v>268</v>
       </c>
-      <c r="C14" s="52">
+      <c r="C14" s="51">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
@@ -4330,7 +4140,7 @@
         <f>B14*Данные!$B$8*Данные!$B$15+C14*Данные!$B$8*Данные!$B$16</f>
         <v>728960</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="52">
         <f>SUM(Данные!$G$23:$G$30)</f>
         <v>15</v>
       </c>
@@ -4338,7 +4148,7 @@
         <f>E14*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="52">
         <f>SUM(Данные!$F$23:$F$30)</f>
         <v>17</v>
       </c>
@@ -4357,11 +4167,11 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="52">
+      <c r="B15" s="51">
         <f>Данные!$D$21</f>
         <v>12</v>
       </c>
-      <c r="C15" s="52">
+      <c r="C15" s="51">
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
@@ -4369,7 +4179,7 @@
         <f>B15*Данные!$B$8*Данные!$B$15+C15*Данные!$B$8*Данные!$B$16</f>
         <v>32640</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="52">
         <f>Данные!$G$21</f>
         <v>1</v>
       </c>
@@ -4377,7 +4187,7 @@
         <f>E15*Данные!$B$6*Данные!$B$15</f>
         <v>5180</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="52">
         <f>Данные!$F$21</f>
         <v>1</v>
       </c>
@@ -4396,11 +4206,11 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="52">
+      <c r="B16" s="51">
         <f>Данные!$D$22</f>
         <v>63</v>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="51">
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
@@ -4408,7 +4218,7 @@
         <f>B16*Данные!$B$8*Данные!$B$15+C16*Данные!$B$8*Данные!$B$16</f>
         <v>171360</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="52">
         <f>Данные!$G$22</f>
         <v>0</v>
       </c>
@@ -4416,7 +4226,7 @@
         <f>E16*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="52">
         <f>Данные!$F$22</f>
         <v>1.3</v>
       </c>
@@ -4459,7 +4269,7 @@
         <f>SUM(D13:D17)</f>
         <v>932960</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="53">
         <f>SUM(E13:E17)</f>
         <v>16</v>
       </c>
@@ -4467,7 +4277,7 @@
         <f>SUM(F13:F17)</f>
         <v>82880</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="53">
         <f>SUM(G13:G17)</f>
         <v>20.3</v>
       </c>
@@ -4531,15 +4341,15 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B22" s="52">
+      <c r="B22" s="51">
         <f>Данные!$B$20</f>
         <v>0</v>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="51">
         <f>Данные!$C$20</f>
         <v>29</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="51">
         <f>B22+C22</f>
         <v>29</v>
       </c>
@@ -4558,15 +4368,15 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B23" s="52">
+      <c r="B23" s="51">
         <f>SUM(Данные!$B$23:$B$30)</f>
         <v>161</v>
       </c>
-      <c r="C23" s="52">
+      <c r="C23" s="51">
         <f>SUM(Данные!$C$23:$C$30)</f>
         <v>1096</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="51">
         <f>B23+C23</f>
         <v>1257</v>
       </c>
@@ -4585,15 +4395,15 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B24" s="52">
+      <c r="B24" s="51">
         <f>Данные!$B$21</f>
         <v>18</v>
       </c>
-      <c r="C24" s="52">
+      <c r="C24" s="51">
         <f>Данные!$C$21</f>
         <v>34</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="51">
         <f>B24+C24</f>
         <v>52</v>
       </c>
@@ -4612,15 +4422,15 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B25" s="52">
+      <c r="B25" s="51">
         <f>Данные!$B$22</f>
         <v>0</v>
       </c>
-      <c r="C25" s="52">
+      <c r="C25" s="51">
         <f>Данные!$C$22</f>
         <v>39</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="51">
         <f>B25+C25</f>
         <v>39</v>
       </c>
@@ -4639,15 +4449,15 @@
           <t>ИТОГО РАЗОВО</t>
         </is>
       </c>
-      <c r="B26" s="55">
+      <c r="B26" s="54">
         <f>SUM(B22:B25)</f>
         <v>179</v>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="54">
         <f>SUM(C22:C25)</f>
         <v>1198</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="54">
         <f>SUM(D22:D25)</f>
         <v>1377</v>
       </c>
@@ -4671,32 +4481,32 @@
       <c r="F28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D29" s="37" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E29" s="37" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F29" s="37" t="inlineStr">
+      <c r="F29" s="36" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
@@ -5024,7 +4834,7 @@
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="42" t="n">
+      <c r="B6" s="41" t="n">
         <v>740</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -5032,7 +4842,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="43" t="inlineStr">
+      <c r="H6" s="42" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -5044,7 +4854,7 @@
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="41" t="n">
         <v>3642.5</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -5052,7 +4862,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="43" t="inlineStr">
+      <c r="H7" s="42" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
@@ -5064,7 +4874,7 @@
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="42" t="n">
+      <c r="B8" s="41" t="n">
         <v>160</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -5072,7 +4882,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="43" t="inlineStr">
+      <c r="H8" s="42" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
@@ -5084,7 +4894,7 @@
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="41" t="n">
         <v>2160</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5092,7 +4902,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H9" s="43" t="inlineStr">
+      <c r="H9" s="42" t="inlineStr">
         <is>
           <t>разовая закупка; цена из прежнего расчёта по ККЗ (29 шт = 62 640 ₸)</t>
         </is>
@@ -5104,7 +4914,7 @@
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="42" t="n">
+      <c r="B10" s="41" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5112,7 +4922,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="43" t="inlineStr">
+      <c r="H10" s="42" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -5124,7 +4934,7 @@
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="42" t="n">
+      <c r="B11" s="41" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5132,7 +4942,7 @@
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="H11" s="43" t="inlineStr">
+      <c r="H11" s="42" t="inlineStr">
         <is>
           <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
         </is>
@@ -5144,7 +4954,7 @@
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="42" t="n">
+      <c r="B12" s="41" t="n">
         <v>258488</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -5152,7 +4962,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="43" t="inlineStr">
+      <c r="H12" s="42" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
@@ -5164,7 +4974,7 @@
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="42" t="n">
+      <c r="B13" s="41" t="n">
         <v>350000</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5172,7 +4982,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H13" s="43" t="inlineStr">
+      <c r="H13" s="42" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
@@ -5184,7 +4994,7 @@
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n">
+      <c r="B14" s="41" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -5192,7 +5002,7 @@
           <t>чел.</t>
         </is>
       </c>
-      <c r="H14" s="43" t="inlineStr">
+      <c r="H14" s="42" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
@@ -5204,7 +5014,7 @@
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="42" t="n">
+      <c r="B15" s="41" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -5212,7 +5022,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="43" t="inlineStr">
+      <c r="H15" s="42" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
@@ -5224,7 +5034,7 @@
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="42" t="n">
+      <c r="B16" s="41" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5232,7 +5042,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H16" s="43" t="inlineStr">
+      <c r="H16" s="42" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
@@ -5254,42 +5064,42 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="37" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="37" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="37" t="inlineStr">
+      <c r="H19" s="36" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -5301,26 +5111,26 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="42" t="n">
+      <c r="B20" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="42" t="n">
+      <c r="C20" s="41" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="42" t="n">
+      <c r="D20" s="41" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="56" t="n">
+      <c r="F20" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="56" t="n">
+      <c r="G20" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="43" t="inlineStr">
+      <c r="H20" s="42" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
@@ -5332,26 +5142,26 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="42" t="n">
+      <c r="B21" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="42" t="n">
+      <c r="C21" s="41" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="42" t="n">
+      <c r="D21" s="41" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
         <v>18</v>
       </c>
-      <c r="F21" s="56" t="n">
+      <c r="F21" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="56" t="n">
+      <c r="G21" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="43" t="inlineStr"/>
+      <c r="H21" s="42" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5359,26 +5169,26 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="42" t="n">
+      <c r="B22" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="42" t="n">
+      <c r="C22" s="41" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="42" t="n">
+      <c r="D22" s="41" t="n">
         <v>63</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="56" t="n">
+      <c r="F22" s="55" t="n">
         <v>1.3</v>
       </c>
-      <c r="G22" s="56" t="n">
+      <c r="G22" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="43" t="inlineStr">
+      <c r="H22" s="42" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
@@ -5390,26 +5200,26 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="42" t="n">
+      <c r="B23" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="42" t="n">
+      <c r="C23" s="41" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="42" t="n">
+      <c r="D23" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
         <v>13</v>
       </c>
-      <c r="F23" s="56" t="n">
+      <c r="F23" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="56" t="n">
+      <c r="G23" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="43" t="inlineStr"/>
+      <c r="H23" s="42" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5417,26 +5227,26 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="42" t="n">
+      <c r="B24" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="42" t="n">
+      <c r="C24" s="41" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="42" t="n">
+      <c r="D24" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
         <v>17</v>
       </c>
-      <c r="F24" s="56" t="n">
+      <c r="F24" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="56" t="n">
+      <c r="G24" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="43" t="inlineStr"/>
+      <c r="H24" s="42" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5444,26 +5254,26 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="42" t="n">
+      <c r="B25" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="42" t="n">
+      <c r="C25" s="41" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="42" t="n">
+      <c r="D25" s="41" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
         <v>50</v>
       </c>
-      <c r="F25" s="56" t="n">
+      <c r="F25" s="55" t="n">
         <v>3.5</v>
       </c>
-      <c r="G25" s="56" t="n">
+      <c r="G25" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="43" t="inlineStr"/>
+      <c r="H25" s="42" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5471,26 +5281,26 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="42" t="n">
+      <c r="B26" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="42" t="n">
+      <c r="C26" s="41" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="42" t="n">
+      <c r="D26" s="41" t="n">
         <v>80</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
         <v>17</v>
       </c>
-      <c r="F26" s="56" t="n">
+      <c r="F26" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="56" t="n">
+      <c r="G26" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="43" t="inlineStr"/>
+      <c r="H26" s="42" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5498,26 +5308,26 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="42" t="n">
+      <c r="B27" s="41" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="42" t="n">
+      <c r="C27" s="41" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="42" t="n">
+      <c r="D27" s="41" t="n">
         <v>64</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
         <v>15</v>
       </c>
-      <c r="F27" s="56" t="n">
+      <c r="F27" s="55" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="56" t="n">
+      <c r="G27" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="43" t="inlineStr"/>
+      <c r="H27" s="42" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5525,26 +5335,26 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="42" t="n">
+      <c r="B28" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="42" t="n">
+      <c r="C28" s="41" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="42" t="n">
+      <c r="D28" s="41" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
         <v>13</v>
       </c>
-      <c r="F28" s="56" t="n">
+      <c r="F28" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="56" t="n">
+      <c r="G28" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="43" t="inlineStr"/>
+      <c r="H28" s="42" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5552,26 +5362,26 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="42" t="n">
+      <c r="B29" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="42" t="n">
+      <c r="C29" s="41" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="42" t="n">
+      <c r="D29" s="41" t="n">
         <v>10</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
         <v>17</v>
       </c>
-      <c r="F29" s="56" t="n">
+      <c r="F29" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="56" t="n">
+      <c r="G29" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="43" t="inlineStr"/>
+      <c r="H29" s="42" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5579,26 +5389,26 @@
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="42" t="n">
+      <c r="B30" s="41" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="42" t="n">
+      <c r="C30" s="41" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="42" t="n">
+      <c r="D30" s="41" t="n">
         <v>24</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
         <v>19</v>
       </c>
-      <c r="F30" s="56" t="n">
+      <c r="F30" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="56" t="n">
+      <c r="G30" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="43" t="inlineStr"/>
+      <c r="H30" s="42" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5610,9 +5420,9 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="53" t="n"/>
-      <c r="G31" s="53" t="n"/>
-      <c r="H31" s="43" t="inlineStr">
+      <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+      <c r="H31" s="42" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5628,9 +5438,9 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="53" t="n"/>
-      <c r="G32" s="53" t="n"/>
-      <c r="H32" s="43" t="inlineStr">
+      <c r="F32" s="52" t="n"/>
+      <c r="G32" s="52" t="n"/>
+      <c r="H32" s="42" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5658,11 +5468,11 @@
         <f>SUM(E20:E32)</f>
         <v>179</v>
       </c>
-      <c r="F33" s="54">
+      <c r="F33" s="53">
         <f>SUM(F20:F32)</f>
         <v>20.3</v>
       </c>
-      <c r="G33" s="54">
+      <c r="G33" s="53">
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
@@ -5715,7 +5525,7 @@
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="42" t="n">
+      <c r="B37" s="41" t="n">
         <v>96600</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5723,7 +5533,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="43" t="inlineStr">
+      <c r="H37" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
@@ -5735,7 +5545,7 @@
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="42" t="n">
+      <c r="B38" s="41" t="n">
         <v>618400</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -5743,7 +5553,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="43" t="inlineStr">
+      <c r="H38" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
@@ -5755,7 +5565,7 @@
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="42" t="n">
+      <c r="B39" s="41" t="n">
         <v>478400</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -5763,7 +5573,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="43" t="inlineStr">
+      <c r="H39" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5775,7 +5585,7 @@
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="42" t="n">
+      <c r="B40" s="41" t="n">
         <v>569800</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -5783,7 +5593,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="43" t="inlineStr">
+      <c r="H40" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
@@ -5795,7 +5605,7 @@
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="42" t="n">
+      <c r="B41" s="41" t="n">
         <v>440700</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -5803,7 +5613,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="43" t="inlineStr">
+      <c r="H41" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5815,7 +5625,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="42" t="n">
+      <c r="B42" s="41" t="n">
         <v>2599100</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -5823,7 +5633,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="43" t="inlineStr">
+      <c r="H42" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
@@ -5835,7 +5645,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="42" t="n">
+      <c r="B43" s="41" t="n">
         <v>2010300</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -5843,7 +5653,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="43" t="inlineStr">
+      <c r="H43" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5855,7 +5665,7 @@
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="42" t="n">
+      <c r="B44" s="41" t="n">
         <v>126200</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5863,7 +5673,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="43" t="inlineStr">
+      <c r="H44" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
@@ -5875,7 +5685,7 @@
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="42" t="n">
+      <c r="B45" s="41" t="n">
         <v>106800</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -5883,7 +5693,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="43" t="inlineStr">
+      <c r="H45" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5895,7 +5705,7 @@
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="42" t="n">
+      <c r="B46" s="41" t="n">
         <v>126200</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -5903,7 +5713,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="43" t="inlineStr">
+      <c r="H46" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5915,7 +5725,7 @@
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="42" t="n">
+      <c r="B47" s="41" t="n">
         <v>106800</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -5923,7 +5733,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="43" t="inlineStr">
+      <c r="H47" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5935,7 +5745,7 @@
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="42" t="n">
+      <c r="B48" s="41" t="n">
         <v>720000</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -5943,7 +5753,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="43" t="inlineStr">
+      <c r="H48" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5955,7 +5765,7 @@
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="42" t="n">
+      <c r="B49" s="41" t="n">
         <v>1080000</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -5963,7 +5773,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="43" t="inlineStr">
+      <c r="H49" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5975,7 +5785,7 @@
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="42" t="n">
+      <c r="B50" s="41" t="n">
         <v>3000000</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -5983,7 +5793,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="43" t="inlineStr">
+      <c r="H50" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5995,7 +5805,7 @@
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="42" t="n">
+      <c r="B51" s="41" t="n">
         <v>100800</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -6003,7 +5813,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="43" t="inlineStr">
+      <c r="H51" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6015,7 +5825,7 @@
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="42" t="n">
+      <c r="B52" s="41" t="n">
         <v>160800</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -6023,7 +5833,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="43" t="inlineStr">
+      <c r="H52" s="42" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6035,7 +5845,7 @@
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="42" t="n">
+      <c r="B53" s="41" t="n">
         <v>75000</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -6043,7 +5853,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="43" t="inlineStr">
+      <c r="H53" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6055,7 +5865,7 @@
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="42" t="n">
+      <c r="B54" s="41" t="n">
         <v>70000</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -6063,7 +5873,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="43" t="inlineStr">
+      <c r="H54" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6075,7 +5885,7 @@
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="42" t="n">
+      <c r="B55" s="41" t="n">
         <v>3172000</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -6083,7 +5893,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="43" t="inlineStr">
+      <c r="H55" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -6095,7 +5905,7 @@
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="42" t="n">
+      <c r="B56" s="41" t="n">
         <v>2074000</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -6103,7 +5913,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="43" t="inlineStr">
+      <c r="H56" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -6115,7 +5925,7 @@
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="42" t="n">
+      <c r="B57" s="41" t="n">
         <v>2806000</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -6123,7 +5933,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="43" t="inlineStr">
+      <c r="H57" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -6135,7 +5945,7 @@
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="42" t="n">
+      <c r="B58" s="41" t="n">
         <v>1830000</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -6143,7 +5953,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="43" t="inlineStr">
+      <c r="H58" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -6155,7 +5965,7 @@
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="42" t="n">
+      <c r="B59" s="41" t="n">
         <v>180000</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -6163,7 +5973,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="43" t="inlineStr">
+      <c r="H59" s="42" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
@@ -6175,7 +5985,7 @@
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="42" t="n">
+      <c r="B60" s="41" t="n">
         <v>80000</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -6183,7 +5993,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="43" t="inlineStr">
+      <c r="H60" s="42" t="inlineStr">
         <is>
           <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
@@ -6195,7 +6005,7 @@
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="42" t="n">
+      <c r="B61" s="41" t="n">
         <v>9</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -6203,7 +6013,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H61" s="43" t="inlineStr">
+      <c r="H61" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6215,7 +6025,7 @@
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="42" t="n">
+      <c r="B62" s="41" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -6223,7 +6033,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H62" s="43" t="inlineStr">
+      <c r="H62" s="42" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6235,7 +6045,7 @@
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="42" t="n">
+      <c r="B63" s="41" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -6243,7 +6053,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H63" s="43" t="inlineStr">
+      <c r="H63" s="42" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
@@ -6255,7 +6065,7 @@
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B64" s="57" t="n">
+      <c r="B64" s="56" t="n">
         <v>0.15</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -6263,7 +6073,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H64" s="43" t="inlineStr">
+      <c r="H64" s="42" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
@@ -6275,7 +6085,7 @@
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B65" s="57" t="n">
+      <c r="B65" s="56" t="n">
         <v>0.15</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -6283,7 +6093,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="43" t="inlineStr">
+      <c r="H65" s="42" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
@@ -6295,7 +6105,7 @@
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B66" s="57" t="n">
+      <c r="B66" s="56" t="n">
         <v>0.16</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -6303,7 +6113,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H66" s="43" t="inlineStr">
+      <c r="H66" s="42" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,9 +257,6 @@
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -289,7 +286,6 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -309,7 +305,6 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -677,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -727,7 +722,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="n"/>
+      <c r="A5" s="43" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>в месяц</t>
@@ -783,11 +778,11 @@
       </c>
       <c r="F6" s="7">
         <f>G6/12</f>
-        <v>2124.791667</v>
+        <v>38664.79167</v>
       </c>
       <c r="G6" s="8">
         <f>'ККЗ'!D5</f>
-        <v>25497.5</v>
+        <v>463977.5</v>
       </c>
     </row>
     <row r="7">
@@ -814,11 +809,11 @@
       </c>
       <c r="F7" s="7">
         <f>G7/12</f>
-        <v>103343.125</v>
+        <v>1687163.125</v>
       </c>
       <c r="G7" s="8">
         <f>'Бройлерные площадки'!D5</f>
-        <v>1240117.5</v>
+        <v>20245957.5</v>
       </c>
     </row>
     <row r="8">
@@ -840,14 +835,14 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n"/>
+      <c r="E8" s="44" t="n"/>
       <c r="F8" s="7">
         <f>G8/12</f>
-        <v>5276.458333</v>
+        <v>70796.45833</v>
       </c>
       <c r="G8" s="8">
         <f>'Инкубаторий'!D5</f>
-        <v>63317.5</v>
+        <v>849557.5</v>
       </c>
     </row>
     <row r="9">
@@ -877,7 +872,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G9" s="46" t="n"/>
+      <c r="G9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -890,7 +885,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n"/>
+      <c r="C10" s="44" t="n"/>
       <c r="D10" s="7">
         <f>E10/12</f>
         <v>60000</v>
@@ -904,7 +899,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G10" s="46" t="n"/>
+      <c r="G10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -917,20 +912,20 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C11" s="46" t="n"/>
+      <c r="C11" s="44" t="n"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E11" s="46" t="n"/>
+      <c r="E11" s="44" t="n"/>
       <c r="F11" s="7">
         <f>G11/12</f>
-        <v>17042.22917</v>
+        <v>66182.22917</v>
       </c>
       <c r="G11" s="8">
         <f>'АБК'!D5</f>
-        <v>204506.75</v>
+        <v>794186.75</v>
       </c>
     </row>
     <row r="12">
@@ -957,11 +952,11 @@
       </c>
       <c r="F12" s="12">
         <f>G12/12</f>
-        <v>127786.6042</v>
+        <v>1862806.604</v>
       </c>
       <c r="G12" s="12">
         <f>SUM(G6:G11)</f>
-        <v>1533439.25</v>
+        <v>22353679.25</v>
       </c>
     </row>
     <row r="13">
@@ -1026,11 +1021,11 @@
       </c>
       <c r="F15" s="14">
         <f>G15/12</f>
-        <v>1163325.271</v>
+        <v>2898345.271</v>
       </c>
       <c r="G15" s="14">
         <f>G12+G13+G14</f>
-        <v>13959903.25</v>
+        <v>34780143.25</v>
       </c>
     </row>
     <row r="16"/>
@@ -1077,15 +1072,15 @@
       </c>
       <c r="B19" s="7">
         <f>C19/12</f>
-        <v>2972974.729</v>
+        <v>1237954.729</v>
       </c>
       <c r="C19" s="8">
         <f>C15-G15</f>
-        <v>35675696.75</v>
-      </c>
-      <c r="D19" s="47">
+        <v>14855456.75</v>
+      </c>
+      <c r="D19" s="45">
         <f>IF(G15=0,0,C15/G15)</f>
-        <v>3.555583381</v>
+        <v>1.427124657</v>
       </c>
     </row>
     <row r="20">
@@ -1096,15 +1091,15 @@
       </c>
       <c r="B20" s="7">
         <f>C20/12</f>
-        <v>2049174.729</v>
+        <v>314154.7292</v>
       </c>
       <c r="C20" s="8">
         <f>E15-G15</f>
-        <v>24590096.75</v>
-      </c>
-      <c r="D20" s="47">
+        <v>3769856.75</v>
+      </c>
+      <c r="D20" s="45">
         <f>IF(G15=0,0,E15/G15)</f>
-        <v>2.761480457</v>
+        <v>1.108391064</v>
       </c>
     </row>
     <row r="21"/>
@@ -1222,40 +1217,40 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t>Приманочные станции 1-го и 2-го контура · тёплый сезон, ежемесячный платёж</t>
+        </is>
+      </c>
+      <c r="B27" s="7">
+        <f>Данные!$B$33+Данные!$C$33</f>
+        <v>1377</v>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D27" s="7">
+        <f>Данные!$B$9</f>
+        <v>2160</v>
+      </c>
+      <c r="E27" s="7">
+        <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9</f>
+        <v>2974320</v>
+      </c>
+      <c r="F27" s="8">
+        <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9*Данные!$B$15</f>
+        <v>20820240</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
           <t>Клеевые станции 3-го контура · апрель — октябрь</t>
         </is>
       </c>
-      <c r="B27" s="7">
+      <c r="B28" s="7">
         <f>Данные!$D$33</f>
         <v>343</v>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>шт/мес</t>
-        </is>
-      </c>
-      <c r="D27" s="7">
-        <f>Данные!$B$8</f>
-        <v>160</v>
-      </c>
-      <c r="E27" s="7">
-        <f>Данные!$D$33*Данные!$B$8</f>
-        <v>54880</v>
-      </c>
-      <c r="F27" s="8">
-        <f>Данные!$D$33*Данные!$B$8*Данные!$B$15</f>
-        <v>384160</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
-        </is>
-      </c>
-      <c r="B28" s="7">
-        <f>Данные!$D$33*2</f>
-        <v>686</v>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
@@ -1267,102 +1262,111 @@
         <v>160</v>
       </c>
       <c r="E28" s="7">
+        <f>Данные!$D$33*Данные!$B$8</f>
+        <v>54880</v>
+      </c>
+      <c r="F28" s="8">
+        <f>Данные!$D$33*Данные!$B$8*Данные!$B$15</f>
+        <v>384160</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
+        </is>
+      </c>
+      <c r="B29" s="7">
+        <f>Данные!$D$33*2</f>
+        <v>686</v>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D29" s="7">
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E29" s="7">
         <f>Данные!$D$33*2*Данные!$B$8</f>
         <v>109760</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F29" s="8">
         <f>Данные!$D$33*2*Данные!$B$8*Данные!$B$16</f>
         <v>548800</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Зерноцид · 2-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B29" s="7">
+      <c r="B30" s="7">
         <f>Данные!$G$33</f>
         <v>16</v>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D29" s="7">
+      <c r="D30" s="7">
         <f>Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E30" s="7">
         <f>Данные!$G$33*Данные!$B$6</f>
         <v>11840</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F30" s="8">
         <f>Данные!$G$33*Данные!$B$6*Данные!$B$15</f>
         <v>82880</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
         </is>
       </c>
-      <c r="B30" s="7">
+      <c r="B31" s="7">
         <f>Данные!$F$33</f>
         <v>20.3</v>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D30" s="7">
+      <c r="D31" s="7">
         <f>Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E31" s="7">
         <f>Данные!$F$33*Данные!$B$7</f>
         <v>73942.75</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F31" s="8">
         <f>Данные!$F$33*Данные!$B$7*Данные!$B$15</f>
         <v>517599.25</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
         </is>
       </c>
-      <c r="B31" s="7">
+      <c r="B32" s="7">
         <f>Данные!$C$33</f>
         <v>1198</v>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>шт</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
-        </is>
-      </c>
-      <c r="B32" s="48">
-        <f>Данные!$F$33/Данные!$C$33</f>
-        <v>0.01694490818</v>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -1372,312 +1376,313 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
+        </is>
+      </c>
+      <c r="B33" s="46">
+        <f>Данные!$F$33/Данные!$C$33</f>
+        <v>0.01694490818</v>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>Бутылки · тёплый сезон</t>
         </is>
       </c>
-      <c r="B33" s="7">
+      <c r="B34" s="7">
         <f>Данные!$B$11</f>
         <v>40</v>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D33" s="7">
+      <c r="D34" s="7">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E34" s="7">
         <f>Данные!$B$11*Данные!$B$10</f>
         <v>2720</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F34" s="8">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>ИТОГО ТЕКУЩИЕ РАСХОДЫ ШТАТА</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="14">
-        <f>F34/12</f>
-        <v>1163325.271</v>
-      </c>
-      <c r="F34" s="14">
-        <f>F26+F27+F28+F29+F30+F33</f>
-        <v>13959903.25</v>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го контура · разовая закупка</t>
-        </is>
-      </c>
-      <c r="B35" s="7">
-        <f>Данные!$B$33</f>
-        <v>179</v>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D35" s="7">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
-      </c>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="8">
-        <f>Данные!$B$33*Данные!$B$9</f>
-        <v>386640</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Приманочные станции 2-го контура · разовая закупка</t>
-        </is>
-      </c>
-      <c r="B36" s="7">
-        <f>Данные!$C$33</f>
-        <v>1198</v>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D36" s="7">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
-      </c>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="8">
-        <f>Данные!$C$33*Данные!$B$9</f>
-        <v>2587680</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО РАЗОВАЯ ЗАКУПКА ОБОРУДОВАНИЯ</t>
-        </is>
-      </c>
-      <c r="B37" s="12">
-        <f>Данные!$B$33+Данные!$C$33</f>
-        <v>1377</v>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="12">
-        <f>F35+F36</f>
-        <v>2974320</v>
-      </c>
-    </row>
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО ШТАТ УКПФ</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="14">
+        <f>F35/12</f>
+        <v>2898345.271</v>
+      </c>
+      <c r="F35" s="14">
+        <f>F26+F27+F28+F29+F30+F31+F34</f>
+        <v>34780143.25</v>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>ИТОГО ПЕРВЫЙ ГОД · с разовой закупкой</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="14">
-        <f>F34+F37</f>
-        <v>16934223.25</v>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Цена КП без скидок</t>
+        </is>
+      </c>
+      <c r="B40" s="7">
+        <f>C40/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C40" s="8">
+        <f>C15</f>
+        <v>49635600</v>
+      </c>
+      <c r="D40" s="10" t="n"/>
+    </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="16" t="n"/>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Вся территория фабрики</t>
+        </is>
+      </c>
+      <c r="B41" s="7">
+        <f>C41/12</f>
+        <v>3515855</v>
+      </c>
+      <c r="C41" s="8">
+        <f>C15*(1-Данные!$B$64)</f>
+        <v>42190260</v>
+      </c>
+      <c r="D41" s="47">
+        <f>Данные!$B$64</f>
+        <v>0.15</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Условие</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Ставка</t>
-        </is>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Вся территория + 100 % предоплата</t>
+        </is>
+      </c>
+      <c r="B42" s="7">
+        <f>C42/12</f>
+        <v>2988476.75</v>
+      </c>
+      <c r="C42" s="8">
+        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+        <v>35861721</v>
+      </c>
+      <c r="D42" s="47">
+        <f>Данные!$B$65</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Цена КП без скидок</t>
+          <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
       <c r="B43" s="7">
         <f>C43/12</f>
-        <v>4136300</v>
+        <v>2510320.47</v>
       </c>
       <c r="C43" s="8">
-        <f>C15</f>
-        <v>49635600</v>
-      </c>
-      <c r="D43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Вся территория фабрики</t>
-        </is>
-      </c>
-      <c r="B44" s="7">
-        <f>C44/12</f>
-        <v>3515855</v>
-      </c>
-      <c r="C44" s="8">
-        <f>C15*(1-Данные!$B$64)</f>
-        <v>42190260</v>
-      </c>
-      <c r="D44" s="49">
-        <f>Данные!$B$64</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Вся территория + 100 % предоплата</t>
-        </is>
-      </c>
-      <c r="B45" s="7">
-        <f>C45/12</f>
-        <v>2988476.75</v>
-      </c>
-      <c r="C45" s="8">
-        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
-        <v>35861721</v>
-      </c>
-      <c r="D45" s="49">
-        <f>Данные!$B$65</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Вся территория + предоплата + неплательщик НДС</t>
-        </is>
-      </c>
-      <c r="B46" s="7">
-        <f>C46/12</f>
-        <v>2510320.47</v>
-      </c>
-      <c r="C46" s="8">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D46" s="49">
+      <c r="D43" s="47">
         <f>Данные!$B$66</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="47"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="16" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Что зафиксировано в документах</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D47" s="27" t="inlineStr">
+        <is>
+          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+        </is>
+      </c>
+      <c r="E47" s="48" t="n"/>
+      <c r="F47" s="48" t="n"/>
+      <c r="G47" s="44" t="n"/>
+    </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="16" t="n"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>выезд по запросу</t>
+        </is>
+      </c>
+      <c r="E48" s="48" t="n"/>
+      <c r="F48" s="48" t="n"/>
+      <c r="G48" s="44" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="D49" s="27" t="inlineStr">
         <is>
-          <t>Что зафиксировано в документах</t>
-        </is>
-      </c>
+          <t>дополнительные визиты по вызову</t>
+        </is>
+      </c>
+      <c r="E49" s="48" t="n"/>
+      <c r="F49" s="48" t="n"/>
+      <c r="G49" s="44" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Indigo Solutions</t>
+          <t>Pest Hunters</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
-        </is>
-      </c>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="50" t="n"/>
-      <c r="G50" s="46" t="n"/>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
+        </is>
+      </c>
+      <c r="E50" s="48" t="n"/>
+      <c r="F50" s="48" t="n"/>
+      <c r="G50" s="44" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -1687,130 +1692,61 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>ККЗ</t>
+          <t>склад ТМЦ</t>
         </is>
       </c>
       <c r="C51" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>выезд по запросу</t>
-        </is>
-      </c>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="46" t="n"/>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>выезд по рекламации за два рабочих дня</t>
+        </is>
+      </c>
+      <c r="E51" s="48" t="n"/>
+      <c r="F51" s="48" t="n"/>
+      <c r="G51" s="44" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Pest Hunters</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>бройлерные площадки</t>
+          <t>все объекты</t>
         </is>
       </c>
       <c r="C52" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>дополнительные визиты по вызову</t>
-        </is>
-      </c>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="50" t="n"/>
-      <c r="G52" s="46" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="C53" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" s="28" t="inlineStr">
-        <is>
-          <t>по графику на 2026 год, бригада из трёх человек</t>
-        </is>
-      </c>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="50" t="n"/>
-      <c r="G53" s="46" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="28" t="inlineStr">
-        <is>
-          <t>выезд по рекламации за два рабочих дня</t>
-        </is>
-      </c>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="50" t="n"/>
-      <c r="G54" s="46" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C55" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D55" s="28" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
         <is>
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="50" t="n"/>
-      <c r="G55" s="46" t="n"/>
+      <c r="E52" s="48" t="n"/>
+      <c r="F52" s="48" t="n"/>
+      <c r="G52" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="D48:G48"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A39:G39"/>
     <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D47:G47"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D53:G53"/>
     <mergeCell ref="D52:G52"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="D49:G49"/>
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="F9:G9"/>
@@ -1825,7 +1761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1842,47 +1778,47 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура, 1 кг брикетов Pest Killer на обработку.</t>
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/мес, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="31">
-        <f>D11+D12+D13+D14</f>
-        <v>25497.5</v>
+      <c r="D5" s="30">
+        <f>D11+D12+D13+D14+D15</f>
+        <v>463977.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -1919,16 +1855,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="32">
         <f>Данные!$B$37</f>
         <v>96600</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -1937,16 +1873,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · дератизация</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="32">
         <f>Данные!$B$53</f>
         <v>75000</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -1955,37 +1891,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
+        <v>62640</v>
+      </c>
+      <c r="C11" s="32">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
+        <v>438480</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B12" s="32">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C12" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
-      </c>
-      <c r="D11" s="8">
-        <f>B11*C11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
-        </is>
-      </c>
-      <c r="B12" s="33">
-        <f>Данные!$D$20*2*Данные!$B$8</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="33">
-        <f>Данные!$B$16</f>
-        <v>5</v>
       </c>
       <c r="D12" s="8">
         <f>B12*C12</f>
@@ -1993,18 +1929,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Зерноцид, 2-й контур</t>
-        </is>
-      </c>
-      <c r="B13" s="33">
-        <f>Данные!$G$20*Данные!$B$6</f>
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
+        </is>
+      </c>
+      <c r="B13" s="32">
+        <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C13" s="33">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+      <c r="C13" s="32">
+        <f>Данные!$B$16</f>
+        <v>5</v>
       </c>
       <c r="D13" s="8">
         <f>B13*C13</f>
@@ -2012,154 +1948,104 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Зерноцид, 2-й контур</t>
+        </is>
+      </c>
+      <c r="B14" s="32">
+        <f>Данные!$G$20*Данные!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="32">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B15" s="32">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C15" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="8">
-        <f>B14*C14</f>
+      <c r="D15" s="8">
+        <f>B15*C15</f>
         <v>25497.5</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B18" s="33">
-        <f>Данные!$B$20*Данные!$B$9</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7">
-        <f>B18*C18</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B19" s="33">
-        <f>Данные!$C$20*Данные!$B$9</f>
-        <v>62640</v>
-      </c>
-      <c r="C19" s="33" t="n">
-        <v>1</v>
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Pest Hunters · дезинсекция</t>
+        </is>
+      </c>
+      <c r="B19" s="32">
+        <f>Данные!$B$54</f>
+        <v>70000</v>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="D19" s="7">
         <f>B19*C19</f>
-        <v>62640</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="20"/>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>Pest Hunters · дезинсекция</t>
-        </is>
-      </c>
-      <c r="B23" s="33">
-        <f>Данные!$B$54</f>
-        <v>70000</v>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" s="7">
-        <f>B23*C23</f>
-        <v>840000</v>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2167,8 +2053,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2181,7 +2067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2198,7 +2084,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2206,39 +2092,39 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <f>D12+D13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="31">
-        <f>D14+D15+D16+D17</f>
-        <v>1240117.5</v>
+      <c r="D5" s="30">
+        <f>D14+D15+D16+D17+D18</f>
+        <v>20245957.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -2275,16 +2161,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="32">
         <f>Данные!$B$38</f>
         <v>618400</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2293,16 +2179,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="32">
         <f>Данные!$B$40</f>
         <v>569800</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -2311,16 +2197,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="32">
         <f>Данные!$B$42</f>
         <v>2599100</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="8">
@@ -2329,16 +2215,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="32">
         <f>Данные!$B$55</f>
         <v>3172000</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="32">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2348,16 +2234,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="32">
         <f>Данные!$B$56</f>
         <v>2074000</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2367,382 +2253,324 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B14" s="32">
+        <f>(SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30))*Данные!$B$9</f>
+        <v>2715120</v>
+      </c>
+      <c r="C14" s="32">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
+        <v>19005840</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B15" s="32">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C15" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="8">
-        <f>B14*C14</f>
+      <c r="D15" s="8">
+        <f>B15*C15</f>
         <v>300160</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B16" s="32">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C16" s="32">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D15" s="8">
-        <f>B15*C15</f>
+      <c r="D16" s="8">
+        <f>B16*C16</f>
         <v>428800</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B17" s="32">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C17" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D16" s="8">
-        <f>B16*C16</f>
+      <c r="D17" s="8">
+        <f>B17*C17</f>
         <v>77700</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B18" s="32">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C18" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D17" s="8">
-        <f>B17*C17</f>
+      <c r="D18" s="8">
+        <f>B18*C18</f>
         <v>433457.5</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B22" s="32">
         <f>Данные!$B$39</f>
         <v>478400</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C22" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="D21" s="7">
-        <f>B21*C21</f>
+      <c r="D22" s="7">
+        <f>B22*C22</f>
         <v>5740800</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="B22" s="33">
+      <c r="B23" s="32">
         <f>Данные!$B$41</f>
         <v>440700</v>
       </c>
-      <c r="C22" s="33" t="n">
+      <c r="C23" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="D22" s="7">
-        <f>B22*C22</f>
+      <c r="D23" s="7">
+        <f>B23*C23</f>
         <v>5288400</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="B23" s="33">
+      <c r="B24" s="32">
         <f>Данные!$B$43</f>
         <v>2010300</v>
       </c>
-      <c r="C23" s="33" t="n">
+      <c r="C24" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="D23" s="7">
-        <f>B23*C23</f>
+      <c r="D24" s="7">
+        <f>B24*C24</f>
         <v>24123600</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B24" s="33">
+      <c r="B25" s="32">
         <f>Данные!$B$57</f>
         <v>2806000</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C25" s="32">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="D24" s="7">
-        <f>B24*C24</f>
+      <c r="D25" s="7">
+        <f>B25*C25</f>
         <v>25254000</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B25" s="33">
+      <c r="B26" s="32">
         <f>Данные!$B$58</f>
         <v>1830000</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C26" s="32">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="D25" s="7">
-        <f>B25*C25</f>
+      <c r="D26" s="7">
+        <f>B26*C26</f>
         <v>5490000</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-    </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B29" s="33">
-        <f>SUM(Данные!$B$23:$B$30)*Данные!$B$9</f>
-        <v>347760</v>
-      </c>
-      <c r="C29" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="7">
-        <f>B29*C29</f>
-        <v>347760</v>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B30" s="33">
-        <f>SUM(Данные!$C$23:$C$30)*Данные!$B$9</f>
-        <v>2367360</v>
-      </c>
-      <c r="C30" s="33" t="n">
-        <v>1</v>
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Айыртау БП</t>
+        </is>
+      </c>
+      <c r="B30" s="32">
+        <f>Данные!$B$48</f>
+        <v>720000</v>
+      </c>
+      <c r="C30" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="D30" s="7">
         <f>B30*C30</f>
-        <v>2367360</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>Indigo Solutions · Айыртау БП</t>
-        </is>
-      </c>
-      <c r="B34" s="33">
-        <f>Данные!$B$48</f>
-        <v>720000</v>
-      </c>
-      <c r="C34" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="D34" s="7">
-        <f>B34*C34</f>
         <v>8640000</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B35" s="33">
+      <c r="B31" s="32">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="C35" s="33" t="n">
+      <c r="C31" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="D35" s="7">
-        <f>B35*C35</f>
+      <c r="D31" s="7">
+        <f>B31*C31</f>
         <v>12960000</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B36" s="33">
+      <c r="B32" s="32">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="C36" s="33" t="n">
+      <c r="C32" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="D36" s="7">
-        <f>B36*C36</f>
+      <c r="D32" s="7">
+        <f>B32*C32</f>
         <v>36000000</v>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="25" t="inlineStr">
+    <row r="33"/>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>Разовая закупка приманочных станций 1-го и 2-го контура показана справочно и в годовой итог не входит.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A38:D38"/>
+  <mergeCells count="2">
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2754,7 +2582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2771,7 +2599,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
@@ -2779,39 +2607,39 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="31">
-        <f>D11+D12+D13+D14</f>
-        <v>63317.5</v>
+      <c r="D5" s="30">
+        <f>D11+D12+D13+D14+D15</f>
+        <v>849557.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -2848,16 +2676,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="32">
         <f>Данные!$B$44</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2866,15 +2694,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -2883,255 +2711,205 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
+        <v>112320</v>
+      </c>
+      <c r="C11" s="32">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
+        <v>786240</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B12" s="32">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C12" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D11" s="8">
-        <f>B11*C11</f>
+      <c r="D12" s="8">
+        <f>B12*C12</f>
         <v>13440</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B13" s="32">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C13" s="32">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D12" s="8">
-        <f>B12*C12</f>
+      <c r="D13" s="8">
+        <f>B13*C13</f>
         <v>19200</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B14" s="32">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C14" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D13" s="8">
-        <f>B13*C13</f>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
         <v>5180</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B15" s="32">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C15" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="8">
-        <f>B14*C14</f>
+      <c r="D15" s="8">
+        <f>B15*C15</f>
         <v>25497.5</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B18" s="33">
+      <c r="B19" s="32">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C19" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="D18" s="7">
-        <f>B18*C18</f>
+      <c r="D19" s="7">
+        <f>B19*C19</f>
         <v>1281600</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-    </row>
+    <row r="20"/>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B22" s="33">
-        <f>Данные!$B$21*Данные!$B$9</f>
-        <v>38880</v>
-      </c>
-      <c r="C22" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7">
-        <f>B22*C22</f>
-        <v>38880</v>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B23" s="33">
-        <f>Данные!$C$21*Данные!$B$9</f>
-        <v>73440</v>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>1</v>
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · дезинсекция</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>Данные!$B$51</f>
+        <v>100800</v>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="D23" s="7">
         <f>B23*C23</f>
-        <v>73440</v>
+        <v>1209600</v>
       </c>
     </row>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>Indigo Solutions · дезинсекция</t>
-        </is>
-      </c>
-      <c r="B27" s="33">
-        <f>Данные!$B$51</f>
-        <v>100800</v>
-      </c>
-      <c r="C27" s="33" t="n">
-        <v>12</v>
-      </c>
-      <c r="D27" s="7">
-        <f>B27*C27</f>
-        <v>1209600</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3139,7 +2917,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3169,7 +2947,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3177,37 +2955,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3246,16 +3024,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="32">
         <f>Данные!$B$46</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -3264,16 +3042,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="32">
         <f>Данные!$B$59</f>
         <v>180000</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -3282,15 +3060,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n">
+      <c r="B11" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3332,16 +3110,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="32">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="C15" s="33" t="n">
+      <c r="C15" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="7">
@@ -3383,16 +3161,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="32">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="C19" s="33" t="n">
+      <c r="C19" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -3402,14 +3180,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3448,7 +3226,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -3456,37 +3234,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>720000</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3525,15 +3303,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3542,16 +3320,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="32">
         <f>Данные!$B$60</f>
         <v>80000</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="32">
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
@@ -3561,15 +3339,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n">
+      <c r="B11" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3579,7 +3357,7 @@
     </row>
     <row r="12"/>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3600,7 +3378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3617,7 +3395,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -3625,39 +3403,39 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="31">
-        <f>D11+D12+D13+D14</f>
-        <v>204506.75</v>
+      <c r="D5" s="30">
+        <f>D11+D12+D13+D14+D15</f>
+        <v>794186.75</v>
       </c>
     </row>
     <row r="6"/>
@@ -3694,15 +3472,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
+      <c r="B9" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3711,15 +3489,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -3728,160 +3506,110 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>(Данные!$B$22+Данные!$C$22)*Данные!$B$9</f>
+        <v>84240</v>
+      </c>
+      <c r="C11" s="32">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D11" s="8">
+        <f>B11*C11</f>
+        <v>589680</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B12" s="32">
         <f>Данные!$D$22*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C12" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D11" s="8">
-        <f>B11*C11</f>
+      <c r="D12" s="8">
+        <f>B12*C12</f>
         <v>70560</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B13" s="32">
         <f>Данные!$D$22*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C13" s="32">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D12" s="8">
-        <f>B12*C12</f>
+      <c r="D13" s="8">
+        <f>B13*C13</f>
         <v>100800</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B14" s="32">
         <f>Данные!$G$22*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C14" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D13" s="8">
-        <f>B13*C13</f>
+      <c r="D14" s="8">
+        <f>B14*C14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B15" s="32">
         <f>Данные!$F$22*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C15" s="32">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="8">
-        <f>B14*C14</f>
+      <c r="D15" s="8">
+        <f>B15*C15</f>
         <v>33146.75</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>РАЗОВЫЕ ЗАТРАТЫ ШТАТА (СПРАВОЧНО)</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Цена в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Месяцев</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 1-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B18" s="33">
-        <f>Данные!$B$22*Данные!$B$9</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7">
-        <f>B18*C18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>Штат УКПФ · Приманочные станции 2-го контура — разовая закупка</t>
-        </is>
-      </c>
-      <c r="B19" s="33">
-        <f>Данные!$C$22*Данные!$B$9</f>
-        <v>84240</v>
-      </c>
-      <c r="C19" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7">
-        <f>B19*C19</f>
-        <v>84240</v>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+    <row r="16"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -3889,8 +3617,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3903,7 +3631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3944,17 +3672,17 @@
       <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
@@ -4006,7 +3734,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -4024,7 +3752,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ, ЗЕРНОЦИД И БРИКЕТЫ РАЗДЕЛЬНО</t>
+          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ И ЯДЫ РАЗДЕЛЬНО, ТОЛЬКО ТЁПЛЫЙ СЕЗОН ДЛЯ 1–2 КОНТУРА</t>
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
@@ -4035,49 +3763,61 @@
       <c r="G11" s="16" t="n"/>
       <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Станций 1–2 к., шт</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>Станции 1–2 к. за год, ₸</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="H12" s="35" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="36" t="inlineStr">
+      <c r="I12" s="35" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="J12" s="35" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="36" t="inlineStr">
+      <c r="K12" s="35" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -4089,37 +3829,45 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="51">
+      <c r="B13" s="49">
+        <f>Данные!$B$20+Данные!$C$20</f>
+        <v>29</v>
+      </c>
+      <c r="C13" s="7">
+        <f>B13*Данные!$B$9*Данные!$B$15</f>
+        <v>438480</v>
+      </c>
+      <c r="D13" s="49">
         <f>Данные!$D$20</f>
         <v>0</v>
       </c>
-      <c r="C13" s="51">
+      <c r="E13" s="49">
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
-      <c r="D13" s="7">
-        <f>B13*Данные!$B$8*Данные!$B$15+C13*Данные!$B$8*Данные!$B$16</f>
+      <c r="F13" s="7">
+        <f>D13*Данные!$B$8*Данные!$B$15+E13*Данные!$B$8*Данные!$B$16</f>
         <v>0</v>
       </c>
-      <c r="E13" s="52">
+      <c r="G13" s="50">
         <f>Данные!$G$20</f>
         <v>0</v>
       </c>
-      <c r="F13" s="7">
-        <f>E13*Данные!$B$6*Данные!$B$15</f>
+      <c r="H13" s="7">
+        <f>G13*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G13" s="52">
+      <c r="I13" s="50">
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
-      <c r="H13" s="7">
-        <f>G13*Данные!$B$7*Данные!$B$15</f>
+      <c r="J13" s="7">
+        <f>I13*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="I13" s="8">
-        <f>D13+F13+H13</f>
-        <v>25497.5</v>
+      <c r="K13" s="8">
+        <f>C13+F13+H13+J13</f>
+        <v>463977.5</v>
       </c>
     </row>
     <row r="14">
@@ -4128,37 +3876,45 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="51">
+      <c r="B14" s="49">
+        <f>SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30)</f>
+        <v>1257</v>
+      </c>
+      <c r="C14" s="7">
+        <f>B14*Данные!$B$9*Данные!$B$15</f>
+        <v>19005840</v>
+      </c>
+      <c r="D14" s="49">
         <f>SUM(Данные!$D$23:$D$30)</f>
         <v>268</v>
       </c>
-      <c r="C14" s="51">
+      <c r="E14" s="49">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
-      <c r="D14" s="7">
-        <f>B14*Данные!$B$8*Данные!$B$15+C14*Данные!$B$8*Данные!$B$16</f>
+      <c r="F14" s="7">
+        <f>D14*Данные!$B$8*Данные!$B$15+E14*Данные!$B$8*Данные!$B$16</f>
         <v>728960</v>
       </c>
-      <c r="E14" s="52">
+      <c r="G14" s="50">
         <f>SUM(Данные!$G$23:$G$30)</f>
         <v>15</v>
       </c>
-      <c r="F14" s="7">
-        <f>E14*Данные!$B$6*Данные!$B$15</f>
+      <c r="H14" s="7">
+        <f>G14*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
-      <c r="G14" s="52">
+      <c r="I14" s="50">
         <f>SUM(Данные!$F$23:$F$30)</f>
         <v>17</v>
       </c>
-      <c r="H14" s="7">
-        <f>G14*Данные!$B$7*Данные!$B$15</f>
+      <c r="J14" s="7">
+        <f>I14*Данные!$B$7*Данные!$B$15</f>
         <v>433457.5</v>
       </c>
-      <c r="I14" s="8">
-        <f>D14+F14+H14</f>
-        <v>1240117.5</v>
+      <c r="K14" s="8">
+        <f>C14+F14+H14+J14</f>
+        <v>20245957.5</v>
       </c>
     </row>
     <row r="15">
@@ -4167,37 +3923,45 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="51">
+      <c r="B15" s="49">
+        <f>Данные!$B$21+Данные!$C$21</f>
+        <v>52</v>
+      </c>
+      <c r="C15" s="7">
+        <f>B15*Данные!$B$9*Данные!$B$15</f>
+        <v>786240</v>
+      </c>
+      <c r="D15" s="49">
         <f>Данные!$D$21</f>
         <v>12</v>
       </c>
-      <c r="C15" s="51">
+      <c r="E15" s="49">
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
-      <c r="D15" s="7">
-        <f>B15*Данные!$B$8*Данные!$B$15+C15*Данные!$B$8*Данные!$B$16</f>
+      <c r="F15" s="7">
+        <f>D15*Данные!$B$8*Данные!$B$15+E15*Данные!$B$8*Данные!$B$16</f>
         <v>32640</v>
       </c>
-      <c r="E15" s="52">
+      <c r="G15" s="50">
         <f>Данные!$G$21</f>
         <v>1</v>
       </c>
-      <c r="F15" s="7">
-        <f>E15*Данные!$B$6*Данные!$B$15</f>
+      <c r="H15" s="7">
+        <f>G15*Данные!$B$6*Данные!$B$15</f>
         <v>5180</v>
       </c>
-      <c r="G15" s="52">
+      <c r="I15" s="50">
         <f>Данные!$F$21</f>
         <v>1</v>
       </c>
-      <c r="H15" s="7">
-        <f>G15*Данные!$B$7*Данные!$B$15</f>
+      <c r="J15" s="7">
+        <f>I15*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="I15" s="8">
-        <f>D15+F15+H15</f>
-        <v>63317.5</v>
+      <c r="K15" s="8">
+        <f>C15+F15+H15+J15</f>
+        <v>849557.5</v>
       </c>
     </row>
     <row r="16">
@@ -4206,37 +3970,45 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="51">
+      <c r="B16" s="49">
+        <f>Данные!$B$22+Данные!$C$22</f>
+        <v>39</v>
+      </c>
+      <c r="C16" s="7">
+        <f>B16*Данные!$B$9*Данные!$B$15</f>
+        <v>589680</v>
+      </c>
+      <c r="D16" s="49">
         <f>Данные!$D$22</f>
         <v>63</v>
       </c>
-      <c r="C16" s="51">
+      <c r="E16" s="49">
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
-      <c r="D16" s="7">
-        <f>B16*Данные!$B$8*Данные!$B$15+C16*Данные!$B$8*Данные!$B$16</f>
+      <c r="F16" s="7">
+        <f>D16*Данные!$B$8*Данные!$B$15+E16*Данные!$B$8*Данные!$B$16</f>
         <v>171360</v>
       </c>
-      <c r="E16" s="52">
+      <c r="G16" s="50">
         <f>Данные!$G$22</f>
         <v>0</v>
       </c>
-      <c r="F16" s="7">
-        <f>E16*Данные!$B$6*Данные!$B$15</f>
+      <c r="H16" s="7">
+        <f>G16*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G16" s="52">
+      <c r="I16" s="50">
         <f>Данные!$F$22</f>
         <v>1.3</v>
       </c>
-      <c r="H16" s="7">
-        <f>G16*Данные!$B$7*Данные!$B$15</f>
+      <c r="J16" s="7">
+        <f>I16*Данные!$B$7*Данные!$B$15</f>
         <v>33146.75</v>
       </c>
-      <c r="I16" s="8">
-        <f>D16+F16+H16</f>
-        <v>204506.75</v>
+      <c r="K16" s="8">
+        <f>C16+F16+H16+J16</f>
+        <v>794186.75</v>
       </c>
     </row>
     <row r="17">
@@ -4252,7 +4024,9 @@
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="8">
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="8">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
@@ -4264,37 +4038,42 @@
         </is>
       </c>
       <c r="B18" s="23" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="12">
-        <f>SUM(D13:D17)</f>
-        <v>932960</v>
-      </c>
-      <c r="E18" s="53">
-        <f>SUM(E13:E17)</f>
-        <v>16</v>
-      </c>
+      <c r="C18" s="12">
+        <f>SUM(C13:C17)</f>
+        <v>20820240</v>
+      </c>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
       <c r="F18" s="12">
         <f>SUM(F13:F17)</f>
-        <v>82880</v>
-      </c>
-      <c r="G18" s="53">
+        <v>932960</v>
+      </c>
+      <c r="G18" s="51">
         <f>SUM(G13:G17)</f>
-        <v>20.3</v>
+        <v>16</v>
       </c>
       <c r="H18" s="12">
         <f>SUM(H13:H17)</f>
+        <v>82880</v>
+      </c>
+      <c r="I18" s="51">
+        <f>SUM(I13:I17)</f>
+        <v>20.3</v>
+      </c>
+      <c r="J18" s="12">
+        <f>SUM(J13:J17)</f>
         <v>517599.25</v>
       </c>
-      <c r="I18" s="12">
-        <f>SUM(I13:I17)</f>
-        <v>1552479.25</v>
+      <c r="K18" s="12">
+        <f>SUM(K13:K17)</f>
+        <v>22372719.25</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>РАЗОВАЯ ЗАКУПКА ПРИМАНОЧНЫХ СТАНЦИЙ</t>
+          <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
         </is>
       </c>
       <c r="B20" s="16" t="n"/>
@@ -4304,442 +4083,265 @@
       <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>1-й контур, шт</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>2-й контур, шт</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>Всего, шт</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>Цена, ₸/шт</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>Разово, ₸</t>
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>Численность, чел.</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>ЗП в месяц, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>ЗП за год, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>Материалы за год, ₸</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Итого за год, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>ККЗ · кормоцех</t>
-        </is>
-      </c>
-      <c r="B22" s="51">
-        <f>Данные!$B$20</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="51">
-        <f>Данные!$C$20</f>
-        <v>29</v>
-      </c>
-      <c r="D22" s="51">
-        <f>B22+C22</f>
-        <v>29</v>
-      </c>
-      <c r="E22" s="33">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
+      <c r="A22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7">
+        <f>A22*Данные!$B$12</f>
+        <v>516976</v>
+      </c>
+      <c r="C22" s="7">
+        <f>B22*12</f>
+        <v>6203712</v>
+      </c>
+      <c r="D22" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E22" s="8">
+        <f>C22+D22</f>
+        <v>28576431.25</v>
       </c>
       <c r="F22" s="8">
-        <f>D22*E22</f>
-        <v>62640</v>
+        <f>A22*Данные!$B$13*12+D22</f>
+        <v>30772719.25</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Бройлерные площадки · 8 шт</t>
-        </is>
-      </c>
-      <c r="B23" s="51">
-        <f>SUM(Данные!$B$23:$B$30)</f>
-        <v>161</v>
-      </c>
-      <c r="C23" s="51">
-        <f>SUM(Данные!$C$23:$C$30)</f>
-        <v>1096</v>
-      </c>
-      <c r="D23" s="51">
-        <f>B23+C23</f>
-        <v>1257</v>
-      </c>
-      <c r="E23" s="33">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
+      <c r="A23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7">
+        <f>A23*Данные!$B$12</f>
+        <v>775464</v>
+      </c>
+      <c r="C23" s="7">
+        <f>B23*12</f>
+        <v>9305568</v>
+      </c>
+      <c r="D23" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E23" s="8">
+        <f>C23+D23</f>
+        <v>31678287.25</v>
       </c>
       <c r="F23" s="8">
-        <f>D23*E23</f>
-        <v>2715120</v>
+        <f>A23*Данные!$B$13*12+D23</f>
+        <v>34972719.25</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Инкубаторий</t>
-        </is>
-      </c>
-      <c r="B24" s="51">
-        <f>Данные!$B$21</f>
-        <v>18</v>
-      </c>
-      <c r="C24" s="51">
-        <f>Данные!$C$21</f>
-        <v>34</v>
-      </c>
-      <c r="D24" s="51">
-        <f>B24+C24</f>
-        <v>52</v>
-      </c>
-      <c r="E24" s="33">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
+      <c r="A24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="7">
+        <f>A24*Данные!$B$12</f>
+        <v>1033952</v>
+      </c>
+      <c r="C24" s="7">
+        <f>B24*12</f>
+        <v>12407424</v>
+      </c>
+      <c r="D24" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E24" s="8">
+        <f>C24+D24</f>
+        <v>34780143.25</v>
       </c>
       <c r="F24" s="8">
-        <f>D24*E24</f>
-        <v>112320</v>
+        <f>A24*Данные!$B$13*12+D24</f>
+        <v>39172719.25</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>АБК · 11 корпусов</t>
-        </is>
-      </c>
-      <c r="B25" s="51">
-        <f>Данные!$B$22</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="51">
-        <f>Данные!$C$22</f>
-        <v>39</v>
-      </c>
-      <c r="D25" s="51">
-        <f>B25+C25</f>
-        <v>39</v>
-      </c>
-      <c r="E25" s="33">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
+      <c r="A25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="7">
+        <f>A25*Данные!$B$12</f>
+        <v>1292440</v>
+      </c>
+      <c r="C25" s="7">
+        <f>B25*12</f>
+        <v>15509280</v>
+      </c>
+      <c r="D25" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E25" s="8">
+        <f>C25+D25</f>
+        <v>37881999.25</v>
       </c>
       <c r="F25" s="8">
-        <f>D25*E25</f>
-        <v>84240</v>
+        <f>A25*Данные!$B$13*12+D25</f>
+        <v>43372719.25</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО РАЗОВО</t>
-        </is>
-      </c>
-      <c r="B26" s="54">
-        <f>SUM(B22:B25)</f>
-        <v>179</v>
-      </c>
-      <c r="C26" s="54">
-        <f>SUM(C22:C25)</f>
-        <v>1198</v>
-      </c>
-      <c r="D26" s="54">
-        <f>SUM(D22:D25)</f>
-        <v>1377</v>
-      </c>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="12">
-        <f>SUM(F22:F25)</f>
-        <v>2974320</v>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="7">
+        <f>A26*Данные!$B$12</f>
+        <v>1550928</v>
+      </c>
+      <c r="C26" s="7">
+        <f>B26*12</f>
+        <v>18611136</v>
+      </c>
+      <c r="D26" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E26" s="8">
+        <f>C26+D26</f>
+        <v>40983855.25</v>
+      </c>
+      <c r="F26" s="8">
+        <f>A26*Данные!$B$13*12+D26</f>
+        <v>47572719.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="7">
+        <f>A27*Данные!$B$12</f>
+        <v>1809416</v>
+      </c>
+      <c r="C27" s="7">
+        <f>B27*12</f>
+        <v>21712992</v>
+      </c>
+      <c r="D27" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E27" s="8">
+        <f>C27+D27</f>
+        <v>44085711.25</v>
+      </c>
+      <c r="F27" s="8">
+        <f>A27*Данные!$B$13*12+D27</f>
+        <v>51772719.25</v>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="A28" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="7">
+        <f>A28*Данные!$B$12</f>
+        <v>2067904</v>
+      </c>
+      <c r="C28" s="7">
+        <f>B28*12</f>
+        <v>24814848</v>
+      </c>
+      <c r="D28" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E28" s="8">
+        <f>C28+D28</f>
+        <v>47187567.25</v>
+      </c>
+      <c r="F28" s="8">
+        <f>A28*Данные!$B$13*12+D28</f>
+        <v>55972719.25</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
-        <is>
-          <t>Численность, чел.</t>
-        </is>
-      </c>
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>ЗП в месяц, ₸ · оклад 258 488</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="inlineStr">
-        <is>
-          <t>ЗП за год, ₸ · оклад 258 488</t>
-        </is>
-      </c>
-      <c r="D29" s="36" t="inlineStr">
-        <is>
-          <t>Материалы за год, ₸</t>
-        </is>
-      </c>
-      <c r="E29" s="36" t="inlineStr">
-        <is>
-          <t>Итого за год, ₸ · оклад 258 488</t>
-        </is>
-      </c>
-      <c r="F29" s="36" t="inlineStr">
-        <is>
-          <t>Итого за год, ₸ · оклад 350 000</t>
-        </is>
+      <c r="A29" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <f>A29*Данные!$B$12</f>
+        <v>2326392</v>
+      </c>
+      <c r="C29" s="7">
+        <f>B29*12</f>
+        <v>27916704</v>
+      </c>
+      <c r="D29" s="7">
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="E29" s="8">
+        <f>C29+D29</f>
+        <v>50289423.25</v>
+      </c>
+      <c r="F29" s="8">
+        <f>A29*Данные!$B$13*12+D29</f>
+        <v>60172719.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B30" s="7">
         <f>A30*Данные!$B$12</f>
-        <v>516976</v>
+        <v>2584880</v>
       </c>
       <c r="C30" s="7">
         <f>B30*12</f>
-        <v>6203712</v>
+        <v>31018560</v>
       </c>
       <c r="D30" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
+        <f>'Штат УКПФ'!$K$18</f>
+        <v>22372719.25</v>
       </c>
       <c r="E30" s="8">
         <f>C30+D30</f>
-        <v>7756191.25</v>
+        <v>53391279.25</v>
       </c>
       <c r="F30" s="8">
         <f>A30*Данные!$B$13*12+D30</f>
-        <v>9952479.25</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="7">
-        <f>A31*Данные!$B$12</f>
-        <v>775464</v>
-      </c>
-      <c r="C31" s="7">
-        <f>B31*12</f>
-        <v>9305568</v>
-      </c>
-      <c r="D31" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E31" s="8">
-        <f>C31+D31</f>
-        <v>10858047.25</v>
-      </c>
-      <c r="F31" s="8">
-        <f>A31*Данные!$B$13*12+D31</f>
-        <v>14152479.25</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B32" s="7">
-        <f>A32*Данные!$B$12</f>
-        <v>1033952</v>
-      </c>
-      <c r="C32" s="7">
-        <f>B32*12</f>
-        <v>12407424</v>
-      </c>
-      <c r="D32" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E32" s="8">
-        <f>C32+D32</f>
-        <v>13959903.25</v>
-      </c>
-      <c r="F32" s="8">
-        <f>A32*Данные!$B$13*12+D32</f>
-        <v>18352479.25</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="7">
-        <f>A33*Данные!$B$12</f>
-        <v>1292440</v>
-      </c>
-      <c r="C33" s="7">
-        <f>B33*12</f>
-        <v>15509280</v>
-      </c>
-      <c r="D33" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E33" s="8">
-        <f>C33+D33</f>
-        <v>17061759.25</v>
-      </c>
-      <c r="F33" s="8">
-        <f>A33*Данные!$B$13*12+D33</f>
-        <v>22552479.25</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="7">
-        <f>A34*Данные!$B$12</f>
-        <v>1550928</v>
-      </c>
-      <c r="C34" s="7">
-        <f>B34*12</f>
-        <v>18611136</v>
-      </c>
-      <c r="D34" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E34" s="8">
-        <f>C34+D34</f>
-        <v>20163615.25</v>
-      </c>
-      <c r="F34" s="8">
-        <f>A34*Данные!$B$13*12+D34</f>
-        <v>26752479.25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B35" s="7">
-        <f>A35*Данные!$B$12</f>
-        <v>1809416</v>
-      </c>
-      <c r="C35" s="7">
-        <f>B35*12</f>
-        <v>21712992</v>
-      </c>
-      <c r="D35" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E35" s="8">
-        <f>C35+D35</f>
-        <v>23265471.25</v>
-      </c>
-      <c r="F35" s="8">
-        <f>A35*Данные!$B$13*12+D35</f>
-        <v>30952479.25</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B36" s="7">
-        <f>A36*Данные!$B$12</f>
-        <v>2067904</v>
-      </c>
-      <c r="C36" s="7">
-        <f>B36*12</f>
-        <v>24814848</v>
-      </c>
-      <c r="D36" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E36" s="8">
-        <f>C36+D36</f>
-        <v>26367327.25</v>
-      </c>
-      <c r="F36" s="8">
-        <f>A36*Данные!$B$13*12+D36</f>
-        <v>35152479.25</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B37" s="7">
-        <f>A37*Данные!$B$12</f>
-        <v>2326392</v>
-      </c>
-      <c r="C37" s="7">
-        <f>B37*12</f>
-        <v>27916704</v>
-      </c>
-      <c r="D37" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E37" s="8">
-        <f>C37+D37</f>
-        <v>29469183.25</v>
-      </c>
-      <c r="F37" s="8">
-        <f>A37*Данные!$B$13*12+D37</f>
-        <v>39352479.25</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B38" s="7">
-        <f>A38*Данные!$B$12</f>
-        <v>2584880</v>
-      </c>
-      <c r="C38" s="7">
-        <f>B38*12</f>
-        <v>31018560</v>
-      </c>
-      <c r="D38" s="7">
-        <f>'Штат УКПФ'!$I$18</f>
-        <v>1552479.25</v>
-      </c>
-      <c r="E38" s="8">
-        <f>C38+D38</f>
-        <v>32571039.25</v>
-      </c>
-      <c r="F38" s="8">
-        <f>A38*Данные!$B$13*12+D38</f>
-        <v>43552479.25</v>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
+        <v>64372719.25</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -4748,7 +4350,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4803,26 +4405,26 @@
       <c r="H4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr"/>
-      <c r="E5" s="27" t="inlineStr"/>
-      <c r="F5" s="27" t="inlineStr"/>
-      <c r="G5" s="27" t="inlineStr"/>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr"/>
+      <c r="E5" s="26" t="inlineStr"/>
+      <c r="F5" s="26" t="inlineStr"/>
+      <c r="G5" s="26" t="inlineStr"/>
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
@@ -4834,7 +4436,7 @@
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="39" t="n">
         <v>740</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4842,7 +4444,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="42" t="inlineStr">
+      <c r="H6" s="40" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -4854,7 +4456,7 @@
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n">
+      <c r="B7" s="39" t="n">
         <v>3642.5</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4862,7 +4464,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="42" t="inlineStr">
+      <c r="H7" s="40" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
@@ -4874,7 +4476,7 @@
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="39" t="n">
         <v>160</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -4882,7 +4484,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="42" t="inlineStr">
+      <c r="H8" s="40" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
@@ -4894,17 +4496,17 @@
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="39" t="n">
         <v>2160</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>₸/шт</t>
-        </is>
-      </c>
-      <c r="H9" s="42" t="inlineStr">
-        <is>
-          <t>разовая закупка; цена из прежнего расчёта по ККЗ (29 шт = 62 640 ₸)</t>
+          <t>₸/шт/мес</t>
+        </is>
+      </c>
+      <c r="H9" s="40" t="inlineStr">
+        <is>
+          <t>ежемесячный платёж за станцию, только тёплый сезон; цена из прежнего расчёта по ККЗ</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4516,7 @@
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="39" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4922,7 +4524,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="42" t="inlineStr">
+      <c r="H10" s="40" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -4934,7 +4536,7 @@
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="41" t="n">
+      <c r="B11" s="39" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4942,7 +4544,7 @@
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="H11" s="42" t="inlineStr">
+      <c r="H11" s="40" t="inlineStr">
         <is>
           <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
         </is>
@@ -4954,7 +4556,7 @@
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="41" t="n">
+      <c r="B12" s="39" t="n">
         <v>258488</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4962,7 +4564,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="42" t="inlineStr">
+      <c r="H12" s="40" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
@@ -4974,7 +4576,7 @@
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="41" t="n">
+      <c r="B13" s="39" t="n">
         <v>350000</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4982,7 +4584,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H13" s="42" t="inlineStr">
+      <c r="H13" s="40" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
@@ -4994,7 +4596,7 @@
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n">
+      <c r="B14" s="39" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -5002,7 +4604,7 @@
           <t>чел.</t>
         </is>
       </c>
-      <c r="H14" s="42" t="inlineStr">
+      <c r="H14" s="40" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
@@ -5014,7 +4616,7 @@
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="41" t="n">
+      <c r="B15" s="39" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -5022,7 +4624,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="42" t="inlineStr">
+      <c r="H15" s="40" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
@@ -5034,7 +4636,7 @@
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="41" t="n">
+      <c r="B16" s="39" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5042,7 +4644,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H16" s="42" t="inlineStr">
+      <c r="H16" s="40" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
@@ -5064,42 +4666,42 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="36" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="36" t="inlineStr">
+      <c r="G19" s="35" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="36" t="inlineStr">
+      <c r="H19" s="35" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -5111,26 +4713,26 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="41" t="n">
+      <c r="B20" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="39" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="41" t="n">
+      <c r="D20" s="39" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="55" t="n">
+      <c r="F20" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="55" t="n">
+      <c r="G20" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="42" t="inlineStr">
+      <c r="H20" s="40" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
@@ -5142,26 +4744,26 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="41" t="n">
+      <c r="B21" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="41" t="n">
+      <c r="C21" s="39" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="41" t="n">
+      <c r="D21" s="39" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
         <v>18</v>
       </c>
-      <c r="F21" s="55" t="n">
+      <c r="F21" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="55" t="n">
+      <c r="G21" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="42" t="inlineStr"/>
+      <c r="H21" s="40" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5169,26 +4771,26 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="41" t="n">
+      <c r="B22" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="41" t="n">
+      <c r="C22" s="39" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="41" t="n">
+      <c r="D22" s="39" t="n">
         <v>63</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="55" t="n">
+      <c r="F22" s="52" t="n">
         <v>1.3</v>
       </c>
-      <c r="G22" s="55" t="n">
+      <c r="G22" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="42" t="inlineStr">
+      <c r="H22" s="40" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
@@ -5200,26 +4802,26 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="41" t="n">
+      <c r="B23" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="39" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="39" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
         <v>13</v>
       </c>
-      <c r="F23" s="55" t="n">
+      <c r="F23" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="55" t="n">
+      <c r="G23" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="42" t="inlineStr"/>
+      <c r="H23" s="40" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5227,26 +4829,26 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="41" t="n">
+      <c r="B24" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C24" s="39" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D24" s="39" t="n">
         <v>20</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
         <v>17</v>
       </c>
-      <c r="F24" s="55" t="n">
+      <c r="F24" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="55" t="n">
+      <c r="G24" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="42" t="inlineStr"/>
+      <c r="H24" s="40" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5254,26 +4856,26 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="41" t="n">
+      <c r="B25" s="39" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="41" t="n">
+      <c r="C25" s="39" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="39" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
         <v>50</v>
       </c>
-      <c r="F25" s="55" t="n">
+      <c r="F25" s="52" t="n">
         <v>3.5</v>
       </c>
-      <c r="G25" s="55" t="n">
+      <c r="G25" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="42" t="inlineStr"/>
+      <c r="H25" s="40" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5281,26 +4883,26 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="41" t="n">
+      <c r="B26" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="41" t="n">
+      <c r="C26" s="39" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="39" t="n">
         <v>80</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
         <v>17</v>
       </c>
-      <c r="F26" s="55" t="n">
+      <c r="F26" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="55" t="n">
+      <c r="G26" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="42" t="inlineStr"/>
+      <c r="H26" s="40" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5308,26 +4910,26 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="41" t="n">
+      <c r="B27" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="41" t="n">
+      <c r="C27" s="39" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="41" t="n">
+      <c r="D27" s="39" t="n">
         <v>64</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
         <v>15</v>
       </c>
-      <c r="F27" s="55" t="n">
+      <c r="F27" s="52" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="55" t="n">
+      <c r="G27" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="42" t="inlineStr"/>
+      <c r="H27" s="40" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5335,26 +4937,26 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="41" t="n">
+      <c r="B28" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="41" t="n">
+      <c r="C28" s="39" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="41" t="n">
+      <c r="D28" s="39" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
         <v>13</v>
       </c>
-      <c r="F28" s="55" t="n">
+      <c r="F28" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="55" t="n">
+      <c r="G28" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="42" t="inlineStr"/>
+      <c r="H28" s="40" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5362,26 +4964,26 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="41" t="n">
+      <c r="B29" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="41" t="n">
+      <c r="C29" s="39" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="41" t="n">
+      <c r="D29" s="39" t="n">
         <v>10</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
         <v>17</v>
       </c>
-      <c r="F29" s="55" t="n">
+      <c r="F29" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="55" t="n">
+      <c r="G29" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="42" t="inlineStr"/>
+      <c r="H29" s="40" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5389,26 +4991,26 @@
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n">
+      <c r="B30" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="41" t="n">
+      <c r="C30" s="39" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="41" t="n">
+      <c r="D30" s="39" t="n">
         <v>24</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
         <v>19</v>
       </c>
-      <c r="F30" s="55" t="n">
+      <c r="F30" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="55" t="n">
+      <c r="G30" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="42" t="inlineStr"/>
+      <c r="H30" s="40" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5420,9 +5022,9 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="52" t="n"/>
-      <c r="G31" s="52" t="n"/>
-      <c r="H31" s="42" t="inlineStr">
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="50" t="n"/>
+      <c r="H31" s="40" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5438,9 +5040,9 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="52" t="n"/>
-      <c r="G32" s="52" t="n"/>
-      <c r="H32" s="42" t="inlineStr">
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="50" t="n"/>
+      <c r="H32" s="40" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5468,11 +5070,11 @@
         <f>SUM(E20:E32)</f>
         <v>179</v>
       </c>
-      <c r="F33" s="53">
+      <c r="F33" s="51">
         <f>SUM(F20:F32)</f>
         <v>20.3</v>
       </c>
-      <c r="G33" s="53">
+      <c r="G33" s="51">
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
@@ -5494,26 +5096,26 @@
       <c r="H35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr"/>
-      <c r="E36" s="27" t="inlineStr"/>
-      <c r="F36" s="27" t="inlineStr"/>
-      <c r="G36" s="27" t="inlineStr"/>
-      <c r="H36" s="27" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr"/>
+      <c r="E36" s="26" t="inlineStr"/>
+      <c r="F36" s="26" t="inlineStr"/>
+      <c r="G36" s="26" t="inlineStr"/>
+      <c r="H36" s="26" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
@@ -5525,7 +5127,7 @@
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="41" t="n">
+      <c r="B37" s="39" t="n">
         <v>96600</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5533,7 +5135,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="42" t="inlineStr">
+      <c r="H37" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
@@ -5545,7 +5147,7 @@
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="41" t="n">
+      <c r="B38" s="39" t="n">
         <v>618400</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -5553,7 +5155,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="42" t="inlineStr">
+      <c r="H38" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
@@ -5565,7 +5167,7 @@
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="41" t="n">
+      <c r="B39" s="39" t="n">
         <v>478400</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -5573,7 +5175,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="42" t="inlineStr">
+      <c r="H39" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5585,7 +5187,7 @@
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="41" t="n">
+      <c r="B40" s="39" t="n">
         <v>569800</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -5593,7 +5195,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="42" t="inlineStr">
+      <c r="H40" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
@@ -5605,7 +5207,7 @@
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="41" t="n">
+      <c r="B41" s="39" t="n">
         <v>440700</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -5613,7 +5215,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="42" t="inlineStr">
+      <c r="H41" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5625,7 +5227,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="41" t="n">
+      <c r="B42" s="39" t="n">
         <v>2599100</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -5633,7 +5235,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="42" t="inlineStr">
+      <c r="H42" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
@@ -5645,7 +5247,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="41" t="n">
+      <c r="B43" s="39" t="n">
         <v>2010300</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -5653,7 +5255,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="42" t="inlineStr">
+      <c r="H43" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5665,7 +5267,7 @@
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="41" t="n">
+      <c r="B44" s="39" t="n">
         <v>126200</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5673,7 +5275,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="42" t="inlineStr">
+      <c r="H44" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
@@ -5685,7 +5287,7 @@
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="41" t="n">
+      <c r="B45" s="39" t="n">
         <v>106800</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -5693,7 +5295,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="42" t="inlineStr">
+      <c r="H45" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5705,7 +5307,7 @@
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="41" t="n">
+      <c r="B46" s="39" t="n">
         <v>126200</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -5713,7 +5315,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="42" t="inlineStr">
+      <c r="H46" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5725,7 +5327,7 @@
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="41" t="n">
+      <c r="B47" s="39" t="n">
         <v>106800</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -5733,7 +5335,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="42" t="inlineStr">
+      <c r="H47" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5745,7 +5347,7 @@
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="41" t="n">
+      <c r="B48" s="39" t="n">
         <v>720000</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -5753,7 +5355,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="42" t="inlineStr">
+      <c r="H48" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5765,7 +5367,7 @@
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="41" t="n">
+      <c r="B49" s="39" t="n">
         <v>1080000</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -5773,7 +5375,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="42" t="inlineStr">
+      <c r="H49" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5785,7 +5387,7 @@
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="41" t="n">
+      <c r="B50" s="39" t="n">
         <v>3000000</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -5793,7 +5395,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="42" t="inlineStr">
+      <c r="H50" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5805,7 +5407,7 @@
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="41" t="n">
+      <c r="B51" s="39" t="n">
         <v>100800</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -5813,7 +5415,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="42" t="inlineStr">
+      <c r="H51" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5825,7 +5427,7 @@
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="41" t="n">
+      <c r="B52" s="39" t="n">
         <v>160800</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -5833,7 +5435,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="42" t="inlineStr">
+      <c r="H52" s="40" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5845,7 +5447,7 @@
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="41" t="n">
+      <c r="B53" s="39" t="n">
         <v>75000</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -5853,7 +5455,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="42" t="inlineStr">
+      <c r="H53" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5865,7 +5467,7 @@
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="41" t="n">
+      <c r="B54" s="39" t="n">
         <v>70000</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -5873,7 +5475,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="42" t="inlineStr">
+      <c r="H54" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5885,7 +5487,7 @@
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="41" t="n">
+      <c r="B55" s="39" t="n">
         <v>3172000</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -5893,7 +5495,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="42" t="inlineStr">
+      <c r="H55" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -5905,7 +5507,7 @@
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="41" t="n">
+      <c r="B56" s="39" t="n">
         <v>2074000</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -5913,7 +5515,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="42" t="inlineStr">
+      <c r="H56" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -5925,7 +5527,7 @@
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="41" t="n">
+      <c r="B57" s="39" t="n">
         <v>2806000</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -5933,7 +5535,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="42" t="inlineStr">
+      <c r="H57" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -5945,7 +5547,7 @@
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="41" t="n">
+      <c r="B58" s="39" t="n">
         <v>1830000</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -5953,7 +5555,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="42" t="inlineStr">
+      <c r="H58" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -5965,7 +5567,7 @@
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="41" t="n">
+      <c r="B59" s="39" t="n">
         <v>180000</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -5973,7 +5575,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="42" t="inlineStr">
+      <c r="H59" s="40" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
@@ -5985,7 +5587,7 @@
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="41" t="n">
+      <c r="B60" s="39" t="n">
         <v>80000</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -5993,7 +5595,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="42" t="inlineStr">
+      <c r="H60" s="40" t="inlineStr">
         <is>
           <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
@@ -6005,7 +5607,7 @@
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="41" t="n">
+      <c r="B61" s="39" t="n">
         <v>9</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -6013,7 +5615,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H61" s="42" t="inlineStr">
+      <c r="H61" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6025,7 +5627,7 @@
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="41" t="n">
+      <c r="B62" s="39" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -6033,7 +5635,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H62" s="42" t="inlineStr">
+      <c r="H62" s="40" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6045,7 +5647,7 @@
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="41" t="n">
+      <c r="B63" s="39" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -6053,7 +5655,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H63" s="42" t="inlineStr">
+      <c r="H63" s="40" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
@@ -6065,7 +5667,7 @@
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B64" s="56" t="n">
+      <c r="B64" s="53" t="n">
         <v>0.15</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -6073,7 +5675,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H64" s="42" t="inlineStr">
+      <c r="H64" s="40" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
@@ -6085,7 +5687,7 @@
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B65" s="56" t="n">
+      <c r="B65" s="53" t="n">
         <v>0.15</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -6093,7 +5695,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="42" t="inlineStr">
+      <c r="H65" s="40" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
@@ -6105,7 +5707,7 @@
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B66" s="56" t="n">
+      <c r="B66" s="53" t="n">
         <v>0.16</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -6113,7 +5715,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H66" s="42" t="inlineStr">
+      <c r="H66" s="40" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -260,6 +260,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -276,6 +285,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -672,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -722,7 +737,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="n"/>
+      <c r="A5" s="48" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>в месяц</t>
@@ -835,7 +850,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n"/>
+      <c r="E8" s="49" t="n"/>
       <c r="F8" s="7">
         <f>G8/12</f>
         <v>70796.45833</v>
@@ -872,7 +887,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G9" s="44" t="n"/>
+      <c r="G9" s="49" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -885,7 +900,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="44" t="n"/>
+      <c r="C10" s="49" t="n"/>
       <c r="D10" s="7">
         <f>E10/12</f>
         <v>60000</v>
@@ -899,7 +914,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G10" s="44" t="n"/>
+      <c r="G10" s="49" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -912,13 +927,13 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n"/>
+      <c r="C11" s="49" t="n"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E11" s="44" t="n"/>
+      <c r="E11" s="49" t="n"/>
       <c r="F11" s="7">
         <f>G11/12</f>
         <v>66182.22917</v>
@@ -1078,7 +1093,7 @@
         <f>C15-G15</f>
         <v>14855456.75</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="50">
         <f>IF(G15=0,0,C15/G15)</f>
         <v>1.427124657</v>
       </c>
@@ -1097,7 +1112,7 @@
         <f>E15-G15</f>
         <v>3769856.75</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="50">
         <f>IF(G15=0,0,E15/G15)</f>
         <v>1.108391064</v>
       </c>
@@ -1379,7 +1394,7 @@
           <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
         </is>
       </c>
-      <c r="B33" s="46">
+      <c r="B33" s="51">
         <f>Данные!$F$33/Данные!$C$33</f>
         <v>0.01694490818</v>
       </c>
@@ -1449,7 +1464,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+          <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 4 ДЕРАТИЗАТОРА</t>
         </is>
       </c>
       <c r="B38" s="16" t="n"/>
@@ -1462,292 +1477,409 @@
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>Условие</t>
+          <t>Показатель</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>в месяц</t>
+          <t>2 дератизатора</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Ставка</t>
+          <t>4 дератизатора</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Оклад одного, ₸/мес</t>
+        </is>
+      </c>
+      <c r="B40" s="25">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+      <c r="C40" s="25">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ФОТ в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="B41" s="25">
+        <f>2*Данные!$B$12</f>
+        <v>516976</v>
+      </c>
+      <c r="C41" s="25">
+        <f>4*Данные!$B$12</f>
+        <v>1033952</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>ФОТ за год, ₸</t>
+        </is>
+      </c>
+      <c r="B42" s="25">
+        <f>2*Данные!$B$12*12</f>
+        <v>6203712</v>
+      </c>
+      <c r="C42" s="25">
+        <f>4*Данные!$B$12*12</f>
+        <v>12407424</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Материалы за год, ₸ (не зависят от численности)</t>
+        </is>
+      </c>
+      <c r="B43" s="25">
+        <f>(F35-F26)</f>
+        <v>22372719.25</v>
+      </c>
+      <c r="C43" s="25">
+        <f>(F35-F26)</f>
+        <v>22372719.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО ЗА ГОД, ₸</t>
+        </is>
+      </c>
+      <c r="B44" s="26">
+        <f>B42+B43</f>
+        <v>28576431.25</v>
+      </c>
+      <c r="C44" s="26">
+        <f>C42+C43</f>
+        <v>34780143.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Разница 4 против 2 чел., ₸/год</t>
+        </is>
+      </c>
+      <c r="C45" s="27">
+        <f>C44-B44</f>
+        <v>6203712</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="16" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>Цена КП без скидок</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>C40/12</f>
+      <c r="B49" s="7">
+        <f>C49/12</f>
         <v>4136300</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C49" s="8">
         <f>C15</f>
         <v>49635600</v>
       </c>
-      <c r="D40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="D49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B41" s="7">
-        <f>C41/12</f>
+      <c r="B50" s="7">
+        <f>C50/12</f>
         <v>3515855</v>
       </c>
-      <c r="C41" s="8">
+      <c r="C50" s="8">
         <f>C15*(1-Данные!$B$64)</f>
         <v>42190260</v>
       </c>
-      <c r="D41" s="47">
+      <c r="D50" s="52">
         <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>C42/12</f>
+      <c r="B51" s="7">
+        <f>C51/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="C42" s="8">
+      <c r="C51" s="8">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
         <v>35861721</v>
       </c>
-      <c r="D42" s="47">
+      <c r="D51" s="52">
         <f>Данные!$B$65</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
-      <c r="B43" s="7">
-        <f>C43/12</f>
+      <c r="B52" s="7">
+        <f>C52/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C52" s="8">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D43" s="47">
+      <c r="D52" s="52">
         <f>Данные!$B$66</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="16" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="16" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C55" s="29" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D46" s="26" t="inlineStr">
+      <c r="D55" s="29" t="inlineStr">
         <is>
           <t>Что зафиксировано в документах</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C47" s="21" t="inlineStr">
+      <c r="C56" s="21" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D47" s="27" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
         </is>
       </c>
-      <c r="E47" s="48" t="n"/>
-      <c r="F47" s="48" t="n"/>
-      <c r="G47" s="44" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="E56" s="53" t="n"/>
+      <c r="F56" s="53" t="n"/>
+      <c r="G56" s="49" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C57" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="27" t="inlineStr">
+      <c r="D57" s="30" t="inlineStr">
         <is>
           <t>выезд по запросу</t>
         </is>
       </c>
-      <c r="E48" s="48" t="n"/>
-      <c r="F48" s="48" t="n"/>
-      <c r="G48" s="44" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="E57" s="53" t="n"/>
+      <c r="F57" s="53" t="n"/>
+      <c r="G57" s="49" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>бройлерные площадки</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C58" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="27" t="inlineStr">
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>дополнительные визиты по вызову</t>
         </is>
       </c>
-      <c r="E49" s="48" t="n"/>
-      <c r="F49" s="48" t="n"/>
-      <c r="G49" s="44" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="E58" s="53" t="n"/>
+      <c r="F58" s="53" t="n"/>
+      <c r="G58" s="49" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n">
+      <c r="C59" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D50" s="27" t="inlineStr">
+      <c r="D59" s="30" t="inlineStr">
         <is>
           <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
-      <c r="E50" s="48" t="n"/>
-      <c r="F50" s="48" t="n"/>
-      <c r="G50" s="44" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="E59" s="53" t="n"/>
+      <c r="F59" s="53" t="n"/>
+      <c r="G59" s="49" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>склад ТМЦ</t>
         </is>
       </c>
-      <c r="C51" s="21" t="n">
+      <c r="C60" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="27" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>выезд по рекламации за два рабочих дня</t>
         </is>
       </c>
-      <c r="E51" s="48" t="n"/>
-      <c r="F51" s="48" t="n"/>
-      <c r="G51" s="44" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="E60" s="53" t="n"/>
+      <c r="F60" s="53" t="n"/>
+      <c r="G60" s="49" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C52" s="21" t="n">
+      <c r="C61" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D52" s="27" t="inlineStr">
+      <c r="D61" s="30" t="inlineStr">
         <is>
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
-      <c r="E52" s="48" t="n"/>
-      <c r="F52" s="48" t="n"/>
-      <c r="G52" s="44" t="n"/>
+      <c r="E61" s="53" t="n"/>
+      <c r="F61" s="53" t="n"/>
+      <c r="G61" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="D56:G56"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D61:G61"/>
+    <mergeCell ref="D59:G59"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="D58:G58"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D60:G60"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D57:G57"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="F9:G9"/>
   </mergeCells>
@@ -1786,37 +1918,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15</f>
         <v>463977.5</v>
       </c>
@@ -1855,16 +1987,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="35">
         <f>Данные!$B$37</f>
         <v>96600</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -1873,16 +2005,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · дератизация</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="35">
         <f>Данные!$B$53</f>
         <v>75000</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -1891,16 +2023,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="35">
         <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1910,16 +2042,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="35">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1929,16 +2061,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="35">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="35">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -1948,16 +2080,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="35">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -1967,16 +2099,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="35">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2019,16 +2151,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="35">
         <f>Данные!$B$54</f>
         <v>70000</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -2067,7 +2199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2092,37 +2224,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="33">
         <f>D12+D13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="33">
         <f>D14+D15+D16+D17+D18</f>
         <v>20245957.5</v>
       </c>
@@ -2161,16 +2293,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="35">
         <f>Данные!$B$38</f>
         <v>618400</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2179,16 +2311,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="35">
         <f>Данные!$B$40</f>
         <v>569800</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -2197,16 +2329,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="35">
         <f>Данные!$B$42</f>
         <v>2599100</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="8">
@@ -2215,16 +2347,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="35">
         <f>Данные!$B$55</f>
         <v>3172000</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="35">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2234,16 +2366,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="35">
         <f>Данные!$B$56</f>
         <v>2074000</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="35">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2253,16 +2385,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="35">
         <f>(SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30))*Данные!$B$9</f>
         <v>2715120</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2272,16 +2404,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="35">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2291,16 +2423,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="35">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="35">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2310,16 +2442,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="35">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2329,16 +2461,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="35">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2381,16 +2513,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="35">
         <f>Данные!$B$39</f>
         <v>478400</v>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D22" s="7">
@@ -2399,16 +2531,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="35">
         <f>Данные!$B$41</f>
         <v>440700</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="7">
@@ -2417,16 +2549,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="35">
         <f>Данные!$B$43</f>
         <v>2010300</v>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="7">
@@ -2435,16 +2567,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="35">
         <f>Данные!$B$57</f>
         <v>2806000</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="35">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2454,16 +2586,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="35">
         <f>Данные!$B$58</f>
         <v>1830000</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="35">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2506,16 +2638,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="35">
         <f>Данные!$B$48</f>
         <v>720000</v>
       </c>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D30" s="7">
@@ -2524,16 +2656,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="35">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="C31" s="32" t="n">
+      <c r="C31" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="7">
@@ -2542,16 +2674,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="35">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="C32" s="32" t="n">
+      <c r="C32" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D32" s="7">
@@ -2567,9 +2699,342 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>КОНТУР 1 И КОНТУР 2 ПО ПЛОЩАДКАМ, шт</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Площадка</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>1-й контур</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>2-й контур</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Площадка А</t>
+        </is>
+      </c>
+      <c r="B39" s="36">
+        <f>Данные!$B$23</f>
+        <v>13</v>
+      </c>
+      <c r="C39" s="36">
+        <f>Данные!$C$23</f>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Площадка Б</t>
+        </is>
+      </c>
+      <c r="B40" s="36">
+        <f>Данные!$B$24</f>
+        <v>17</v>
+      </c>
+      <c r="C40" s="36">
+        <f>Данные!$C$24</f>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>В / Восточка</t>
+        </is>
+      </c>
+      <c r="B41" s="36">
+        <f>Данные!$B$25</f>
+        <v>50</v>
+      </c>
+      <c r="C41" s="36">
+        <f>Данные!$C$25</f>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Площадка Г</t>
+        </is>
+      </c>
+      <c r="B42" s="36">
+        <f>Данные!$B$26</f>
+        <v>17</v>
+      </c>
+      <c r="C42" s="36">
+        <f>Данные!$C$26</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Площадка Д</t>
+        </is>
+      </c>
+      <c r="B43" s="36">
+        <f>Данные!$B$27</f>
+        <v>15</v>
+      </c>
+      <c r="C43" s="36">
+        <f>Данные!$C$27</f>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Площадка Е</t>
+        </is>
+      </c>
+      <c r="B44" s="36">
+        <f>Данные!$B$28</f>
+        <v>13</v>
+      </c>
+      <c r="C44" s="36">
+        <f>Данные!$C$28</f>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Площадка Ж</t>
+        </is>
+      </c>
+      <c r="B45" s="36">
+        <f>Данные!$B$29</f>
+        <v>17</v>
+      </c>
+      <c r="C45" s="36">
+        <f>Данные!$C$29</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Айыртау</t>
+        </is>
+      </c>
+      <c r="B46" s="36">
+        <f>Данные!$B$30</f>
+        <v>19</v>
+      </c>
+      <c r="C46" s="36">
+        <f>Данные!$C$30</f>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Итого по площадкам</t>
+        </is>
+      </c>
+      <c r="B47" s="37">
+        <f>SUM(B39:B46)</f>
+        <v>161</v>
+      </c>
+      <c r="C47" s="37">
+        <f>SUM(C39:C46)</f>
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ ПО БРОЙЛЕРНЫМ ПЛОЩАДКАМ — ДЕТАЛЬНАЯ РАСШИФРОВКА</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>₸/мес</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Мес.</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Приманочные станции 1-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B51" s="7">
+        <f>B47*Данные!$B$9</f>
+        <v>347760</v>
+      </c>
+      <c r="C51" s="25">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D51" s="7">
+        <f>B47*Данные!$B$9*Данные!$B$15</f>
+        <v>2434320</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Приманочные станции 2-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B52" s="7">
+        <f>C47*Данные!$B$9</f>
+        <v>2367360</v>
+      </c>
+      <c r="C52" s="25">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D52" s="7">
+        <f>C47*Данные!$B$9*Данные!$B$15</f>
+        <v>16571520</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B53" s="7">
+        <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
+        <v>42880</v>
+      </c>
+      <c r="C53" s="25">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D53" s="7">
+        <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8*Данные!$B$15</f>
+        <v>300160</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
+        </is>
+      </c>
+      <c r="B54" s="7">
+        <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
+        <v>85760</v>
+      </c>
+      <c r="C54" s="25">
+        <f>Данные!$B$16</f>
+        <v>5</v>
+      </c>
+      <c r="D54" s="7">
+        <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8*Данные!$B$16</f>
+        <v>428800</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Зерноцид, 2-й контур</t>
+        </is>
+      </c>
+      <c r="B55" s="7">
+        <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
+        <v>11100</v>
+      </c>
+      <c r="C55" s="25">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D55" s="7">
+        <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6*Данные!$B$15</f>
+        <v>77700</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Pest Killer, брикеты</t>
+        </is>
+      </c>
+      <c r="B56" s="7">
+        <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
+        <v>61922.5</v>
+      </c>
+      <c r="C56" s="25">
+        <f>Данные!$B$15</f>
+        <v>7</v>
+      </c>
+      <c r="D56" s="7">
+        <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7*Данные!$B$15</f>
+        <v>433457.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ ЗА ГОД</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="n"/>
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="14">
+        <f>SUM(D51:D56)</f>
+        <v>20245957.5</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт/мес), но количество точек по контурам разное — см. таблицу выше.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2607,37 +3072,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15</f>
         <v>849557.5</v>
       </c>
@@ -2676,16 +3141,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="35">
         <f>Данные!$B$44</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2694,15 +3159,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -2711,16 +3176,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="35">
         <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
         <v>112320</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2730,16 +3195,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="35">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2749,16 +3214,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="35">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="35">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2768,16 +3233,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="35">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2787,16 +3252,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="35">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2839,16 +3304,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="35">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -2890,16 +3355,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="35">
         <f>Данные!$B$51</f>
         <v>100800</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="7">
@@ -2955,37 +3420,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="33">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3024,16 +3489,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования</t>
         </is>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="35">
         <f>Данные!$B$46</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -3042,16 +3507,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="35">
         <f>Данные!$B$59</f>
         <v>180000</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -3060,15 +3525,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3110,16 +3575,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="35">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="7">
@@ -3161,16 +3626,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="35">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -3234,37 +3699,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>720000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="33">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3303,15 +3768,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
+      <c r="B9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3320,16 +3785,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="35">
         <f>Данные!$B$60</f>
         <v>80000</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="35">
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
@@ -3339,15 +3804,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3403,37 +3868,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="30">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15</f>
         <v>794186.75</v>
       </c>
@@ -3472,15 +3937,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
+      <c r="B9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3489,15 +3954,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -3506,16 +3971,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="35">
         <f>(Данные!$B$22+Данные!$C$22)*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3525,16 +3990,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="35">
         <f>Данные!$D$22*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3544,16 +4009,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="35">
         <f>Данные!$D$22*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="35">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -3563,16 +4028,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="35">
         <f>Данные!$G$22*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3582,16 +4047,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="35">
         <f>Данные!$F$22*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="35">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3672,17 +4137,17 @@
       <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
@@ -3734,7 +4199,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -3767,57 +4232,57 @@
       <c r="K11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Станций 1–2 к., шт</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>Станции 1–2 к. за год, ₸</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="40" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="40" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="40" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="40" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="J12" s="35" t="inlineStr">
+      <c r="J12" s="40" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="K12" s="35" t="inlineStr">
+      <c r="K12" s="40" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -3829,7 +4294,7 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="49">
+      <c r="B13" s="54">
         <f>Данные!$B$20+Данные!$C$20</f>
         <v>29</v>
       </c>
@@ -3837,11 +4302,11 @@
         <f>B13*Данные!$B$9*Данные!$B$15</f>
         <v>438480</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="54">
         <f>Данные!$D$20</f>
         <v>0</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="54">
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
@@ -3849,7 +4314,7 @@
         <f>D13*Данные!$B$8*Данные!$B$15+E13*Данные!$B$8*Данные!$B$16</f>
         <v>0</v>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="55">
         <f>Данные!$G$20</f>
         <v>0</v>
       </c>
@@ -3857,7 +4322,7 @@
         <f>G13*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="55">
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
@@ -3876,7 +4341,7 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="49">
+      <c r="B14" s="54">
         <f>SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30)</f>
         <v>1257</v>
       </c>
@@ -3884,11 +4349,11 @@
         <f>B14*Данные!$B$9*Данные!$B$15</f>
         <v>19005840</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="54">
         <f>SUM(Данные!$D$23:$D$30)</f>
         <v>268</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="54">
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
@@ -3896,7 +4361,7 @@
         <f>D14*Данные!$B$8*Данные!$B$15+E14*Данные!$B$8*Данные!$B$16</f>
         <v>728960</v>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="55">
         <f>SUM(Данные!$G$23:$G$30)</f>
         <v>15</v>
       </c>
@@ -3904,7 +4369,7 @@
         <f>G14*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
-      <c r="I14" s="50">
+      <c r="I14" s="55">
         <f>SUM(Данные!$F$23:$F$30)</f>
         <v>17</v>
       </c>
@@ -3923,7 +4388,7 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="49">
+      <c r="B15" s="54">
         <f>Данные!$B$21+Данные!$C$21</f>
         <v>52</v>
       </c>
@@ -3931,11 +4396,11 @@
         <f>B15*Данные!$B$9*Данные!$B$15</f>
         <v>786240</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="54">
         <f>Данные!$D$21</f>
         <v>12</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="54">
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
@@ -3943,7 +4408,7 @@
         <f>D15*Данные!$B$8*Данные!$B$15+E15*Данные!$B$8*Данные!$B$16</f>
         <v>32640</v>
       </c>
-      <c r="G15" s="50">
+      <c r="G15" s="55">
         <f>Данные!$G$21</f>
         <v>1</v>
       </c>
@@ -3951,7 +4416,7 @@
         <f>G15*Данные!$B$6*Данные!$B$15</f>
         <v>5180</v>
       </c>
-      <c r="I15" s="50">
+      <c r="I15" s="55">
         <f>Данные!$F$21</f>
         <v>1</v>
       </c>
@@ -3970,7 +4435,7 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="49">
+      <c r="B16" s="54">
         <f>Данные!$B$22+Данные!$C$22</f>
         <v>39</v>
       </c>
@@ -3978,11 +4443,11 @@
         <f>B16*Данные!$B$9*Данные!$B$15</f>
         <v>589680</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="54">
         <f>Данные!$D$22</f>
         <v>63</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="54">
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
@@ -3990,7 +4455,7 @@
         <f>D16*Данные!$B$8*Данные!$B$15+E16*Данные!$B$8*Данные!$B$16</f>
         <v>171360</v>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="55">
         <f>Данные!$G$22</f>
         <v>0</v>
       </c>
@@ -3998,7 +4463,7 @@
         <f>G16*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="I16" s="50">
+      <c r="I16" s="55">
         <f>Данные!$F$22</f>
         <v>1.3</v>
       </c>
@@ -4048,7 +4513,7 @@
         <f>SUM(F13:F17)</f>
         <v>932960</v>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="56">
         <f>SUM(G13:G17)</f>
         <v>16</v>
       </c>
@@ -4056,7 +4521,7 @@
         <f>SUM(H13:H17)</f>
         <v>82880</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="56">
         <f>SUM(I13:I17)</f>
         <v>20.3</v>
       </c>
@@ -4083,32 +4548,32 @@
       <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="40" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="40" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F21" s="35" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
@@ -4405,26 +4870,26 @@
       <c r="H4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr"/>
-      <c r="E5" s="26" t="inlineStr"/>
-      <c r="F5" s="26" t="inlineStr"/>
-      <c r="G5" s="26" t="inlineStr"/>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr"/>
+      <c r="E5" s="29" t="inlineStr"/>
+      <c r="F5" s="29" t="inlineStr"/>
+      <c r="G5" s="29" t="inlineStr"/>
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
@@ -4436,7 +4901,7 @@
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="44" t="n">
         <v>740</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4444,7 +4909,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="40" t="inlineStr">
+      <c r="H6" s="45" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -4456,7 +4921,7 @@
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="44" t="n">
         <v>3642.5</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4464,7 +4929,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="40" t="inlineStr">
+      <c r="H7" s="45" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
@@ -4476,7 +4941,7 @@
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="44" t="n">
         <v>160</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -4484,7 +4949,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="40" t="inlineStr">
+      <c r="H8" s="45" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
@@ -4496,7 +4961,7 @@
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="44" t="n">
         <v>2160</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -4504,7 +4969,7 @@
           <t>₸/шт/мес</t>
         </is>
       </c>
-      <c r="H9" s="40" t="inlineStr">
+      <c r="H9" s="45" t="inlineStr">
         <is>
           <t>ежемесячный платёж за станцию, только тёплый сезон; цена из прежнего расчёта по ККЗ</t>
         </is>
@@ -4516,7 +4981,7 @@
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="39" t="n">
+      <c r="B10" s="44" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -4524,7 +4989,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="40" t="inlineStr">
+      <c r="H10" s="45" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -4536,7 +5001,7 @@
           <t>Бутылки, расход</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n">
+      <c r="B11" s="44" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4544,7 +5009,7 @@
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="H11" s="40" t="inlineStr">
+      <c r="H11" s="45" t="inlineStr">
         <is>
           <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
         </is>
@@ -4556,7 +5021,7 @@
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B12" s="39" t="n">
+      <c r="B12" s="44" t="n">
         <v>258488</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -4564,7 +5029,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="40" t="inlineStr">
+      <c r="H12" s="45" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
@@ -4576,7 +5041,7 @@
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B13" s="39" t="n">
+      <c r="B13" s="44" t="n">
         <v>350000</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4584,7 +5049,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H13" s="40" t="inlineStr">
+      <c r="H13" s="45" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
@@ -4596,7 +5061,7 @@
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B14" s="39" t="n">
+      <c r="B14" s="44" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -4604,7 +5069,7 @@
           <t>чел.</t>
         </is>
       </c>
-      <c r="H14" s="40" t="inlineStr">
+      <c r="H14" s="45" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
@@ -4616,7 +5081,7 @@
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B15" s="39" t="n">
+      <c r="B15" s="44" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4624,7 +5089,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="40" t="inlineStr">
+      <c r="H15" s="45" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
@@ -4636,7 +5101,7 @@
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B16" s="39" t="n">
+      <c r="B16" s="44" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4644,7 +5109,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H16" s="40" t="inlineStr">
+      <c r="H16" s="45" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
@@ -4666,42 +5131,42 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="35" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="40" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -4713,26 +5178,26 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B20" s="39" t="n">
+      <c r="B20" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="39" t="n">
+      <c r="C20" s="44" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="44" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="7">
         <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="52" t="n">
+      <c r="F20" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="52" t="n">
+      <c r="G20" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="40" t="inlineStr">
+      <c r="H20" s="45" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
@@ -4744,26 +5209,26 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B21" s="39" t="n">
+      <c r="B21" s="44" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="39" t="n">
+      <c r="C21" s="44" t="n">
         <v>34</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D21" s="44" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="7">
         <f>SUM(B21:D21)</f>
         <v>18</v>
       </c>
-      <c r="F21" s="52" t="n">
+      <c r="F21" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="52" t="n">
+      <c r="G21" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="40" t="inlineStr"/>
+      <c r="H21" s="45" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -4771,26 +5236,26 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B22" s="39" t="n">
+      <c r="B22" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="39" t="n">
+      <c r="C22" s="44" t="n">
         <v>39</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="44" t="n">
         <v>63</v>
       </c>
       <c r="E22" s="7">
         <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="52" t="n">
+      <c r="F22" s="57" t="n">
         <v>1.3</v>
       </c>
-      <c r="G22" s="52" t="n">
+      <c r="G22" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="40" t="inlineStr">
+      <c r="H22" s="45" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
@@ -4802,26 +5267,26 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B23" s="39" t="n">
+      <c r="B23" s="44" t="n">
         <v>13</v>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="44" t="n">
         <v>147</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="44" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="7">
         <f>SUM(B23:D23)</f>
         <v>13</v>
       </c>
-      <c r="F23" s="52" t="n">
+      <c r="F23" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="52" t="n">
+      <c r="G23" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="40" t="inlineStr"/>
+      <c r="H23" s="45" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -4829,26 +5294,26 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B24" s="39" t="n">
+      <c r="B24" s="44" t="n">
         <v>17</v>
       </c>
-      <c r="C24" s="39" t="n">
+      <c r="C24" s="44" t="n">
         <v>146</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="44" t="n">
         <v>20</v>
       </c>
       <c r="E24" s="7">
         <f>SUM(B24:D24)</f>
         <v>17</v>
       </c>
-      <c r="F24" s="52" t="n">
+      <c r="F24" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="52" t="n">
+      <c r="G24" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="40" t="inlineStr"/>
+      <c r="H24" s="45" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -4856,26 +5321,26 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B25" s="39" t="n">
+      <c r="B25" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="C25" s="39" t="n">
+      <c r="C25" s="44" t="n">
         <v>239</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D25" s="44" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="7">
         <f>SUM(B25:D25)</f>
         <v>50</v>
       </c>
-      <c r="F25" s="52" t="n">
+      <c r="F25" s="57" t="n">
         <v>3.5</v>
       </c>
-      <c r="G25" s="52" t="n">
+      <c r="G25" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="40" t="inlineStr"/>
+      <c r="H25" s="45" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -4883,26 +5348,26 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B26" s="39" t="n">
+      <c r="B26" s="44" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="44" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="44" t="n">
         <v>80</v>
       </c>
       <c r="E26" s="7">
         <f>SUM(B26:D26)</f>
         <v>17</v>
       </c>
-      <c r="F26" s="52" t="n">
+      <c r="F26" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="52" t="n">
+      <c r="G26" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="40" t="inlineStr"/>
+      <c r="H26" s="45" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -4910,26 +5375,26 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B27" s="39" t="n">
+      <c r="B27" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="39" t="n">
+      <c r="C27" s="44" t="n">
         <v>69</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D27" s="44" t="n">
         <v>64</v>
       </c>
       <c r="E27" s="7">
         <f>SUM(B27:D27)</f>
         <v>15</v>
       </c>
-      <c r="F27" s="52" t="n">
+      <c r="F27" s="57" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="52" t="n">
+      <c r="G27" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="40" t="inlineStr"/>
+      <c r="H27" s="45" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4937,26 +5402,26 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B28" s="39" t="n">
+      <c r="B28" s="44" t="n">
         <v>13</v>
       </c>
-      <c r="C28" s="39" t="n">
+      <c r="C28" s="44" t="n">
         <v>147</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D28" s="44" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="7">
         <f>SUM(B28:D28)</f>
         <v>13</v>
       </c>
-      <c r="F28" s="52" t="n">
+      <c r="F28" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="52" t="n">
+      <c r="G28" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="40" t="inlineStr"/>
+      <c r="H28" s="45" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -4964,26 +5429,26 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B29" s="39" t="n">
+      <c r="B29" s="44" t="n">
         <v>17</v>
       </c>
-      <c r="C29" s="39" t="n">
+      <c r="C29" s="44" t="n">
         <v>73</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D29" s="44" t="n">
         <v>10</v>
       </c>
       <c r="E29" s="7">
         <f>SUM(B29:D29)</f>
         <v>17</v>
       </c>
-      <c r="F29" s="52" t="n">
+      <c r="F29" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="52" t="n">
+      <c r="G29" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="40" t="inlineStr"/>
+      <c r="H29" s="45" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4991,26 +5456,26 @@
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B30" s="39" t="n">
+      <c r="B30" s="44" t="n">
         <v>19</v>
       </c>
-      <c r="C30" s="39" t="n">
+      <c r="C30" s="44" t="n">
         <v>187</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D30" s="44" t="n">
         <v>24</v>
       </c>
       <c r="E30" s="7">
         <f>SUM(B30:D30)</f>
         <v>19</v>
       </c>
-      <c r="F30" s="52" t="n">
+      <c r="F30" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="52" t="n">
+      <c r="G30" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="40" t="inlineStr"/>
+      <c r="H30" s="45" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5022,9 +5487,9 @@
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="50" t="n"/>
-      <c r="G31" s="50" t="n"/>
-      <c r="H31" s="40" t="inlineStr">
+      <c r="F31" s="55" t="n"/>
+      <c r="G31" s="55" t="n"/>
+      <c r="H31" s="45" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5040,9 +5505,9 @@
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="50" t="n"/>
-      <c r="G32" s="50" t="n"/>
-      <c r="H32" s="40" t="inlineStr">
+      <c r="F32" s="55" t="n"/>
+      <c r="G32" s="55" t="n"/>
+      <c r="H32" s="45" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5070,11 +5535,11 @@
         <f>SUM(E20:E32)</f>
         <v>179</v>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="56">
         <f>SUM(F20:F32)</f>
         <v>20.3</v>
       </c>
-      <c r="G33" s="51">
+      <c r="G33" s="56">
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
@@ -5096,26 +5561,26 @@
       <c r="H35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr"/>
-      <c r="E36" s="26" t="inlineStr"/>
-      <c r="F36" s="26" t="inlineStr"/>
-      <c r="G36" s="26" t="inlineStr"/>
-      <c r="H36" s="26" t="inlineStr">
+      <c r="D36" s="29" t="inlineStr"/>
+      <c r="E36" s="29" t="inlineStr"/>
+      <c r="F36" s="29" t="inlineStr"/>
+      <c r="G36" s="29" t="inlineStr"/>
+      <c r="H36" s="29" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
@@ -5127,7 +5592,7 @@
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B37" s="39" t="n">
+      <c r="B37" s="44" t="n">
         <v>96600</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -5135,7 +5600,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="40" t="inlineStr">
+      <c r="H37" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
@@ -5147,7 +5612,7 @@
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B38" s="39" t="n">
+      <c r="B38" s="44" t="n">
         <v>618400</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -5155,7 +5620,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="40" t="inlineStr">
+      <c r="H38" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
@@ -5167,7 +5632,7 @@
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B39" s="39" t="n">
+      <c r="B39" s="44" t="n">
         <v>478400</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -5175,7 +5640,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="40" t="inlineStr">
+      <c r="H39" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5187,7 +5652,7 @@
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B40" s="39" t="n">
+      <c r="B40" s="44" t="n">
         <v>569800</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -5195,7 +5660,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="40" t="inlineStr">
+      <c r="H40" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
@@ -5207,7 +5672,7 @@
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B41" s="39" t="n">
+      <c r="B41" s="44" t="n">
         <v>440700</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -5215,7 +5680,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="40" t="inlineStr">
+      <c r="H41" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5227,7 +5692,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B42" s="39" t="n">
+      <c r="B42" s="44" t="n">
         <v>2599100</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -5235,7 +5700,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="40" t="inlineStr">
+      <c r="H42" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
@@ -5247,7 +5712,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B43" s="39" t="n">
+      <c r="B43" s="44" t="n">
         <v>2010300</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -5255,7 +5720,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="40" t="inlineStr">
+      <c r="H43" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5267,7 +5732,7 @@
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B44" s="39" t="n">
+      <c r="B44" s="44" t="n">
         <v>126200</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -5275,7 +5740,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="40" t="inlineStr">
+      <c r="H44" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
@@ -5287,7 +5752,7 @@
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B45" s="39" t="n">
+      <c r="B45" s="44" t="n">
         <v>106800</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -5295,7 +5760,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="40" t="inlineStr">
+      <c r="H45" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5307,7 +5772,7 @@
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B46" s="39" t="n">
+      <c r="B46" s="44" t="n">
         <v>126200</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -5315,7 +5780,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="40" t="inlineStr">
+      <c r="H46" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5327,7 +5792,7 @@
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B47" s="39" t="n">
+      <c r="B47" s="44" t="n">
         <v>106800</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -5335,7 +5800,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="40" t="inlineStr">
+      <c r="H47" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5347,7 +5812,7 @@
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B48" s="39" t="n">
+      <c r="B48" s="44" t="n">
         <v>720000</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -5355,7 +5820,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="40" t="inlineStr">
+      <c r="H48" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5367,7 +5832,7 @@
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B49" s="39" t="n">
+      <c r="B49" s="44" t="n">
         <v>1080000</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -5375,7 +5840,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="40" t="inlineStr">
+      <c r="H49" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5387,7 +5852,7 @@
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B50" s="39" t="n">
+      <c r="B50" s="44" t="n">
         <v>3000000</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -5395,7 +5860,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="40" t="inlineStr">
+      <c r="H50" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5407,7 +5872,7 @@
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B51" s="39" t="n">
+      <c r="B51" s="44" t="n">
         <v>100800</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -5415,7 +5880,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="40" t="inlineStr">
+      <c r="H51" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5427,7 +5892,7 @@
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B52" s="39" t="n">
+      <c r="B52" s="44" t="n">
         <v>160800</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -5435,7 +5900,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="40" t="inlineStr">
+      <c r="H52" s="45" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5447,7 +5912,7 @@
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B53" s="39" t="n">
+      <c r="B53" s="44" t="n">
         <v>75000</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -5455,7 +5920,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="40" t="inlineStr">
+      <c r="H53" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5467,7 +5932,7 @@
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B54" s="39" t="n">
+      <c r="B54" s="44" t="n">
         <v>70000</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -5475,7 +5940,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="40" t="inlineStr">
+      <c r="H54" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5487,7 +5952,7 @@
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B55" s="39" t="n">
+      <c r="B55" s="44" t="n">
         <v>3172000</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -5495,7 +5960,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="40" t="inlineStr">
+      <c r="H55" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -5507,7 +5972,7 @@
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B56" s="39" t="n">
+      <c r="B56" s="44" t="n">
         <v>2074000</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -5515,7 +5980,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="40" t="inlineStr">
+      <c r="H56" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -5527,7 +5992,7 @@
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B57" s="39" t="n">
+      <c r="B57" s="44" t="n">
         <v>2806000</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -5535,7 +6000,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="40" t="inlineStr">
+      <c r="H57" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -5547,7 +6012,7 @@
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B58" s="39" t="n">
+      <c r="B58" s="44" t="n">
         <v>1830000</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -5555,7 +6020,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="40" t="inlineStr">
+      <c r="H58" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -5567,7 +6032,7 @@
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B59" s="39" t="n">
+      <c r="B59" s="44" t="n">
         <v>180000</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -5575,7 +6040,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="40" t="inlineStr">
+      <c r="H59" s="45" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
@@ -5587,7 +6052,7 @@
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
-      <c r="B60" s="39" t="n">
+      <c r="B60" s="44" t="n">
         <v>80000</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -5595,7 +6060,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="40" t="inlineStr">
+      <c r="H60" s="45" t="inlineStr">
         <is>
           <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
@@ -5607,7 +6072,7 @@
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B61" s="39" t="n">
+      <c r="B61" s="44" t="n">
         <v>9</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -5615,7 +6080,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H61" s="40" t="inlineStr">
+      <c r="H61" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5627,7 +6092,7 @@
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B62" s="39" t="n">
+      <c r="B62" s="44" t="n">
         <v>3</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -5635,7 +6100,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H62" s="40" t="inlineStr">
+      <c r="H62" s="45" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -5647,7 +6112,7 @@
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B63" s="39" t="n">
+      <c r="B63" s="44" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -5655,7 +6120,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H63" s="40" t="inlineStr">
+      <c r="H63" s="45" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
@@ -5667,7 +6132,7 @@
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B64" s="53" t="n">
+      <c r="B64" s="58" t="n">
         <v>0.15</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -5675,7 +6140,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H64" s="40" t="inlineStr">
+      <c r="H64" s="45" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
@@ -5687,7 +6152,7 @@
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B65" s="53" t="n">
+      <c r="B65" s="58" t="n">
         <v>0.15</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -5695,7 +6160,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="40" t="inlineStr">
+      <c r="H65" s="45" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
@@ -5707,7 +6172,7 @@
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B66" s="53" t="n">
+      <c r="B66" s="58" t="n">
         <v>0.16</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -5715,7 +6180,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H66" s="40" t="inlineStr">
+      <c r="H66" s="45" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -793,11 +793,11 @@
       </c>
       <c r="F6" s="7">
         <f>G6/12</f>
-        <v>38664.79167</v>
+        <v>7344.791667</v>
       </c>
       <c r="G6" s="8">
         <f>'ККЗ'!D5</f>
-        <v>463977.5</v>
+        <v>88137.5</v>
       </c>
     </row>
     <row r="7">
@@ -824,11 +824,11 @@
       </c>
       <c r="F7" s="7">
         <f>G7/12</f>
-        <v>1687163.125</v>
+        <v>329603.125</v>
       </c>
       <c r="G7" s="8">
         <f>'Бройлерные площадки'!D5</f>
-        <v>20245957.5</v>
+        <v>3955237.5</v>
       </c>
     </row>
     <row r="8">
@@ -853,11 +853,11 @@
       <c r="E8" s="49" t="n"/>
       <c r="F8" s="7">
         <f>G8/12</f>
-        <v>70796.45833</v>
+        <v>14636.45833</v>
       </c>
       <c r="G8" s="8">
         <f>'Инкубаторий'!D5</f>
-        <v>849557.5</v>
+        <v>175637.5</v>
       </c>
     </row>
     <row r="9">
@@ -936,11 +936,11 @@
       <c r="E11" s="49" t="n"/>
       <c r="F11" s="7">
         <f>G11/12</f>
-        <v>66182.22917</v>
+        <v>24062.22917</v>
       </c>
       <c r="G11" s="8">
         <f>'АБК'!D5</f>
-        <v>794186.75</v>
+        <v>288746.75</v>
       </c>
     </row>
     <row r="12">
@@ -967,11 +967,11 @@
       </c>
       <c r="F12" s="12">
         <f>G12/12</f>
-        <v>1862806.604</v>
+        <v>375646.6042</v>
       </c>
       <c r="G12" s="12">
         <f>SUM(G6:G11)</f>
-        <v>22353679.25</v>
+        <v>4507759.25</v>
       </c>
     </row>
     <row r="13">
@@ -1036,11 +1036,11 @@
       </c>
       <c r="F15" s="14">
         <f>G15/12</f>
-        <v>2898345.271</v>
+        <v>1411185.271</v>
       </c>
       <c r="G15" s="14">
         <f>G12+G13+G14</f>
-        <v>34780143.25</v>
+        <v>16934223.25</v>
       </c>
     </row>
     <row r="16"/>
@@ -1087,15 +1087,15 @@
       </c>
       <c r="B19" s="7">
         <f>C19/12</f>
-        <v>1237954.729</v>
+        <v>2725114.729</v>
       </c>
       <c r="C19" s="8">
         <f>C15-G15</f>
-        <v>14855456.75</v>
+        <v>32701376.75</v>
       </c>
       <c r="D19" s="50">
         <f>IF(G15=0,0,C15/G15)</f>
-        <v>1.427124657</v>
+        <v>2.93108218</v>
       </c>
     </row>
     <row r="20">
@@ -1106,15 +1106,15 @@
       </c>
       <c r="B20" s="7">
         <f>C20/12</f>
-        <v>314154.7292</v>
+        <v>1801314.729</v>
       </c>
       <c r="C20" s="8">
         <f>E15-G15</f>
-        <v>3769856.75</v>
+        <v>21615776.75</v>
       </c>
       <c r="D20" s="50">
         <f>IF(G15=0,0,E15/G15)</f>
-        <v>1.108391064</v>
+        <v>2.276455166</v>
       </c>
     </row>
     <row r="21"/>
@@ -1232,7 +1232,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура · тёплый сезон, ежемесячный платёж</t>
+          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B27" s="7">
@@ -1241,20 +1241,17 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>шт/мес</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D27" s="7">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="8">
         <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9</f>
         <v>2974320</v>
-      </c>
-      <c r="F27" s="8">
-        <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9*Данные!$B$15</f>
-        <v>20820240</v>
       </c>
     </row>
     <row r="28">
@@ -1438,7 +1435,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>ИТОГО ШТАТ УКПФ</t>
+          <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
         </is>
       </c>
       <c r="B35" s="23" t="n"/>
@@ -1446,17 +1443,17 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="14">
         <f>F35/12</f>
-        <v>2898345.271</v>
+        <v>1411185.271</v>
       </c>
       <c r="F35" s="14">
         <f>F26+F27+F28+F29+F30+F31+F34</f>
-        <v>34780143.25</v>
+        <v>16934223.25</v>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
+          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
       </c>
     </row>
@@ -1539,31 +1536,31 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Материалы за год, ₸ (не зависят от численности)</t>
+          <t>Материалы, первый год, ₸ (не зависят от численности, включая разовую закупку станций)</t>
         </is>
       </c>
       <c r="B43" s="25">
         <f>(F35-F26)</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="C43" s="25">
         <f>(F35-F26)</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>ИТОГО ЗА ГОД, ₸</t>
+          <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
         </is>
       </c>
       <c r="B44" s="26">
         <f>B42+B43</f>
-        <v>28576431.25</v>
+        <v>10730511.25</v>
       </c>
       <c r="C44" s="26">
         <f>C42+C43</f>
-        <v>34780143.25</v>
+        <v>16934223.25</v>
       </c>
     </row>
     <row r="45">
@@ -1912,7 +1909,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/мес, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
+          <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/шт разовой закупки, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1947,7 @@
       </c>
       <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15</f>
-        <v>463977.5</v>
+        <v>88137.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -2025,20 +2022,19 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B11" s="35">
         <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C11" s="35">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+      <c r="C11" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D11" s="8">
         <f>B11*C11</f>
-        <v>438480</v>
+        <v>62640</v>
       </c>
     </row>
     <row r="12">
@@ -2256,7 +2252,7 @@
       </c>
       <c r="D5" s="33">
         <f>D14+D15+D16+D17+D18</f>
-        <v>20245957.5</v>
+        <v>3955237.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -2387,20 +2383,19 @@
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B14" s="35">
         <f>(SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30))*Данные!$B$9</f>
         <v>2715120</v>
       </c>
-      <c r="C14" s="35">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+      <c r="C14" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D14" s="8">
         <f>B14*C14</f>
-        <v>19005840</v>
+        <v>2715120</v>
       </c>
     </row>
     <row r="15">
@@ -2875,63 +2870,65 @@
       <c r="D49" s="16" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>₸/мес</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>₸/мес (разово — цена за шт)</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>Мес.</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>За год, ₸</t>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>За год / разово, ₸</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го контура, тёплый сезон</t>
+          <t>Приманочные станции 1-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B51" s="7">
         <f>B47*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C51" s="25">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>разово</t>
+        </is>
       </c>
       <c r="D51" s="7">
-        <f>B47*Данные!$B$9*Данные!$B$15</f>
-        <v>2434320</v>
+        <f>B47*Данные!$B$9</f>
+        <v>347760</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Приманочные станции 2-го контура, тёплый сезон</t>
+          <t>Приманочные станции 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B52" s="7">
         <f>C47*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C52" s="25">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>разово</t>
+        </is>
       </c>
       <c r="D52" s="7">
-        <f>C47*Данные!$B$9*Данные!$B$15</f>
-        <v>16571520</v>
+        <f>C47*Данные!$B$9</f>
+        <v>2367360</v>
       </c>
     </row>
     <row r="53">
@@ -3013,21 +3010,21 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ ЗА ГОД</t>
+          <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
       <c r="B57" s="23" t="n"/>
       <c r="C57" s="23" t="n"/>
       <c r="D57" s="14">
         <f>SUM(D51:D56)</f>
-        <v>20245957.5</v>
+        <v>3955237.5</v>
       </c>
     </row>
     <row r="58"/>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт/мес), но количество точек по контурам разное — см. таблицу выше.</t>
+          <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт, разовая закупка), но количество точек по контурам разное — см. таблицу выше.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3101,7 @@
       </c>
       <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15</f>
-        <v>849557.5</v>
+        <v>175637.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -3178,20 +3175,19 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B11" s="35">
         <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
         <v>112320</v>
       </c>
-      <c r="C11" s="35">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+      <c r="C11" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D11" s="8">
         <f>B11*C11</f>
-        <v>786240</v>
+        <v>112320</v>
       </c>
     </row>
     <row r="12">
@@ -3900,7 +3896,7 @@
       </c>
       <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15</f>
-        <v>794186.75</v>
+        <v>288746.75</v>
       </c>
     </row>
     <row r="6"/>
@@ -3973,20 +3969,19 @@
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура, тёплый сезон</t>
+          <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B11" s="35">
         <f>(Данные!$B$22+Данные!$C$22)*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C11" s="35">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+      <c r="C11" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D11" s="8">
         <f>B11*C11</f>
-        <v>589680</v>
+        <v>84240</v>
       </c>
     </row>
     <row r="12">
@@ -4217,7 +4212,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ И ЯДЫ РАЗДЕЛЬНО, ТОЛЬКО ТЁПЛЫЙ СЕЗОН ДЛЯ 1–2 КОНТУРА</t>
+          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ (РАЗОВАЯ ЗАКУПКА) И ЯДЫ (ТОЛЬКО ТЁПЛЫЙ СЕЗОН) РАЗДЕЛЬНО</t>
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
@@ -4244,7 +4239,7 @@
       </c>
       <c r="C12" s="40" t="inlineStr">
         <is>
-          <t>Станции 1–2 к. за год, ₸</t>
+          <t>Станции 1–2 к., разово, ₸</t>
         </is>
       </c>
       <c r="D12" s="40" t="inlineStr">
@@ -4299,8 +4294,8 @@
         <v>29</v>
       </c>
       <c r="C13" s="7">
-        <f>B13*Данные!$B$9*Данные!$B$15</f>
-        <v>438480</v>
+        <f>B13*Данные!$B$9</f>
+        <v>62640</v>
       </c>
       <c r="D13" s="54">
         <f>Данные!$D$20</f>
@@ -4332,7 +4327,7 @@
       </c>
       <c r="K13" s="8">
         <f>C13+F13+H13+J13</f>
-        <v>463977.5</v>
+        <v>88137.5</v>
       </c>
     </row>
     <row r="14">
@@ -4346,8 +4341,8 @@
         <v>1257</v>
       </c>
       <c r="C14" s="7">
-        <f>B14*Данные!$B$9*Данные!$B$15</f>
-        <v>19005840</v>
+        <f>B14*Данные!$B$9</f>
+        <v>2715120</v>
       </c>
       <c r="D14" s="54">
         <f>SUM(Данные!$D$23:$D$30)</f>
@@ -4379,7 +4374,7 @@
       </c>
       <c r="K14" s="8">
         <f>C14+F14+H14+J14</f>
-        <v>20245957.5</v>
+        <v>3955237.5</v>
       </c>
     </row>
     <row r="15">
@@ -4393,8 +4388,8 @@
         <v>52</v>
       </c>
       <c r="C15" s="7">
-        <f>B15*Данные!$B$9*Данные!$B$15</f>
-        <v>786240</v>
+        <f>B15*Данные!$B$9</f>
+        <v>112320</v>
       </c>
       <c r="D15" s="54">
         <f>Данные!$D$21</f>
@@ -4426,7 +4421,7 @@
       </c>
       <c r="K15" s="8">
         <f>C15+F15+H15+J15</f>
-        <v>849557.5</v>
+        <v>175637.5</v>
       </c>
     </row>
     <row r="16">
@@ -4440,8 +4435,8 @@
         <v>39</v>
       </c>
       <c r="C16" s="7">
-        <f>B16*Данные!$B$9*Данные!$B$15</f>
-        <v>589680</v>
+        <f>B16*Данные!$B$9</f>
+        <v>84240</v>
       </c>
       <c r="D16" s="54">
         <f>Данные!$D$22</f>
@@ -4473,7 +4468,7 @@
       </c>
       <c r="K16" s="8">
         <f>C16+F16+H16+J16</f>
-        <v>794186.75</v>
+        <v>288746.75</v>
       </c>
     </row>
     <row r="17">
@@ -4499,13 +4494,13 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>МАТЕРИАЛЫ ЗА ГОД, ИТОГО</t>
+          <t>МАТЕРИАЛЫ, ПЕРВЫЙ ГОД ИТОГО (с разовой закупкой станций)</t>
         </is>
       </c>
       <c r="B18" s="23" t="n"/>
       <c r="C18" s="12">
         <f>SUM(C13:C17)</f>
-        <v>20820240</v>
+        <v>2974320</v>
       </c>
       <c r="D18" s="23" t="n"/>
       <c r="E18" s="23" t="n"/>
@@ -4531,7 +4526,7 @@
       </c>
       <c r="K18" s="12">
         <f>SUM(K13:K17)</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
     </row>
     <row r="19"/>
@@ -4593,15 +4588,15 @@
       </c>
       <c r="D22" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E22" s="8">
         <f>C22+D22</f>
-        <v>28576431.25</v>
+        <v>10730511.25</v>
       </c>
       <c r="F22" s="8">
         <f>A22*Данные!$B$13*12+D22</f>
-        <v>30772719.25</v>
+        <v>12926799.25</v>
       </c>
     </row>
     <row r="23">
@@ -4618,15 +4613,15 @@
       </c>
       <c r="D23" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E23" s="8">
         <f>C23+D23</f>
-        <v>31678287.25</v>
+        <v>13832367.25</v>
       </c>
       <c r="F23" s="8">
         <f>A23*Данные!$B$13*12+D23</f>
-        <v>34972719.25</v>
+        <v>17126799.25</v>
       </c>
     </row>
     <row r="24">
@@ -4643,15 +4638,15 @@
       </c>
       <c r="D24" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E24" s="8">
         <f>C24+D24</f>
-        <v>34780143.25</v>
+        <v>16934223.25</v>
       </c>
       <c r="F24" s="8">
         <f>A24*Данные!$B$13*12+D24</f>
-        <v>39172719.25</v>
+        <v>21326799.25</v>
       </c>
     </row>
     <row r="25">
@@ -4668,15 +4663,15 @@
       </c>
       <c r="D25" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E25" s="8">
         <f>C25+D25</f>
-        <v>37881999.25</v>
+        <v>20036079.25</v>
       </c>
       <c r="F25" s="8">
         <f>A25*Данные!$B$13*12+D25</f>
-        <v>43372719.25</v>
+        <v>25526799.25</v>
       </c>
     </row>
     <row r="26">
@@ -4693,15 +4688,15 @@
       </c>
       <c r="D26" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E26" s="8">
         <f>C26+D26</f>
-        <v>40983855.25</v>
+        <v>23137935.25</v>
       </c>
       <c r="F26" s="8">
         <f>A26*Данные!$B$13*12+D26</f>
-        <v>47572719.25</v>
+        <v>29726799.25</v>
       </c>
     </row>
     <row r="27">
@@ -4718,15 +4713,15 @@
       </c>
       <c r="D27" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E27" s="8">
         <f>C27+D27</f>
-        <v>44085711.25</v>
+        <v>26239791.25</v>
       </c>
       <c r="F27" s="8">
         <f>A27*Данные!$B$13*12+D27</f>
-        <v>51772719.25</v>
+        <v>33926799.25</v>
       </c>
     </row>
     <row r="28">
@@ -4743,15 +4738,15 @@
       </c>
       <c r="D28" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E28" s="8">
         <f>C28+D28</f>
-        <v>47187567.25</v>
+        <v>29341647.25</v>
       </c>
       <c r="F28" s="8">
         <f>A28*Данные!$B$13*12+D28</f>
-        <v>55972719.25</v>
+        <v>38126799.25</v>
       </c>
     </row>
     <row r="29">
@@ -4768,15 +4763,15 @@
       </c>
       <c r="D29" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E29" s="8">
         <f>C29+D29</f>
-        <v>50289423.25</v>
+        <v>32443503.25</v>
       </c>
       <c r="F29" s="8">
         <f>A29*Данные!$B$13*12+D29</f>
-        <v>60172719.25</v>
+        <v>42326799.25</v>
       </c>
     </row>
     <row r="30">
@@ -4793,15 +4788,15 @@
       </c>
       <c r="D30" s="7">
         <f>'Штат УКПФ'!$K$18</f>
-        <v>22372719.25</v>
+        <v>4526799.25</v>
       </c>
       <c r="E30" s="8">
         <f>C30+D30</f>
-        <v>53391279.25</v>
+        <v>35545359.25</v>
       </c>
       <c r="F30" s="8">
         <f>A30*Данные!$B$13*12+D30</f>
-        <v>64372719.25</v>
+        <v>46526799.25</v>
       </c>
     </row>
     <row r="31"/>
@@ -4966,12 +4961,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>₸/шт/мес</t>
+          <t>₸/шт</t>
         </is>
       </c>
       <c r="H9" s="45" t="inlineStr">
         <is>
-          <t>ежемесячный платёж за станцию, только тёплый сезон; цена из прежнего расчёта по ККЗ</t>
+          <t>разовая закупка оборудования; цена из прежнего расчёта по ККЗ</t>
         </is>
       </c>
     </row>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -155,9 +155,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00C8C2AE"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -168,7 +166,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -225,7 +225,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,22 +243,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -268,6 +257,17 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -308,6 +308,7 @@
     <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -316,7 +317,6 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -736,36 +736,36 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="48" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>в месяц</t>
+          <t>месяц (расходники)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>за год</t>
+          <t>год (расходники)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>в месяц</t>
+          <t>месяц (расходники)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>за год</t>
+          <t>год (расходники)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>в месяц</t>
+          <t>месяц (расходники)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>за год</t>
+          <t>год (расходники)</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Фонд оплаты труда дератизаторов</t>
+          <t>Бутылки · 1-й контур</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -986,17 +986,17 @@
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="7">
         <f>G13/12</f>
-        <v>1033952</v>
+        <v>1586.666667</v>
       </c>
       <c r="G13" s="7">
-        <f>Данные!$B$14*Данные!$B$12*12</f>
-        <v>12407424</v>
+        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
+        <v>19040</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Бутылки</t>
+          <t>Фонд оплаты труда дератизаторов</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -1005,11 +1005,11 @@
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="7">
         <f>G14/12</f>
-        <v>1586.666667</v>
+        <v>1033952</v>
       </c>
       <c r="G14" s="7">
-        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v>19040</v>
+        <f>Данные!$B$14*Данные!$B$12*12</f>
+        <v>12407424</v>
       </c>
     </row>
     <row r="15">
@@ -1053,9 +1053,13 @@
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="16" t="n"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 5 ДЕРАТИЗАТОРА</t>
+        </is>
+      </c>
+      <c r="F17" s="50" t="n"/>
+      <c r="G17" s="49" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -1063,19 +1067,34 @@
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>во сколько раз</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>2 дератизатора</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>5 дератизаторов</t>
         </is>
       </c>
     </row>
@@ -1093,9 +1112,22 @@
         <f>C15-G15</f>
         <v>32701376.75</v>
       </c>
-      <c r="D19" s="50">
+      <c r="D19" s="51">
         <f>IF(G15=0,0,C15/G15)</f>
         <v>2.93108218</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Оклад одного, ₸/мес</t>
+        </is>
+      </c>
+      <c r="F19" s="20">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+      <c r="G19" s="20">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
       </c>
     </row>
     <row r="20">
@@ -1112,617 +1144,686 @@
         <f>E15-G15</f>
         <v>21615776.75</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="51">
         <f>IF(G15=0,0,E15/G15)</f>
         <v>2.276455166</v>
       </c>
-    </row>
-    <row r="21"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>ФОТ в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="F20" s="20">
+        <f>2*Данные!$B$12</f>
+        <v>516976</v>
+      </c>
+      <c r="G20" s="20">
+        <f>5*Данные!$B$12</f>
+        <v>1292440</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>ФОТ за год, ₸</t>
+        </is>
+      </c>
+      <c r="F21" s="20">
+        <f>2*Данные!$B$12*12</f>
+        <v>6203712</v>
+      </c>
+      <c r="G21" s="20">
+        <f>5*Данные!$B$12*12</f>
+        <v>15509280</v>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Материалы, первый год, ₸ (не завис. от численности)</t>
+        </is>
+      </c>
+      <c r="F22" s="20">
+        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
+        <v>4526799.25</v>
+      </c>
+      <c r="G22" s="20">
+        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
+        <v>4526799.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
+        </is>
+      </c>
+      <c r="F23" s="21">
+        <f>F21+F22</f>
+        <v>10730511.25</v>
+      </c>
+      <c r="G23" s="21">
+        <f>G21+G22</f>
+        <v>20036079.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Разница 5 против 2 чел., ₸/год</t>
+        </is>
+      </c>
+      <c r="G24" s="22">
+        <f>G23-F23</f>
+        <v>9305568</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Цена за ед., ₸</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>в месяц, ₸</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>за год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B24" s="7">
+      <c r="B28" s="7">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Оклад одного дератизатора</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="D25" s="7">
+      <c r="D29" s="7">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Фонд оплаты труда</t>
         </is>
       </c>
-      <c r="B26" s="7">
+      <c r="B30" s="7">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="D26" s="7">
+      <c r="D30" s="7">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E30" s="7">
         <f>Данные!$B$14*Данные!$B$12</f>
         <v>1033952</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F30" s="8">
         <f>Данные!$B$14*Данные!$B$12*12</f>
         <v>12407424</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B27" s="7">
+      <c r="B31" s="7">
         <f>Данные!$B$33+Данные!$C$33</f>
         <v>1377</v>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D27" s="7">
+      <c r="D31" s="7">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="8">
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="8">
         <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9</f>
         <v>2974320</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура · апрель — октябрь</t>
         </is>
       </c>
-      <c r="B28" s="7">
+      <c r="B32" s="7">
         <f>Данные!$D$33</f>
         <v>343</v>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D28" s="7">
+      <c r="D32" s="7">
         <f>Данные!$B$8</f>
         <v>160</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E32" s="7">
         <f>Данные!$D$33*Данные!$B$8</f>
         <v>54880</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F32" s="8">
         <f>Данные!$D$33*Данные!$B$8*Данные!$B$15</f>
         <v>384160</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
         </is>
       </c>
-      <c r="B29" s="7">
+      <c r="B33" s="7">
         <f>Данные!$D$33*2</f>
         <v>686</v>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D29" s="7">
+      <c r="D33" s="7">
         <f>Данные!$B$8</f>
         <v>160</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E33" s="7">
         <f>Данные!$D$33*2*Данные!$B$8</f>
         <v>109760</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F33" s="8">
         <f>Данные!$D$33*2*Данные!$B$8*Данные!$B$16</f>
         <v>548800</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Зерноцид · 2-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B30" s="7">
+      <c r="B34" s="7">
         <f>Данные!$G$33</f>
         <v>16</v>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D30" s="7">
+      <c r="D34" s="7">
         <f>Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E34" s="7">
         <f>Данные!$G$33*Данные!$B$6</f>
         <v>11840</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F34" s="8">
         <f>Данные!$G$33*Данные!$B$6*Данные!$B$15</f>
         <v>82880</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
         </is>
       </c>
-      <c r="B31" s="7">
+      <c r="B35" s="7">
         <f>Данные!$F$33</f>
         <v>20.3</v>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D31" s="7">
+      <c r="D35" s="7">
         <f>Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E35" s="7">
         <f>Данные!$F$33*Данные!$B$7</f>
         <v>73942.75</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F35" s="8">
         <f>Данные!$F$33*Данные!$B$7*Данные!$B$15</f>
         <v>517599.25</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
         </is>
       </c>
-      <c r="B32" s="7">
+      <c r="B36" s="7">
         <f>Данные!$C$33</f>
         <v>1198</v>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
         </is>
       </c>
-      <c r="B33" s="51">
+      <c r="B37" s="52">
         <f>Данные!$F$33/Данные!$C$33</f>
         <v>0.01694490818</v>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Бутылки · тёплый сезон</t>
         </is>
       </c>
-      <c r="B34" s="7">
+      <c r="B38" s="7">
         <f>Данные!$B$11</f>
         <v>40</v>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D34" s="7">
+      <c r="D38" s="7">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E38" s="7">
         <f>Данные!$B$11*Данные!$B$10</f>
         <v>2720</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F38" s="8">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="14">
-        <f>F35/12</f>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="14">
+        <f>F39/12</f>
         <v>1411185.271</v>
       </c>
-      <c r="F35" s="14">
-        <f>F26+F27+F28+F29+F30+F31+F34</f>
+      <c r="F39" s="14">
+        <f>F30+F31+F32+F33+F34+F35+F38</f>
         <v>16934223.25</v>
       </c>
     </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 4 ДЕРАТИЗАТОРА</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="16" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>2 дератизатора</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>4 дератизатора</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Оклад одного, ₸/мес</t>
-        </is>
-      </c>
-      <c r="B40" s="25">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
-      <c r="C40" s="25">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>ФОТ в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="B41" s="25">
-        <f>2*Данные!$B$12</f>
-        <v>516976</v>
-      </c>
-      <c r="C41" s="25">
-        <f>4*Данные!$B$12</f>
-        <v>1033952</v>
-      </c>
-    </row>
+    <row r="41"/>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>ФОТ за год, ₸</t>
-        </is>
-      </c>
-      <c r="B42" s="25">
-        <f>2*Данные!$B$12*12</f>
-        <v>6203712</v>
-      </c>
-      <c r="C42" s="25">
-        <f>4*Данные!$B$12*12</f>
-        <v>12407424</v>
-      </c>
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="16" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Материалы, первый год, ₸ (не зависят от численности, включая разовую закупку станций)</t>
-        </is>
-      </c>
-      <c r="B43" s="25">
-        <f>(F35-F26)</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="C43" s="25">
-        <f>(F35-F26)</f>
-        <v>4526799.25</v>
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
-        </is>
-      </c>
-      <c r="B44" s="26">
-        <f>B42+B43</f>
-        <v>10730511.25</v>
-      </c>
-      <c r="C44" s="26">
-        <f>C42+C43</f>
-        <v>16934223.25</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Разница 4 против 2 чел., ₸/год</t>
-        </is>
-      </c>
-      <c r="C45" s="27">
-        <f>C44-B44</f>
-        <v>6203712</v>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="16" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>Условие</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Ставка</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Цена КП без скидок</t>
         </is>
       </c>
-      <c r="B49" s="7">
-        <f>C49/12</f>
+      <c r="B44" s="7">
+        <f>C44/12</f>
         <v>4136300</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C44" s="8">
         <f>C15</f>
         <v>49635600</v>
       </c>
-      <c r="D49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="D44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B50" s="7">
-        <f>C50/12</f>
+      <c r="B45" s="7">
+        <f>C45/12</f>
         <v>3515855</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C45" s="8">
         <f>C15*(1-Данные!$B$64)</f>
         <v>42190260</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D45" s="53">
         <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Вся территория + 100 % предоплата</t>
+        </is>
+      </c>
+      <c r="B46" s="7">
+        <f>C46/12</f>
+        <v>2988476.75</v>
+      </c>
+      <c r="C46" s="8">
+        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+        <v>35861721</v>
+      </c>
+      <c r="D46" s="53">
+        <f>Данные!$B$65</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Вся территория + предоплата + неплательщик НДС</t>
+        </is>
+      </c>
+      <c r="B47" s="7">
+        <f>C47/12</f>
+        <v>2510320.47</v>
+      </c>
+      <c r="C47" s="8">
+        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
+        <v>30123845.64</v>
+      </c>
+      <c r="D47" s="53">
+        <f>Данные!$B$66</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="16" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="16" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D50" s="29" t="inlineStr">
+        <is>
+          <t>Что зафиксировано в документах</t>
+        </is>
+      </c>
+    </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Вся территория + 100 % предоплата</t>
-        </is>
-      </c>
-      <c r="B51" s="7">
-        <f>C51/12</f>
-        <v>2988476.75</v>
-      </c>
-      <c r="C51" s="8">
-        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
-        <v>35861721</v>
-      </c>
-      <c r="D51" s="52">
-        <f>Данные!$B$65</f>
-        <v>0.15</v>
-      </c>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D51" s="30" t="inlineStr">
+        <is>
+          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+        </is>
+      </c>
+      <c r="E51" s="50" t="n"/>
+      <c r="F51" s="50" t="n"/>
+      <c r="G51" s="49" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Вся территория + предоплата + неплательщик НДС</t>
-        </is>
-      </c>
-      <c r="B52" s="7">
-        <f>C52/12</f>
-        <v>2510320.47</v>
-      </c>
-      <c r="C52" s="8">
-        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
-        <v>30123845.64</v>
-      </c>
-      <c r="D52" s="52">
-        <f>Данные!$B$66</f>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="53"/>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>выезд по запросу</t>
+        </is>
+      </c>
+      <c r="E52" s="50" t="n"/>
+      <c r="F52" s="50" t="n"/>
+      <c r="G52" s="49" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>дополнительные визиты по вызову</t>
+        </is>
+      </c>
+      <c r="E53" s="50" t="n"/>
+      <c r="F53" s="50" t="n"/>
+      <c r="G53" s="49" t="n"/>
+    </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="16" t="n"/>
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="30" t="inlineStr">
+        <is>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
+        </is>
+      </c>
+      <c r="E54" s="50" t="n"/>
+      <c r="F54" s="50" t="n"/>
+      <c r="G54" s="49" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D55" s="29" t="inlineStr">
-        <is>
-          <t>Что зафиксировано в документах</t>
-        </is>
-      </c>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>выезд по рекламации за два рабочих дня</t>
+        </is>
+      </c>
+      <c r="E55" s="50" t="n"/>
+      <c r="F55" s="50" t="n"/>
+      <c r="G55" s="49" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Indigo Solutions</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -1730,155 +1831,39 @@
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C56" s="21" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
+      <c r="C56" s="24" t="n">
+        <v>8</v>
       </c>
       <c r="D56" s="30" t="inlineStr">
         <is>
-          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
-        </is>
-      </c>
-      <c r="E56" s="53" t="n"/>
-      <c r="F56" s="53" t="n"/>
+          <t>присутствие 5/2, реакция в тот же день</t>
+        </is>
+      </c>
+      <c r="E56" s="50" t="n"/>
+      <c r="F56" s="50" t="n"/>
       <c r="G56" s="49" t="n"/>
     </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>ККЗ</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="30" t="inlineStr">
-        <is>
-          <t>выезд по запросу</t>
-        </is>
-      </c>
-      <c r="E57" s="53" t="n"/>
-      <c r="F57" s="53" t="n"/>
-      <c r="G57" s="49" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>бройлерные площадки</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="30" t="inlineStr">
-        <is>
-          <t>дополнительные визиты по вызову</t>
-        </is>
-      </c>
-      <c r="E58" s="53" t="n"/>
-      <c r="F58" s="53" t="n"/>
-      <c r="G58" s="49" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" s="30" t="inlineStr">
-        <is>
-          <t>по графику на 2026 год, бригада из трёх человек</t>
-        </is>
-      </c>
-      <c r="E59" s="53" t="n"/>
-      <c r="F59" s="53" t="n"/>
-      <c r="G59" s="49" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="30" t="inlineStr">
-        <is>
-          <t>выезд по рекламации за два рабочих дня</t>
-        </is>
-      </c>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
-      <c r="G60" s="49" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C61" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D61" s="30" t="inlineStr">
-        <is>
-          <t>присутствие 5/2, реакция в тот же день</t>
-        </is>
-      </c>
-      <c r="E61" s="53" t="n"/>
-      <c r="F61" s="53" t="n"/>
-      <c r="G61" s="49" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="D8:E8"/>
+  <mergeCells count="19">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="D56:G56"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="D61:G61"/>
-    <mergeCell ref="D59:G59"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D58:G58"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="E17:G17"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D57:G57"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1907,7 +1892,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/шт разовой закупки, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
         </is>
@@ -1967,17 +1952,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2130,17 +2115,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2166,14 +2151,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2212,7 +2197,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2272,17 +2257,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2491,17 +2476,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2616,17 +2601,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2688,7 +2673,7 @@
     </row>
     <row r="33"/>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
@@ -2712,12 +2697,12 @@
           <t>Площадка</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>1-й контур</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>2-й контур</t>
         </is>
@@ -2870,22 +2855,22 @@
       <c r="D49" s="16" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>₸/мес (разово — цена за шт)</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Мес.</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>За год / разово, ₸</t>
         </is>
@@ -2901,7 +2886,7 @@
         <f>B47*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C51" s="25" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
@@ -2921,7 +2906,7 @@
         <f>C47*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C52" s="25" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
@@ -2941,7 +2926,7 @@
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="20">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2960,7 +2945,7 @@
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="20">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2979,7 +2964,7 @@
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="20">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2998,7 +2983,7 @@
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="20">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3013,8 +2998,8 @@
           <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
-      <c r="B57" s="23" t="n"/>
-      <c r="C57" s="23" t="n"/>
+      <c r="B57" s="26" t="n"/>
+      <c r="C57" s="26" t="n"/>
       <c r="D57" s="14">
         <f>SUM(D51:D56)</f>
         <v>3955237.5</v>
@@ -3022,7 +3007,7 @@
     </row>
     <row r="58"/>
     <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт, разовая закупка), но количество точек по контурам разное — см. таблицу выше.</t>
         </is>
@@ -3061,7 +3046,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
@@ -3121,17 +3106,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3283,17 +3268,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3334,17 +3319,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3370,7 +3355,7 @@
     </row>
     <row r="24"/>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3408,7 +3393,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3468,17 +3453,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3554,17 +3539,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3605,17 +3590,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3641,14 +3626,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3687,7 +3672,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -3747,17 +3732,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3818,7 +3803,7 @@
     </row>
     <row r="12"/>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3856,7 +3841,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -3916,17 +3901,17 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -4062,14 +4047,14 @@
     </row>
     <row r="16"/>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4497,13 +4482,13 @@
           <t>МАТЕРИАЛЫ, ПЕРВЫЙ ГОД ИТОГО (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n"/>
+      <c r="B18" s="26" t="n"/>
       <c r="C18" s="12">
         <f>SUM(C13:C17)</f>
         <v>2974320</v>
       </c>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
       <c r="F18" s="12">
         <f>SUM(F13:F17)</f>
         <v>932960</v>
@@ -4801,7 +4786,7 @@
     </row>
     <row r="31"/>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -5538,7 +5523,7 @@
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
-      <c r="H33" s="23" t="n"/>
+      <c r="H33" s="26" t="n"/>
     </row>
     <row r="34"/>
     <row r="35">

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,22 +741,22 @@
       <c r="A5" s="48" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>месяц (расходники)</t>
+          <t>месяц</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>год (расходники)</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>месяц (расходники)</t>
+          <t>месяц</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>год (расходники)</t>
+          <t>год</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -1053,13 +1054,13 @@
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 5 ДЕРАТИЗАТОРА</t>
         </is>
       </c>
-      <c r="F17" s="50" t="n"/>
-      <c r="G17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
+      <c r="H17" s="49" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
@@ -1082,17 +1083,17 @@
           <t>во сколько раз</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>2 дератизатора</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>5 дератизаторов</t>
         </is>
@@ -1116,19 +1117,19 @@
         <f>IF(G15=0,0,C15/G15)</f>
         <v>2.93108218</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Оклад одного, ₸/мес</t>
         </is>
-      </c>
-      <c r="F19" s="20">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
       </c>
       <c r="G19" s="20">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
+      <c r="H19" s="20">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1148,73 +1149,73 @@
         <f>IF(G15=0,0,E15/G15)</f>
         <v>2.276455166</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>ФОТ в месяц, ₸</t>
         </is>
       </c>
-      <c r="F20" s="20">
+      <c r="G20" s="20">
         <f>2*Данные!$B$12</f>
         <v>516976</v>
       </c>
-      <c r="G20" s="20">
+      <c r="H20" s="20">
         <f>5*Данные!$B$12</f>
         <v>1292440</v>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>ФОТ за год, ₸</t>
         </is>
       </c>
-      <c r="F21" s="20">
+      <c r="G21" s="20">
         <f>2*Данные!$B$12*12</f>
         <v>6203712</v>
       </c>
-      <c r="G21" s="20">
+      <c r="H21" s="20">
         <f>5*Данные!$B$12*12</f>
         <v>15509280</v>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Материалы, первый год, ₸ (не завис. от численности)</t>
         </is>
-      </c>
-      <c r="F22" s="20">
-        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
-        <v>4526799.25</v>
       </c>
       <c r="G22" s="20">
         <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
         <v>4526799.25</v>
       </c>
+      <c r="H22" s="20">
+        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
+        <v>4526799.25</v>
+      </c>
     </row>
     <row r="23">
-      <c r="E23" s="13" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
         </is>
-      </c>
-      <c r="F23" s="21">
-        <f>F21+F22</f>
-        <v>10730511.25</v>
       </c>
       <c r="G23" s="21">
         <f>G21+G22</f>
+        <v>10730511.25</v>
+      </c>
+      <c r="H23" s="21">
+        <f>H21+H22</f>
         <v>20036079.25</v>
       </c>
     </row>
     <row r="24">
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Разница 5 против 2 чел., ₸/год</t>
         </is>
       </c>
-      <c r="G24" s="22">
-        <f>G23-F23</f>
+      <c r="H24" s="22">
+        <f>H23-G23</f>
         <v>9305568</v>
       </c>
     </row>
@@ -1848,6 +1849,7 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="D56:G56"/>
     <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="D55:G55"/>
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="D54:G54"/>
@@ -1861,7 +1863,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D53:G53"/>
-    <mergeCell ref="E17:G17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -246,6 +246,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -292,12 +298,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -695,9 +695,9 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,7 +1062,7 @@
       <c r="G17" s="50" t="n"/>
       <c r="H17" s="49" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Показатель</t>
@@ -1083,17 +1083,17 @@
           <t>во сколько раз</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>2 дератизатора</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>5 дератизаторов</t>
         </is>
@@ -1122,11 +1122,11 @@
           <t>Оклад одного, ₸/мес</t>
         </is>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="22">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="22">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
@@ -1154,11 +1154,11 @@
           <t>ФОТ в месяц, ₸</t>
         </is>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="22">
         <f>2*Данные!$B$12</f>
         <v>516976</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="22">
         <f>5*Данные!$B$12</f>
         <v>1292440</v>
       </c>
@@ -1169,11 +1169,11 @@
           <t>ФОТ за год, ₸</t>
         </is>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="22">
         <f>2*Данные!$B$12*12</f>
         <v>6203712</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="22">
         <f>5*Данные!$B$12*12</f>
         <v>15509280</v>
       </c>
@@ -1181,14 +1181,14 @@
     <row r="22">
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Материалы, первый год, ₸ (не завис. от численности)</t>
-        </is>
-      </c>
-      <c r="G22" s="20">
+          <t>Материалы, первый год, ₸</t>
+        </is>
+      </c>
+      <c r="G22" s="22">
         <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
         <v>4526799.25</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="22">
         <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
         <v>4526799.25</v>
       </c>
@@ -1199,11 +1199,11 @@
           <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
         </is>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="23">
         <f>G21+G22</f>
         <v>10730511.25</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="23">
         <f>H21+H22</f>
         <v>20036079.25</v>
       </c>
@@ -1214,7 +1214,7 @@
           <t>Разница 5 против 2 чел., ₸/год</t>
         </is>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="24">
         <f>H23-G23</f>
         <v>9305568</v>
       </c>
@@ -1234,7 +1234,7 @@
       <c r="G26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
@@ -1275,7 +1275,7 @@
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="B29" s="10" t="n"/>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -1313,7 +1313,7 @@
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
@@ -1341,7 +1341,7 @@
         <f>Данные!$B$33+Данные!$C$33</f>
         <v>1377</v>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -1366,7 +1366,7 @@
         <f>Данные!$D$33</f>
         <v>343</v>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
@@ -1394,7 +1394,7 @@
         <f>Данные!$D$33*2</f>
         <v>686</v>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
@@ -1422,7 +1422,7 @@
         <f>Данные!$G$33</f>
         <v>16</v>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
@@ -1450,7 +1450,7 @@
         <f>Данные!$F$33</f>
         <v>20.3</v>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
@@ -1478,7 +1478,7 @@
         <f>Данные!$C$33</f>
         <v>1198</v>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -1497,7 +1497,7 @@
         <f>Данные!$F$33/Данные!$C$33</f>
         <v>0.01694490818</v>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
@@ -1516,7 +1516,7 @@
         <f>Данные!$B$11</f>
         <v>40</v>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
@@ -1540,9 +1540,9 @@
           <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B39" s="26" t="n"/>
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="26" t="n"/>
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="28" t="n"/>
       <c r="E39" s="14">
         <f>F39/12</f>
         <v>1411185.271</v>
@@ -1553,7 +1553,7 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -1683,22 +1683,22 @@
       <c r="G49" s="16" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="31" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B50" s="29" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C50" s="29" t="inlineStr">
+      <c r="C50" s="31" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D50" s="29" t="inlineStr">
+      <c r="D50" s="31" t="inlineStr">
         <is>
           <t>Что зафиксировано в документах</t>
         </is>
@@ -1715,12 +1715,12 @@
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D51" s="30" t="inlineStr">
+      <c r="D51" s="32" t="inlineStr">
         <is>
           <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
         </is>
@@ -1740,10 +1740,10 @@
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="C52" s="24" t="n">
+      <c r="C52" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="30" t="inlineStr">
+      <c r="D52" s="32" t="inlineStr">
         <is>
           <t>выезд по запросу</t>
         </is>
@@ -1763,10 +1763,10 @@
           <t>бройлерные площадки</t>
         </is>
       </c>
-      <c r="C53" s="24" t="n">
+      <c r="C53" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D53" s="30" t="inlineStr">
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t>дополнительные визиты по вызову</t>
         </is>
@@ -1786,10 +1786,10 @@
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="C54" s="24" t="n">
+      <c r="C54" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="30" t="inlineStr">
+      <c r="D54" s="32" t="inlineStr">
         <is>
           <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
@@ -1809,10 +1809,10 @@
           <t>склад ТМЦ</t>
         </is>
       </c>
-      <c r="C55" s="24" t="n">
+      <c r="C55" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="30" t="inlineStr">
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>выезд по рекламации за два рабочих дня</t>
         </is>
@@ -1832,10 +1832,10 @@
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C56" s="24" t="n">
+      <c r="C56" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="D56" s="30" t="inlineStr">
+      <c r="D56" s="32" t="inlineStr">
         <is>
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
@@ -1893,7 +1893,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/шт разовой закупки, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
         </is>
@@ -1901,37 +1901,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11+D12+D13+D14+D15</f>
         <v>88137.5</v>
       </c>
@@ -1970,16 +1970,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$37</f>
         <v>96600</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -1988,16 +1988,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · дератизация</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$53</f>
         <v>75000</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -2006,16 +2006,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="8">
@@ -2024,16 +2024,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2043,16 +2043,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2062,16 +2062,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2081,16 +2081,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2133,16 +2133,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="37">
         <f>Данные!$B$54</f>
         <v>70000</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -2152,14 +2152,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2198,7 +2198,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2206,37 +2206,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D12+D13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D14+D15+D16+D17+D18</f>
         <v>3955237.5</v>
       </c>
@@ -2275,16 +2275,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$38</f>
         <v>618400</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -2293,16 +2293,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$40</f>
         <v>569800</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -2311,16 +2311,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>Данные!$B$42</f>
         <v>2599100</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="8">
@@ -2329,16 +2329,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$B$55</f>
         <v>3172000</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2348,16 +2348,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$B$56</f>
         <v>2074000</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2367,16 +2367,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>(SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30))*Данные!$B$9</f>
         <v>2715120</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="8">
@@ -2385,16 +2385,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2404,16 +2404,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="37">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="37">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2423,16 +2423,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="37">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2442,16 +2442,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="37">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2494,16 +2494,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="37">
         <f>Данные!$B$39</f>
         <v>478400</v>
       </c>
-      <c r="C22" s="35" t="n">
+      <c r="C22" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D22" s="7">
@@ -2512,16 +2512,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="37">
         <f>Данные!$B$41</f>
         <v>440700</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="7">
@@ -2530,16 +2530,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="37">
         <f>Данные!$B$43</f>
         <v>2010300</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="7">
@@ -2548,16 +2548,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="37">
         <f>Данные!$B$57</f>
         <v>2806000</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="37">
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
@@ -2567,16 +2567,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="37">
         <f>Данные!$B$58</f>
         <v>1830000</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="37">
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
@@ -2619,16 +2619,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="37">
         <f>Данные!$B$48</f>
         <v>720000</v>
       </c>
-      <c r="C30" s="35" t="n">
+      <c r="C30" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D30" s="7">
@@ -2637,16 +2637,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="37">
         <f>Данные!$B$49</f>
         <v>1080000</v>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="7">
@@ -2655,16 +2655,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="37">
         <f>Данные!$B$50</f>
         <v>3000000</v>
       </c>
-      <c r="C32" s="35" t="n">
+      <c r="C32" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D32" s="7">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="33"/>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
@@ -2715,11 +2715,11 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B39" s="36">
+      <c r="B39" s="38">
         <f>Данные!$B$23</f>
         <v>13</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="38">
         <f>Данные!$C$23</f>
         <v>147</v>
       </c>
@@ -2730,11 +2730,11 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B40" s="36">
+      <c r="B40" s="38">
         <f>Данные!$B$24</f>
         <v>17</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="38">
         <f>Данные!$C$24</f>
         <v>146</v>
       </c>
@@ -2745,11 +2745,11 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B41" s="36">
+      <c r="B41" s="38">
         <f>Данные!$B$25</f>
         <v>50</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="38">
         <f>Данные!$C$25</f>
         <v>239</v>
       </c>
@@ -2760,11 +2760,11 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B42" s="36">
+      <c r="B42" s="38">
         <f>Данные!$B$26</f>
         <v>17</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="38">
         <f>Данные!$C$26</f>
         <v>88</v>
       </c>
@@ -2775,11 +2775,11 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B43" s="36">
+      <c r="B43" s="38">
         <f>Данные!$B$27</f>
         <v>15</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="38">
         <f>Данные!$C$27</f>
         <v>69</v>
       </c>
@@ -2790,11 +2790,11 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B44" s="36">
+      <c r="B44" s="38">
         <f>Данные!$B$28</f>
         <v>13</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="38">
         <f>Данные!$C$28</f>
         <v>147</v>
       </c>
@@ -2805,11 +2805,11 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B45" s="36">
+      <c r="B45" s="38">
         <f>Данные!$B$29</f>
         <v>17</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="38">
         <f>Данные!$C$29</f>
         <v>73</v>
       </c>
@@ -2820,11 +2820,11 @@
           <t>Айыртау</t>
         </is>
       </c>
-      <c r="B46" s="36">
+      <c r="B46" s="38">
         <f>Данные!$B$30</f>
         <v>19</v>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="38">
         <f>Данные!$C$30</f>
         <v>187</v>
       </c>
@@ -2835,11 +2835,11 @@
           <t>Итого по площадкам</t>
         </is>
       </c>
-      <c r="B47" s="37">
+      <c r="B47" s="39">
         <f>SUM(B39:B46)</f>
         <v>161</v>
       </c>
-      <c r="C47" s="37">
+      <c r="C47" s="39">
         <f>SUM(C39:C46)</f>
         <v>1096</v>
       </c>
@@ -2856,7 +2856,7 @@
       <c r="D49" s="16" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="25" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
@@ -2887,7 +2887,7 @@
         <f>B47*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
@@ -2907,7 +2907,7 @@
         <f>C47*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
@@ -2927,7 +2927,7 @@
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="22">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2946,7 +2946,7 @@
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="22">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2965,7 +2965,7 @@
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="22">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2984,7 +2984,7 @@
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="22">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2999,8 +2999,8 @@
           <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
-      <c r="B57" s="26" t="n"/>
-      <c r="C57" s="26" t="n"/>
+      <c r="B57" s="28" t="n"/>
+      <c r="C57" s="28" t="n"/>
       <c r="D57" s="14">
         <f>SUM(D51:D56)</f>
         <v>3955237.5</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="58"/>
     <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="27" t="inlineStr">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт, разовая закупка), но количество точек по контурам разное — см. таблицу выше.</t>
         </is>
@@ -3047,7 +3047,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
@@ -3055,37 +3055,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11+D12+D13+D14+D15</f>
         <v>175637.5</v>
       </c>
@@ -3124,16 +3124,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$44</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -3142,15 +3142,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -3159,16 +3159,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
         <v>112320</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="8">
@@ -3177,16 +3177,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3196,16 +3196,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -3215,16 +3215,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3234,16 +3234,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3286,16 +3286,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="37">
         <f>Данные!$B$45</f>
         <v>106800</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -3337,16 +3337,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="37">
         <f>Данные!$B$51</f>
         <v>100800</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="7">
@@ -3356,7 +3356,7 @@
     </row>
     <row r="24"/>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3394,7 +3394,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3402,37 +3402,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3471,16 +3471,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$46</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="8">
@@ -3489,16 +3489,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$59</f>
         <v>180000</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="8">
@@ -3507,15 +3507,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3557,16 +3557,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$B$47</f>
         <v>106800</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="7">
@@ -3608,16 +3608,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="37">
         <f>Данные!$B$52</f>
         <v>160800</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="7">
@@ -3627,14 +3627,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3673,7 +3673,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -3681,37 +3681,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>720000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3750,15 +3750,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3767,16 +3767,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$60</f>
         <v>80000</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="37">
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
@@ -3786,15 +3786,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="8">
@@ -3804,7 +3804,7 @@
     </row>
     <row r="12"/>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3842,7 +3842,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -3850,37 +3850,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11+D12+D13+D14+D15</f>
         <v>288746.75</v>
       </c>
@@ -3919,15 +3919,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="8">
@@ -3936,15 +3936,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="8">
@@ -3953,16 +3953,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>(Данные!$B$22+Данные!$C$22)*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="8">
@@ -3971,16 +3971,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$D$22*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3990,16 +3990,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$D$22*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -4009,16 +4009,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>Данные!$G$22*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -4028,16 +4028,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$F$22*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -4048,14 +4048,14 @@
     </row>
     <row r="16"/>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4118,17 +4118,17 @@
       <c r="E4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
@@ -4180,7 +4180,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -4213,57 +4213,57 @@
       <c r="K11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Станций 1–2 к., шт</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Станции 1–2 к., разово, ₸</t>
         </is>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="40" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="40" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="40" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="J12" s="40" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="K12" s="40" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
@@ -4483,13 +4483,13 @@
           <t>МАТЕРИАЛЫ, ПЕРВЫЙ ГОД ИТОГО (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n"/>
+      <c r="B18" s="28" t="n"/>
       <c r="C18" s="12">
         <f>SUM(C13:C17)</f>
         <v>2974320</v>
       </c>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
       <c r="F18" s="12">
         <f>SUM(F13:F17)</f>
         <v>932960</v>
@@ -4529,32 +4529,32 @@
       <c r="F20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D21" s="40" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E21" s="40" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F21" s="40" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
@@ -4787,7 +4787,7 @@
     </row>
     <row r="31"/>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -4851,26 +4851,26 @@
       <c r="H4" s="16" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr"/>
-      <c r="E5" s="29" t="inlineStr"/>
-      <c r="F5" s="29" t="inlineStr"/>
-      <c r="G5" s="29" t="inlineStr"/>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="D5" s="31" t="inlineStr"/>
+      <c r="E5" s="31" t="inlineStr"/>
+      <c r="F5" s="31" t="inlineStr"/>
+      <c r="G5" s="31" t="inlineStr"/>
+      <c r="H5" s="31" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
@@ -5112,42 +5112,42 @@
       <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="40" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="40" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -5524,7 +5524,7 @@
         <f>SUM(G20:G32)</f>
         <v>16</v>
       </c>
-      <c r="H33" s="26" t="n"/>
+      <c r="H33" s="28" t="n"/>
     </row>
     <row r="34"/>
     <row r="35">
@@ -5542,26 +5542,26 @@
       <c r="H35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
+      <c r="C36" s="31" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D36" s="29" t="inlineStr"/>
-      <c r="E36" s="29" t="inlineStr"/>
-      <c r="F36" s="29" t="inlineStr"/>
-      <c r="G36" s="29" t="inlineStr"/>
-      <c r="H36" s="29" t="inlineStr">
+      <c r="D36" s="31" t="inlineStr"/>
+      <c r="E36" s="31" t="inlineStr"/>
+      <c r="F36" s="31" t="inlineStr"/>
+      <c r="G36" s="31" t="inlineStr"/>
+      <c r="H36" s="31" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -695,9 +695,9 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -155,7 +155,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -166,9 +168,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00C8C2AE"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -224,19 +224,34 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -246,22 +261,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -307,9 +307,9 @@
     </xf>
     <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -695,9 +695,12 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -736,380 +739,454 @@
           <t>Штат УКПФ</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 5 ДЕРАТИЗАТОРА</t>
+        </is>
+      </c>
+      <c r="J4" s="48" t="n"/>
+      <c r="K4" s="49" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="48" t="n"/>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="50" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>год</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>год</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>месяц (расходники)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>год (расходники)</t>
         </is>
       </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>2 дератизатора</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>5 дератизаторов</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <f>C6/12</f>
         <v>96600</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <f>'ККЗ'!B5</f>
         <v>1159200</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="10">
         <f>E6/12</f>
         <v>75000</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <f>'ККЗ'!C5</f>
         <v>900000</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="10">
         <f>G6/12</f>
         <v>7344.791667</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="11">
         <f>'ККЗ'!D5</f>
         <v>88137.5</v>
       </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Оклад одного, ₸/мес</t>
+        </is>
+      </c>
+      <c r="J6" s="12">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+      <c r="K6" s="12">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Бройлерные площадки</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <f>C7/12</f>
         <v>3787300</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <f>'Бройлерные площадки'!B5</f>
         <v>45447600</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="10">
         <f>E7/12</f>
         <v>2897500</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <f>'Бройлерные площадки'!C5</f>
         <v>34770000</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="10">
         <f>G7/12</f>
         <v>329603.125</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="11">
         <f>'Бройлерные площадки'!D5</f>
         <v>3955237.5</v>
       </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>ФОТ в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="J7" s="12">
+        <f>2*Данные!$B$12</f>
+        <v>516976</v>
+      </c>
+      <c r="K7" s="12">
+        <f>5*Данные!$B$12</f>
+        <v>1292440</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <f>C8/12</f>
         <v>126200</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <f>'Инкубаторий'!B5</f>
         <v>1514400</v>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
       <c r="E8" s="49" t="n"/>
-      <c r="F8" s="7">
+      <c r="F8" s="10">
         <f>G8/12</f>
         <v>14636.45833</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="11">
         <f>'Инкубаторий'!D5</f>
         <v>175637.5</v>
       </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>ФОТ за год, ₸</t>
+        </is>
+      </c>
+      <c r="J8" s="12">
+        <f>2*Данные!$B$12*12</f>
+        <v>6203712</v>
+      </c>
+      <c r="K8" s="12">
+        <f>5*Данные!$B$12*12</f>
+        <v>15509280</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <f>C9/12</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <f>'ЗПП'!B5</f>
         <v>1514400</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="10">
         <f>E9/12</f>
         <v>180000</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <f>'ЗПП'!C5</f>
         <v>2160000</v>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>нормы не заданы</t>
         </is>
       </c>
       <c r="G9" s="49" t="n"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Материалы, первый год, ₸</t>
+        </is>
+      </c>
+      <c r="J9" s="12">
+        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
+        <v>4526799.25</v>
+      </c>
+      <c r="K9" s="12">
+        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
+        <v>4526799.25</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Склад ТМЦ</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
       <c r="C10" s="49" t="n"/>
-      <c r="D10" s="7">
+      <c r="D10" s="10">
         <f>E10/12</f>
         <v>60000</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <f>'Склад ТМЦ'!C5</f>
         <v>720000</v>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>нормы не заданы</t>
         </is>
       </c>
       <c r="G10" s="49" t="n"/>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
+        </is>
+      </c>
+      <c r="J10" s="15">
+        <f>J8+J9</f>
+        <v>10730511.25</v>
+      </c>
+      <c r="K10" s="15">
+        <f>K8+K9</f>
+        <v>20036079.25</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
       <c r="C11" s="49" t="n"/>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
       <c r="E11" s="49" t="n"/>
-      <c r="F11" s="7">
+      <c r="F11" s="10">
         <f>G11/12</f>
         <v>24062.22917</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="11">
         <f>'АБК'!D5</f>
         <v>288746.75</v>
       </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Разница 5 против 2 чел., ₸/год</t>
+        </is>
+      </c>
+      <c r="K11" s="16">
+        <f>K10-J10</f>
+        <v>9305568</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Сумма по объектам</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="18">
         <f>C12/12</f>
         <v>4136300</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="18">
         <f>SUM(C6:C11)</f>
         <v>49635600</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="18">
         <f>E12/12</f>
         <v>3212500</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="18">
         <f>SUM(E6:E11)</f>
         <v>38550000</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="18">
         <f>G12/12</f>
         <v>375646.6042</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="18">
         <f>SUM(G6:G11)</f>
         <v>4507759.25</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Бутылки · 1-й контур</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="7">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="10">
         <f>G13/12</f>
         <v>1586.666667</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="10">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Фонд оплаты труда дератизаторов</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="7">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="10">
         <f>G14/12</f>
         <v>1033952</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="10">
         <f>Данные!$B$14*Данные!$B$12*12</f>
         <v>12407424</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>ВСЕГО ЗА ГОД</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="19">
         <f>C15/12</f>
         <v>4136300</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="19">
         <f>C12</f>
         <v>49635600</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="19">
         <f>E15/12</f>
         <v>3212500</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="19">
         <f>E12</f>
         <v>38550000</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="19">
         <f>G15/12</f>
         <v>1411185.271</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="19">
         <f>G12+G13+G14</f>
         <v>16934223.25</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 5 ДЕРАТИЗАТОРА</t>
-        </is>
-      </c>
-      <c r="G17" s="50" t="n"/>
-      <c r="H17" s="49" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>во сколько раз</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>2 дератизатора</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>5 дератизаторов</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Indigo Solutions дороже штата</t>
         </is>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="10">
         <f>C19/12</f>
         <v>2725114.729</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <f>C15-G15</f>
         <v>32701376.75</v>
       </c>
@@ -1117,31 +1194,18 @@
         <f>IF(G15=0,0,C15/G15)</f>
         <v>2.93108218</v>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Оклад одного, ₸/мес</t>
-        </is>
-      </c>
-      <c r="G19" s="22">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
-      <c r="H19" s="22">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters дороже штата</t>
         </is>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="10">
         <f>C20/12</f>
         <v>1801314.729</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <f>E15-G15</f>
         <v>21615776.75</v>
       </c>
@@ -1149,720 +1213,651 @@
         <f>IF(G15=0,0,E15/G15)</f>
         <v>2.276455166</v>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>ФОТ в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="G20" s="22">
-        <f>2*Данные!$B$12</f>
-        <v>516976</v>
-      </c>
-      <c r="H20" s="22">
-        <f>5*Данные!$B$12</f>
-        <v>1292440</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>ФОТ за год, ₸</t>
-        </is>
-      </c>
-      <c r="G21" s="22">
-        <f>2*Данные!$B$12*12</f>
-        <v>6203712</v>
-      </c>
-      <c r="H21" s="22">
-        <f>5*Данные!$B$12*12</f>
-        <v>15509280</v>
-      </c>
-    </row>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Материалы, первый год, ₸</t>
-        </is>
-      </c>
-      <c r="G22" s="22">
-        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="H22" s="22">
-        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
-        <v>4526799.25</v>
-      </c>
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
     </row>
     <row r="23">
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
-        </is>
-      </c>
-      <c r="G23" s="23">
-        <f>G21+G22</f>
-        <v>10730511.25</v>
-      </c>
-      <c r="H23" s="23">
-        <f>H21+H22</f>
-        <v>20036079.25</v>
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Цена за ед., ₸</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>за год, ₸</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Разница 5 против 2 чел., ₸/год</t>
-        </is>
-      </c>
-      <c r="H24" s="24">
-        <f>H23-G23</f>
-        <v>9305568</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Ед. изм.</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Цена за ед., ₸</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>за год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B28" s="7">
+      <c r="B24" s="10">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Оклад одного дератизатора</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="D29" s="7">
+      <c r="D25" s="10">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Фонд оплаты труда</t>
         </is>
       </c>
-      <c r="B30" s="7">
+      <c r="B26" s="10">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="D30" s="7">
+      <c r="D26" s="10">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E26" s="10">
         <f>Данные!$B$14*Данные!$B$12</f>
         <v>1033952</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F26" s="11">
         <f>Данные!$B$14*Данные!$B$12*12</f>
         <v>12407424</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B31" s="7">
+      <c r="B27" s="10">
         <f>Данные!$B$33+Данные!$C$33</f>
         <v>1377</v>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D31" s="7">
+      <c r="D27" s="10">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="8">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="11">
         <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9</f>
         <v>2974320</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура · апрель — октябрь</t>
         </is>
       </c>
-      <c r="B32" s="7">
+      <c r="B28" s="10">
         <f>Данные!$D$33</f>
         <v>343</v>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D32" s="7">
+      <c r="D28" s="10">
         <f>Данные!$B$8</f>
         <v>160</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E28" s="10">
         <f>Данные!$D$33*Данные!$B$8</f>
         <v>54880</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F28" s="11">
         <f>Данные!$D$33*Данные!$B$8*Данные!$B$15</f>
         <v>384160</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
         </is>
       </c>
-      <c r="B33" s="7">
+      <c r="B29" s="10">
         <f>Данные!$D$33*2</f>
         <v>686</v>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D33" s="7">
+      <c r="D29" s="10">
         <f>Данные!$B$8</f>
         <v>160</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E29" s="10">
         <f>Данные!$D$33*2*Данные!$B$8</f>
         <v>109760</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F29" s="11">
         <f>Данные!$D$33*2*Данные!$B$8*Данные!$B$16</f>
         <v>548800</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Зерноцид · 2-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B34" s="7">
+      <c r="B30" s="10">
         <f>Данные!$G$33</f>
         <v>16</v>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D34" s="7">
+      <c r="D30" s="10">
         <f>Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E30" s="10">
         <f>Данные!$G$33*Данные!$B$6</f>
         <v>11840</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F30" s="11">
         <f>Данные!$G$33*Данные!$B$6*Данные!$B$15</f>
         <v>82880</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
         </is>
       </c>
-      <c r="B35" s="7">
+      <c r="B31" s="10">
         <f>Данные!$F$33</f>
         <v>20.3</v>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D35" s="7">
+      <c r="D31" s="10">
         <f>Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E31" s="10">
         <f>Данные!$F$33*Данные!$B$7</f>
         <v>73942.75</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F31" s="11">
         <f>Данные!$F$33*Данные!$B$7*Данные!$B$15</f>
         <v>517599.25</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
         </is>
       </c>
-      <c r="B36" s="7">
+      <c r="B32" s="10">
         <f>Данные!$C$33</f>
         <v>1198</v>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
         </is>
       </c>
-      <c r="B37" s="52">
+      <c r="B33" s="52">
         <f>Данные!$F$33/Данные!$C$33</f>
         <v>0.01694490818</v>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Бутылки · тёплый сезон</t>
         </is>
       </c>
-      <c r="B38" s="7">
+      <c r="B34" s="10">
         <f>Данные!$B$11</f>
         <v>40</v>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D38" s="7">
+      <c r="D34" s="10">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E34" s="10">
         <f>Данные!$B$11*Данные!$B$10</f>
         <v>2720</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F34" s="11">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="19">
+        <f>F35/12</f>
+        <v>1411185.271</v>
+      </c>
+      <c r="F35" s="19">
+        <f>F26+F27+F28+F29+F30+F31+F34</f>
+        <v>16934223.25</v>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="21" t="n"/>
+    </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
-        </is>
-      </c>
-      <c r="B39" s="28" t="n"/>
-      <c r="C39" s="28" t="n"/>
-      <c r="D39" s="28" t="n"/>
-      <c r="E39" s="14">
-        <f>F39/12</f>
-        <v>1411185.271</v>
-      </c>
-      <c r="F39" s="14">
-        <f>F30+F31+F32+F33+F34+F35+F38</f>
-        <v>16934223.25</v>
-      </c>
-    </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>Условие</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>Ставка</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Цена КП без скидок</t>
         </is>
       </c>
-      <c r="B44" s="7">
-        <f>C44/12</f>
+      <c r="B40" s="10">
+        <f>C40/12</f>
         <v>4136300</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C40" s="11">
         <f>C15</f>
         <v>49635600</v>
       </c>
-      <c r="D44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="D40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B45" s="7">
-        <f>C45/12</f>
+      <c r="B41" s="10">
+        <f>C41/12</f>
         <v>3515855</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C41" s="11">
         <f>C15*(1-Данные!$B$64)</f>
         <v>42190260</v>
       </c>
-      <c r="D45" s="53">
+      <c r="D41" s="53">
         <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
-      <c r="B46" s="7">
-        <f>C46/12</f>
+      <c r="B42" s="10">
+        <f>C42/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="C46" s="8">
+      <c r="C42" s="11">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
         <v>35861721</v>
       </c>
-      <c r="D46" s="53">
+      <c r="D42" s="53">
         <f>Данные!$B$65</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
-      <c r="B47" s="7">
-        <f>C47/12</f>
+      <c r="B43" s="10">
+        <f>C43/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C43" s="11">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D47" s="53">
+      <c r="D43" s="53">
         <f>Данные!$B$66</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="48"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="n"/>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>Что зафиксировано в документах</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
+        <is>
+          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+        </is>
+      </c>
+      <c r="E47" s="48" t="n"/>
+      <c r="F47" s="48" t="n"/>
+      <c r="G47" s="49" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>выезд по запросу</t>
+        </is>
+      </c>
+      <c r="E48" s="48" t="n"/>
+      <c r="F48" s="48" t="n"/>
+      <c r="G48" s="49" t="n"/>
+    </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="16" t="n"/>
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
+        <is>
+          <t>дополнительные визиты по вызову</t>
+        </is>
+      </c>
+      <c r="E49" s="48" t="n"/>
+      <c r="F49" s="48" t="n"/>
+      <c r="G49" s="49" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="31" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B50" s="31" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="C50" s="31" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D50" s="31" t="inlineStr">
-        <is>
-          <t>Что зафиксировано в документах</t>
-        </is>
-      </c>
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
+        </is>
+      </c>
+      <c r="E50" s="48" t="n"/>
+      <c r="F50" s="48" t="n"/>
+      <c r="G50" s="49" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>выезд по рекламации за два рабочих дня</t>
+        </is>
+      </c>
+      <c r="E51" s="48" t="n"/>
+      <c r="F51" s="48" t="n"/>
+      <c r="G51" s="49" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Штат УКПФ</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="inlineStr">
-        <is>
-          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
-        </is>
-      </c>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="49" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>ККЗ</t>
-        </is>
-      </c>
       <c r="C52" s="26" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D52" s="32" t="inlineStr">
         <is>
-          <t>выезд по запросу</t>
-        </is>
-      </c>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="50" t="n"/>
+          <t>присутствие 5/2, реакция в тот же день</t>
+        </is>
+      </c>
+      <c r="E52" s="48" t="n"/>
+      <c r="F52" s="48" t="n"/>
       <c r="G52" s="49" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>бройлерные площадки</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="32" t="inlineStr">
-        <is>
-          <t>дополнительные визиты по вызову</t>
-        </is>
-      </c>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="50" t="n"/>
-      <c r="G53" s="49" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" s="32" t="inlineStr">
-        <is>
-          <t>по графику на 2026 год, бригада из трёх человек</t>
-        </is>
-      </c>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="50" t="n"/>
-      <c r="G54" s="49" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="32" t="inlineStr">
-        <is>
-          <t>выезд по рекламации за два рабочих дня</t>
-        </is>
-      </c>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="50" t="n"/>
-      <c r="G55" s="49" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C56" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" s="32" t="inlineStr">
-        <is>
-          <t>присутствие 5/2, реакция в тот же день</t>
-        </is>
-      </c>
-      <c r="E56" s="50" t="n"/>
-      <c r="F56" s="50" t="n"/>
-      <c r="G56" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D56:G56"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="D55:G55"/>
     <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="A40:G40"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D50:G50"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D52:G52"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D49:G49"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D47:G47"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
@@ -1938,32 +1933,32 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -1982,7 +1977,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>1159200</v>
       </c>
@@ -2000,7 +1995,7 @@
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>900000</v>
       </c>
@@ -2018,7 +2013,7 @@
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>62640</v>
       </c>
@@ -2037,7 +2032,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>0</v>
       </c>
@@ -2056,7 +2051,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>0</v>
       </c>
@@ -2075,7 +2070,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>0</v>
       </c>
@@ -2094,39 +2089,39 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2145,7 +2140,7 @@
       <c r="C19" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="10">
         <f>B19*C19</f>
         <v>840000</v>
       </c>
@@ -2243,32 +2238,32 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ОСНОВНОЙ ВАРИАНТ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2287,7 +2282,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>7420800</v>
       </c>
@@ -2305,7 +2300,7 @@
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>6837600</v>
       </c>
@@ -2323,7 +2318,7 @@
       <c r="C11" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>31189200</v>
       </c>
@@ -2342,7 +2337,7 @@
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>28548000</v>
       </c>
@@ -2361,7 +2356,7 @@
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>6222000</v>
       </c>
@@ -2379,7 +2374,7 @@
       <c r="C14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>2715120</v>
       </c>
@@ -2398,7 +2393,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>300160</v>
       </c>
@@ -2417,7 +2412,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="11">
         <f>B16*C16</f>
         <v>428800</v>
       </c>
@@ -2436,7 +2431,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="11">
         <f>B17*C17</f>
         <v>77700</v>
       </c>
@@ -2455,39 +2450,39 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="11">
         <f>B18*C18</f>
         <v>433457.5</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2506,7 +2501,7 @@
       <c r="C22" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="10">
         <f>B22*C22</f>
         <v>5740800</v>
       </c>
@@ -2524,7 +2519,7 @@
       <c r="C23" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="10">
         <f>B23*C23</f>
         <v>5288400</v>
       </c>
@@ -2542,7 +2537,7 @@
       <c r="C24" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="10">
         <f>B24*C24</f>
         <v>24123600</v>
       </c>
@@ -2561,7 +2556,7 @@
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="10">
         <f>B25*C25</f>
         <v>25254000</v>
       </c>
@@ -2580,39 +2575,39 @@
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="10">
         <f>B26*C26</f>
         <v>5490000</v>
       </c>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -2631,7 +2626,7 @@
       <c r="C30" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="10">
         <f>B30*C30</f>
         <v>8640000</v>
       </c>
@@ -2649,7 +2644,7 @@
       <c r="C31" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="10">
         <f>B31*C31</f>
         <v>12960000</v>
       </c>
@@ -2667,7 +2662,7 @@
       <c r="C32" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="10">
         <f>B32*C32</f>
         <v>36000000</v>
       </c>
@@ -2683,34 +2678,34 @@
     <row r="35"/>
     <row r="36"/>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>КОНТУР 1 И КОНТУР 2 ПО ПЛОЩАДКАМ, шт</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="21" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>Площадка</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>1-й контур</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>2-й контур</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Площадка А</t>
         </is>
@@ -2725,7 +2720,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Площадка Б</t>
         </is>
@@ -2740,7 +2735,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>В / Восточка</t>
         </is>
@@ -2755,7 +2750,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Площадка Г</t>
         </is>
@@ -2770,7 +2765,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Площадка Д</t>
         </is>
@@ -2785,7 +2780,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Площадка Е</t>
         </is>
@@ -2800,7 +2795,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Площадка Ж</t>
         </is>
@@ -2815,7 +2810,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Айыртау</t>
         </is>
@@ -2830,7 +2825,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>Итого по площадкам</t>
         </is>
@@ -2846,14 +2841,14 @@
     </row>
     <row r="48"/>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>ШТАТ УКПФ ПО БРОЙЛЕРНЫМ ПЛОЩАДКАМ — ДЕТАЛЬНАЯ РАСШИФРОВКА</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="25" t="inlineStr">
@@ -2861,147 +2856,147 @@
           <t>Статья</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>₸/мес (разово — цена за шт)</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>Мес.</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>За год / разово, ₸</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="10">
         <f>B47*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="10">
         <f>B47*Данные!$B$9</f>
         <v>347760</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Приманочные станции 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="10">
         <f>C47*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C52" s="22" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="10">
         <f>C47*Данные!$B$9</f>
         <v>2367360</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="10">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="12">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="10">
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8*Данные!$B$15</f>
         <v>300160</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="10">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="12">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="10">
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8*Данные!$B$16</f>
         <v>428800</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="10">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="12">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="10">
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="10">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="12">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="10">
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7*Данные!$B$15</f>
         <v>433457.5</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
       <c r="B57" s="28" t="n"/>
       <c r="C57" s="28" t="n"/>
-      <c r="D57" s="14">
+      <c r="D57" s="19">
         <f>SUM(D51:D56)</f>
         <v>3955237.5</v>
       </c>
@@ -3092,32 +3087,32 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3136,7 +3131,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>1514400</v>
       </c>
@@ -3153,7 +3148,7 @@
       <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>0</v>
       </c>
@@ -3171,7 +3166,7 @@
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>112320</v>
       </c>
@@ -3190,7 +3185,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>13440</v>
       </c>
@@ -3209,7 +3204,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>19200</v>
       </c>
@@ -3228,7 +3223,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>5180</v>
       </c>
@@ -3247,39 +3242,39 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>25497.5</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3298,39 +3293,39 @@
       <c r="C19" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="10">
         <f>B19*C19</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3349,7 +3344,7 @@
       <c r="C23" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="10">
         <f>B23*C23</f>
         <v>1209600</v>
       </c>
@@ -3439,32 +3434,32 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3483,7 +3478,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>1514400</v>
       </c>
@@ -3501,7 +3496,7 @@
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>2160000</v>
       </c>
@@ -3518,39 +3513,39 @@
       <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3569,39 +3564,39 @@
       <c r="C15" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="10">
         <f>B15*C15</f>
         <v>1281600</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3620,7 +3615,7 @@
       <c r="C19" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="10">
         <f>B19*C19</f>
         <v>1929600</v>
       </c>
@@ -3718,32 +3713,32 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3761,7 +3756,7 @@
       <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>0</v>
       </c>
@@ -3780,7 +3775,7 @@
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>720000</v>
       </c>
@@ -3797,7 +3792,7 @@
       <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>0</v>
       </c>
@@ -3887,32 +3882,32 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
@@ -3930,7 +3925,7 @@
       <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>0</v>
       </c>
@@ -3947,7 +3942,7 @@
       <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>0</v>
       </c>
@@ -3965,7 +3960,7 @@
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>84240</v>
       </c>
@@ -3984,7 +3979,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>70560</v>
       </c>
@@ -4003,7 +3998,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>100800</v>
       </c>
@@ -4022,7 +4017,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>0</v>
       </c>
@@ -4041,7 +4036,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>33146.75</v>
       </c>
@@ -4107,15 +4102,15 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>ФОНД ОПЛАТЫ ТРУДА</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
@@ -4135,46 +4130,46 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Оклад одного дератизатора, ₸/мес</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <f>Данные!$B$12</f>
         <v>258488</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="10">
         <f>Данные!$B$13</f>
         <v>350000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="10">
         <f>Данные!$B$14</f>
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Зарплата в месяц</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <f>B6*B7</f>
         <v>1033952</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="10">
         <f>C6*C7</f>
         <v>1400000</v>
       </c>
@@ -4185,92 +4180,92 @@
           <t>Зарплата за год</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="11">
         <f>B8*12</f>
         <v>12407424</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <f>C8*12</f>
         <v>16800000</v>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ (РАЗОВАЯ ЗАКУПКА) И ЯДЫ (ТОЛЬКО ТЁПЛЫЙ СЕЗОН) РАЗДЕЛЬНО</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Станций 1–2 к., шт</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Станции 1–2 к., разово, ₸</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес лето</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Клеевых 3-го к., шт/мес зима</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Клеевые за год, ₸</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Зерноцид, кг/мес</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Зерноцид за год, ₸</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Pest Killer, кг/мес</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Pest Killer за год, ₸</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
@@ -4279,7 +4274,7 @@
         <f>Данные!$B$20+Данные!$C$20</f>
         <v>29</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="10">
         <f>B13*Данные!$B$9</f>
         <v>62640</v>
       </c>
@@ -4291,7 +4286,7 @@
         <f>Данные!$D$20*2</f>
         <v>0</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="10">
         <f>D13*Данные!$B$8*Данные!$B$15+E13*Данные!$B$8*Данные!$B$16</f>
         <v>0</v>
       </c>
@@ -4299,7 +4294,7 @@
         <f>Данные!$G$20</f>
         <v>0</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="10">
         <f>G13*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
@@ -4307,17 +4302,17 @@
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="10">
         <f>I13*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="11">
         <f>C13+F13+H13+J13</f>
         <v>88137.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Бройлерные площадки · 8 шт</t>
         </is>
@@ -4326,7 +4321,7 @@
         <f>SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30)</f>
         <v>1257</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="10">
         <f>B14*Данные!$B$9</f>
         <v>2715120</v>
       </c>
@@ -4338,7 +4333,7 @@
         <f>SUM(Данные!$D$23:$D$30)*2</f>
         <v>536</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="10">
         <f>D14*Данные!$B$8*Данные!$B$15+E14*Данные!$B$8*Данные!$B$16</f>
         <v>728960</v>
       </c>
@@ -4346,7 +4341,7 @@
         <f>SUM(Данные!$G$23:$G$30)</f>
         <v>15</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="10">
         <f>G14*Данные!$B$6*Данные!$B$15</f>
         <v>77700</v>
       </c>
@@ -4354,17 +4349,17 @@
         <f>SUM(Данные!$F$23:$F$30)</f>
         <v>17</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="10">
         <f>I14*Данные!$B$7*Данные!$B$15</f>
         <v>433457.5</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="11">
         <f>C14+F14+H14+J14</f>
         <v>3955237.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
@@ -4373,7 +4368,7 @@
         <f>Данные!$B$21+Данные!$C$21</f>
         <v>52</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="10">
         <f>B15*Данные!$B$9</f>
         <v>112320</v>
       </c>
@@ -4385,7 +4380,7 @@
         <f>Данные!$D$21*2</f>
         <v>24</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="10">
         <f>D15*Данные!$B$8*Данные!$B$15+E15*Данные!$B$8*Данные!$B$16</f>
         <v>32640</v>
       </c>
@@ -4393,7 +4388,7 @@
         <f>Данные!$G$21</f>
         <v>1</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="10">
         <f>G15*Данные!$B$6*Данные!$B$15</f>
         <v>5180</v>
       </c>
@@ -4401,17 +4396,17 @@
         <f>Данные!$F$21</f>
         <v>1</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="10">
         <f>I15*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="11">
         <f>C15+F15+H15+J15</f>
         <v>175637.5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
@@ -4420,7 +4415,7 @@
         <f>Данные!$B$22+Данные!$C$22</f>
         <v>39</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="10">
         <f>B16*Данные!$B$9</f>
         <v>84240</v>
       </c>
@@ -4432,7 +4427,7 @@
         <f>Данные!$D$22*2</f>
         <v>126</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="10">
         <f>D16*Данные!$B$8*Данные!$B$15+E16*Данные!$B$8*Данные!$B$16</f>
         <v>171360</v>
       </c>
@@ -4440,7 +4435,7 @@
         <f>Данные!$G$22</f>
         <v>0</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="10">
         <f>G16*Данные!$B$6*Данные!$B$15</f>
         <v>0</v>
       </c>
@@ -4448,49 +4443,49 @@
         <f>Данные!$F$22</f>
         <v>1.3</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="10">
         <f>I16*Данные!$B$7*Данные!$B$15</f>
         <v>33146.75</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="11">
         <f>C16+F16+H16+J16</f>
         <v>288746.75</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Бутылки (по объектам не разносятся)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="8">
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="11">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ, ПЕРВЫЙ ГОД ИТОГО (с разовой закупкой станций)</t>
         </is>
       </c>
       <c r="B18" s="28" t="n"/>
-      <c r="C18" s="12">
+      <c r="C18" s="18">
         <f>SUM(C13:C17)</f>
         <v>2974320</v>
       </c>
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="28" t="n"/>
-      <c r="F18" s="12">
+      <c r="F18" s="18">
         <f>SUM(F13:F17)</f>
         <v>932960</v>
       </c>
@@ -4498,7 +4493,7 @@
         <f>SUM(G13:G17)</f>
         <v>16</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="18">
         <f>SUM(H13:H17)</f>
         <v>82880</v>
       </c>
@@ -4506,281 +4501,281 @@
         <f>SUM(I13:I17)</f>
         <v>20.3</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="18">
         <f>SUM(J13:J17)</f>
         <v>517599.25</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="18">
         <f>SUM(K13:K17)</f>
         <v>4526799.25</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Численность, чел.</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="10">
         <f>A22*Данные!$B$12</f>
         <v>516976</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="10">
         <f>B22*12</f>
         <v>6203712</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="11">
         <f>C22+D22</f>
         <v>10730511.25</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="11">
         <f>A22*Данные!$B$13*12+D22</f>
         <v>12926799.25</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <f>A23*Данные!$B$12</f>
         <v>775464</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="10">
         <f>B23*12</f>
         <v>9305568</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="11">
         <f>C23+D23</f>
         <v>13832367.25</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="11">
         <f>A23*Данные!$B$13*12+D23</f>
         <v>17126799.25</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="10">
         <f>A24*Данные!$B$12</f>
         <v>1033952</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="10">
         <f>B24*12</f>
         <v>12407424</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="11">
         <f>C24+D24</f>
         <v>16934223.25</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="11">
         <f>A24*Данные!$B$13*12+D24</f>
         <v>21326799.25</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="10">
         <f>A25*Данные!$B$12</f>
         <v>1292440</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="10">
         <f>B25*12</f>
         <v>15509280</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="11">
         <f>C25+D25</f>
         <v>20036079.25</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="11">
         <f>A25*Данные!$B$13*12+D25</f>
         <v>25526799.25</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="10">
         <f>A26*Данные!$B$12</f>
         <v>1550928</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="10">
         <f>B26*12</f>
         <v>18611136</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="11">
         <f>C26+D26</f>
         <v>23137935.25</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="11">
         <f>A26*Данные!$B$13*12+D26</f>
         <v>29726799.25</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="10">
         <f>A27*Данные!$B$12</f>
         <v>1809416</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="10">
         <f>B27*12</f>
         <v>21712992</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="11">
         <f>C27+D27</f>
         <v>26239791.25</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="11">
         <f>A27*Данные!$B$13*12+D27</f>
         <v>33926799.25</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="10">
         <f>A28*Данные!$B$12</f>
         <v>2067904</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="10">
         <f>B28*12</f>
         <v>24814848</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="11">
         <f>C28+D28</f>
         <v>29341647.25</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="11">
         <f>A28*Данные!$B$13*12+D28</f>
         <v>38126799.25</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="10">
         <f>A29*Данные!$B$12</f>
         <v>2326392</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="10">
         <f>B29*12</f>
         <v>27916704</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="11">
         <f>C29+D29</f>
         <v>32443503.25</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="11">
         <f>A29*Данные!$B$13*12+D29</f>
         <v>42326799.25</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="10">
         <f>A30*Данные!$B$12</f>
         <v>2584880</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="10">
         <f>B30*12</f>
         <v>31018560</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="10">
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="11">
         <f>C30+D30</f>
         <v>35545359.25</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="11">
         <f>A30*Данные!$B$13*12+D30</f>
         <v>46526799.25</v>
       </c>
@@ -4837,18 +4832,18 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>ЦЕНЫ И ПАРАМЕТРЫ ШТАТА УКПФ</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16" t="n"/>
-      <c r="H4" s="16" t="n"/>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
@@ -4877,7 +4872,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Зерноцид</t>
         </is>
@@ -4885,7 +4880,7 @@
       <c r="B6" s="44" t="n">
         <v>740</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>₸/кг</t>
         </is>
@@ -4897,7 +4892,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты</t>
         </is>
@@ -4905,7 +4900,7 @@
       <c r="B7" s="44" t="n">
         <v>3642.5</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>₸/кг</t>
         </is>
@@ -4917,7 +4912,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Клеевая станция 3-го контура</t>
         </is>
@@ -4925,7 +4920,7 @@
       <c r="B8" s="44" t="n">
         <v>160</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
@@ -4937,7 +4932,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Приманочная станция 1–2 контура</t>
         </is>
@@ -4945,7 +4940,7 @@
       <c r="B9" s="44" t="n">
         <v>2160</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
@@ -4957,7 +4952,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Бутылка</t>
         </is>
@@ -4965,7 +4960,7 @@
       <c r="B10" s="44" t="n">
         <v>68</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>₸/шт</t>
         </is>
@@ -4977,7 +4972,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Бутылки, расход</t>
         </is>
@@ -4985,7 +4980,7 @@
       <c r="B11" s="44" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
@@ -4997,7 +4992,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Оклад дератизатора · вариант 1</t>
         </is>
@@ -5005,7 +5000,7 @@
       <c r="B12" s="44" t="n">
         <v>258488</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5017,7 +5012,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Оклад дератизатора · вариант 2</t>
         </is>
@@ -5025,7 +5020,7 @@
       <c r="B13" s="44" t="n">
         <v>350000</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5037,7 +5032,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Численность штата</t>
         </is>
@@ -5045,7 +5040,7 @@
       <c r="B14" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
@@ -5057,7 +5052,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
@@ -5065,7 +5060,7 @@
       <c r="B15" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
@@ -5077,7 +5072,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
@@ -5085,7 +5080,7 @@
       <c r="B16" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
@@ -5098,63 +5093,63 @@
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>ПРИМАНОЧНЫЕ СТАНЦИИ И НОРМЫ ЯДОВ ПО ОБЪЕКТАМ УКПФ</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>1-й контур, шт</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>2-й контур, шт</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>3-й контур, шт</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Всего точек, шт</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Pest Killer, кг</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Зерноцид, кг</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>ККЗ · кормоцех</t>
         </is>
@@ -5168,7 +5163,7 @@
       <c r="D20" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="10">
         <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
@@ -5185,7 +5180,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
@@ -5199,7 +5194,7 @@
       <c r="D21" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="10">
         <f>SUM(B21:D21)</f>
         <v>18</v>
       </c>
@@ -5212,7 +5207,7 @@
       <c r="H21" s="45" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
@@ -5226,7 +5221,7 @@
       <c r="D22" s="44" t="n">
         <v>63</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="10">
         <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
@@ -5243,7 +5238,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Площадка А</t>
         </is>
@@ -5257,7 +5252,7 @@
       <c r="D23" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="10">
         <f>SUM(B23:D23)</f>
         <v>13</v>
       </c>
@@ -5270,7 +5265,7 @@
       <c r="H23" s="45" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Площадка Б</t>
         </is>
@@ -5284,7 +5279,7 @@
       <c r="D24" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="10">
         <f>SUM(B24:D24)</f>
         <v>17</v>
       </c>
@@ -5297,7 +5292,7 @@
       <c r="H24" s="45" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>В / Восточка</t>
         </is>
@@ -5311,7 +5306,7 @@
       <c r="D25" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="10">
         <f>SUM(B25:D25)</f>
         <v>50</v>
       </c>
@@ -5324,7 +5319,7 @@
       <c r="H25" s="45" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Площадка Г</t>
         </is>
@@ -5338,7 +5333,7 @@
       <c r="D26" s="44" t="n">
         <v>80</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="10">
         <f>SUM(B26:D26)</f>
         <v>17</v>
       </c>
@@ -5351,7 +5346,7 @@
       <c r="H26" s="45" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Площадка Д</t>
         </is>
@@ -5365,7 +5360,7 @@
       <c r="D27" s="44" t="n">
         <v>64</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="10">
         <f>SUM(B27:D27)</f>
         <v>15</v>
       </c>
@@ -5378,7 +5373,7 @@
       <c r="H27" s="45" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Площадка Е</t>
         </is>
@@ -5392,7 +5387,7 @@
       <c r="D28" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="10">
         <f>SUM(B28:D28)</f>
         <v>13</v>
       </c>
@@ -5405,7 +5400,7 @@
       <c r="H28" s="45" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Площадка Ж</t>
         </is>
@@ -5419,7 +5414,7 @@
       <c r="D29" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="10">
         <f>SUM(B29:D29)</f>
         <v>17</v>
       </c>
@@ -5432,7 +5427,7 @@
       <c r="H29" s="45" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Айыртау (БП)</t>
         </is>
@@ -5446,7 +5441,7 @@
       <c r="D30" s="44" t="n">
         <v>24</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="10">
         <f>SUM(B30:D30)</f>
         <v>19</v>
       </c>
@@ -5459,15 +5454,15 @@
       <c r="H30" s="45" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>ЗПП · завод по переработке птицы</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
       <c r="F31" s="55" t="n"/>
       <c r="G31" s="55" t="n"/>
       <c r="H31" s="45" t="inlineStr">
@@ -5477,15 +5472,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Склад лузги</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
       <c r="F32" s="55" t="n"/>
       <c r="G32" s="55" t="n"/>
       <c r="H32" s="45" t="inlineStr">
@@ -5495,24 +5490,24 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>ИТОГО ПО ФАБРИКЕ</t>
         </is>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="18">
         <f>SUM(B20:B32)</f>
         <v>179</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="18">
         <f>SUM(C20:C32)</f>
         <v>1198</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="18">
         <f>SUM(D20:D32)</f>
         <v>343</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="18">
         <f>SUM(E20:E32)</f>
         <v>179</v>
       </c>
@@ -5528,18 +5523,18 @@
     </row>
     <row r="34"/>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>ЦЕНЫ ПОДРЯДЧИКОВ ИЗ КП И ДОГОВОРОВ</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="16" t="n"/>
+      <c r="B35" s="21" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
@@ -5568,7 +5563,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Indigo · ККЗ, дератизация</t>
         </is>
@@ -5576,7 +5571,7 @@
       <c r="B37" s="44" t="n">
         <v>96600</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5588,7 +5583,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
@@ -5596,7 +5591,7 @@
       <c r="B38" s="44" t="n">
         <v>618400</v>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5608,7 +5603,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
@@ -5616,7 +5611,7 @@
       <c r="B39" s="44" t="n">
         <v>478400</v>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5628,7 +5623,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
@@ -5636,7 +5631,7 @@
       <c r="B40" s="44" t="n">
         <v>569800</v>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5648,7 +5643,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
@@ -5656,7 +5651,7 @@
       <c r="B41" s="44" t="n">
         <v>440700</v>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5668,7 +5663,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
@@ -5676,7 +5671,7 @@
       <c r="B42" s="44" t="n">
         <v>2599100</v>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5688,7 +5683,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
@@ -5696,7 +5691,7 @@
       <c r="B43" s="44" t="n">
         <v>2010300</v>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5708,7 +5703,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
@@ -5716,7 +5711,7 @@
       <c r="B44" s="44" t="n">
         <v>126200</v>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5728,7 +5723,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
@@ -5736,7 +5731,7 @@
       <c r="B45" s="44" t="n">
         <v>106800</v>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5748,7 +5743,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Indigo · ЗПП, полная замена</t>
         </is>
@@ -5756,7 +5751,7 @@
       <c r="B46" s="44" t="n">
         <v>126200</v>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5768,7 +5763,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
@@ -5776,7 +5771,7 @@
       <c r="B47" s="44" t="n">
         <v>106800</v>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5788,7 +5783,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
@@ -5796,7 +5791,7 @@
       <c r="B48" s="44" t="n">
         <v>720000</v>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5808,7 +5803,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
@@ -5816,7 +5811,7 @@
       <c r="B49" s="44" t="n">
         <v>1080000</v>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5828,7 +5823,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
@@ -5836,7 +5831,7 @@
       <c r="B50" s="44" t="n">
         <v>3000000</v>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5848,7 +5843,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
@@ -5856,7 +5851,7 @@
       <c r="B51" s="44" t="n">
         <v>100800</v>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5868,7 +5863,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
@@ -5876,7 +5871,7 @@
       <c r="B52" s="44" t="n">
         <v>160800</v>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5888,7 +5883,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
@@ -5896,7 +5891,7 @@
       <c r="B53" s="44" t="n">
         <v>75000</v>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5908,7 +5903,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
@@ -5916,7 +5911,7 @@
       <c r="B54" s="44" t="n">
         <v>70000</v>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5928,7 +5923,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
@@ -5936,7 +5931,7 @@
       <c r="B55" s="44" t="n">
         <v>3172000</v>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5948,7 +5943,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
@@ -5956,7 +5951,7 @@
       <c r="B56" s="44" t="n">
         <v>2074000</v>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5968,7 +5963,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
@@ -5976,7 +5971,7 @@
       <c r="B57" s="44" t="n">
         <v>2806000</v>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -5988,7 +5983,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
@@ -5996,7 +5991,7 @@
       <c r="B58" s="44" t="n">
         <v>1830000</v>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -6008,7 +6003,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · ЗПП</t>
         </is>
@@ -6016,7 +6011,7 @@
       <c r="B59" s="44" t="n">
         <v>180000</v>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -6028,7 +6023,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters · склад ТМЦ</t>
         </is>
@@ -6036,7 +6031,7 @@
       <c r="B60" s="44" t="n">
         <v>80000</v>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
@@ -6048,7 +6043,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
@@ -6056,7 +6051,7 @@
       <c r="B61" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
@@ -6068,7 +6063,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
@@ -6076,7 +6071,7 @@
       <c r="B62" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
@@ -6088,7 +6083,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
@@ -6096,7 +6091,7 @@
       <c r="B63" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>мес.</t>
         </is>
@@ -6108,7 +6103,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
@@ -6116,7 +6111,7 @@
       <c r="B64" s="58" t="n">
         <v>0.15</v>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
@@ -6128,7 +6123,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
@@ -6136,7 +6131,7 @@
       <c r="B65" s="58" t="n">
         <v>0.15</v>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
@@ -6148,7 +6143,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
@@ -6156,7 +6151,7 @@
       <c r="B66" s="58" t="n">
         <v>0.16</v>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>доля</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -236,10 +236,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -798,129 +798,119 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
+          <t>Бутылки · 1-й контур (расход по фабрике, не разносится по объектам)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="10">
+        <f>Данные!$B$11*Данные!$B$10</f>
+        <v>2720</v>
+      </c>
+      <c r="G6" s="10">
+        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
+        <v>19040</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Оклад одного, ₸/мес</t>
+        </is>
+      </c>
+      <c r="J6" s="11">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+      <c r="K6" s="11">
+        <f>Данные!$B$12</f>
+        <v>258488</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="B6" s="10">
-        <f>C6/12</f>
+      <c r="B7" s="10">
+        <f>C7/12</f>
         <v>96600</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C7" s="12">
         <f>'ККЗ'!B5</f>
         <v>1159200</v>
       </c>
-      <c r="D6" s="10">
-        <f>E6/12</f>
+      <c r="D7" s="10">
+        <f>E7/12</f>
         <v>75000</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E7" s="12">
         <f>'ККЗ'!C5</f>
         <v>900000</v>
       </c>
-      <c r="F6" s="10">
-        <f>G6/12</f>
+      <c r="F7" s="10">
+        <f>G7/12</f>
         <v>7344.791667</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G7" s="12">
         <f>'ККЗ'!D5</f>
         <v>88137.5</v>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Оклад одного, ₸/мес</t>
-        </is>
-      </c>
-      <c r="J6" s="12">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
-      <c r="K6" s="12">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>ФОТ в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="J7" s="11">
+        <f>2*Данные!$B$12</f>
+        <v>516976</v>
+      </c>
+      <c r="K7" s="11">
+        <f>5*Данные!$B$12</f>
+        <v>1292440</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Бройлерные площадки</t>
         </is>
       </c>
-      <c r="B7" s="10">
-        <f>C7/12</f>
+      <c r="B8" s="10">
+        <f>C8/12</f>
         <v>3787300</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C8" s="12">
         <f>'Бройлерные площадки'!B5</f>
         <v>45447600</v>
       </c>
-      <c r="D7" s="10">
-        <f>E7/12</f>
+      <c r="D8" s="10">
+        <f>E8/12</f>
         <v>2897500</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E8" s="12">
         <f>'Бройлерные площадки'!C5</f>
         <v>34770000</v>
       </c>
-      <c r="F7" s="10">
-        <f>G7/12</f>
+      <c r="F8" s="10">
+        <f>G8/12</f>
         <v>329603.125</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G8" s="12">
         <f>'Бройлерные площадки'!D5</f>
         <v>3955237.5</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>ФОТ в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="J7" s="12">
-        <f>2*Данные!$B$12</f>
-        <v>516976</v>
-      </c>
-      <c r="K7" s="12">
-        <f>5*Данные!$B$12</f>
-        <v>1292440</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Инкубаторий</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
-        <f>C8/12</f>
-        <v>126200</v>
-      </c>
-      <c r="C8" s="11">
-        <f>'Инкубаторий'!B5</f>
-        <v>1514400</v>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="E8" s="49" t="n"/>
-      <c r="F8" s="10">
-        <f>G8/12</f>
-        <v>14636.45833</v>
-      </c>
-      <c r="G8" s="11">
-        <f>'Инкубаторий'!D5</f>
-        <v>175637.5</v>
-      </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>ФОТ за год, ₸</t>
         </is>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <f>2*Данные!$B$12*12</f>
         <v>6203712</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="11">
         <f>5*Данные!$B$12*12</f>
         <v>15509280</v>
       </c>
@@ -928,64 +918,66 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>ЗПП</t>
+          <t>Инкубаторий</t>
         </is>
       </c>
       <c r="B9" s="10">
         <f>C9/12</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
+        <f>'Инкубаторий'!B5</f>
+        <v>1514400</v>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="10">
+        <f>G9/12</f>
+        <v>14636.45833</v>
+      </c>
+      <c r="G9" s="12">
+        <f>'Инкубаторий'!D5</f>
+        <v>175637.5</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Материалы, первый год, ₸</t>
+        </is>
+      </c>
+      <c r="J9" s="11">
+        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
+        <v>4526799.25</v>
+      </c>
+      <c r="K9" s="11">
+        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
+        <v>4526799.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <f>C10/12</f>
+        <v>126200</v>
+      </c>
+      <c r="C10" s="12">
         <f>'ЗПП'!B5</f>
         <v>1514400</v>
       </c>
-      <c r="D9" s="10">
-        <f>E9/12</f>
+      <c r="D10" s="10">
+        <f>E10/12</f>
         <v>180000</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E10" s="12">
         <f>'ЗПП'!C5</f>
         <v>2160000</v>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>нормы не заданы</t>
-        </is>
-      </c>
-      <c r="G9" s="49" t="n"/>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Материалы, первый год, ₸</t>
-        </is>
-      </c>
-      <c r="J9" s="12">
-        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="K9" s="12">
-        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
-        <v>4526799.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="10">
-        <f>E10/12</f>
-        <v>60000</v>
-      </c>
-      <c r="E10" s="11">
-        <f>'Склад ТМЦ'!C5</f>
-        <v>720000</v>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
@@ -1010,7 +1002,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>АБК · 11 корпусов</t>
+          <t>Склад ТМЦ</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -1019,20 +1011,20 @@
         </is>
       </c>
       <c r="C11" s="49" t="n"/>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="10">
-        <f>G11/12</f>
-        <v>24062.22917</v>
-      </c>
-      <c r="G11" s="11">
-        <f>'АБК'!D5</f>
-        <v>288746.75</v>
-      </c>
+      <c r="D11" s="10">
+        <f>E11/12</f>
+        <v>60000</v>
+      </c>
+      <c r="E11" s="12">
+        <f>'Склад ТМЦ'!C5</f>
+        <v>720000</v>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>нормы не заданы</t>
+        </is>
+      </c>
+      <c r="G11" s="49" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Разница 5 против 2 чел., ₸/год</t>
@@ -1044,53 +1036,61 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>АБК · 11 корпусов</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="10">
+        <f>G12/12</f>
+        <v>24062.22917</v>
+      </c>
+      <c r="G12" s="12">
+        <f>'АБК'!D5</f>
+        <v>288746.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Сумма по объектам</t>
         </is>
       </c>
-      <c r="B12" s="18">
-        <f>C12/12</f>
+      <c r="B13" s="18">
+        <f>C13/12</f>
         <v>4136300</v>
       </c>
-      <c r="C12" s="18">
-        <f>SUM(C6:C11)</f>
+      <c r="C13" s="18">
+        <f>SUM(C7:C12)</f>
         <v>49635600</v>
       </c>
-      <c r="D12" s="18">
-        <f>E12/12</f>
+      <c r="D13" s="18">
+        <f>E13/12</f>
         <v>3212500</v>
       </c>
-      <c r="E12" s="18">
-        <f>SUM(E6:E11)</f>
+      <c r="E13" s="18">
+        <f>SUM(E7:E12)</f>
         <v>38550000</v>
       </c>
-      <c r="F12" s="18">
-        <f>G12/12</f>
+      <c r="F13" s="18">
+        <f>G13/12</f>
         <v>375646.6042</v>
       </c>
-      <c r="G12" s="18">
-        <f>SUM(G6:G11)</f>
+      <c r="G13" s="18">
+        <f>SUM(G7:G12)</f>
         <v>4507759.25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Бутылки · 1-й контур</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="10">
-        <f>G13/12</f>
-        <v>1586.666667</v>
-      </c>
-      <c r="G13" s="10">
-        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v>19040</v>
       </c>
     </row>
     <row r="14">
@@ -1123,7 +1123,7 @@
         <v>4136300</v>
       </c>
       <c r="C15" s="19">
-        <f>C12</f>
+        <f>C13</f>
         <v>49635600</v>
       </c>
       <c r="D15" s="19">
@@ -1131,7 +1131,7 @@
         <v>3212500</v>
       </c>
       <c r="E15" s="19">
-        <f>E12</f>
+        <f>E13</f>
         <v>38550000</v>
       </c>
       <c r="F15" s="19">
@@ -1139,7 +1139,7 @@
         <v>1411185.271</v>
       </c>
       <c r="G15" s="19">
-        <f>G12+G13+G14</f>
+        <f>G13+G6+G14</f>
         <v>16934223.25</v>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         <f>C19/12</f>
         <v>2725114.729</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="12">
         <f>C15-G15</f>
         <v>32701376.75</v>
       </c>
@@ -1205,7 +1205,7 @@
         <f>C20/12</f>
         <v>1801314.729</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="12">
         <f>E15-G15</f>
         <v>21615776.75</v>
       </c>
@@ -1321,7 +1321,7 @@
         <f>Данные!$B$14*Данные!$B$12</f>
         <v>1033952</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="12">
         <f>Данные!$B$14*Данные!$B$12*12</f>
         <v>12407424</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>2160</v>
       </c>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="11">
+      <c r="F27" s="12">
         <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9</f>
         <v>2974320</v>
       </c>
@@ -1374,7 +1374,7 @@
         <f>Данные!$D$33*Данные!$B$8</f>
         <v>54880</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="12">
         <f>Данные!$D$33*Данные!$B$8*Данные!$B$15</f>
         <v>384160</v>
       </c>
@@ -1402,7 +1402,7 @@
         <f>Данные!$D$33*2*Данные!$B$8</f>
         <v>109760</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="12">
         <f>Данные!$D$33*2*Данные!$B$8*Данные!$B$16</f>
         <v>548800</v>
       </c>
@@ -1430,7 +1430,7 @@
         <f>Данные!$G$33*Данные!$B$6</f>
         <v>11840</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="12">
         <f>Данные!$G$33*Данные!$B$6*Данные!$B$15</f>
         <v>82880</v>
       </c>
@@ -1458,7 +1458,7 @@
         <f>Данные!$F$33*Данные!$B$7</f>
         <v>73942.75</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="12">
         <f>Данные!$F$33*Данные!$B$7*Данные!$B$15</f>
         <v>517599.25</v>
       </c>
@@ -1524,7 +1524,7 @@
         <f>Данные!$B$11*Данные!$B$10</f>
         <v>2720</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="12">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
@@ -1600,7 +1600,7 @@
         <f>C40/12</f>
         <v>4136300</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="12">
         <f>C15</f>
         <v>49635600</v>
       </c>
@@ -1616,7 +1616,7 @@
         <f>C41/12</f>
         <v>3515855</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="12">
         <f>C15*(1-Данные!$B$64)</f>
         <v>42190260</v>
       </c>
@@ -1635,7 +1635,7 @@
         <f>C42/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="12">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
         <v>35861721</v>
       </c>
@@ -1654,7 +1654,7 @@
         <f>C43/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="12">
         <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
         <v>30123845.64</v>
       </c>
@@ -1842,20 +1842,20 @@
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F11:G11"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="D51:G51"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D11:E11"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="D52:G52"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D49:G49"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="D48:G48"/>
     <mergeCell ref="D47:G47"/>
     <mergeCell ref="A2:G2"/>
@@ -1977,7 +1977,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>B9*C9</f>
         <v>1159200</v>
       </c>
@@ -1995,7 +1995,7 @@
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>B10*C10</f>
         <v>900000</v>
       </c>
@@ -2013,7 +2013,7 @@
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>B11*C11</f>
         <v>62640</v>
       </c>
@@ -2032,7 +2032,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="12">
         <f>B12*C12</f>
         <v>0</v>
       </c>
@@ -2051,7 +2051,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <f>B13*C13</f>
         <v>0</v>
       </c>
@@ -2070,7 +2070,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="12">
         <f>B14*C14</f>
         <v>0</v>
       </c>
@@ -2089,7 +2089,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="12">
         <f>B15*C15</f>
         <v>25497.5</v>
       </c>
@@ -2282,7 +2282,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>B9*C9</f>
         <v>7420800</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>B10*C10</f>
         <v>6837600</v>
       </c>
@@ -2318,7 +2318,7 @@
       <c r="C11" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>B11*C11</f>
         <v>31189200</v>
       </c>
@@ -2337,7 +2337,7 @@
         <f>Данные!$B$61</f>
         <v>9</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="12">
         <f>B12*C12</f>
         <v>28548000</v>
       </c>
@@ -2356,7 +2356,7 @@
         <f>Данные!$B$62</f>
         <v>3</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <f>B13*C13</f>
         <v>6222000</v>
       </c>
@@ -2374,7 +2374,7 @@
       <c r="C14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="12">
         <f>B14*C14</f>
         <v>2715120</v>
       </c>
@@ -2393,7 +2393,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="12">
         <f>B15*C15</f>
         <v>300160</v>
       </c>
@@ -2412,7 +2412,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="12">
         <f>B16*C16</f>
         <v>428800</v>
       </c>
@@ -2431,7 +2431,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="12">
         <f>B17*C17</f>
         <v>77700</v>
       </c>
@@ -2450,7 +2450,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="12">
         <f>B18*C18</f>
         <v>433457.5</v>
       </c>
@@ -2882,7 +2882,7 @@
         <f>B47*Данные!$B$9</f>
         <v>347760</v>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
@@ -2902,7 +2902,7 @@
         <f>C47*Данные!$B$9</f>
         <v>2367360</v>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
@@ -2922,7 +2922,7 @@
         <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="11">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2941,7 +2941,7 @@
         <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="11">
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
@@ -2960,7 +2960,7 @@
         <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="11">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -2979,7 +2979,7 @@
         <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="11">
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
@@ -3131,7 +3131,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>B9*C9</f>
         <v>1514400</v>
       </c>
@@ -3148,7 +3148,7 @@
       <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>B10*C10</f>
         <v>0</v>
       </c>
@@ -3166,7 +3166,7 @@
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>B11*C11</f>
         <v>112320</v>
       </c>
@@ -3185,7 +3185,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="12">
         <f>B12*C12</f>
         <v>13440</v>
       </c>
@@ -3204,7 +3204,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <f>B13*C13</f>
         <v>19200</v>
       </c>
@@ -3223,7 +3223,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="12">
         <f>B14*C14</f>
         <v>5180</v>
       </c>
@@ -3242,7 +3242,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="12">
         <f>B15*C15</f>
         <v>25497.5</v>
       </c>
@@ -3478,7 +3478,7 @@
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>B9*C9</f>
         <v>1514400</v>
       </c>
@@ -3496,7 +3496,7 @@
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>B10*C10</f>
         <v>2160000</v>
       </c>
@@ -3513,7 +3513,7 @@
       <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>B11*C11</f>
         <v>0</v>
       </c>
@@ -3756,7 +3756,7 @@
       <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>B9*C9</f>
         <v>0</v>
       </c>
@@ -3775,7 +3775,7 @@
         <f>Данные!$B$63</f>
         <v>9</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>B10*C10</f>
         <v>720000</v>
       </c>
@@ -3792,7 +3792,7 @@
       <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>B11*C11</f>
         <v>0</v>
       </c>
@@ -3925,7 +3925,7 @@
       <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>B9*C9</f>
         <v>0</v>
       </c>
@@ -3942,7 +3942,7 @@
       <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>B10*C10</f>
         <v>0</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>B11*C11</f>
         <v>84240</v>
       </c>
@@ -3979,7 +3979,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="12">
         <f>B12*C12</f>
         <v>70560</v>
       </c>
@@ -3998,7 +3998,7 @@
         <f>Данные!$B$16</f>
         <v>5</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <f>B13*C13</f>
         <v>100800</v>
       </c>
@@ -4017,7 +4017,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="12">
         <f>B14*C14</f>
         <v>0</v>
       </c>
@@ -4036,7 +4036,7 @@
         <f>Данные!$B$15</f>
         <v>7</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="12">
         <f>B15*C15</f>
         <v>33146.75</v>
       </c>
@@ -4180,11 +4180,11 @@
           <t>Зарплата за год</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="12">
         <f>B8*12</f>
         <v>12407424</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <f>C8*12</f>
         <v>16800000</v>
       </c>
@@ -4306,7 +4306,7 @@
         <f>I13*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="12">
         <f>C13+F13+H13+J13</f>
         <v>88137.5</v>
       </c>
@@ -4353,7 +4353,7 @@
         <f>I14*Данные!$B$7*Данные!$B$15</f>
         <v>433457.5</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="12">
         <f>C14+F14+H14+J14</f>
         <v>3955237.5</v>
       </c>
@@ -4400,7 +4400,7 @@
         <f>I15*Данные!$B$7*Данные!$B$15</f>
         <v>25497.5</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="12">
         <f>C15+F15+H15+J15</f>
         <v>175637.5</v>
       </c>
@@ -4447,7 +4447,7 @@
         <f>I16*Данные!$B$7*Данные!$B$15</f>
         <v>33146.75</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="12">
         <f>C16+F16+H16+J16</f>
         <v>288746.75</v>
       </c>
@@ -4467,7 +4467,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="11">
+      <c r="K17" s="12">
         <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
         <v>19040</v>
       </c>
@@ -4571,11 +4571,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="12">
         <f>C22+D22</f>
         <v>10730511.25</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="12">
         <f>A22*Данные!$B$13*12+D22</f>
         <v>12926799.25</v>
       </c>
@@ -4596,11 +4596,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="12">
         <f>C23+D23</f>
         <v>13832367.25</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="12">
         <f>A23*Данные!$B$13*12+D23</f>
         <v>17126799.25</v>
       </c>
@@ -4621,11 +4621,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="12">
         <f>C24+D24</f>
         <v>16934223.25</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="12">
         <f>A24*Данные!$B$13*12+D24</f>
         <v>21326799.25</v>
       </c>
@@ -4646,11 +4646,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="12">
         <f>C25+D25</f>
         <v>20036079.25</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="12">
         <f>A25*Данные!$B$13*12+D25</f>
         <v>25526799.25</v>
       </c>
@@ -4671,11 +4671,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="12">
         <f>C26+D26</f>
         <v>23137935.25</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="12">
         <f>A26*Данные!$B$13*12+D26</f>
         <v>29726799.25</v>
       </c>
@@ -4696,11 +4696,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="12">
         <f>C27+D27</f>
         <v>26239791.25</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="12">
         <f>A27*Данные!$B$13*12+D27</f>
         <v>33926799.25</v>
       </c>
@@ -4721,11 +4721,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="12">
         <f>C28+D28</f>
         <v>29341647.25</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="12">
         <f>A28*Данные!$B$13*12+D28</f>
         <v>38126799.25</v>
       </c>
@@ -4746,11 +4746,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="12">
         <f>C29+D29</f>
         <v>32443503.25</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="12">
         <f>A29*Данные!$B$13*12+D29</f>
         <v>42326799.25</v>
       </c>
@@ -4771,11 +4771,11 @@
         <f>'Штат УКПФ'!$K$18</f>
         <v>4526799.25</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="12">
         <f>C30+D30</f>
         <v>35545359.25</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="12">
         <f>A30*Данные!$B$13*12+D30</f>
         <v>46526799.25</v>
       </c>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -236,10 +236,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -798,186 +798,194 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Бутылки · 1-й контур (расход по фабрике, не разносится по объектам)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <f>C6/12</f>
+        <v>96600</v>
+      </c>
+      <c r="C6" s="11">
+        <f>'ККЗ'!B5</f>
+        <v>1159200</v>
+      </c>
+      <c r="D6" s="10">
+        <f>E6/12</f>
+        <v>75000</v>
+      </c>
+      <c r="E6" s="11">
+        <f>'ККЗ'!C5</f>
+        <v>900000</v>
+      </c>
       <c r="F6" s="10">
-        <f>Данные!$B$11*Данные!$B$10</f>
-        <v>2720</v>
-      </c>
-      <c r="G6" s="10">
-        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v>19040</v>
+        <f>G6/12</f>
+        <v>7344.791667</v>
+      </c>
+      <c r="G6" s="11">
+        <f>'ККЗ'!D5</f>
+        <v>88137.5</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Оклад одного, ₸/мес</t>
         </is>
       </c>
-      <c r="J6" s="11">
-        <f>Данные!$B$12</f>
+      <c r="J6" s="12">
+        <f>Данные!$B$11</f>
         <v>258488</v>
       </c>
-      <c r="K6" s="11">
-        <f>Данные!$B$12</f>
+      <c r="K6" s="12">
+        <f>Данные!$B$11</f>
         <v>258488</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>ККЗ</t>
+          <t>Бройлерные площадки</t>
         </is>
       </c>
       <c r="B7" s="10">
         <f>C7/12</f>
-        <v>96600</v>
-      </c>
-      <c r="C7" s="12">
-        <f>'ККЗ'!B5</f>
-        <v>1159200</v>
+        <v>3787300</v>
+      </c>
+      <c r="C7" s="11">
+        <f>'Бройлерные площадки'!B5</f>
+        <v>45447600</v>
       </c>
       <c r="D7" s="10">
         <f>E7/12</f>
-        <v>75000</v>
-      </c>
-      <c r="E7" s="12">
-        <f>'ККЗ'!C5</f>
-        <v>900000</v>
+        <v>2897500</v>
+      </c>
+      <c r="E7" s="11">
+        <f>'Бройлерные площадки'!C5</f>
+        <v>34770000</v>
       </c>
       <c r="F7" s="10">
         <f>G7/12</f>
-        <v>7344.791667</v>
-      </c>
-      <c r="G7" s="12">
-        <f>'ККЗ'!D5</f>
-        <v>88137.5</v>
+        <v>335989.4583</v>
+      </c>
+      <c r="G7" s="11">
+        <f>'Бройлерные площадки'!D5</f>
+        <v>4031873.5</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>ФОТ в месяц, ₸</t>
         </is>
       </c>
-      <c r="J7" s="11">
-        <f>2*Данные!$B$12</f>
+      <c r="J7" s="12">
+        <f>2*Данные!$B$11</f>
         <v>516976</v>
       </c>
-      <c r="K7" s="11">
-        <f>5*Данные!$B$12</f>
+      <c r="K7" s="12">
+        <f>5*Данные!$B$11</f>
         <v>1292440</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Бройлерные площадки</t>
+          <t>Инкубаторий</t>
         </is>
       </c>
       <c r="B8" s="10">
         <f>C8/12</f>
-        <v>3787300</v>
-      </c>
-      <c r="C8" s="12">
-        <f>'Бройлерные площадки'!B5</f>
-        <v>45447600</v>
-      </c>
-      <c r="D8" s="10">
-        <f>E8/12</f>
-        <v>2897500</v>
-      </c>
-      <c r="E8" s="12">
-        <f>'Бройлерные площадки'!C5</f>
-        <v>34770000</v>
-      </c>
+        <v>126200</v>
+      </c>
+      <c r="C8" s="11">
+        <f>'Инкубаторий'!B5</f>
+        <v>1514400</v>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="n"/>
       <c r="F8" s="10">
         <f>G8/12</f>
-        <v>329603.125</v>
-      </c>
-      <c r="G8" s="12">
-        <f>'Бройлерные площадки'!D5</f>
-        <v>3955237.5</v>
+        <v>15350.45833</v>
+      </c>
+      <c r="G8" s="11">
+        <f>'Инкубаторий'!D5</f>
+        <v>184205.5</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>ФОТ за год, ₸</t>
         </is>
       </c>
-      <c r="J8" s="11">
-        <f>2*Данные!$B$12*12</f>
+      <c r="J8" s="12">
+        <f>2*Данные!$B$11*12</f>
         <v>6203712</v>
       </c>
-      <c r="K8" s="11">
-        <f>5*Данные!$B$12*12</f>
+      <c r="K8" s="12">
+        <f>5*Данные!$B$11*12</f>
         <v>15509280</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Инкубаторий</t>
+          <t>ЗПП</t>
         </is>
       </c>
       <c r="B9" s="10">
         <f>C9/12</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="12">
-        <f>'Инкубаторий'!B5</f>
+      <c r="C9" s="11">
+        <f>'ЗПП'!B5</f>
         <v>1514400</v>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="E9" s="49" t="n"/>
-      <c r="F9" s="10">
-        <f>G9/12</f>
-        <v>14636.45833</v>
-      </c>
-      <c r="G9" s="12">
-        <f>'Инкубаторий'!D5</f>
-        <v>175637.5</v>
-      </c>
+      <c r="D9" s="10">
+        <f>E9/12</f>
+        <v>180000</v>
+      </c>
+      <c r="E9" s="11">
+        <f>'ЗПП'!C5</f>
+        <v>2160000</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>нормы не заданы</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="n"/>
       <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Материалы, первый год, ₸</t>
         </is>
       </c>
-      <c r="J9" s="11">
-        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="K9" s="11">
-        <f>((Данные!$B$33+Данные!$C$33)*Данные!$B$9+Данные!$D$33*Данные!$B$8*Данные!$B$15+Данные!$D$33*2*Данные!$B$8*Данные!$B$16+Данные!$G$33*Данные!$B$6*Данные!$B$15+Данные!$F$33*Данные!$B$7*Данные!$B$15+Данные!$B$11*Данные!$B$10*Данные!$B$15)</f>
-        <v>4526799.25</v>
+      <c r="J9" s="12">
+        <f>((Данные!$B$32+Данные!$C$32)*Данные!$B$9+Данные!$D$32*Данные!$B$8*Данные!$B$14+Данные!$D$32*2*Данные!$B$8*Данные!$B$15+Данные!$G$32*Данные!$B$6*Данные!$B$14+Данные!$F$32*Данные!$B$7*Данные!$B$14+Данные!$B$32*Данные!$B$10*Данные!$B$14)</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="K9" s="12">
+        <f>((Данные!$B$32+Данные!$C$32)*Данные!$B$9+Данные!$D$32*Данные!$B$8*Данные!$B$14+Данные!$D$32*2*Данные!$B$8*Данные!$B$15+Данные!$G$32*Данные!$B$6*Данные!$B$14+Данные!$F$32*Данные!$B$7*Данные!$B$14+Данные!$B$32*Данные!$B$10*Данные!$B$14)</f>
+        <v>4592963.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
-        <f>C10/12</f>
-        <v>126200</v>
-      </c>
-      <c r="C10" s="12">
-        <f>'ЗПП'!B5</f>
-        <v>1514400</v>
-      </c>
+          <t>Склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="n"/>
       <c r="D10" s="10">
         <f>E10/12</f>
-        <v>180000</v>
-      </c>
-      <c r="E10" s="12">
-        <f>'ЗПП'!C5</f>
-        <v>2160000</v>
+        <v>60000</v>
+      </c>
+      <c r="E10" s="11">
+        <f>'Склад ТМЦ'!C5</f>
+        <v>720000</v>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
@@ -992,17 +1000,17 @@
       </c>
       <c r="J10" s="15">
         <f>J8+J9</f>
-        <v>10730511.25</v>
+        <v>10796675.25</v>
       </c>
       <c r="K10" s="15">
         <f>K8+K9</f>
-        <v>20036079.25</v>
+        <v>20102243.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Склад ТМЦ</t>
+          <t>АБК · 11 корпусов</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -1011,20 +1019,20 @@
         </is>
       </c>
       <c r="C11" s="49" t="n"/>
-      <c r="D11" s="10">
-        <f>E11/12</f>
-        <v>60000</v>
-      </c>
-      <c r="E11" s="12">
-        <f>'Склад ТМЦ'!C5</f>
-        <v>720000</v>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>нормы не заданы</t>
-        </is>
-      </c>
-      <c r="G11" s="49" t="n"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="10">
+        <f>G11/12</f>
+        <v>24062.22917</v>
+      </c>
+      <c r="G11" s="11">
+        <f>'АБК'!D5</f>
+        <v>288746.75</v>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Разница 5 против 2 чел., ₸/год</t>
@@ -1036,330 +1044,331 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>АБК · 11 корпусов</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="10">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Сумма по объектам</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>C12/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C12" s="18">
+        <f>SUM(C6:C11)</f>
+        <v>49635600</v>
+      </c>
+      <c r="D12" s="18">
+        <f>E12/12</f>
+        <v>3212500</v>
+      </c>
+      <c r="E12" s="18">
+        <f>SUM(E6:E11)</f>
+        <v>38550000</v>
+      </c>
+      <c r="F12" s="18">
         <f>G12/12</f>
-        <v>24062.22917</v>
-      </c>
-      <c r="G12" s="12">
-        <f>'АБК'!D5</f>
-        <v>288746.75</v>
+        <v>382746.9375</v>
+      </c>
+      <c r="G12" s="18">
+        <f>SUM(G6:G11)</f>
+        <v>4592963.25</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Сумма по объектам</t>
-        </is>
-      </c>
-      <c r="B13" s="18">
-        <f>C13/12</f>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Фонд оплаты труда дератизаторов</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="10">
+        <f>G13/12</f>
+        <v>1033952</v>
+      </c>
+      <c r="G13" s="10">
+        <f>Данные!$B$13*Данные!$B$11*12</f>
+        <v>12407424</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>ВСЕГО ЗА ГОД</t>
+        </is>
+      </c>
+      <c r="B14" s="19">
+        <f>C14/12</f>
         <v>4136300</v>
       </c>
-      <c r="C13" s="18">
-        <f>SUM(C7:C12)</f>
+      <c r="C14" s="19">
+        <f>C12</f>
         <v>49635600</v>
       </c>
-      <c r="D13" s="18">
-        <f>E13/12</f>
+      <c r="D14" s="19">
+        <f>E14/12</f>
         <v>3212500</v>
       </c>
-      <c r="E13" s="18">
-        <f>SUM(E7:E12)</f>
+      <c r="E14" s="19">
+        <f>E12</f>
         <v>38550000</v>
       </c>
-      <c r="F13" s="18">
-        <f>G13/12</f>
-        <v>375646.6042</v>
-      </c>
-      <c r="G13" s="18">
-        <f>SUM(G7:G12)</f>
-        <v>4507759.25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Фонд оплаты труда дератизаторов</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="10">
+      <c r="F14" s="19">
         <f>G14/12</f>
-        <v>1033952</v>
-      </c>
-      <c r="G14" s="10">
-        <f>Данные!$B$14*Данные!$B$12*12</f>
-        <v>12407424</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>ВСЕГО ЗА ГОД</t>
-        </is>
-      </c>
-      <c r="B15" s="19">
-        <f>C15/12</f>
-        <v>4136300</v>
-      </c>
-      <c r="C15" s="19">
-        <f>C13</f>
-        <v>49635600</v>
-      </c>
-      <c r="D15" s="19">
-        <f>E15/12</f>
-        <v>3212500</v>
-      </c>
-      <c r="E15" s="19">
-        <f>E13</f>
-        <v>38550000</v>
-      </c>
-      <c r="F15" s="19">
-        <f>G15/12</f>
-        <v>1411185.271</v>
-      </c>
-      <c r="G15" s="19">
-        <f>G13+G6+G14</f>
-        <v>16934223.25</v>
-      </c>
-    </row>
-    <row r="16"/>
+        <v>1416698.938</v>
+      </c>
+      <c r="G14" s="19">
+        <f>G12+G13</f>
+        <v>17000387.25</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>во сколько раз</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>во сколько раз</t>
-        </is>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Indigo Solutions дороже штата</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>C18/12</f>
+        <v>2719601.062</v>
+      </c>
+      <c r="C18" s="11">
+        <f>C14-G14</f>
+        <v>32635212.75</v>
+      </c>
+      <c r="D18" s="51">
+        <f>IF(G14=0,0,C14/G14)</f>
+        <v>2.919674668</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Indigo Solutions дороже штата</t>
+          <t>Pest Hunters дороже штата</t>
         </is>
       </c>
       <c r="B19" s="10">
         <f>C19/12</f>
-        <v>2725114.729</v>
-      </c>
-      <c r="C19" s="12">
-        <f>C15-G15</f>
-        <v>32701376.75</v>
+        <v>1795801.062</v>
+      </c>
+      <c r="C19" s="11">
+        <f>E14-G14</f>
+        <v>21549612.75</v>
       </c>
       <c r="D19" s="51">
-        <f>IF(G15=0,0,C15/G15)</f>
-        <v>2.93108218</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Pest Hunters дороже штата</t>
-        </is>
-      </c>
-      <c r="B20" s="10">
-        <f>C20/12</f>
-        <v>1801314.729</v>
-      </c>
-      <c r="C20" s="12">
-        <f>E15-G15</f>
-        <v>21615776.75</v>
-      </c>
-      <c r="D20" s="51">
-        <f>IF(G15=0,0,E15/G15)</f>
-        <v>2.276455166</v>
-      </c>
-    </row>
-    <row r="21"/>
+        <f>IF(G14=0,0,E14/G14)</f>
+        <v>2.267595404</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="21" t="n"/>
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Цена за ед., ₸</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>за год, ₸</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Ед. изм.</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Цена за ед., ₸</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>за год, ₸</t>
-        </is>
-      </c>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Численность штата</t>
+        </is>
+      </c>
+      <c r="B23" s="10">
+        <f>Данные!$B$13</f>
+        <v>4</v>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>чел.</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Численность штата</t>
-        </is>
-      </c>
-      <c r="B24" s="10">
-        <f>Данные!$B$14</f>
-        <v>4</v>
-      </c>
+          <t>Оклад одного дератизатора</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>чел.</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
+          <t>₸/мес</t>
+        </is>
+      </c>
+      <c r="D24" s="10">
+        <f>Данные!$B$11</f>
+        <v>258488</v>
+      </c>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Оклад одного дератизатора</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
+          <t>Фонд оплаты труда</t>
+        </is>
+      </c>
+      <c r="B25" s="10">
+        <f>Данные!$B$13</f>
+        <v>4</v>
+      </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>₸/мес</t>
+          <t>чел.</t>
         </is>
       </c>
       <c r="D25" s="10">
-        <f>Данные!$B$12</f>
+        <f>Данные!$B$11</f>
         <v>258488</v>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="E25" s="10">
+        <f>Данные!$B$13*Данные!$B$11</f>
+        <v>1033952</v>
+      </c>
+      <c r="F25" s="11">
+        <f>Данные!$B$13*Данные!$B$11*12</f>
+        <v>12407424</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Фонд оплаты труда</t>
+          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B26" s="10">
-        <f>Данные!$B$14</f>
-        <v>4</v>
+        <f>Данные!$B$32+Данные!$C$32</f>
+        <v>1377</v>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>чел.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D26" s="10">
-        <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
-      <c r="E26" s="10">
-        <f>Данные!$B$14*Данные!$B$12</f>
-        <v>1033952</v>
-      </c>
-      <c r="F26" s="12">
-        <f>Данные!$B$14*Данные!$B$12*12</f>
-        <v>12407424</v>
+        <f>Данные!$B$9</f>
+        <v>2160</v>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="11">
+        <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
+        <v>2974320</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
+          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
         </is>
       </c>
       <c r="B27" s="10">
-        <f>Данные!$B$33+Данные!$C$33</f>
-        <v>1377</v>
+        <f>Данные!$D$32</f>
+        <v>343</v>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>шт/мес</t>
         </is>
       </c>
       <c r="D27" s="10">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
-      </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="12">
-        <f>(Данные!$B$33+Данные!$C$33)*Данные!$B$9</f>
-        <v>2974320</v>
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E27" s="10">
+        <f>Данные!$D$32*Данные!$B$8</f>
+        <v>54880</v>
+      </c>
+      <c r="F27" s="11">
+        <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
+        <v>384160</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
+          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
         </is>
       </c>
       <c r="B28" s="10">
-        <f>Данные!$D$33</f>
-        <v>343</v>
+        <f>Данные!$D$32*2</f>
+        <v>686</v>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
@@ -1371,51 +1380,51 @@
         <v>160</v>
       </c>
       <c r="E28" s="10">
-        <f>Данные!$D$33*Данные!$B$8</f>
-        <v>54880</v>
-      </c>
-      <c r="F28" s="12">
-        <f>Данные!$D$33*Данные!$B$8*Данные!$B$15</f>
-        <v>384160</v>
+        <f>Данные!$D$32*2*Данные!$B$8</f>
+        <v>109760</v>
+      </c>
+      <c r="F28" s="11">
+        <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
+        <v>548800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
+          <t>Зерноцид · 2-й контур, тёплый сезон</t>
         </is>
       </c>
       <c r="B29" s="10">
-        <f>Данные!$D$33*2</f>
-        <v>686</v>
+        <f>Данные!$G$32</f>
+        <v>16</v>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>шт/мес</t>
+          <t>кг/мес</t>
         </is>
       </c>
       <c r="D29" s="10">
-        <f>Данные!$B$8</f>
-        <v>160</v>
+        <f>Данные!$B$6</f>
+        <v>740</v>
       </c>
       <c r="E29" s="10">
-        <f>Данные!$D$33*2*Данные!$B$8</f>
-        <v>109760</v>
-      </c>
-      <c r="F29" s="12">
-        <f>Данные!$D$33*2*Данные!$B$8*Данные!$B$16</f>
-        <v>548800</v>
+        <f>Данные!$G$32*Данные!$B$6</f>
+        <v>11840</v>
+      </c>
+      <c r="F29" s="11">
+        <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
+        <v>82880</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Зерноцид · 2-й контур, тёплый сезон</t>
+          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
         </is>
       </c>
       <c r="B30" s="10">
-        <f>Данные!$G$33</f>
-        <v>16</v>
+        <f>Данные!$F$32</f>
+        <v>20.3</v>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
@@ -1423,59 +1432,50 @@
         </is>
       </c>
       <c r="D30" s="10">
-        <f>Данные!$B$6</f>
-        <v>740</v>
+        <f>Данные!$B$7</f>
+        <v>3642.5</v>
       </c>
       <c r="E30" s="10">
-        <f>Данные!$G$33*Данные!$B$6</f>
-        <v>11840</v>
-      </c>
-      <c r="F30" s="12">
-        <f>Данные!$G$33*Данные!$B$6*Данные!$B$15</f>
-        <v>82880</v>
+        <f>Данные!$F$32*Данные!$B$7</f>
+        <v>73942.75</v>
+      </c>
+      <c r="F30" s="11">
+        <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
+        <v>517599.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
+          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
         </is>
       </c>
       <c r="B31" s="10">
-        <f>Данные!$F$33</f>
-        <v>20.3</v>
+        <f>Данные!$C$32</f>
+        <v>1198</v>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D31" s="10">
-        <f>Данные!$B$7</f>
-        <v>3642.5</v>
-      </c>
-      <c r="E31" s="10">
-        <f>Данные!$F$33*Данные!$B$7</f>
-        <v>73942.75</v>
-      </c>
-      <c r="F31" s="12">
-        <f>Данные!$F$33*Данные!$B$7*Данные!$B$15</f>
-        <v>517599.25</v>
-      </c>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
-        </is>
-      </c>
-      <c r="B32" s="10">
-        <f>Данные!$C$33</f>
-        <v>1198</v>
+          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
+        </is>
+      </c>
+      <c r="B32" s="52">
+        <f>Данные!$F$32/Данные!$C$32</f>
+        <v>0.01694490818</v>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>кг/мес</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
@@ -1485,140 +1485,140 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
-        </is>
-      </c>
-      <c r="B33" s="52">
-        <f>Данные!$F$33/Данные!$C$33</f>
-        <v>0.01694490818</v>
+          <t>Бутылки, 1-й контур · тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B33" s="10">
+        <f>Данные!$B$32</f>
+        <v>179</v>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Бутылки · тёплый сезон</t>
-        </is>
-      </c>
-      <c r="B34" s="10">
-        <f>Данные!$B$11</f>
-        <v>40</v>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D34" s="10">
+      <c r="D33" s="10">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E34" s="10">
-        <f>Данные!$B$11*Данные!$B$10</f>
-        <v>2720</v>
-      </c>
-      <c r="F34" s="12">
-        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v>19040</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="E33" s="10">
+        <f>Данные!$B$32*Данные!$B$10</f>
+        <v>12172</v>
+      </c>
+      <c r="F33" s="11">
+        <f>Данные!$B$32*Данные!$B$10*Данные!$B$14</f>
+        <v>85204</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B35" s="28" t="n"/>
-      <c r="C35" s="28" t="n"/>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="19">
-        <f>F35/12</f>
-        <v>1411185.271</v>
-      </c>
-      <c r="F35" s="19">
-        <f>F26+F27+F28+F29+F30+F31+F34</f>
-        <v>16934223.25</v>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="19">
+        <f>F34/12</f>
+        <v>1416698.938</v>
+      </c>
+      <c r="F34" s="19">
+        <f>F25+F26+F27+F28+F29+F30+F33</f>
+        <v>17000387.25</v>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="21" t="n"/>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="21" t="n"/>
+    </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="21" t="n"/>
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>Условие</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>Ставка</t>
-        </is>
-      </c>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Цена КП без скидок</t>
+        </is>
+      </c>
+      <c r="B39" s="10">
+        <f>C39/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C39" s="11">
+        <f>C14</f>
+        <v>49635600</v>
+      </c>
+      <c r="D39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Цена КП без скидок</t>
+          <t>Вся территория фабрики</t>
         </is>
       </c>
       <c r="B40" s="10">
         <f>C40/12</f>
-        <v>4136300</v>
-      </c>
-      <c r="C40" s="12">
-        <f>C15</f>
-        <v>49635600</v>
-      </c>
-      <c r="D40" s="5" t="n"/>
+        <v>3515855</v>
+      </c>
+      <c r="C40" s="11">
+        <f>C14*(1-Данные!$B$63)</f>
+        <v>42190260</v>
+      </c>
+      <c r="D40" s="53">
+        <f>Данные!$B$63</f>
+        <v>0.15</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Вся территория фабрики</t>
+          <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
       <c r="B41" s="10">
         <f>C41/12</f>
-        <v>3515855</v>
-      </c>
-      <c r="C41" s="12">
-        <f>C15*(1-Данные!$B$64)</f>
-        <v>42190260</v>
+        <v>2988476.75</v>
+      </c>
+      <c r="C41" s="11">
+        <f>C14*(1-Данные!$B$63)*(1-Данные!$B$64)</f>
+        <v>35861721</v>
       </c>
       <c r="D41" s="53">
         <f>Данные!$B$64</f>
@@ -1628,96 +1628,100 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Вся территория + 100 % предоплата</t>
+          <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
       <c r="B42" s="10">
         <f>C42/12</f>
-        <v>2988476.75</v>
-      </c>
-      <c r="C42" s="12">
-        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
-        <v>35861721</v>
+        <v>2510320.47</v>
+      </c>
+      <c r="C42" s="11">
+        <f>C14*(1-Данные!$B$63)*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+        <v>30123845.64</v>
       </c>
       <c r="D42" s="53">
         <f>Данные!$B$65</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Вся территория + предоплата + неплательщик НДС</t>
-        </is>
-      </c>
-      <c r="B43" s="10">
-        <f>C43/12</f>
-        <v>2510320.47</v>
-      </c>
-      <c r="C43" s="12">
-        <f>C15*(1-Данные!$B$64)*(1-Данные!$B$65)*(1-Данные!$B$66)</f>
-        <v>30123845.64</v>
-      </c>
-      <c r="D43" s="53">
-        <f>Данные!$B$66</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="44"/>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
-        </is>
-      </c>
-      <c r="B45" s="21" t="n"/>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>Что зафиксировано в документах</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B46" s="31" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D46" s="31" t="inlineStr">
-        <is>
-          <t>Что зафиксировано в документах</t>
-        </is>
-      </c>
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+        </is>
+      </c>
+      <c r="E46" s="48" t="n"/>
+      <c r="F46" s="48" t="n"/>
+      <c r="G46" s="49" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Indigo Solutions</t>
+          <t>Pest Hunters</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="D47" s="32" t="inlineStr">
         <is>
-          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+          <t>выезд по запросу</t>
         </is>
       </c>
       <c r="E47" s="48" t="n"/>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>ККЗ</t>
+          <t>бройлерные площадки</t>
         </is>
       </c>
       <c r="C48" s="26" t="n">
@@ -1740,7 +1744,7 @@
       </c>
       <c r="D48" s="32" t="inlineStr">
         <is>
-          <t>выезд по запросу</t>
+          <t>дополнительные визиты по вызову</t>
         </is>
       </c>
       <c r="E48" s="48" t="n"/>
@@ -1755,15 +1759,15 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>бройлерные площадки</t>
+          <t>ЗПП</t>
         </is>
       </c>
       <c r="C49" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" s="32" t="inlineStr">
         <is>
-          <t>дополнительные визиты по вызову</t>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
       <c r="E49" s="48" t="n"/>
@@ -1778,15 +1782,15 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>ЗПП</t>
+          <t>склад ТМЦ</t>
         </is>
       </c>
       <c r="C50" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" s="32" t="inlineStr">
         <is>
-          <t>по графику на 2026 год, бригада из трёх человек</t>
+          <t>выезд по рекламации за два рабочих дня</t>
         </is>
       </c>
       <c r="E50" s="48" t="n"/>
@@ -1796,66 +1800,43 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>склад ТМЦ</t>
+          <t>все объекты</t>
         </is>
       </c>
       <c r="C51" s="26" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D51" s="32" t="inlineStr">
         <is>
-          <t>выезд по рекламации за два рабочих дня</t>
+          <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
       <c r="E51" s="48" t="n"/>
       <c r="F51" s="48" t="n"/>
       <c r="G51" s="49" t="n"/>
     </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="32" t="inlineStr">
-        <is>
-          <t>присутствие 5/2, реакция в тот же день</t>
-        </is>
-      </c>
-      <c r="E52" s="48" t="n"/>
-      <c r="F52" s="48" t="n"/>
-      <c r="G52" s="49" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
     <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="D51:G51"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="D46:G46"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="D48:G48"/>
     <mergeCell ref="D47:G47"/>
     <mergeCell ref="A2:G2"/>
@@ -1871,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1927,7 +1908,7 @@
         <v>900000</v>
       </c>
       <c r="D5" s="35">
-        <f>D11+D12+D13+D14+D15</f>
+        <f>D11+D12+D13+D14+D15+D16</f>
         <v>88137.5</v>
       </c>
     </row>
@@ -1971,13 +1952,13 @@
         </is>
       </c>
       <c r="B9" s="37">
-        <f>Данные!$B$37</f>
+        <f>Данные!$B$36</f>
         <v>96600</v>
       </c>
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>1159200</v>
       </c>
@@ -1989,13 +1970,13 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>Данные!$B$53</f>
+        <f>Данные!$B$52</f>
         <v>75000</v>
       </c>
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>900000</v>
       </c>
@@ -2007,13 +1988,13 @@
         </is>
       </c>
       <c r="B11" s="37">
-        <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
+        <f>(Данные!$B$19+Данные!$C$19)*Данные!$B$9</f>
         <v>62640</v>
       </c>
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>62640</v>
       </c>
@@ -2025,14 +2006,14 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>Данные!$D$20*Данные!$B$8</f>
+        <f>Данные!$D$19*Данные!$B$8</f>
         <v>0</v>
       </c>
       <c r="C12" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>0</v>
       </c>
@@ -2044,14 +2025,14 @@
         </is>
       </c>
       <c r="B13" s="37">
-        <f>Данные!$D$20*2*Данные!$B$8</f>
+        <f>Данные!$D$19*2*Данные!$B$8</f>
         <v>0</v>
       </c>
       <c r="C13" s="37">
-        <f>Данные!$B$16</f>
+        <f>Данные!$B$15</f>
         <v>5</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>0</v>
       </c>
@@ -2063,14 +2044,14 @@
         </is>
       </c>
       <c r="B14" s="37">
-        <f>Данные!$G$20*Данные!$B$6</f>
+        <f>Данные!$G$19*Данные!$B$6</f>
         <v>0</v>
       </c>
       <c r="C14" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>0</v>
       </c>
@@ -2082,79 +2063,98 @@
         </is>
       </c>
       <c r="B15" s="37">
-        <f>Данные!$F$20*Данные!$B$7</f>
+        <f>Данные!$F$19*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
       <c r="C15" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>25497.5</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B16" s="37">
+        <f>Данные!$B$19*Данные!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="37">
+        <f>Данные!$B$14</f>
+        <v>7</v>
+      </c>
+      <c r="D16" s="11">
+        <f>B16*C16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="37">
-        <f>Данные!$B$54</f>
+      <c r="B20" s="37">
+        <f>Данные!$B$53</f>
         <v>70000</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C20" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="10">
-        <f>B19*C19</f>
+      <c r="D20" s="10">
+        <f>B20*C20</f>
         <v>840000</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2163,7 +2163,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2176,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2232,8 +2232,8 @@
         <v>34770000</v>
       </c>
       <c r="D5" s="35">
-        <f>D14+D15+D16+D17+D18</f>
-        <v>3955237.5</v>
+        <f>D14+D15+D16+D17+D18+D19</f>
+        <v>4031873.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="B9" s="37">
-        <f>Данные!$B$38</f>
+        <f>Данные!$B$37</f>
         <v>618400</v>
       </c>
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>7420800</v>
       </c>
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>Данные!$B$40</f>
+        <f>Данные!$B$39</f>
         <v>569800</v>
       </c>
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>6837600</v>
       </c>
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="B11" s="37">
-        <f>Данные!$B$42</f>
+        <f>Данные!$B$41</f>
         <v>2599100</v>
       </c>
       <c r="C11" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>31189200</v>
       </c>
@@ -2330,14 +2330,14 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>Данные!$B$55</f>
+        <f>Данные!$B$54</f>
         <v>3172000</v>
       </c>
       <c r="C12" s="37">
-        <f>Данные!$B$61</f>
+        <f>Данные!$B$60</f>
         <v>9</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>28548000</v>
       </c>
@@ -2349,14 +2349,14 @@
         </is>
       </c>
       <c r="B13" s="37">
-        <f>Данные!$B$56</f>
+        <f>Данные!$B$55</f>
         <v>2074000</v>
       </c>
       <c r="C13" s="37">
-        <f>Данные!$B$62</f>
+        <f>Данные!$B$61</f>
         <v>3</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>6222000</v>
       </c>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="B14" s="37">
-        <f>(SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30))*Данные!$B$9</f>
+        <f>(SUM(Данные!$B$22:$B$29)+SUM(Данные!$C$22:$C$29))*Данные!$B$9</f>
         <v>2715120</v>
       </c>
       <c r="C14" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>2715120</v>
       </c>
@@ -2386,14 +2386,14 @@
         </is>
       </c>
       <c r="B15" s="37">
-        <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
+        <f>SUM(Данные!$D$22:$D$29)*Данные!$B$8</f>
         <v>42880</v>
       </c>
       <c r="C15" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>300160</v>
       </c>
@@ -2405,14 +2405,14 @@
         </is>
       </c>
       <c r="B16" s="37">
-        <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
+        <f>SUM(Данные!$D$22:$D$29)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
       <c r="C16" s="37">
-        <f>Данные!$B$16</f>
+        <f>Данные!$B$15</f>
         <v>5</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f>B16*C16</f>
         <v>428800</v>
       </c>
@@ -2424,14 +2424,14 @@
         </is>
       </c>
       <c r="B17" s="37">
-        <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
+        <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6</f>
         <v>11100</v>
       </c>
       <c r="C17" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>B17*C17</f>
         <v>77700</v>
       </c>
@@ -2443,567 +2443,605 @@
         </is>
       </c>
       <c r="B18" s="37">
-        <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
+        <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
       <c r="C18" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f>B18*C18</f>
         <v>433457.5</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B19" s="37">
+        <f>SUM(Данные!$B$22:$B$29)*Данные!$B$10</f>
+        <v>10948</v>
+      </c>
+      <c r="C19" s="37">
+        <f>Данные!$B$14</f>
+        <v>7</v>
+      </c>
+      <c r="D19" s="11">
+        <f>B19*C19</f>
+        <v>76636</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="36" t="inlineStr">
-        <is>
-          <t>Indigo Solutions · Айыртау БП — частичная замена</t>
-        </is>
-      </c>
-      <c r="B22" s="37">
-        <f>Данные!$B$39</f>
-        <v>478400</v>
-      </c>
-      <c r="C22" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="D22" s="10">
-        <f>B22*C22</f>
-        <v>5740800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="36" t="inlineStr">
         <is>
-          <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
+          <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
       <c r="B23" s="37">
-        <f>Данные!$B$41</f>
-        <v>440700</v>
+        <f>Данные!$B$38</f>
+        <v>478400</v>
       </c>
       <c r="C23" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="10">
         <f>B23*C23</f>
-        <v>5288400</v>
+        <v>5740800</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="36" t="inlineStr">
         <is>
-          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
+          <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
       <c r="B24" s="37">
-        <f>Данные!$B$43</f>
-        <v>2010300</v>
+        <f>Данные!$B$40</f>
+        <v>440700</v>
       </c>
       <c r="C24" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="10">
         <f>B24*C24</f>
-        <v>24123600</v>
+        <v>5288400</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="36" t="inlineStr">
         <is>
-          <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
+          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
       <c r="B25" s="37">
-        <f>Данные!$B$57</f>
-        <v>2806000</v>
-      </c>
-      <c r="C25" s="37">
-        <f>Данные!$B$61</f>
-        <v>9</v>
+        <f>Данные!$B$42</f>
+        <v>2010300</v>
+      </c>
+      <c r="C25" s="37" t="n">
+        <v>12</v>
       </c>
       <c r="D25" s="10">
         <f>B25*C25</f>
-        <v>25254000</v>
+        <v>24123600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="36" t="inlineStr">
         <is>
-          <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
+          <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
       <c r="B26" s="37">
-        <f>Данные!$B$58</f>
-        <v>1830000</v>
+        <f>Данные!$B$56</f>
+        <v>2806000</v>
       </c>
       <c r="C26" s="37">
-        <f>Данные!$B$62</f>
-        <v>3</v>
+        <f>Данные!$B$60</f>
+        <v>9</v>
       </c>
       <c r="D26" s="10">
         <f>B26*C26</f>
+        <v>25254000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
+        </is>
+      </c>
+      <c r="B27" s="37">
+        <f>Данные!$B$57</f>
+        <v>1830000</v>
+      </c>
+      <c r="C27" s="37">
+        <f>Данные!$B$61</f>
+        <v>3</v>
+      </c>
+      <c r="D27" s="10">
+        <f>B27*C27</f>
         <v>5490000</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="36" t="inlineStr">
-        <is>
-          <t>Indigo Solutions · Айыртау БП</t>
-        </is>
-      </c>
-      <c r="B30" s="37">
-        <f>Данные!$B$48</f>
-        <v>720000</v>
-      </c>
-      <c r="C30" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="D30" s="10">
-        <f>B30*C30</f>
-        <v>8640000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="36" t="inlineStr">
         <is>
-          <t>Indigo Solutions · Многоэтажки Д и Г</t>
+          <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
       <c r="B31" s="37">
-        <f>Данные!$B$49</f>
-        <v>1080000</v>
+        <f>Данные!$B$47</f>
+        <v>720000</v>
       </c>
       <c r="C31" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="10">
         <f>B31*C31</f>
-        <v>12960000</v>
+        <v>8640000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="36" t="inlineStr">
         <is>
-          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
+          <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
       <c r="B32" s="37">
-        <f>Данные!$B$50</f>
-        <v>3000000</v>
+        <f>Данные!$B$48</f>
+        <v>1080000</v>
       </c>
       <c r="C32" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D32" s="10">
         <f>B32*C32</f>
+        <v>12960000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
+        </is>
+      </c>
+      <c r="B33" s="37">
+        <f>Данные!$B$49</f>
+        <v>3000000</v>
+      </c>
+      <c r="C33" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="10">
+        <f>B33*C33</f>
         <v>36000000</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="29" t="inlineStr">
+    <row r="34"/>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36"/>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>КОНТУР 1 И КОНТУР 2 ПО ПЛОЩАДКАМ, шт</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="21" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>Площадка</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>1-й контур</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>2-й контур</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Площадка А</t>
-        </is>
-      </c>
-      <c r="B39" s="38">
-        <f>Данные!$B$23</f>
-        <v>13</v>
-      </c>
-      <c r="C39" s="38">
-        <f>Данные!$C$23</f>
-        <v>147</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Площадка Б</t>
+          <t>Площадка А</t>
         </is>
       </c>
       <c r="B40" s="38">
-        <f>Данные!$B$24</f>
-        <v>17</v>
+        <f>Данные!$B$22</f>
+        <v>13</v>
       </c>
       <c r="C40" s="38">
-        <f>Данные!$C$24</f>
-        <v>146</v>
+        <f>Данные!$C$22</f>
+        <v>147</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>В / Восточка</t>
+          <t>Площадка Б</t>
         </is>
       </c>
       <c r="B41" s="38">
-        <f>Данные!$B$25</f>
-        <v>50</v>
+        <f>Данные!$B$23</f>
+        <v>17</v>
       </c>
       <c r="C41" s="38">
-        <f>Данные!$C$25</f>
-        <v>239</v>
+        <f>Данные!$C$23</f>
+        <v>146</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Площадка Г</t>
+          <t>В / Восточка</t>
         </is>
       </c>
       <c r="B42" s="38">
-        <f>Данные!$B$26</f>
-        <v>17</v>
+        <f>Данные!$B$24</f>
+        <v>50</v>
       </c>
       <c r="C42" s="38">
-        <f>Данные!$C$26</f>
-        <v>88</v>
+        <f>Данные!$C$24</f>
+        <v>239</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Площадка Д</t>
+          <t>Площадка Г</t>
         </is>
       </c>
       <c r="B43" s="38">
-        <f>Данные!$B$27</f>
-        <v>15</v>
+        <f>Данные!$B$25</f>
+        <v>17</v>
       </c>
       <c r="C43" s="38">
-        <f>Данные!$C$27</f>
-        <v>69</v>
+        <f>Данные!$C$25</f>
+        <v>88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Площадка Е</t>
+          <t>Площадка Д</t>
         </is>
       </c>
       <c r="B44" s="38">
-        <f>Данные!$B$28</f>
-        <v>13</v>
+        <f>Данные!$B$26</f>
+        <v>15</v>
       </c>
       <c r="C44" s="38">
-        <f>Данные!$C$28</f>
-        <v>147</v>
+        <f>Данные!$C$26</f>
+        <v>69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Площадка Ж</t>
+          <t>Площадка Е</t>
         </is>
       </c>
       <c r="B45" s="38">
-        <f>Данные!$B$29</f>
-        <v>17</v>
+        <f>Данные!$B$27</f>
+        <v>13</v>
       </c>
       <c r="C45" s="38">
-        <f>Данные!$C$29</f>
-        <v>73</v>
+        <f>Данные!$C$27</f>
+        <v>147</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
+          <t>Площадка Ж</t>
+        </is>
+      </c>
+      <c r="B46" s="38">
+        <f>Данные!$B$28</f>
+        <v>17</v>
+      </c>
+      <c r="C46" s="38">
+        <f>Данные!$C$28</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
           <t>Айыртау</t>
         </is>
       </c>
-      <c r="B46" s="38">
-        <f>Данные!$B$30</f>
+      <c r="B47" s="38">
+        <f>Данные!$B$29</f>
         <v>19</v>
       </c>
-      <c r="C46" s="38">
-        <f>Данные!$C$30</f>
+      <c r="C47" s="38">
+        <f>Данные!$C$29</f>
         <v>187</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Итого по площадкам</t>
         </is>
       </c>
-      <c r="B47" s="39">
-        <f>SUM(B39:B46)</f>
+      <c r="B48" s="39">
+        <f>SUM(B40:B47)</f>
         <v>161</v>
       </c>
-      <c r="C47" s="39">
-        <f>SUM(C39:C46)</f>
+      <c r="C48" s="39">
+        <f>SUM(C40:C47)</f>
         <v>1096</v>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>ШТАТ УКПФ ПО БРОЙЛЕРНЫМ ПЛОЩАДКАМ — ДЕТАЛЬНАЯ РАСШИФРОВКА</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>₸/мес (разово — цена за шт)</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Мес.</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>За год / разово, ₸</t>
         </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го контура · разовая закупка</t>
-        </is>
-      </c>
-      <c r="B51" s="10">
-        <f>B47*Данные!$B$9</f>
-        <v>347760</v>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>разово</t>
-        </is>
-      </c>
-      <c r="D51" s="10">
-        <f>B47*Данные!$B$9</f>
-        <v>347760</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>Приманочные станции 2-го контура · разовая закупка</t>
+          <t>Приманочные станции 1-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B52" s="10">
-        <f>C47*Данные!$B$9</f>
-        <v>2367360</v>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
+        <f>B48*Данные!$B$9</f>
+        <v>347760</v>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
       <c r="D52" s="10">
-        <f>C47*Данные!$B$9</f>
-        <v>2367360</v>
+        <f>B48*Данные!$B$9</f>
+        <v>347760</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Клеевые станции 3-го контура, тёплый сезон</t>
+          <t>Приманочные станции 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B53" s="10">
-        <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8</f>
-        <v>42880</v>
-      </c>
-      <c r="C53" s="11">
-        <f>Данные!$B$15</f>
-        <v>7</v>
+        <f>C48*Данные!$B$9</f>
+        <v>2367360</v>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>разово</t>
+        </is>
       </c>
       <c r="D53" s="10">
-        <f>SUM(Данные!$D$23:$D$30)*Данные!$B$8*Данные!$B$15</f>
-        <v>300160</v>
+        <f>C48*Данные!$B$9</f>
+        <v>2367360</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
+          <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
       <c r="B54" s="10">
-        <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8</f>
-        <v>85760</v>
-      </c>
-      <c r="C54" s="11">
-        <f>Данные!$B$16</f>
-        <v>5</v>
+        <f>SUM(Данные!$D$22:$D$29)*Данные!$B$8</f>
+        <v>42880</v>
+      </c>
+      <c r="C54" s="12">
+        <f>Данные!$B$14</f>
+        <v>7</v>
       </c>
       <c r="D54" s="10">
-        <f>SUM(Данные!$D$23:$D$30)*2*Данные!$B$8*Данные!$B$16</f>
-        <v>428800</v>
+        <f>SUM(Данные!$D$22:$D$29)*Данные!$B$8*Данные!$B$14</f>
+        <v>300160</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Зерноцид, 2-й контур</t>
+          <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
       <c r="B55" s="10">
-        <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6</f>
-        <v>11100</v>
-      </c>
-      <c r="C55" s="11">
+        <f>SUM(Данные!$D$22:$D$29)*2*Данные!$B$8</f>
+        <v>85760</v>
+      </c>
+      <c r="C55" s="12">
         <f>Данные!$B$15</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D55" s="10">
-        <f>SUM(Данные!$G$23:$G$30)*Данные!$B$6*Данные!$B$15</f>
-        <v>77700</v>
+        <f>SUM(Данные!$D$22:$D$29)*2*Данные!$B$8*Данные!$B$15</f>
+        <v>428800</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
+          <t>Зерноцид, 2-й контур</t>
+        </is>
+      </c>
+      <c r="B56" s="10">
+        <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6</f>
+        <v>11100</v>
+      </c>
+      <c r="C56" s="12">
+        <f>Данные!$B$14</f>
+        <v>7</v>
+      </c>
+      <c r="D56" s="10">
+        <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6*Данные!$B$14</f>
+        <v>77700</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B56" s="10">
-        <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7</f>
+      <c r="B57" s="10">
+        <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C56" s="11">
-        <f>Данные!$B$15</f>
+      <c r="C57" s="12">
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D56" s="10">
-        <f>SUM(Данные!$F$23:$F$30)*Данные!$B$7*Данные!$B$15</f>
+      <c r="D57" s="10">
+        <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7*Данные!$B$14</f>
         <v>433457.5</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Бутылки, 1-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B58" s="10">
+        <f>B48*Данные!$B$10</f>
+        <v>10948</v>
+      </c>
+      <c r="C58" s="12">
+        <f>Данные!$B$14</f>
+        <v>7</v>
+      </c>
+      <c r="D58" s="10">
+        <f>B48*Данные!$B$10*Данные!$B$14</f>
+        <v>76636</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
-      <c r="B57" s="28" t="n"/>
-      <c r="C57" s="28" t="n"/>
-      <c r="D57" s="19">
-        <f>SUM(D51:D56)</f>
-        <v>3955237.5</v>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="29" t="inlineStr">
+      <c r="B59" s="28" t="n"/>
+      <c r="C59" s="28" t="n"/>
+      <c r="D59" s="19">
+        <f>SUM(D52:D58)</f>
+        <v>4031873.5</v>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт, разовая закупка), но количество точек по контурам разное — см. таблицу выше.</t>
         </is>
@@ -3011,8 +3049,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3025,7 +3063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3081,8 +3119,8 @@
         <v>0</v>
       </c>
       <c r="D5" s="35">
-        <f>D11+D12+D13+D14+D15</f>
-        <v>175637.5</v>
+        <f>D11+D12+D13+D14+D15+D16</f>
+        <v>184205.5</v>
       </c>
     </row>
     <row r="6"/>
@@ -3125,13 +3163,13 @@
         </is>
       </c>
       <c r="B9" s="37">
-        <f>Данные!$B$44</f>
+        <f>Данные!$B$43</f>
         <v>126200</v>
       </c>
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>1514400</v>
       </c>
@@ -3148,7 +3186,7 @@
       <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>0</v>
       </c>
@@ -3160,13 +3198,13 @@
         </is>
       </c>
       <c r="B11" s="37">
-        <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
+        <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
         <v>112320</v>
       </c>
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>112320</v>
       </c>
@@ -3178,14 +3216,14 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>Данные!$D$21*Данные!$B$8</f>
+        <f>Данные!$D$20*Данные!$B$8</f>
         <v>1920</v>
       </c>
       <c r="C12" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>13440</v>
       </c>
@@ -3197,14 +3235,14 @@
         </is>
       </c>
       <c r="B13" s="37">
-        <f>Данные!$D$21*2*Данные!$B$8</f>
+        <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
       <c r="C13" s="37">
-        <f>Данные!$B$16</f>
+        <f>Данные!$B$15</f>
         <v>5</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>19200</v>
       </c>
@@ -3216,14 +3254,14 @@
         </is>
       </c>
       <c r="B14" s="37">
-        <f>Данные!$G$21*Данные!$B$6</f>
+        <f>Данные!$G$20*Данные!$B$6</f>
         <v>740</v>
       </c>
       <c r="C14" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>5180</v>
       </c>
@@ -3235,123 +3273,142 @@
         </is>
       </c>
       <c r="B15" s="37">
-        <f>Данные!$F$21*Данные!$B$7</f>
+        <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
       <c r="C15" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>25497.5</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B16" s="37">
+        <f>Данные!$B$20*Данные!$B$10</f>
+        <v>1224</v>
+      </c>
+      <c r="C16" s="37">
+        <f>Данные!$B$14</f>
+        <v>7</v>
+      </c>
+      <c r="D16" s="11">
+        <f>B16*C16</f>
+        <v>8568</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B19" s="37">
-        <f>Данные!$B$45</f>
+      <c r="B20" s="37">
+        <f>Данные!$B$44</f>
         <v>106800</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C20" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="10">
-        <f>B19*C19</f>
+      <c r="D20" s="10">
+        <f>B20*C20</f>
         <v>1281600</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B23" s="37">
-        <f>Данные!$B$51</f>
+      <c r="B24" s="37">
+        <f>Данные!$B$50</f>
         <v>100800</v>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C24" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D23" s="10">
-        <f>B23*C23</f>
+      <c r="D24" s="10">
+        <f>B24*C24</f>
         <v>1209600</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+    <row r="25"/>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3359,7 +3416,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3472,13 +3529,13 @@
         </is>
       </c>
       <c r="B9" s="37">
-        <f>Данные!$B$46</f>
+        <f>Данные!$B$45</f>
         <v>126200</v>
       </c>
       <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>1514400</v>
       </c>
@@ -3490,13 +3547,13 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>Данные!$B$59</f>
+        <f>Данные!$B$58</f>
         <v>180000</v>
       </c>
       <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>2160000</v>
       </c>
@@ -3513,7 +3570,7 @@
       <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>0</v>
       </c>
@@ -3558,7 +3615,7 @@
         </is>
       </c>
       <c r="B15" s="37">
-        <f>Данные!$B$47</f>
+        <f>Данные!$B$46</f>
         <v>106800</v>
       </c>
       <c r="C15" s="37" t="n">
@@ -3609,7 +3666,7 @@
         </is>
       </c>
       <c r="B19" s="37">
-        <f>Данные!$B$52</f>
+        <f>Данные!$B$51</f>
         <v>160800</v>
       </c>
       <c r="C19" s="37" t="n">
@@ -3756,7 +3813,7 @@
       <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>0</v>
       </c>
@@ -3768,14 +3825,14 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>Данные!$B$60</f>
+        <f>Данные!$B$59</f>
         <v>80000</v>
       </c>
       <c r="C10" s="37">
-        <f>Данные!$B$63</f>
+        <f>Данные!$B$62</f>
         <v>9</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>720000</v>
       </c>
@@ -3792,7 +3849,7 @@
       <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>0</v>
       </c>
@@ -3820,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3876,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="35">
-        <f>D11+D12+D13+D14+D15</f>
+        <f>D11+D12+D13+D14+D15+D16</f>
         <v>288746.75</v>
       </c>
     </row>
@@ -3925,7 +3982,7 @@
       <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>B9*C9</f>
         <v>0</v>
       </c>
@@ -3942,7 +3999,7 @@
       <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>B10*C10</f>
         <v>0</v>
       </c>
@@ -3954,13 +4011,13 @@
         </is>
       </c>
       <c r="B11" s="37">
-        <f>(Данные!$B$22+Данные!$C$22)*Данные!$B$9</f>
+        <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
         <v>84240</v>
       </c>
       <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>B11*C11</f>
         <v>84240</v>
       </c>
@@ -3972,14 +4029,14 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>Данные!$D$22*Данные!$B$8</f>
+        <f>Данные!$D$21*Данные!$B$8</f>
         <v>10080</v>
       </c>
       <c r="C12" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>B12*C12</f>
         <v>70560</v>
       </c>
@@ -3991,14 +4048,14 @@
         </is>
       </c>
       <c r="B13" s="37">
-        <f>Данные!$D$22*2*Данные!$B$8</f>
+        <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
       <c r="C13" s="37">
-        <f>Данные!$B$16</f>
+        <f>Данные!$B$15</f>
         <v>5</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>B13*C13</f>
         <v>100800</v>
       </c>
@@ -4010,14 +4067,14 @@
         </is>
       </c>
       <c r="B14" s="37">
-        <f>Данные!$G$22*Данные!$B$6</f>
+        <f>Данные!$G$21*Данные!$B$6</f>
         <v>0</v>
       </c>
       <c r="C14" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>B14*C14</f>
         <v>0</v>
       </c>
@@ -4029,36 +4086,55 @@
         </is>
       </c>
       <c r="B15" s="37">
-        <f>Данные!$F$22*Данные!$B$7</f>
+        <f>Данные!$F$21*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
       <c r="C15" s="37">
-        <f>Данные!$B$15</f>
+        <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>B15*C15</f>
         <v>33146.75</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
-        </is>
-      </c>
-    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B16" s="37">
+        <f>Данные!$B$21*Данные!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="37">
+        <f>Данные!$B$14</f>
+        <v>7</v>
+      </c>
+      <c r="D16" s="11">
+        <f>B16*C16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
         <is>
+          <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
@@ -4072,7 +4148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4083,7 +4159,11 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4136,11 +4216,11 @@
         </is>
       </c>
       <c r="B6" s="10">
+        <f>Данные!$B$11</f>
+        <v>258488</v>
+      </c>
+      <c r="C6" s="10">
         <f>Данные!$B$12</f>
-        <v>258488</v>
-      </c>
-      <c r="C6" s="10">
-        <f>Данные!$B$13</f>
         <v>350000</v>
       </c>
     </row>
@@ -4151,11 +4231,11 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>Данные!$B$14</f>
+        <f>Данные!$B$13</f>
         <v>4</v>
       </c>
       <c r="C7" s="10">
-        <f>Данные!$B$14</f>
+        <f>Данные!$B$13</f>
         <v>4</v>
       </c>
     </row>
@@ -4180,11 +4260,11 @@
           <t>Зарплата за год</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f>B8*12</f>
         <v>12407424</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f>C8*12</f>
         <v>16800000</v>
       </c>
@@ -4193,7 +4273,7 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ (РАЗОВАЯ ЗАКУПКА) И ЯДЫ (ТОЛЬКО ТЁПЛЫЙ СЕЗОН) РАЗДЕЛЬНО</t>
+          <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ (РАЗОВАЯ ЗАКУПКА), ЯДЫ И БУТЫЛКИ (ТОЛЬКО ТЁПЛЫЙ СЕЗОН) РАЗДЕЛЬНО</t>
         </is>
       </c>
       <c r="B11" s="21" t="n"/>
@@ -4206,6 +4286,8 @@
       <c r="I11" s="21" t="n"/>
       <c r="J11" s="21" t="n"/>
       <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
+      <c r="M11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4260,6 +4342,16 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
+          <t>Бутылки 1-го к., шт/мес</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Бутылки за год, ₸</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
           <t>Материалы за год, ₸</t>
         </is>
       </c>
@@ -4271,7 +4363,7 @@
         </is>
       </c>
       <c r="B13" s="54">
-        <f>Данные!$B$20+Данные!$C$20</f>
+        <f>Данные!$B$19+Данные!$C$19</f>
         <v>29</v>
       </c>
       <c r="C13" s="10">
@@ -4279,35 +4371,43 @@
         <v>62640</v>
       </c>
       <c r="D13" s="54">
-        <f>Данные!$D$20</f>
+        <f>Данные!$D$19</f>
         <v>0</v>
       </c>
       <c r="E13" s="54">
-        <f>Данные!$D$20*2</f>
+        <f>Данные!$D$19*2</f>
         <v>0</v>
       </c>
       <c r="F13" s="10">
-        <f>D13*Данные!$B$8*Данные!$B$15+E13*Данные!$B$8*Данные!$B$16</f>
+        <f>D13*Данные!$B$8*Данные!$B$14+E13*Данные!$B$8*Данные!$B$15</f>
         <v>0</v>
       </c>
       <c r="G13" s="55">
-        <f>Данные!$G$20</f>
+        <f>Данные!$G$19</f>
         <v>0</v>
       </c>
       <c r="H13" s="10">
-        <f>G13*Данные!$B$6*Данные!$B$15</f>
+        <f>G13*Данные!$B$6*Данные!$B$14</f>
         <v>0</v>
       </c>
       <c r="I13" s="55">
-        <f>Данные!$F$20</f>
+        <f>Данные!$F$19</f>
         <v>1</v>
       </c>
       <c r="J13" s="10">
-        <f>I13*Данные!$B$7*Данные!$B$15</f>
+        <f>I13*Данные!$B$7*Данные!$B$14</f>
         <v>25497.5</v>
       </c>
-      <c r="K13" s="12">
-        <f>C13+F13+H13+J13</f>
+      <c r="K13" s="54">
+        <f>Данные!$B$19</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <f>K13*Данные!$B$10*Данные!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="11">
+        <f>C13+F13+H13+J13+L13</f>
         <v>88137.5</v>
       </c>
     </row>
@@ -4318,7 +4418,7 @@
         </is>
       </c>
       <c r="B14" s="54">
-        <f>SUM(Данные!$B$23:$B$30)+SUM(Данные!$C$23:$C$30)</f>
+        <f>SUM(Данные!$B$22:$B$29)+SUM(Данные!$C$22:$C$29)</f>
         <v>1257</v>
       </c>
       <c r="C14" s="10">
@@ -4326,36 +4426,44 @@
         <v>2715120</v>
       </c>
       <c r="D14" s="54">
-        <f>SUM(Данные!$D$23:$D$30)</f>
+        <f>SUM(Данные!$D$22:$D$29)</f>
         <v>268</v>
       </c>
       <c r="E14" s="54">
-        <f>SUM(Данные!$D$23:$D$30)*2</f>
+        <f>SUM(Данные!$D$22:$D$29)*2</f>
         <v>536</v>
       </c>
       <c r="F14" s="10">
-        <f>D14*Данные!$B$8*Данные!$B$15+E14*Данные!$B$8*Данные!$B$16</f>
+        <f>D14*Данные!$B$8*Данные!$B$14+E14*Данные!$B$8*Данные!$B$15</f>
         <v>728960</v>
       </c>
       <c r="G14" s="55">
-        <f>SUM(Данные!$G$23:$G$30)</f>
+        <f>SUM(Данные!$G$22:$G$29)</f>
         <v>15</v>
       </c>
       <c r="H14" s="10">
-        <f>G14*Данные!$B$6*Данные!$B$15</f>
+        <f>G14*Данные!$B$6*Данные!$B$14</f>
         <v>77700</v>
       </c>
       <c r="I14" s="55">
-        <f>SUM(Данные!$F$23:$F$30)</f>
+        <f>SUM(Данные!$F$22:$F$29)</f>
         <v>17</v>
       </c>
       <c r="J14" s="10">
-        <f>I14*Данные!$B$7*Данные!$B$15</f>
+        <f>I14*Данные!$B$7*Данные!$B$14</f>
         <v>433457.5</v>
       </c>
-      <c r="K14" s="12">
-        <f>C14+F14+H14+J14</f>
-        <v>3955237.5</v>
+      <c r="K14" s="54">
+        <f>SUM(Данные!$B$22:$B$29)</f>
+        <v>161</v>
+      </c>
+      <c r="L14" s="10">
+        <f>K14*Данные!$B$10*Данные!$B$14</f>
+        <v>76636</v>
+      </c>
+      <c r="M14" s="11">
+        <f>C14+F14+H14+J14+L14</f>
+        <v>4031873.5</v>
       </c>
     </row>
     <row r="15">
@@ -4365,7 +4473,7 @@
         </is>
       </c>
       <c r="B15" s="54">
-        <f>Данные!$B$21+Данные!$C$21</f>
+        <f>Данные!$B$20+Данные!$C$20</f>
         <v>52</v>
       </c>
       <c r="C15" s="10">
@@ -4373,36 +4481,44 @@
         <v>112320</v>
       </c>
       <c r="D15" s="54">
-        <f>Данные!$D$21</f>
+        <f>Данные!$D$20</f>
         <v>12</v>
       </c>
       <c r="E15" s="54">
-        <f>Данные!$D$21*2</f>
+        <f>Данные!$D$20*2</f>
         <v>24</v>
       </c>
       <c r="F15" s="10">
-        <f>D15*Данные!$B$8*Данные!$B$15+E15*Данные!$B$8*Данные!$B$16</f>
+        <f>D15*Данные!$B$8*Данные!$B$14+E15*Данные!$B$8*Данные!$B$15</f>
         <v>32640</v>
       </c>
       <c r="G15" s="55">
-        <f>Данные!$G$21</f>
+        <f>Данные!$G$20</f>
         <v>1</v>
       </c>
       <c r="H15" s="10">
-        <f>G15*Данные!$B$6*Данные!$B$15</f>
+        <f>G15*Данные!$B$6*Данные!$B$14</f>
         <v>5180</v>
       </c>
       <c r="I15" s="55">
-        <f>Данные!$F$21</f>
+        <f>Данные!$F$20</f>
         <v>1</v>
       </c>
       <c r="J15" s="10">
-        <f>I15*Данные!$B$7*Данные!$B$15</f>
+        <f>I15*Данные!$B$7*Данные!$B$14</f>
         <v>25497.5</v>
       </c>
-      <c r="K15" s="12">
-        <f>C15+F15+H15+J15</f>
-        <v>175637.5</v>
+      <c r="K15" s="54">
+        <f>Данные!$B$20</f>
+        <v>18</v>
+      </c>
+      <c r="L15" s="10">
+        <f>K15*Данные!$B$10*Данные!$B$14</f>
+        <v>8568</v>
+      </c>
+      <c r="M15" s="11">
+        <f>C15+F15+H15+J15+L15</f>
+        <v>184205.5</v>
       </c>
     </row>
     <row r="16">
@@ -4412,7 +4528,7 @@
         </is>
       </c>
       <c r="B16" s="54">
-        <f>Данные!$B$22+Данные!$C$22</f>
+        <f>Данные!$B$21+Данные!$C$21</f>
         <v>39</v>
       </c>
       <c r="C16" s="10">
@@ -4420,369 +4536,362 @@
         <v>84240</v>
       </c>
       <c r="D16" s="54">
-        <f>Данные!$D$22</f>
+        <f>Данные!$D$21</f>
         <v>63</v>
       </c>
       <c r="E16" s="54">
-        <f>Данные!$D$22*2</f>
+        <f>Данные!$D$21*2</f>
         <v>126</v>
       </c>
       <c r="F16" s="10">
-        <f>D16*Данные!$B$8*Данные!$B$15+E16*Данные!$B$8*Данные!$B$16</f>
+        <f>D16*Данные!$B$8*Данные!$B$14+E16*Данные!$B$8*Данные!$B$15</f>
         <v>171360</v>
       </c>
       <c r="G16" s="55">
-        <f>Данные!$G$22</f>
+        <f>Данные!$G$21</f>
         <v>0</v>
       </c>
       <c r="H16" s="10">
-        <f>G16*Данные!$B$6*Данные!$B$15</f>
+        <f>G16*Данные!$B$6*Данные!$B$14</f>
         <v>0</v>
       </c>
       <c r="I16" s="55">
-        <f>Данные!$F$22</f>
+        <f>Данные!$F$21</f>
         <v>1.3</v>
       </c>
       <c r="J16" s="10">
-        <f>I16*Данные!$B$7*Данные!$B$15</f>
+        <f>I16*Данные!$B$7*Данные!$B$14</f>
         <v>33146.75</v>
       </c>
-      <c r="K16" s="12">
-        <f>C16+F16+H16+J16</f>
+      <c r="K16" s="54">
+        <f>Данные!$B$21</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <f>K16*Данные!$B$10*Данные!$B$14</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="11">
+        <f>C16+F16+H16+J16+L16</f>
         <v>288746.75</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Бутылки (по объектам не разносятся)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="12">
-        <f>Данные!$B$11*Данные!$B$10*Данные!$B$15</f>
-        <v>19040</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ, ПЕРВЫЙ ГОД ИТОГО (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B18" s="28" t="n"/>
-      <c r="C18" s="18">
-        <f>SUM(C13:C17)</f>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="18">
+        <f>SUM(C13:C16)</f>
         <v>2974320</v>
       </c>
-      <c r="D18" s="28" t="n"/>
-      <c r="E18" s="28" t="n"/>
-      <c r="F18" s="18">
-        <f>SUM(F13:F17)</f>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="18">
+        <f>SUM(F13:F16)</f>
         <v>932960</v>
       </c>
-      <c r="G18" s="56">
-        <f>SUM(G13:G17)</f>
+      <c r="G17" s="56">
+        <f>SUM(G13:G16)</f>
         <v>16</v>
       </c>
-      <c r="H18" s="18">
-        <f>SUM(H13:H17)</f>
+      <c r="H17" s="18">
+        <f>SUM(H13:H16)</f>
         <v>82880</v>
       </c>
-      <c r="I18" s="56">
-        <f>SUM(I13:I17)</f>
+      <c r="I17" s="56">
+        <f>SUM(I13:I16)</f>
         <v>20.3</v>
       </c>
-      <c r="J18" s="18">
-        <f>SUM(J13:J17)</f>
+      <c r="J17" s="18">
+        <f>SUM(J13:J16)</f>
         <v>517599.25</v>
       </c>
-      <c r="K18" s="18">
-        <f>SUM(K13:K17)</f>
-        <v>4526799.25</v>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="18">
+        <f>SUM(L13:L16)</f>
+        <v>85204</v>
+      </c>
+      <c r="M17" s="18">
+        <f>SUM(M13:M16)</f>
+        <v>4592963.25</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Численность, чел.</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>ЗП в месяц, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>ЗП за год, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Материалы за год, ₸</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Итого за год, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Итого за год, ₸ · оклад 350 000</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Численность, чел.</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>ЗП в месяц, ₸ · оклад 258 488</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>ЗП за год, ₸ · оклад 258 488</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Материалы за год, ₸</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Итого за год, ₸ · оклад 258 488</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Итого за год, ₸ · оклад 350 000</t>
-        </is>
+      <c r="A21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="10">
+        <f>A21*Данные!$B$11</f>
+        <v>516976</v>
+      </c>
+      <c r="C21" s="10">
+        <f>B21*12</f>
+        <v>6203712</v>
+      </c>
+      <c r="D21" s="10">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E21" s="11">
+        <f>C21+D21</f>
+        <v>10796675.25</v>
+      </c>
+      <c r="F21" s="11">
+        <f>A21*Данные!$B$12*12+D21</f>
+        <v>12992963.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="10">
-        <f>A22*Данные!$B$12</f>
-        <v>516976</v>
+        <f>A22*Данные!$B$11</f>
+        <v>775464</v>
       </c>
       <c r="C22" s="10">
         <f>B22*12</f>
-        <v>6203712</v>
+        <v>9305568</v>
       </c>
       <c r="D22" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E22" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>10730511.25</v>
-      </c>
-      <c r="F22" s="12">
-        <f>A22*Данные!$B$13*12+D22</f>
-        <v>12926799.25</v>
+        <v>13898531.25</v>
+      </c>
+      <c r="F22" s="11">
+        <f>A22*Данные!$B$12*12+D22</f>
+        <v>17192963.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" s="10">
-        <f>A23*Данные!$B$12</f>
-        <v>775464</v>
+        <f>A23*Данные!$B$11</f>
+        <v>1033952</v>
       </c>
       <c r="C23" s="10">
         <f>B23*12</f>
-        <v>9305568</v>
+        <v>12407424</v>
       </c>
       <c r="D23" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E23" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>13832367.25</v>
-      </c>
-      <c r="F23" s="12">
-        <f>A23*Данные!$B$13*12+D23</f>
-        <v>17126799.25</v>
+        <v>17000387.25</v>
+      </c>
+      <c r="F23" s="11">
+        <f>A23*Данные!$B$12*12+D23</f>
+        <v>21392963.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" s="10">
-        <f>A24*Данные!$B$12</f>
-        <v>1033952</v>
+        <f>A24*Данные!$B$11</f>
+        <v>1292440</v>
       </c>
       <c r="C24" s="10">
         <f>B24*12</f>
-        <v>12407424</v>
+        <v>15509280</v>
       </c>
       <c r="D24" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E24" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>16934223.25</v>
-      </c>
-      <c r="F24" s="12">
-        <f>A24*Данные!$B$13*12+D24</f>
-        <v>21326799.25</v>
+        <v>20102243.25</v>
+      </c>
+      <c r="F24" s="11">
+        <f>A24*Данные!$B$12*12+D24</f>
+        <v>25592963.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" s="10">
-        <f>A25*Данные!$B$12</f>
-        <v>1292440</v>
+        <f>A25*Данные!$B$11</f>
+        <v>1550928</v>
       </c>
       <c r="C25" s="10">
         <f>B25*12</f>
-        <v>15509280</v>
+        <v>18611136</v>
       </c>
       <c r="D25" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E25" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E25" s="11">
         <f>C25+D25</f>
-        <v>20036079.25</v>
-      </c>
-      <c r="F25" s="12">
-        <f>A25*Данные!$B$13*12+D25</f>
-        <v>25526799.25</v>
+        <v>23204099.25</v>
+      </c>
+      <c r="F25" s="11">
+        <f>A25*Данные!$B$12*12+D25</f>
+        <v>29792963.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" s="10">
-        <f>A26*Данные!$B$12</f>
-        <v>1550928</v>
+        <f>A26*Данные!$B$11</f>
+        <v>1809416</v>
       </c>
       <c r="C26" s="10">
         <f>B26*12</f>
-        <v>18611136</v>
+        <v>21712992</v>
       </c>
       <c r="D26" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E26" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E26" s="11">
         <f>C26+D26</f>
-        <v>23137935.25</v>
-      </c>
-      <c r="F26" s="12">
-        <f>A26*Данные!$B$13*12+D26</f>
-        <v>29726799.25</v>
+        <v>26305955.25</v>
+      </c>
+      <c r="F26" s="11">
+        <f>A26*Данные!$B$12*12+D26</f>
+        <v>33992963.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B27" s="10">
-        <f>A27*Данные!$B$12</f>
-        <v>1809416</v>
+        <f>A27*Данные!$B$11</f>
+        <v>2067904</v>
       </c>
       <c r="C27" s="10">
         <f>B27*12</f>
-        <v>21712992</v>
+        <v>24814848</v>
       </c>
       <c r="D27" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E27" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E27" s="11">
         <f>C27+D27</f>
-        <v>26239791.25</v>
-      </c>
-      <c r="F27" s="12">
-        <f>A27*Данные!$B$13*12+D27</f>
-        <v>33926799.25</v>
+        <v>29407811.25</v>
+      </c>
+      <c r="F27" s="11">
+        <f>A27*Данные!$B$12*12+D27</f>
+        <v>38192963.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="10">
-        <f>A28*Данные!$B$12</f>
-        <v>2067904</v>
+        <f>A28*Данные!$B$11</f>
+        <v>2326392</v>
       </c>
       <c r="C28" s="10">
         <f>B28*12</f>
-        <v>24814848</v>
+        <v>27916704</v>
       </c>
       <c r="D28" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E28" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E28" s="11">
         <f>C28+D28</f>
-        <v>29341647.25</v>
-      </c>
-      <c r="F28" s="12">
-        <f>A28*Данные!$B$13*12+D28</f>
-        <v>38126799.25</v>
+        <v>32509667.25</v>
+      </c>
+      <c r="F28" s="11">
+        <f>A28*Данные!$B$12*12+D28</f>
+        <v>42392963.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B29" s="10">
-        <f>A29*Данные!$B$12</f>
-        <v>2326392</v>
+        <f>A29*Данные!$B$11</f>
+        <v>2584880</v>
       </c>
       <c r="C29" s="10">
         <f>B29*12</f>
-        <v>27916704</v>
+        <v>31018560</v>
       </c>
       <c r="D29" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E29" s="12">
+        <f>'Штат УКПФ'!$M$17</f>
+        <v>4592963.25</v>
+      </c>
+      <c r="E29" s="11">
         <f>C29+D29</f>
-        <v>32443503.25</v>
-      </c>
-      <c r="F29" s="12">
-        <f>A29*Данные!$B$13*12+D29</f>
-        <v>42326799.25</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B30" s="10">
-        <f>A30*Данные!$B$12</f>
-        <v>2584880</v>
-      </c>
-      <c r="C30" s="10">
-        <f>B30*12</f>
-        <v>31018560</v>
-      </c>
-      <c r="D30" s="10">
-        <f>'Штат УКПФ'!$K$18</f>
-        <v>4526799.25</v>
-      </c>
-      <c r="E30" s="12">
-        <f>C30+D30</f>
-        <v>35545359.25</v>
-      </c>
-      <c r="F30" s="12">
-        <f>A30*Данные!$B$13*12+D30</f>
-        <v>46526799.25</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="29" t="inlineStr">
+        <v>35611523.25</v>
+      </c>
+      <c r="F29" s="11">
+        <f>A29*Данные!$B$12*12+D29</f>
+        <v>46592963.25</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -4790,8 +4899,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4803,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4967,38 +5076,38 @@
       </c>
       <c r="H10" s="45" t="inlineStr">
         <is>
-          <t>внутренние данные УКПФ</t>
+          <t>внутренние данные УКПФ; расход = число точек 1-го контура, тёплый сезон</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Бутылки, расход</t>
+          <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
       <c r="B11" s="44" t="n">
-        <v>40</v>
+        <v>258488</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>шт/мес</t>
+          <t>₸/мес</t>
         </is>
       </c>
       <c r="H11" s="45" t="inlineStr">
         <is>
-          <t>тёплый сезон, зимой ноль; оценка, по объектам не разносится</t>
+          <t>действующий оклад</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Оклад дератизатора · вариант 1</t>
+          <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
       <c r="B12" s="44" t="n">
-        <v>258488</v>
+        <v>350000</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -5007,58 +5116,58 @@
       </c>
       <c r="H12" s="45" t="inlineStr">
         <is>
-          <t>действующий оклад</t>
+          <t>альтернативный уровень для сравнения</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Оклад дератизатора · вариант 2</t>
+          <t>Численность штата</t>
         </is>
       </c>
       <c r="B13" s="44" t="n">
-        <v>350000</v>
+        <v>4</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>₸/мес</t>
+          <t>чел.</t>
         </is>
       </c>
       <c r="H13" s="45" t="inlineStr">
         <is>
-          <t>альтернативный уровень для сравнения</t>
+          <t>измените — пересчитаются все листы</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Численность штата</t>
+          <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
       <c r="B14" s="44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>чел.</t>
+          <t>мес.</t>
         </is>
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
-          <t>измените — пересчитаются все листы</t>
+          <t>заряжаются все три контура</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Тёплых месяцев (апрель — октябрь)</t>
+          <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
       <c r="B15" s="44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
@@ -5067,194 +5176,201 @@
       </c>
       <c r="H15" s="45" t="inlineStr">
         <is>
-          <t>заряжаются все три контура</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Зимних месяцев (ноябрь — март)</t>
-        </is>
-      </c>
-      <c r="B16" s="44" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>мес.</t>
-        </is>
-      </c>
-      <c r="H16" s="45" t="inlineStr">
-        <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>ПРИМАНОЧНЫЕ СТАНЦИИ И НОРМЫ ЯДОВ ПО ОБЪЕКТАМ УКПФ</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+    </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>ПРИМАНОЧНЫЕ СТАНЦИИ И НОРМЫ ЯДОВ ПО ОБЪЕКТАМ УКПФ</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>1-й контур, шт</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>2-й контур, шт</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>3-й контур, шт</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Всего точек, шт</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Pest Killer, кг</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Зерноцид, кг</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>1-й контур, шт</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>2-й контур, шт</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>3-й контур, шт</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Всего точек, шт</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Pest Killer, кг</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Зерноцид, кг</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Примечание</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ККЗ · кормоцех</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="44" t="n">
+        <v>29</v>
+      </c>
+      <c r="D19" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10">
+        <f>SUM(B19:D19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="45" t="inlineStr">
+        <is>
+          <t>29 приманочных станций 2-го контура</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ККЗ · кормоцех</t>
+          <t>Инкубаторий</t>
         </is>
       </c>
       <c r="B20" s="44" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C20" s="44" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D20" s="44" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E20" s="10">
         <f>SUM(B20:D20)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F20" s="57" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="45" t="inlineStr">
-        <is>
-          <t>29 приманочных станций 2-го контура</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H20" s="45" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Инкубаторий</t>
+          <t>АБК · 11 корпусов</t>
         </is>
       </c>
       <c r="B21" s="44" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C21" s="44" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D21" s="44" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="E21" s="10">
         <f>SUM(B21:D21)</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F21" s="57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G21" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="45" t="inlineStr">
+        <is>
+          <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>АБК · 11 корпусов</t>
+          <t>Площадка А</t>
         </is>
       </c>
       <c r="B22" s="44" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C22" s="44" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="D22" s="44" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="E22" s="10">
         <f>SUM(B22:D22)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F22" s="57" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="45" t="inlineStr">
-        <is>
-          <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H22" s="45" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Площадка А</t>
+          <t>Площадка Б</t>
         </is>
       </c>
       <c r="B23" s="44" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C23" s="44" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D23" s="44" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="10">
         <f>SUM(B23:D23)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F23" s="57" t="n">
         <v>2</v>
@@ -5267,78 +5383,78 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Площадка Б</t>
+          <t>В / Восточка</t>
         </is>
       </c>
       <c r="B24" s="44" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C24" s="44" t="n">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="D24" s="44" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E24" s="10">
         <f>SUM(B24:D24)</f>
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F24" s="57" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G24" s="57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="45" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>В / Восточка</t>
+          <t>Площадка Г</t>
         </is>
       </c>
       <c r="B25" s="44" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C25" s="44" t="n">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="D25" s="44" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E25" s="10">
         <f>SUM(B25:D25)</f>
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F25" s="57" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G25" s="57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" s="45" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Площадка Г</t>
+          <t>Площадка Д</t>
         </is>
       </c>
       <c r="B26" s="44" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C26" s="44" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D26" s="44" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E26" s="10">
         <f>SUM(B26:D26)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" s="57" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G26" s="57" t="n">
         <v>1</v>
@@ -5348,115 +5464,106 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Площадка Д</t>
+          <t>Площадка Е</t>
         </is>
       </c>
       <c r="B27" s="44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" s="44" t="n">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="D27" s="44" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E27" s="10">
         <f>SUM(B27:D27)</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F27" s="57" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G27" s="57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="45" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Площадка Е</t>
+          <t>Площадка Ж</t>
         </is>
       </c>
       <c r="B28" s="44" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C28" s="44" t="n">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="D28" s="44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E28" s="10">
         <f>SUM(B28:D28)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F28" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="45" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Площадка Ж</t>
+          <t>Айыртау (БП)</t>
         </is>
       </c>
       <c r="B29" s="44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C29" s="44" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D29" s="44" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E29" s="10">
         <f>SUM(B29:D29)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F29" s="57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="45" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Айыртау (БП)</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="n">
-        <v>19</v>
-      </c>
-      <c r="C30" s="44" t="n">
-        <v>187</v>
-      </c>
-      <c r="D30" s="44" t="n">
-        <v>24</v>
-      </c>
-      <c r="E30" s="10">
-        <f>SUM(B30:D30)</f>
-        <v>19</v>
-      </c>
-      <c r="F30" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="45" t="inlineStr"/>
+          <t>ЗПП · завод по переработке птицы</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="55" t="n"/>
+      <c r="G30" s="55" t="n"/>
+      <c r="H30" s="45" t="inlineStr">
+        <is>
+          <t>нормы расхода не заданы</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>ЗПП · завод по переработке птицы</t>
+          <t>Склад лузги</t>
         </is>
       </c>
       <c r="B31" s="10" t="n"/>
@@ -5472,104 +5579,106 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Склад лузги</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="55" t="n"/>
-      <c r="G32" s="55" t="n"/>
-      <c r="H32" s="45" t="inlineStr">
-        <is>
-          <t>нормы расхода не заданы</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>ИТОГО ПО ФАБРИКЕ</t>
         </is>
       </c>
-      <c r="B33" s="18">
-        <f>SUM(B20:B32)</f>
+      <c r="B32" s="18">
+        <f>SUM(B19:B31)</f>
         <v>179</v>
       </c>
-      <c r="C33" s="18">
-        <f>SUM(C20:C32)</f>
+      <c r="C32" s="18">
+        <f>SUM(C19:C31)</f>
         <v>1198</v>
       </c>
-      <c r="D33" s="18">
-        <f>SUM(D20:D32)</f>
+      <c r="D32" s="18">
+        <f>SUM(D19:D31)</f>
         <v>343</v>
       </c>
-      <c r="E33" s="18">
-        <f>SUM(E20:E32)</f>
+      <c r="E32" s="18">
+        <f>SUM(E19:E31)</f>
         <v>179</v>
       </c>
-      <c r="F33" s="56">
-        <f>SUM(F20:F32)</f>
+      <c r="F32" s="56">
+        <f>SUM(F19:F31)</f>
         <v>20.3</v>
       </c>
-      <c r="G33" s="56">
-        <f>SUM(G20:G32)</f>
+      <c r="G32" s="56">
+        <f>SUM(G19:G31)</f>
         <v>16</v>
       </c>
-      <c r="H33" s="28" t="n"/>
-    </row>
-    <row r="34"/>
+      <c r="H32" s="28" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ ПОДРЯДЧИКОВ ИЗ КП И ДОГОВОРОВ</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="21" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="21" t="n"/>
+    </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ ПОДРЯДЧИКОВ ИЗ КП И ДОГОВОРОВ</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="F35" s="21" t="n"/>
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr"/>
+      <c r="E35" s="31" t="inlineStr"/>
+      <c r="F35" s="31" t="inlineStr"/>
+      <c r="G35" s="31" t="inlineStr"/>
+      <c r="H35" s="31" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
-        <is>
-          <t>Позиция</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>Ед. изм.</t>
-        </is>
-      </c>
-      <c r="D36" s="31" t="inlineStr"/>
-      <c r="E36" s="31" t="inlineStr"/>
-      <c r="F36" s="31" t="inlineStr"/>
-      <c r="G36" s="31" t="inlineStr"/>
-      <c r="H36" s="31" t="inlineStr">
-        <is>
-          <t>Источник</t>
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Indigo · ККЗ, дератизация</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="n">
+        <v>96600</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>₸/мес</t>
+        </is>
+      </c>
+      <c r="H36" s="45" t="inlineStr">
+        <is>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Indigo · ККЗ, дератизация</t>
+          <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
       <c r="B37" s="44" t="n">
-        <v>96600</v>
+        <v>618400</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
@@ -5578,18 +5687,18 @@
       </c>
       <c r="H37" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Айыртау БП, полная замена</t>
+          <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
       <c r="B38" s="44" t="n">
-        <v>618400</v>
+        <v>478400</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
@@ -5598,18 +5707,18 @@
       </c>
       <c r="H38" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Айыртау БП, частичная замена</t>
+          <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
       <c r="B39" s="44" t="n">
-        <v>478400</v>
+        <v>569800</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -5618,18 +5727,18 @@
       </c>
       <c r="H39" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Многоэтажки Д и Г, полная замена</t>
+          <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
       <c r="B40" s="44" t="n">
-        <v>569800</v>
+        <v>440700</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -5638,18 +5747,18 @@
       </c>
       <c r="H40" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
+          <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
       <c r="B41" s="44" t="n">
-        <v>440700</v>
+        <v>2599100</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
@@ -5658,18 +5767,18 @@
       </c>
       <c r="H41" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
+          <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
       <c r="B42" s="44" t="n">
-        <v>2599100</v>
+        <v>2010300</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
@@ -5678,18 +5787,18 @@
       </c>
       <c r="H42" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
+          <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
       <c r="B43" s="44" t="n">
-        <v>2010300</v>
+        <v>126200</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
@@ -5698,18 +5807,18 @@
       </c>
       <c r="H43" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Инкубаторий, полная замена</t>
+          <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
       <c r="B44" s="44" t="n">
-        <v>126200</v>
+        <v>106800</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
@@ -5718,18 +5827,18 @@
       </c>
       <c r="H44" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
+          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Indigo · Инкубаторий, частичная замена</t>
+          <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
       <c r="B45" s="44" t="n">
-        <v>106800</v>
+        <v>126200</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
@@ -5745,11 +5854,11 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Indigo · ЗПП, полная замена</t>
+          <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
       <c r="B46" s="44" t="n">
-        <v>126200</v>
+        <v>106800</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
@@ -5765,11 +5874,11 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Indigo · ЗПП, частичная замена</t>
+          <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
       <c r="B47" s="44" t="n">
-        <v>106800</v>
+        <v>720000</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
@@ -5785,11 +5894,11 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Indigo · дезинсекция, Айыртау БП</t>
+          <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
       <c r="B48" s="44" t="n">
-        <v>720000</v>
+        <v>1080000</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
@@ -5805,11 +5914,11 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Indigo · дезинсекция, Многоэтажки</t>
+          <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
       <c r="B49" s="44" t="n">
-        <v>1080000</v>
+        <v>3000000</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
@@ -5825,11 +5934,11 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Indigo · дезинсекция, Площадки</t>
+          <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
       <c r="B50" s="44" t="n">
-        <v>3000000</v>
+        <v>100800</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
@@ -5845,11 +5954,11 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Indigo · дезинсекция, Инкубаторий</t>
+          <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
       <c r="B51" s="44" t="n">
-        <v>100800</v>
+        <v>160800</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
@@ -5865,11 +5974,11 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>Indigo · дезинсекция, ЗПП</t>
+          <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
       <c r="B52" s="44" t="n">
-        <v>160800</v>
+        <v>75000</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -5878,18 +5987,18 @@
       </c>
       <c r="H52" s="45" t="inlineStr">
         <is>
-          <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · ККЗ, дератизация</t>
+          <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
       <c r="B53" s="44" t="n">
-        <v>75000</v>
+        <v>70000</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
@@ -5905,11 +6014,11 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · ККЗ, дезинсекция</t>
+          <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
       <c r="B54" s="44" t="n">
-        <v>70000</v>
+        <v>3172000</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
@@ -5918,18 +6027,18 @@
       </c>
       <c r="H54" s="45" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки, март — ноябрь</t>
+          <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
       <c r="B55" s="44" t="n">
-        <v>3172000</v>
+        <v>2074000</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
@@ -5945,11 +6054,11 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки, декабрь — февраль</t>
+          <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
       <c r="B56" s="44" t="n">
-        <v>2074000</v>
+        <v>2806000</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
@@ -5958,18 +6067,18 @@
       </c>
       <c r="H56" s="45" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки альт., март — ноябрь</t>
+          <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
       <c r="B57" s="44" t="n">
-        <v>2806000</v>
+        <v>1830000</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
@@ -5985,11 +6094,11 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки альт., дек. — февраль</t>
+          <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
       <c r="B58" s="44" t="n">
-        <v>1830000</v>
+        <v>180000</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
@@ -5998,18 +6107,18 @@
       </c>
       <c r="H58" s="45" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
+          <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · ЗПП</t>
+          <t>Pest Hunters · склад ТМЦ</t>
         </is>
       </c>
       <c r="B59" s="44" t="n">
-        <v>180000</v>
+        <v>80000</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
@@ -6018,38 +6127,38 @@
       </c>
       <c r="H59" s="45" t="inlineStr">
         <is>
-          <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
+          <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · склад ТМЦ</t>
+          <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
       <c r="B60" s="44" t="n">
-        <v>80000</v>
+        <v>9</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>₸/мес</t>
+          <t>мес.</t>
         </is>
       </c>
       <c r="H60" s="45" t="inlineStr">
         <is>
-          <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
+          <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
       <c r="B61" s="44" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
@@ -6065,11 +6174,11 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>Месяцев низкого тарифа площадок (дек — фев)</t>
+          <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
       <c r="B62" s="44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
@@ -6078,34 +6187,34 @@
       </c>
       <c r="H62" s="45" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
+          <t>апрель — декабрь 2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>Месяцев действия договора по складу ТМЦ</t>
-        </is>
-      </c>
-      <c r="B63" s="44" t="n">
-        <v>9</v>
+          <t>Скидка Indigo за всю территорию фабрики</t>
+        </is>
+      </c>
+      <c r="B63" s="58" t="n">
+        <v>0.15</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>мес.</t>
+          <t>доля</t>
         </is>
       </c>
       <c r="H63" s="45" t="inlineStr">
         <is>
-          <t>апрель — декабрь 2026</t>
+          <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>Скидка Indigo за всю территорию фабрики</t>
+          <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
       <c r="B64" s="58" t="n">
@@ -6118,18 +6227,18 @@
       </c>
       <c r="H64" s="45" t="inlineStr">
         <is>
-          <t>КП от 19.08.2026, условия предоставления скидок</t>
+          <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>Скидка Indigo за 100 % предоплату за год</t>
+          <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
       <c r="B65" s="58" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
@@ -6137,26 +6246,6 @@
         </is>
       </c>
       <c r="H65" s="45" t="inlineStr">
-        <is>
-          <t>КП от 19.08.2026, дополнительно к предыдущей</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>Скидка Indigo неплательщику НДС</t>
-        </is>
-      </c>
-      <c r="B66" s="58" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>доля</t>
-        </is>
-      </c>
-      <c r="H66" s="45" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -250,8 +250,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -294,12 +292,14 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1044,305 +1044,290 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Сумма по объектам</t>
-        </is>
-      </c>
-      <c r="B12" s="18">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>ВСЕГО ЗА ГОД, РАСХОДНИКИ</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
         <f>C12/12</f>
         <v>4136300</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <f>SUM(C6:C11)</f>
         <v>49635600</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <f>E12/12</f>
         <v>3212500</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <f>SUM(E6:E11)</f>
         <v>38550000</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>G12/12</f>
         <v>382746.9375</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <f>SUM(G6:G11)</f>
         <v>4592963.25</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Фонд оплаты труда дератизаторов</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="10">
-        <f>G13/12</f>
-        <v>1033952</v>
-      </c>
-      <c r="G13" s="10">
-        <f>Данные!$B$13*Данные!$B$11*12</f>
-        <v>12407424</v>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>ВСЕГО ЗА ГОД</t>
-        </is>
-      </c>
-      <c r="B14" s="19">
-        <f>C14/12</f>
-        <v>4136300</v>
-      </c>
-      <c r="C14" s="19">
-        <f>C12</f>
-        <v>49635600</v>
-      </c>
-      <c r="D14" s="19">
-        <f>E14/12</f>
-        <v>3212500</v>
-      </c>
-      <c r="E14" s="19">
-        <f>E12</f>
-        <v>38550000</v>
-      </c>
-      <c r="F14" s="19">
-        <f>G14/12</f>
-        <v>1416698.938</v>
-      </c>
-      <c r="G14" s="19">
-        <f>G12+G13</f>
-        <v>17000387.25</v>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>во сколько раз</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Indigo Solutions дороже штата</t>
+        </is>
+      </c>
+      <c r="B16" s="10">
+        <f>C16/12</f>
+        <v>2719601.062</v>
+      </c>
+      <c r="C16" s="11">
+        <f>C12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
+        <v>32635212.75</v>
+      </c>
+      <c r="D16" s="51">
+        <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
+        <v>2.919674668</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>во сколько раз</t>
-        </is>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Pest Hunters дороже штата</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>C17/12</f>
+        <v>1795801.062</v>
+      </c>
+      <c r="C17" s="11">
+        <f>E12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
+        <v>21549612.75</v>
+      </c>
+      <c r="D17" s="51">
+        <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
+        <v>2.267595404</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Indigo Solutions дороже штата</t>
-        </is>
-      </c>
-      <c r="B18" s="10">
-        <f>C18/12</f>
-        <v>2719601.062</v>
-      </c>
-      <c r="C18" s="11">
-        <f>C14-G14</f>
-        <v>32635212.75</v>
-      </c>
-      <c r="D18" s="51">
-        <f>IF(G14=0,0,C14/G14)</f>
-        <v>2.919674668</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Pest Hunters дороже штата</t>
-        </is>
-      </c>
-      <c r="B19" s="10">
-        <f>C19/12</f>
-        <v>1795801.062</v>
-      </c>
-      <c r="C19" s="11">
-        <f>E14-G14</f>
-        <v>21549612.75</v>
-      </c>
-      <c r="D19" s="51">
-        <f>IF(G14=0,0,E14/G14)</f>
-        <v>2.267595404</v>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Штат посчитан вместе с ФОТ (расходники + зарплата), КП подрядчиков — как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="21" t="n"/>
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Цена за ед., ₸</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>за год, ₸</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Ед. изм.</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Цена за ед., ₸</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>за год, ₸</t>
-        </is>
-      </c>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Численность штата</t>
+        </is>
+      </c>
+      <c r="B22" s="10">
+        <f>Данные!$B$13</f>
+        <v>4</v>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>чел.</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Численность штата</t>
-        </is>
-      </c>
-      <c r="B23" s="10">
+          <t>Оклад одного дератизатора</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>₸/мес</t>
+        </is>
+      </c>
+      <c r="D23" s="10">
+        <f>Данные!$B$11</f>
+        <v>258488</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Фонд оплаты труда</t>
+        </is>
+      </c>
+      <c r="B24" s="10">
         <f>Данные!$B$13</f>
         <v>4</v>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>чел.</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Оклад одного дератизатора</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>₸/мес</t>
         </is>
       </c>
       <c r="D24" s="10">
         <f>Данные!$B$11</f>
         <v>258488</v>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="E24" s="10">
+        <f>Данные!$B$13*Данные!$B$11</f>
+        <v>1033952</v>
+      </c>
+      <c r="F24" s="11">
+        <f>Данные!$B$13*Данные!$B$11*12</f>
+        <v>12407424</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Фонд оплаты труда</t>
+          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B25" s="10">
-        <f>Данные!$B$13</f>
-        <v>4</v>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>чел.</t>
+        <f>Данные!$B$32+Данные!$C$32</f>
+        <v>1377</v>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>шт</t>
         </is>
       </c>
       <c r="D25" s="10">
-        <f>Данные!$B$11</f>
-        <v>258488</v>
-      </c>
-      <c r="E25" s="10">
-        <f>Данные!$B$13*Данные!$B$11</f>
-        <v>1033952</v>
-      </c>
+        <f>Данные!$B$9</f>
+        <v>2160</v>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="11">
-        <f>Данные!$B$13*Данные!$B$11*12</f>
-        <v>12407424</v>
+        <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
+        <v>2974320</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
+          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
         </is>
       </c>
       <c r="B26" s="10">
-        <f>Данные!$B$32+Данные!$C$32</f>
-        <v>1377</v>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>шт</t>
+        <f>Данные!$D$32</f>
+        <v>343</v>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
         </is>
       </c>
       <c r="D26" s="10">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
-      </c>
-      <c r="E26" s="5" t="n"/>
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E26" s="10">
+        <f>Данные!$D$32*Данные!$B$8</f>
+        <v>54880</v>
+      </c>
       <c r="F26" s="11">
-        <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
-        <v>2974320</v>
+        <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
+        <v>384160</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
+          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
         </is>
       </c>
       <c r="B27" s="10">
-        <f>Данные!$D$32</f>
-        <v>343</v>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
+        <f>Данные!$D$32*2</f>
+        <v>686</v>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
@@ -1352,111 +1337,102 @@
         <v>160</v>
       </c>
       <c r="E27" s="10">
-        <f>Данные!$D$32*Данные!$B$8</f>
-        <v>54880</v>
+        <f>Данные!$D$32*2*Данные!$B$8</f>
+        <v>109760</v>
       </c>
       <c r="F27" s="11">
-        <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
-        <v>384160</v>
+        <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
+        <v>548800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
+          <t>Зерноцид · 2-й контур, тёплый сезон</t>
         </is>
       </c>
       <c r="B28" s="10">
-        <f>Данные!$D$32*2</f>
-        <v>686</v>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>шт/мес</t>
+        <f>Данные!$G$32</f>
+        <v>16</v>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
         </is>
       </c>
       <c r="D28" s="10">
-        <f>Данные!$B$8</f>
-        <v>160</v>
+        <f>Данные!$B$6</f>
+        <v>740</v>
       </c>
       <c r="E28" s="10">
-        <f>Данные!$D$32*2*Данные!$B$8</f>
-        <v>109760</v>
+        <f>Данные!$G$32*Данные!$B$6</f>
+        <v>11840</v>
       </c>
       <c r="F28" s="11">
-        <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
-        <v>548800</v>
+        <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
+        <v>82880</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Зерноцид · 2-й контур, тёплый сезон</t>
+          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
         </is>
       </c>
       <c r="B29" s="10">
-        <f>Данные!$G$32</f>
-        <v>16</v>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
+        <f>Данные!$F$32</f>
+        <v>20.3</v>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
       <c r="D29" s="10">
-        <f>Данные!$B$6</f>
-        <v>740</v>
+        <f>Данные!$B$7</f>
+        <v>3642.5</v>
       </c>
       <c r="E29" s="10">
-        <f>Данные!$G$32*Данные!$B$6</f>
-        <v>11840</v>
+        <f>Данные!$F$32*Данные!$B$7</f>
+        <v>73942.75</v>
       </c>
       <c r="F29" s="11">
-        <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
-        <v>82880</v>
+        <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
+        <v>517599.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
+          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
         </is>
       </c>
       <c r="B30" s="10">
-        <f>Данные!$F$32</f>
-        <v>20.3</v>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D30" s="10">
-        <f>Данные!$B$7</f>
-        <v>3642.5</v>
-      </c>
-      <c r="E30" s="10">
-        <f>Данные!$F$32*Данные!$B$7</f>
-        <v>73942.75</v>
-      </c>
-      <c r="F30" s="11">
-        <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
-        <v>517599.25</v>
-      </c>
+        <f>Данные!$C$32</f>
+        <v>1198</v>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
-        </is>
-      </c>
-      <c r="B31" s="10">
-        <f>Данные!$C$32</f>
-        <v>1198</v>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>шт</t>
+          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
+        </is>
+      </c>
+      <c r="B31" s="52">
+        <f>Данные!$F$32/Данные!$C$32</f>
+        <v>0.01694490818</v>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
         </is>
       </c>
       <c r="D31" s="5" t="n"/>
@@ -1466,239 +1442,243 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
-        </is>
-      </c>
-      <c r="B32" s="52">
-        <f>Данные!$F$32/Данные!$C$32</f>
-        <v>0.01694490818</v>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
           <t>Бутылки, 1-й контур · тёплый сезон</t>
         </is>
       </c>
-      <c r="B33" s="10">
+      <c r="B32" s="10">
         <f>Данные!$B$32</f>
         <v>179</v>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D33" s="10">
+      <c r="D32" s="10">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E32" s="10">
         <f>Данные!$B$32*Данные!$B$10</f>
         <v>12172</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F32" s="11">
         <f>Данные!$B$32*Данные!$B$10*Данные!$B$14</f>
         <v>85204</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n"/>
-      <c r="C34" s="28" t="n"/>
-      <c r="D34" s="28" t="n"/>
-      <c r="E34" s="19">
-        <f>F34/12</f>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="17">
+        <f>F33/12</f>
         <v>1416698.938</v>
       </c>
-      <c r="F34" s="19">
-        <f>F25+F26+F27+F28+F29+F30+F33</f>
+      <c r="F33" s="17">
+        <f>F24+F25+F26+F27+F28+F29+F32</f>
         <v>17000387.25</v>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+    </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="21" t="n"/>
-      <c r="F37" s="21" t="n"/>
-      <c r="G37" s="21" t="n"/>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>Условие</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>Ставка</t>
-        </is>
-      </c>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Цена КП без скидок</t>
+        </is>
+      </c>
+      <c r="B38" s="10">
+        <f>C38/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C38" s="11">
+        <f>C12</f>
+        <v>49635600</v>
+      </c>
+      <c r="D38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Цена КП без скидок</t>
+          <t>Вся территория фабрики</t>
         </is>
       </c>
       <c r="B39" s="10">
         <f>C39/12</f>
-        <v>4136300</v>
+        <v>3515855</v>
       </c>
       <c r="C39" s="11">
-        <f>C14</f>
-        <v>49635600</v>
-      </c>
-      <c r="D39" s="5" t="n"/>
+        <f>C12*(1-Данные!$B$63)</f>
+        <v>42190260</v>
+      </c>
+      <c r="D39" s="53">
+        <f>Данные!$B$63</f>
+        <v>0.15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Вся территория фабрики</t>
+          <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
       <c r="B40" s="10">
         <f>C40/12</f>
-        <v>3515855</v>
+        <v>2988476.75</v>
       </c>
       <c r="C40" s="11">
-        <f>C14*(1-Данные!$B$63)</f>
-        <v>42190260</v>
+        <f>C12*(1-Данные!$B$63)*(1-Данные!$B$64)</f>
+        <v>35861721</v>
       </c>
       <c r="D40" s="53">
-        <f>Данные!$B$63</f>
+        <f>Данные!$B$64</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Вся территория + 100 % предоплата</t>
+          <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
       <c r="B41" s="10">
         <f>C41/12</f>
-        <v>2988476.75</v>
+        <v>2510320.47</v>
       </c>
       <c r="C41" s="11">
-        <f>C14*(1-Данные!$B$63)*(1-Данные!$B$64)</f>
-        <v>35861721</v>
+        <f>C12*(1-Данные!$B$63)*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+        <v>30123845.64</v>
       </c>
       <c r="D41" s="53">
-        <f>Данные!$B$64</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Вся территория + предоплата + неплательщик НДС</t>
-        </is>
-      </c>
-      <c r="B42" s="10">
-        <f>C42/12</f>
-        <v>2510320.47</v>
-      </c>
-      <c r="C42" s="11">
-        <f>C14*(1-Данные!$B$63)*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
-        <v>30123845.64</v>
-      </c>
-      <c r="D42" s="53">
         <f>Данные!$B$65</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="43"/>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="19" t="n"/>
+    </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
-        </is>
-      </c>
-      <c r="B44" s="21" t="n"/>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>Обходов в месяц</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="inlineStr">
+        <is>
+          <t>Что зафиксировано в документах</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>Обходов в месяц</t>
-        </is>
-      </c>
-      <c r="D45" s="31" t="inlineStr">
-        <is>
-          <t>Что зафиксировано в документах</t>
-        </is>
-      </c>
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>в КП не указана</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+        </is>
+      </c>
+      <c r="E45" s="48" t="n"/>
+      <c r="F45" s="48" t="n"/>
+      <c r="G45" s="49" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Indigo Solutions</t>
+          <t>Pest Hunters</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>в КП не указана</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="inlineStr">
-        <is>
-          <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>выезд по запросу</t>
         </is>
       </c>
       <c r="E46" s="48" t="n"/>
@@ -1713,15 +1693,15 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>ККЗ</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="n">
+          <t>бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="32" t="inlineStr">
-        <is>
-          <t>выезд по запросу</t>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>дополнительные визиты по вызову</t>
         </is>
       </c>
       <c r="E47" s="48" t="n"/>
@@ -1736,15 +1716,15 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>бройлерные площадки</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="32" t="inlineStr">
-        <is>
-          <t>дополнительные визиты по вызову</t>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
       <c r="E48" s="48" t="n"/>
@@ -1759,15 +1739,15 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" s="32" t="inlineStr">
-        <is>
-          <t>по графику на 2026 год, бригада из трёх человек</t>
+          <t>склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="30" t="inlineStr">
+        <is>
+          <t>выезд по рекламации за два рабочих дня</t>
         </is>
       </c>
       <c r="E49" s="48" t="n"/>
@@ -1777,60 +1757,37 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters</t>
+          <t>Штат УКПФ</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="C50" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="32" t="inlineStr">
-        <is>
-          <t>выезд по рекламации за два рабочих дня</t>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
       <c r="E50" s="48" t="n"/>
       <c r="F50" s="48" t="n"/>
       <c r="G50" s="49" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Штат УКПФ</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>все объекты</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D51" s="32" t="inlineStr">
-        <is>
-          <t>присутствие 5/2, реакция в тот же день</t>
-        </is>
-      </c>
-      <c r="E51" s="48" t="n"/>
-      <c r="F51" s="48" t="n"/>
-      <c r="G51" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="D51:G51"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D50:G50"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D45:G45"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D4:E4"/>
@@ -1869,7 +1826,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/шт разовой закупки, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
         </is>
@@ -1877,85 +1834,85 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15+D16</f>
         <v>88137.5</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="35">
         <f>Данные!$B$36</f>
         <v>96600</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -1964,16 +1921,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · дератизация</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="35">
         <f>Данные!$B$52</f>
         <v>75000</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -1982,16 +1939,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="35">
         <f>(Данные!$B$19+Данные!$C$19)*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="11">
@@ -2000,16 +1957,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="35">
         <f>Данные!$D$19*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2019,16 +1976,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="35">
         <f>Данные!$D$19*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="35">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -2038,16 +1995,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="35">
         <f>Данные!$G$19*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2057,16 +2014,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="35">
         <f>Данные!$F$19*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2076,16 +2033,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="35">
         <f>Данные!$B$19*Данные!$B$10</f>
         <v>0</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2096,48 +2053,48 @@
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="35">
         <f>Данные!$B$53</f>
         <v>70000</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="10">
@@ -2147,14 +2104,14 @@
     </row>
     <row r="21"/>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2193,7 +2150,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2201,85 +2158,85 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>D12+D13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f>D14+D15+D16+D17+D18+D19</f>
         <v>4031873.5</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ОСНОВНОЙ ВАРИАНТ</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="35">
         <f>Данные!$B$37</f>
         <v>618400</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -2288,16 +2245,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="35">
         <f>Данные!$B$39</f>
         <v>569800</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -2306,16 +2263,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="35">
         <f>Данные!$B$41</f>
         <v>2599100</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="11">
@@ -2324,16 +2281,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="35">
         <f>Данные!$B$54</f>
         <v>3172000</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="35">
         <f>Данные!$B$60</f>
         <v>9</v>
       </c>
@@ -2343,16 +2300,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="35">
         <f>Данные!$B$55</f>
         <v>2074000</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="35">
         <f>Данные!$B$61</f>
         <v>3</v>
       </c>
@@ -2362,16 +2319,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="35">
         <f>(SUM(Данные!$B$22:$B$29)+SUM(Данные!$C$22:$C$29))*Данные!$B$9</f>
         <v>2715120</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="11">
@@ -2380,16 +2337,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="35">
         <f>SUM(Данные!$D$22:$D$29)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2399,16 +2356,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="35">
         <f>SUM(Данные!$D$22:$D$29)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="35">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -2418,16 +2375,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="35">
         <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2437,16 +2394,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="35">
         <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2456,16 +2413,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="35">
         <f>SUM(Данные!$B$22:$B$29)*Данные!$B$10</f>
         <v>10948</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2476,48 +2433,48 @@
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ ИЗ ТЕХ ЖЕ КП</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="B23" s="37">
+      <c r="B23" s="35">
         <f>Данные!$B$38</f>
         <v>478400</v>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C23" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="10">
@@ -2526,16 +2483,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="35">
         <f>Данные!$B$40</f>
         <v>440700</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="10">
@@ -2544,16 +2501,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="35">
         <f>Данные!$B$42</f>
         <v>2010300</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="10">
@@ -2562,16 +2519,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B26" s="37">
+      <c r="B26" s="35">
         <f>Данные!$B$56</f>
         <v>2806000</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="35">
         <f>Данные!$B$60</f>
         <v>9</v>
       </c>
@@ -2581,16 +2538,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="35">
         <f>Данные!$B$57</f>
         <v>1830000</v>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="35">
         <f>Данные!$B$61</f>
         <v>3</v>
       </c>
@@ -2601,48 +2558,48 @@
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n"/>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="21" t="n"/>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="35">
         <f>Данные!$B$47</f>
         <v>720000</v>
       </c>
-      <c r="C31" s="37" t="n">
+      <c r="C31" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="10">
@@ -2651,16 +2608,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="35">
         <f>Данные!$B$48</f>
         <v>1080000</v>
       </c>
-      <c r="C32" s="37" t="n">
+      <c r="C32" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D32" s="10">
@@ -2669,16 +2626,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B33" s="37">
+      <c r="B33" s="35">
         <f>Данные!$B$49</f>
         <v>3000000</v>
       </c>
-      <c r="C33" s="37" t="n">
+      <c r="C33" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D33" s="10">
@@ -2688,7 +2645,7 @@
     </row>
     <row r="34"/>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
@@ -2697,27 +2654,27 @@
     <row r="36"/>
     <row r="37"/>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>КОНТУР 1 И КОНТУР 2 ПО ПЛОЩАДКАМ, шт</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Площадка</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>1-й контур</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>2-й контур</t>
         </is>
@@ -2729,11 +2686,11 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B40" s="38">
+      <c r="B40" s="36">
         <f>Данные!$B$22</f>
         <v>13</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="36">
         <f>Данные!$C$22</f>
         <v>147</v>
       </c>
@@ -2744,11 +2701,11 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B41" s="38">
+      <c r="B41" s="36">
         <f>Данные!$B$23</f>
         <v>17</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="36">
         <f>Данные!$C$23</f>
         <v>146</v>
       </c>
@@ -2759,11 +2716,11 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B42" s="38">
+      <c r="B42" s="36">
         <f>Данные!$B$24</f>
         <v>50</v>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="36">
         <f>Данные!$C$24</f>
         <v>239</v>
       </c>
@@ -2774,11 +2731,11 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B43" s="38">
+      <c r="B43" s="36">
         <f>Данные!$B$25</f>
         <v>17</v>
       </c>
-      <c r="C43" s="38">
+      <c r="C43" s="36">
         <f>Данные!$C$25</f>
         <v>88</v>
       </c>
@@ -2789,11 +2746,11 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B44" s="38">
+      <c r="B44" s="36">
         <f>Данные!$B$26</f>
         <v>15</v>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="36">
         <f>Данные!$C$26</f>
         <v>69</v>
       </c>
@@ -2804,11 +2761,11 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B45" s="38">
+      <c r="B45" s="36">
         <f>Данные!$B$27</f>
         <v>13</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="36">
         <f>Данные!$C$27</f>
         <v>147</v>
       </c>
@@ -2819,11 +2776,11 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B46" s="38">
+      <c r="B46" s="36">
         <f>Данные!$B$28</f>
         <v>17</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="36">
         <f>Данные!$C$28</f>
         <v>73</v>
       </c>
@@ -2834,43 +2791,43 @@
           <t>Айыртау</t>
         </is>
       </c>
-      <c r="B47" s="38">
+      <c r="B47" s="36">
         <f>Данные!$B$29</f>
         <v>19</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="36">
         <f>Данные!$C$29</f>
         <v>187</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="37" t="inlineStr">
         <is>
           <t>Итого по площадкам</t>
         </is>
       </c>
-      <c r="B48" s="39">
+      <c r="B48" s="38">
         <f>SUM(B40:B47)</f>
         <v>161</v>
       </c>
-      <c r="C48" s="39">
+      <c r="C48" s="38">
         <f>SUM(C40:C47)</f>
         <v>1096</v>
       </c>
     </row>
     <row r="49"/>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>ШТАТ УКПФ ПО БРОЙЛЕРНЫМ ПЛОЩАДКАМ — ДЕТАЛЬНАЯ РАСШИФРОВКА</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="inlineStr">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
@@ -3032,16 +2989,16 @@
           <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
-      <c r="B59" s="28" t="n"/>
-      <c r="C59" s="28" t="n"/>
-      <c r="D59" s="19">
+      <c r="B59" s="26" t="n"/>
+      <c r="C59" s="26" t="n"/>
+      <c r="D59" s="17">
         <f>SUM(D52:D58)</f>
         <v>4031873.5</v>
       </c>
     </row>
     <row r="60"/>
     <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт, разовая закупка), но количество точек по контурам разное — см. таблицу выше.</t>
         </is>
@@ -3080,7 +3037,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
         </is>
@@ -3088,85 +3045,85 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15+D16</f>
         <v>184205.5</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="35">
         <f>Данные!$B$43</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -3175,15 +3132,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="11">
@@ -3192,16 +3149,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="35">
         <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
         <v>112320</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="11">
@@ -3210,16 +3167,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="35">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3229,16 +3186,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="35">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="35">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -3248,16 +3205,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="35">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3267,16 +3224,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="35">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3286,16 +3243,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="35">
         <f>Данные!$B$20*Данные!$B$10</f>
         <v>1224</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3306,48 +3263,48 @@
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B20" s="37">
+      <c r="B20" s="35">
         <f>Данные!$B$44</f>
         <v>106800</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="10">
@@ -3357,48 +3314,48 @@
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="35">
         <f>Данные!$B$50</f>
         <v>100800</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="10">
@@ -3408,7 +3365,7 @@
     </row>
     <row r="25"/>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3446,7 +3403,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3454,85 +3411,85 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f>D11</f>
         <v>0</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования</t>
         </is>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="35">
         <f>Данные!$B$45</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -3541,16 +3498,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="35">
         <f>Данные!$B$58</f>
         <v>180000</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -3559,15 +3516,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="11">
@@ -3577,48 +3534,48 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="35">
         <f>Данные!$B$46</f>
         <v>106800</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="10">
@@ -3628,48 +3585,48 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="35">
         <f>Данные!$B$51</f>
         <v>160800</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="35" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="10">
@@ -3679,14 +3636,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3725,7 +3682,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -3733,84 +3690,84 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>720000</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f>D11</f>
         <v>0</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="11">
@@ -3819,16 +3776,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="35">
         <f>Данные!$B$59</f>
         <v>80000</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="35">
         <f>Данные!$B$62</f>
         <v>9</v>
       </c>
@@ -3838,15 +3795,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="11">
@@ -3856,7 +3813,7 @@
     </row>
     <row r="12"/>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
         </is>
@@ -3894,7 +3851,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -3902,84 +3859,84 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15+D16</f>
         <v>288746.75</v>
       </c>
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ДЕРАТИЗАЦИЯ — ЧТО ВХОДИТ В СРАВНЕНИЕ</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
+      <c r="B7" s="19" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="11">
@@ -3988,15 +3945,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="11">
@@ -4005,16 +3962,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="35">
         <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="11">
@@ -4023,16 +3980,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="35">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4042,16 +3999,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="35">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="35">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -4061,16 +4018,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="35">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4080,16 +4037,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="35">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4099,16 +4056,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="35">
         <f>Данные!$B$21*Данные!$B$10</f>
         <v>0</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="35">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4119,14 +4076,14 @@
     </row>
     <row r="17"/>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4182,28 +4139,28 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>ФОНД ОПЛАТЫ ТРУДА</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
@@ -4255,7 +4212,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -4271,23 +4228,23 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ ПО ОБЪЕКТАМ — СТАНЦИИ (РАЗОВАЯ ЗАКУПКА), ЯДЫ И БУТЫЛКИ (ТОЛЬКО ТЁПЛЫЙ СЕЗОН) РАЗДЕЛЬНО</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="19" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4577,19 +4534,19 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ, ПЕРВЫЙ ГОД ИТОГО (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n"/>
-      <c r="C17" s="18">
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="42">
         <f>SUM(C13:C16)</f>
         <v>2974320</v>
       </c>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="28" t="n"/>
-      <c r="F17" s="18">
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="42">
         <f>SUM(F13:F16)</f>
         <v>932960</v>
       </c>
@@ -4597,7 +4554,7 @@
         <f>SUM(G13:G16)</f>
         <v>16</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="42">
         <f>SUM(H13:H16)</f>
         <v>82880</v>
       </c>
@@ -4605,32 +4562,32 @@
         <f>SUM(I13:I16)</f>
         <v>20.3</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="42">
         <f>SUM(J13:J16)</f>
         <v>517599.25</v>
       </c>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="18">
+      <c r="K17" s="26" t="n"/>
+      <c r="L17" s="42">
         <f>SUM(L13:L16)</f>
         <v>85204</v>
       </c>
-      <c r="M17" s="18">
+      <c r="M17" s="42">
         <f>SUM(M13:M16)</f>
         <v>4592963.25</v>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>ЧИСЛЕННОСТЬ: СКОЛЬКО СТОИТ ШТАТ ПРИ РАЗНОМ ЧИСЛЕ ЛЮДЕЙ</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -4891,7 +4848,7 @@
     </row>
     <row r="30"/>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -4941,40 +4898,40 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>ЦЕНЫ И ПАРАМЕТРЫ ШТАТА УКПФ</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr"/>
-      <c r="E5" s="31" t="inlineStr"/>
-      <c r="F5" s="31" t="inlineStr"/>
-      <c r="G5" s="31" t="inlineStr"/>
-      <c r="H5" s="31" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr"/>
+      <c r="E5" s="29" t="inlineStr"/>
+      <c r="F5" s="29" t="inlineStr"/>
+      <c r="G5" s="29" t="inlineStr"/>
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
@@ -5182,18 +5139,18 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>ПРИМАНОЧНЫЕ СТАНЦИИ И НОРМЫ ЯДОВ ПО ОБЪЕКТАМ УКПФ</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -5579,24 +5536,24 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>ИТОГО ПО ФАБРИКЕ</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="42">
         <f>SUM(B19:B31)</f>
         <v>179</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="42">
         <f>SUM(C19:C31)</f>
         <v>1198</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="42">
         <f>SUM(D19:D31)</f>
         <v>343</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="42">
         <f>SUM(E19:E31)</f>
         <v>179</v>
       </c>
@@ -5608,44 +5565,44 @@
         <f>SUM(G19:G31)</f>
         <v>16</v>
       </c>
-      <c r="H32" s="28" t="n"/>
+      <c r="H32" s="26" t="n"/>
     </row>
     <row r="33"/>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>ЦЕНЫ ПОДРЯДЧИКОВ ИЗ КП И ДОГОВОРОВ</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="19" t="n"/>
+      <c r="H34" s="19" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="31" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B35" s="31" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr"/>
-      <c r="E35" s="31" t="inlineStr"/>
-      <c r="F35" s="31" t="inlineStr"/>
-      <c r="G35" s="31" t="inlineStr"/>
-      <c r="H35" s="31" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr"/>
+      <c r="E35" s="29" t="inlineStr"/>
+      <c r="F35" s="29" t="inlineStr"/>
+      <c r="G35" s="29" t="inlineStr"/>
+      <c r="H35" s="29" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -1115,15 +1115,15 @@
       </c>
       <c r="B16" s="10">
         <f>C16/12</f>
-        <v>2719601.062</v>
+        <v>2461113.062</v>
       </c>
       <c r="C16" s="11">
         <f>C12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>32635212.75</v>
+        <v>29533356.75</v>
       </c>
       <c r="D16" s="51">
         <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>2.919674668</v>
+        <v>2.469157267</v>
       </c>
     </row>
     <row r="17">
@@ -1134,15 +1134,15 @@
       </c>
       <c r="B17" s="10">
         <f>C17/12</f>
-        <v>1795801.062</v>
+        <v>1537313.062</v>
       </c>
       <c r="C17" s="11">
         <f>E12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>21549612.75</v>
+        <v>18447756.75</v>
       </c>
       <c r="D17" s="51">
         <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>2.267595404</v>
+        <v>1.917696424</v>
       </c>
     </row>
     <row r="18">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B22" s="10">
         <f>Данные!$B$13</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B24" s="10">
         <f>Данные!$B$13</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
@@ -1257,11 +1257,11 @@
       </c>
       <c r="E24" s="10">
         <f>Данные!$B$13*Данные!$B$11</f>
-        <v>1033952</v>
+        <v>1292440</v>
       </c>
       <c r="F24" s="11">
         <f>Данные!$B$13*Данные!$B$11*12</f>
-        <v>12407424</v>
+        <v>15509280</v>
       </c>
     </row>
     <row r="25">
@@ -1478,11 +1478,11 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="17">
         <f>F33/12</f>
-        <v>1416698.938</v>
+        <v>1675186.938</v>
       </c>
       <c r="F33" s="17">
         <f>F24+F25+F26+F27+F28+F29+F32</f>
-        <v>17000387.25</v>
+        <v>20102243.25</v>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
@@ -4189,11 +4189,11 @@
       </c>
       <c r="B7" s="10">
         <f>Данные!$B$13</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="10">
         <f>Данные!$B$13</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4204,11 +4204,11 @@
       </c>
       <c r="B8" s="10">
         <f>B6*B7</f>
-        <v>1033952</v>
+        <v>1292440</v>
       </c>
       <c r="C8" s="10">
         <f>C6*C7</f>
-        <v>1400000</v>
+        <v>1750000</v>
       </c>
     </row>
     <row r="9">
@@ -4219,11 +4219,11 @@
       </c>
       <c r="B9" s="11">
         <f>B8*12</f>
-        <v>12407424</v>
+        <v>15509280</v>
       </c>
       <c r="C9" s="11">
         <f>C8*12</f>
-        <v>16800000</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="10"/>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="B13" s="44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -832,11 +832,11 @@
       </c>
       <c r="J6" s="12">
         <f>Данные!$B$11</f>
-        <v>258488</v>
+        <v>350000</v>
       </c>
       <c r="K6" s="12">
         <f>Данные!$B$11</f>
-        <v>258488</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="7">
@@ -876,11 +876,11 @@
       </c>
       <c r="J7" s="12">
         <f>2*Данные!$B$11</f>
-        <v>516976</v>
+        <v>700000</v>
       </c>
       <c r="K7" s="12">
         <f>5*Данные!$B$11</f>
-        <v>1292440</v>
+        <v>1750000</v>
       </c>
     </row>
     <row r="8">
@@ -918,11 +918,11 @@
       </c>
       <c r="J8" s="12">
         <f>2*Данные!$B$11*12</f>
-        <v>6203712</v>
+        <v>8400000</v>
       </c>
       <c r="K8" s="12">
         <f>5*Данные!$B$11*12</f>
-        <v>15509280</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="9">
@@ -1000,11 +1000,11 @@
       </c>
       <c r="J10" s="15">
         <f>J8+J9</f>
-        <v>10796675.25</v>
+        <v>12992963.25</v>
       </c>
       <c r="K10" s="15">
         <f>K8+K9</f>
-        <v>20102243.25</v>
+        <v>25592963.25</v>
       </c>
     </row>
     <row r="11">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K11" s="16">
         <f>K10-J10</f>
-        <v>9305568</v>
+        <v>12600000</v>
       </c>
     </row>
     <row r="12">
@@ -1115,15 +1115,15 @@
       </c>
       <c r="B16" s="10">
         <f>C16/12</f>
-        <v>2461113.062</v>
+        <v>2003553.062</v>
       </c>
       <c r="C16" s="11">
         <f>C12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>29533356.75</v>
+        <v>24042636.75</v>
       </c>
       <c r="D16" s="51">
         <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>2.469157267</v>
+        <v>1.93942372</v>
       </c>
     </row>
     <row r="17">
@@ -1134,15 +1134,15 @@
       </c>
       <c r="B17" s="10">
         <f>C17/12</f>
-        <v>1537313.062</v>
+        <v>1079753.062</v>
       </c>
       <c r="C17" s="11">
         <f>E12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>18447756.75</v>
+        <v>12957036.75</v>
       </c>
       <c r="D17" s="51">
         <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>1.917696424</v>
+        <v>1.506273409</v>
       </c>
     </row>
     <row r="18">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D23" s="10">
         <f>Данные!$B$11</f>
-        <v>258488</v>
+        <v>350000</v>
       </c>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
@@ -1253,15 +1253,15 @@
       </c>
       <c r="D24" s="10">
         <f>Данные!$B$11</f>
-        <v>258488</v>
+        <v>350000</v>
       </c>
       <c r="E24" s="10">
         <f>Данные!$B$13*Данные!$B$11</f>
-        <v>1292440</v>
+        <v>1750000</v>
       </c>
       <c r="F24" s="11">
         <f>Данные!$B$13*Данные!$B$11*12</f>
-        <v>15509280</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="25">
@@ -1478,11 +1478,11 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="17">
         <f>F33/12</f>
-        <v>1675186.938</v>
+        <v>2132746.938</v>
       </c>
       <c r="F33" s="17">
         <f>F24+F25+F26+F27+F28+F29+F32</f>
-        <v>20102243.25</v>
+        <v>25592963.25</v>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
+          <t>Оклад 350 000 ₸</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
           <t>Оклад 258 488 ₸</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="inlineStr">
-        <is>
-          <t>Оклад 350 000 ₸</t>
         </is>
       </c>
     </row>
@@ -4174,11 +4174,11 @@
       </c>
       <c r="B6" s="10">
         <f>Данные!$B$11</f>
-        <v>258488</v>
+        <v>350000</v>
       </c>
       <c r="C6" s="10">
         <f>Данные!$B$12</f>
-        <v>350000</v>
+        <v>258488</v>
       </c>
     </row>
     <row r="7">
@@ -4204,11 +4204,11 @@
       </c>
       <c r="B8" s="10">
         <f>B6*B7</f>
-        <v>1292440</v>
+        <v>1750000</v>
       </c>
       <c r="C8" s="10">
         <f>C6*C7</f>
-        <v>1750000</v>
+        <v>1292440</v>
       </c>
     </row>
     <row r="9">
@@ -4219,11 +4219,11 @@
       </c>
       <c r="B9" s="11">
         <f>B8*12</f>
-        <v>15509280</v>
+        <v>21000000</v>
       </c>
       <c r="C9" s="11">
         <f>C8*12</f>
-        <v>21000000</v>
+        <v>15509280</v>
       </c>
     </row>
     <row r="10"/>
@@ -4597,12 +4597,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ЗП в месяц, ₸ · оклад 258 488</t>
+          <t>ЗП в месяц, ₸ · оклад 350 000</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>ЗП за год, ₸ · оклад 258 488</t>
+          <t>ЗП за год, ₸ · оклад 350 000</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
+          <t>Итого за год, ₸ · оклад 350 000</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
           <t>Итого за год, ₸ · оклад 258 488</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Итого за год, ₸ · оклад 350 000</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
       </c>
       <c r="B21" s="10">
         <f>A21*Данные!$B$11</f>
-        <v>516976</v>
+        <v>700000</v>
       </c>
       <c r="C21" s="10">
         <f>B21*12</f>
-        <v>6203712</v>
+        <v>8400000</v>
       </c>
       <c r="D21" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4639,11 +4639,11 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>10796675.25</v>
+        <v>12992963.25</v>
       </c>
       <c r="F21" s="11">
         <f>A21*Данные!$B$12*12+D21</f>
-        <v>12992963.25</v>
+        <v>10796675.25</v>
       </c>
     </row>
     <row r="22">
@@ -4652,11 +4652,11 @@
       </c>
       <c r="B22" s="10">
         <f>A22*Данные!$B$11</f>
-        <v>775464</v>
+        <v>1050000</v>
       </c>
       <c r="C22" s="10">
         <f>B22*12</f>
-        <v>9305568</v>
+        <v>12600000</v>
       </c>
       <c r="D22" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>13898531.25</v>
+        <v>17192963.25</v>
       </c>
       <c r="F22" s="11">
         <f>A22*Данные!$B$12*12+D22</f>
-        <v>17192963.25</v>
+        <v>13898531.25</v>
       </c>
     </row>
     <row r="23">
@@ -4677,11 +4677,11 @@
       </c>
       <c r="B23" s="10">
         <f>A23*Данные!$B$11</f>
-        <v>1033952</v>
+        <v>1400000</v>
       </c>
       <c r="C23" s="10">
         <f>B23*12</f>
-        <v>12407424</v>
+        <v>16800000</v>
       </c>
       <c r="D23" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4689,11 +4689,11 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>17000387.25</v>
+        <v>21392963.25</v>
       </c>
       <c r="F23" s="11">
         <f>A23*Данные!$B$12*12+D23</f>
-        <v>21392963.25</v>
+        <v>17000387.25</v>
       </c>
     </row>
     <row r="24">
@@ -4702,11 +4702,11 @@
       </c>
       <c r="B24" s="10">
         <f>A24*Данные!$B$11</f>
-        <v>1292440</v>
+        <v>1750000</v>
       </c>
       <c r="C24" s="10">
         <f>B24*12</f>
-        <v>15509280</v>
+        <v>21000000</v>
       </c>
       <c r="D24" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4714,11 +4714,11 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>20102243.25</v>
+        <v>25592963.25</v>
       </c>
       <c r="F24" s="11">
         <f>A24*Данные!$B$12*12+D24</f>
-        <v>25592963.25</v>
+        <v>20102243.25</v>
       </c>
     </row>
     <row r="25">
@@ -4727,11 +4727,11 @@
       </c>
       <c r="B25" s="10">
         <f>A25*Данные!$B$11</f>
-        <v>1550928</v>
+        <v>2100000</v>
       </c>
       <c r="C25" s="10">
         <f>B25*12</f>
-        <v>18611136</v>
+        <v>25200000</v>
       </c>
       <c r="D25" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4739,11 +4739,11 @@
       </c>
       <c r="E25" s="11">
         <f>C25+D25</f>
-        <v>23204099.25</v>
+        <v>29792963.25</v>
       </c>
       <c r="F25" s="11">
         <f>A25*Данные!$B$12*12+D25</f>
-        <v>29792963.25</v>
+        <v>23204099.25</v>
       </c>
     </row>
     <row r="26">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B26" s="10">
         <f>A26*Данные!$B$11</f>
-        <v>1809416</v>
+        <v>2450000</v>
       </c>
       <c r="C26" s="10">
         <f>B26*12</f>
-        <v>21712992</v>
+        <v>29400000</v>
       </c>
       <c r="D26" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4764,11 +4764,11 @@
       </c>
       <c r="E26" s="11">
         <f>C26+D26</f>
-        <v>26305955.25</v>
+        <v>33992963.25</v>
       </c>
       <c r="F26" s="11">
         <f>A26*Данные!$B$12*12+D26</f>
-        <v>33992963.25</v>
+        <v>26305955.25</v>
       </c>
     </row>
     <row r="27">
@@ -4777,11 +4777,11 @@
       </c>
       <c r="B27" s="10">
         <f>A27*Данные!$B$11</f>
-        <v>2067904</v>
+        <v>2800000</v>
       </c>
       <c r="C27" s="10">
         <f>B27*12</f>
-        <v>24814848</v>
+        <v>33600000</v>
       </c>
       <c r="D27" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4789,11 +4789,11 @@
       </c>
       <c r="E27" s="11">
         <f>C27+D27</f>
-        <v>29407811.25</v>
+        <v>38192963.25</v>
       </c>
       <c r="F27" s="11">
         <f>A27*Данные!$B$12*12+D27</f>
-        <v>38192963.25</v>
+        <v>29407811.25</v>
       </c>
     </row>
     <row r="28">
@@ -4802,11 +4802,11 @@
       </c>
       <c r="B28" s="10">
         <f>A28*Данные!$B$11</f>
-        <v>2326392</v>
+        <v>3150000</v>
       </c>
       <c r="C28" s="10">
         <f>B28*12</f>
-        <v>27916704</v>
+        <v>37800000</v>
       </c>
       <c r="D28" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4814,11 +4814,11 @@
       </c>
       <c r="E28" s="11">
         <f>C28+D28</f>
-        <v>32509667.25</v>
+        <v>42392963.25</v>
       </c>
       <c r="F28" s="11">
         <f>A28*Данные!$B$12*12+D28</f>
-        <v>42392963.25</v>
+        <v>32509667.25</v>
       </c>
     </row>
     <row r="29">
@@ -4827,11 +4827,11 @@
       </c>
       <c r="B29" s="10">
         <f>A29*Данные!$B$11</f>
-        <v>2584880</v>
+        <v>3500000</v>
       </c>
       <c r="C29" s="10">
         <f>B29*12</f>
-        <v>31018560</v>
+        <v>42000000</v>
       </c>
       <c r="D29" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4839,11 +4839,11 @@
       </c>
       <c r="E29" s="11">
         <f>C29+D29</f>
-        <v>35611523.25</v>
+        <v>46592963.25</v>
       </c>
       <c r="F29" s="11">
         <f>A29*Данные!$B$12*12+D29</f>
-        <v>46592963.25</v>
+        <v>35611523.25</v>
       </c>
     </row>
     <row r="30"/>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="B11" s="44" t="n">
-        <v>258488</v>
+        <v>350000</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="B12" s="44" t="n">
-        <v>350000</v>
+        <v>258488</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -832,10 +832,10 @@
       </c>
       <c r="J6" s="12">
         <f>Данные!$B$11</f>
-        <v>350000</v>
+        <v>258488</v>
       </c>
       <c r="K6" s="12">
-        <f>Данные!$B$11</f>
+        <f>Данные!$B$12</f>
         <v>350000</v>
       </c>
     </row>
@@ -876,10 +876,10 @@
       </c>
       <c r="J7" s="12">
         <f>2*Данные!$B$11</f>
-        <v>700000</v>
+        <v>516976</v>
       </c>
       <c r="K7" s="12">
-        <f>5*Данные!$B$11</f>
+        <f>5*Данные!$B$12</f>
         <v>1750000</v>
       </c>
     </row>
@@ -918,10 +918,10 @@
       </c>
       <c r="J8" s="12">
         <f>2*Данные!$B$11*12</f>
-        <v>8400000</v>
+        <v>6203712</v>
       </c>
       <c r="K8" s="12">
-        <f>5*Данные!$B$11*12</f>
+        <f>5*Данные!$B$12*12</f>
         <v>21000000</v>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="J10" s="15">
         <f>J8+J9</f>
-        <v>12992963.25</v>
+        <v>10796675.25</v>
       </c>
       <c r="K10" s="15">
         <f>K8+K9</f>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K11" s="16">
         <f>K10-J10</f>
-        <v>12600000</v>
+        <v>14796288</v>
       </c>
     </row>
     <row r="12">
@@ -1115,15 +1115,15 @@
       </c>
       <c r="B16" s="10">
         <f>C16/12</f>
-        <v>2003553.062</v>
+        <v>2461113.062</v>
       </c>
       <c r="C16" s="11">
         <f>C12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>24042636.75</v>
+        <v>29533356.75</v>
       </c>
       <c r="D16" s="51">
         <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>1.93942372</v>
+        <v>2.469157267</v>
       </c>
     </row>
     <row r="17">
@@ -1134,15 +1134,15 @@
       </c>
       <c r="B17" s="10">
         <f>C17/12</f>
-        <v>1079753.062</v>
+        <v>1537313.062</v>
       </c>
       <c r="C17" s="11">
         <f>E12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>12957036.75</v>
+        <v>18447756.75</v>
       </c>
       <c r="D17" s="51">
         <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>1.506273409</v>
+        <v>1.917696424</v>
       </c>
     </row>
     <row r="18">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D23" s="10">
         <f>Данные!$B$11</f>
-        <v>350000</v>
+        <v>258488</v>
       </c>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
@@ -1253,15 +1253,15 @@
       </c>
       <c r="D24" s="10">
         <f>Данные!$B$11</f>
-        <v>350000</v>
+        <v>258488</v>
       </c>
       <c r="E24" s="10">
         <f>Данные!$B$13*Данные!$B$11</f>
-        <v>1750000</v>
+        <v>1292440</v>
       </c>
       <c r="F24" s="11">
         <f>Данные!$B$13*Данные!$B$11*12</f>
-        <v>21000000</v>
+        <v>15509280</v>
       </c>
     </row>
     <row r="25">
@@ -1478,11 +1478,11 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="17">
         <f>F33/12</f>
-        <v>2132746.938</v>
+        <v>1675186.938</v>
       </c>
       <c r="F33" s="17">
         <f>F24+F25+F26+F27+F28+F29+F32</f>
-        <v>25592963.25</v>
+        <v>20102243.25</v>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
+          <t>Оклад 258 488 ₸</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
           <t>Оклад 350 000 ₸</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="inlineStr">
-        <is>
-          <t>Оклад 258 488 ₸</t>
         </is>
       </c>
     </row>
@@ -4174,11 +4174,11 @@
       </c>
       <c r="B6" s="10">
         <f>Данные!$B$11</f>
-        <v>350000</v>
+        <v>258488</v>
       </c>
       <c r="C6" s="10">
         <f>Данные!$B$12</f>
-        <v>258488</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="7">
@@ -4204,11 +4204,11 @@
       </c>
       <c r="B8" s="10">
         <f>B6*B7</f>
-        <v>1750000</v>
+        <v>1292440</v>
       </c>
       <c r="C8" s="10">
         <f>C6*C7</f>
-        <v>1292440</v>
+        <v>1750000</v>
       </c>
     </row>
     <row r="9">
@@ -4219,11 +4219,11 @@
       </c>
       <c r="B9" s="11">
         <f>B8*12</f>
-        <v>21000000</v>
+        <v>15509280</v>
       </c>
       <c r="C9" s="11">
         <f>C8*12</f>
-        <v>15509280</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="10"/>
@@ -4597,12 +4597,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ЗП в месяц, ₸ · оклад 350 000</t>
+          <t>ЗП в месяц, ₸ · оклад 258 488</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>ЗП за год, ₸ · оклад 350 000</t>
+          <t>ЗП за год, ₸ · оклад 258 488</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
+          <t>Итого за год, ₸ · оклад 258 488</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
           <t>Итого за год, ₸ · оклад 350 000</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Итого за год, ₸ · оклад 258 488</t>
         </is>
       </c>
     </row>
@@ -4627,11 +4627,11 @@
       </c>
       <c r="B21" s="10">
         <f>A21*Данные!$B$11</f>
-        <v>700000</v>
+        <v>516976</v>
       </c>
       <c r="C21" s="10">
         <f>B21*12</f>
-        <v>8400000</v>
+        <v>6203712</v>
       </c>
       <c r="D21" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4639,11 +4639,11 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>12992963.25</v>
+        <v>10796675.25</v>
       </c>
       <c r="F21" s="11">
         <f>A21*Данные!$B$12*12+D21</f>
-        <v>10796675.25</v>
+        <v>12992963.25</v>
       </c>
     </row>
     <row r="22">
@@ -4652,11 +4652,11 @@
       </c>
       <c r="B22" s="10">
         <f>A22*Данные!$B$11</f>
-        <v>1050000</v>
+        <v>775464</v>
       </c>
       <c r="C22" s="10">
         <f>B22*12</f>
-        <v>12600000</v>
+        <v>9305568</v>
       </c>
       <c r="D22" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>17192963.25</v>
+        <v>13898531.25</v>
       </c>
       <c r="F22" s="11">
         <f>A22*Данные!$B$12*12+D22</f>
-        <v>13898531.25</v>
+        <v>17192963.25</v>
       </c>
     </row>
     <row r="23">
@@ -4677,11 +4677,11 @@
       </c>
       <c r="B23" s="10">
         <f>A23*Данные!$B$11</f>
-        <v>1400000</v>
+        <v>1033952</v>
       </c>
       <c r="C23" s="10">
         <f>B23*12</f>
-        <v>16800000</v>
+        <v>12407424</v>
       </c>
       <c r="D23" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4689,11 +4689,11 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>21392963.25</v>
+        <v>17000387.25</v>
       </c>
       <c r="F23" s="11">
         <f>A23*Данные!$B$12*12+D23</f>
-        <v>17000387.25</v>
+        <v>21392963.25</v>
       </c>
     </row>
     <row r="24">
@@ -4702,11 +4702,11 @@
       </c>
       <c r="B24" s="10">
         <f>A24*Данные!$B$11</f>
-        <v>1750000</v>
+        <v>1292440</v>
       </c>
       <c r="C24" s="10">
         <f>B24*12</f>
-        <v>21000000</v>
+        <v>15509280</v>
       </c>
       <c r="D24" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4714,11 +4714,11 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>25592963.25</v>
+        <v>20102243.25</v>
       </c>
       <c r="F24" s="11">
         <f>A24*Данные!$B$12*12+D24</f>
-        <v>20102243.25</v>
+        <v>25592963.25</v>
       </c>
     </row>
     <row r="25">
@@ -4727,11 +4727,11 @@
       </c>
       <c r="B25" s="10">
         <f>A25*Данные!$B$11</f>
-        <v>2100000</v>
+        <v>1550928</v>
       </c>
       <c r="C25" s="10">
         <f>B25*12</f>
-        <v>25200000</v>
+        <v>18611136</v>
       </c>
       <c r="D25" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4739,11 +4739,11 @@
       </c>
       <c r="E25" s="11">
         <f>C25+D25</f>
-        <v>29792963.25</v>
+        <v>23204099.25</v>
       </c>
       <c r="F25" s="11">
         <f>A25*Данные!$B$12*12+D25</f>
-        <v>23204099.25</v>
+        <v>29792963.25</v>
       </c>
     </row>
     <row r="26">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B26" s="10">
         <f>A26*Данные!$B$11</f>
-        <v>2450000</v>
+        <v>1809416</v>
       </c>
       <c r="C26" s="10">
         <f>B26*12</f>
-        <v>29400000</v>
+        <v>21712992</v>
       </c>
       <c r="D26" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4764,11 +4764,11 @@
       </c>
       <c r="E26" s="11">
         <f>C26+D26</f>
-        <v>33992963.25</v>
+        <v>26305955.25</v>
       </c>
       <c r="F26" s="11">
         <f>A26*Данные!$B$12*12+D26</f>
-        <v>26305955.25</v>
+        <v>33992963.25</v>
       </c>
     </row>
     <row r="27">
@@ -4777,11 +4777,11 @@
       </c>
       <c r="B27" s="10">
         <f>A27*Данные!$B$11</f>
-        <v>2800000</v>
+        <v>2067904</v>
       </c>
       <c r="C27" s="10">
         <f>B27*12</f>
-        <v>33600000</v>
+        <v>24814848</v>
       </c>
       <c r="D27" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4789,11 +4789,11 @@
       </c>
       <c r="E27" s="11">
         <f>C27+D27</f>
-        <v>38192963.25</v>
+        <v>29407811.25</v>
       </c>
       <c r="F27" s="11">
         <f>A27*Данные!$B$12*12+D27</f>
-        <v>29407811.25</v>
+        <v>38192963.25</v>
       </c>
     </row>
     <row r="28">
@@ -4802,11 +4802,11 @@
       </c>
       <c r="B28" s="10">
         <f>A28*Данные!$B$11</f>
-        <v>3150000</v>
+        <v>2326392</v>
       </c>
       <c r="C28" s="10">
         <f>B28*12</f>
-        <v>37800000</v>
+        <v>27916704</v>
       </c>
       <c r="D28" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4814,11 +4814,11 @@
       </c>
       <c r="E28" s="11">
         <f>C28+D28</f>
-        <v>42392963.25</v>
+        <v>32509667.25</v>
       </c>
       <c r="F28" s="11">
         <f>A28*Данные!$B$12*12+D28</f>
-        <v>32509667.25</v>
+        <v>42392963.25</v>
       </c>
     </row>
     <row r="29">
@@ -4827,11 +4827,11 @@
       </c>
       <c r="B29" s="10">
         <f>A29*Данные!$B$11</f>
-        <v>3500000</v>
+        <v>2584880</v>
       </c>
       <c r="C29" s="10">
         <f>B29*12</f>
-        <v>42000000</v>
+        <v>31018560</v>
       </c>
       <c r="D29" s="10">
         <f>'Штат УКПФ'!$M$17</f>
@@ -4839,11 +4839,11 @@
       </c>
       <c r="E29" s="11">
         <f>C29+D29</f>
-        <v>46592963.25</v>
+        <v>35611523.25</v>
       </c>
       <c r="F29" s="11">
         <f>A29*Данные!$B$12*12+D29</f>
-        <v>35611523.25</v>
+        <v>46592963.25</v>
       </c>
     </row>
     <row r="30"/>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="B11" s="44" t="n">
-        <v>350000</v>
+        <v>258488</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="B12" s="44" t="n">
-        <v>258488</v>
+        <v>350000</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -1115,15 +1115,15 @@
       </c>
       <c r="B16" s="10">
         <f>C16/12</f>
-        <v>2461113.062</v>
+        <v>2003553.062</v>
       </c>
       <c r="C16" s="11">
-        <f>C12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>29533356.75</v>
+        <f>C12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
+        <v>24042636.75</v>
       </c>
       <c r="D16" s="51">
-        <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>2.469157267</v>
+        <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
+        <v>1.93942372</v>
       </c>
     </row>
     <row r="17">
@@ -1134,15 +1134,15 @@
       </c>
       <c r="B17" s="10">
         <f>C17/12</f>
-        <v>1537313.062</v>
+        <v>1079753.062</v>
       </c>
       <c r="C17" s="11">
-        <f>E12-(G12+Данные!$B$13*Данные!$B$11*12)</f>
-        <v>18447756.75</v>
+        <f>E12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
+        <v>12957036.75</v>
       </c>
       <c r="D17" s="51">
-        <f>IF((G12+Данные!$B$13*Данные!$B$11*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$11*12))</f>
-        <v>1.917696424</v>
+        <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
+        <v>1.506273409</v>
       </c>
     </row>
     <row r="18">
@@ -1230,8 +1230,8 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>Данные!$B$11</f>
-        <v>258488</v>
+        <f>Данные!$B$12</f>
+        <v>350000</v>
       </c>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>Данные!$B$11</f>
-        <v>258488</v>
+        <f>Данные!$B$12</f>
+        <v>350000</v>
       </c>
       <c r="E24" s="10">
-        <f>Данные!$B$13*Данные!$B$11</f>
-        <v>1292440</v>
+        <f>Данные!$B$13*Данные!$B$12</f>
+        <v>1750000</v>
       </c>
       <c r="F24" s="11">
-        <f>Данные!$B$13*Данные!$B$11*12</f>
-        <v>15509280</v>
+        <f>Данные!$B$13*Данные!$B$12*12</f>
+        <v>21000000</v>
       </c>
     </row>
     <row r="25">
@@ -1478,11 +1478,11 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="17">
         <f>F33/12</f>
-        <v>1675186.938</v>
+        <v>2132746.938</v>
       </c>
       <c r="F33" s="17">
         <f>F24+F25+F26+F27+F28+F29+F32</f>
-        <v>20102243.25</v>
+        <v>25592963.25</v>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -897,12 +897,14 @@
         <f>'Инкубаторий'!B5</f>
         <v>1514400</v>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="E8" s="49" t="n"/>
+      <c r="D8" s="10">
+        <f>E8/12</f>
+        <v>120000</v>
+      </c>
+      <c r="E8" s="11">
+        <f>'Инкубаторий'!C5</f>
+        <v>1440000</v>
+      </c>
       <c r="F8" s="10">
         <f>G8/12</f>
         <v>15350.45833</v>
@@ -981,11 +983,11 @@
       <c r="C10" s="49" t="n"/>
       <c r="D10" s="10">
         <f>E10/12</f>
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="E10" s="11">
         <f>'Склад ТМЦ'!C5</f>
-        <v>720000</v>
+        <v>480000</v>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
@@ -1059,11 +1061,11 @@
       </c>
       <c r="D12" s="17">
         <f>E12/12</f>
-        <v>3212500</v>
+        <v>3312500</v>
       </c>
       <c r="E12" s="17">
         <f>SUM(E6:E11)</f>
-        <v>38550000</v>
+        <v>39750000</v>
       </c>
       <c r="F12" s="17">
         <f>G12/12</f>
@@ -1134,15 +1136,15 @@
       </c>
       <c r="B17" s="10">
         <f>C17/12</f>
-        <v>1079753.062</v>
+        <v>1179753.062</v>
       </c>
       <c r="C17" s="11">
         <f>E12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
-        <v>12957036.75</v>
+        <v>14157036.75</v>
       </c>
       <c r="D17" s="51">
         <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
-        <v>1.506273409</v>
+        <v>1.553161297</v>
       </c>
     </row>
     <row r="18">
@@ -1555,11 +1557,11 @@
         <v>3515855</v>
       </c>
       <c r="C39" s="11">
-        <f>C12*(1-Данные!$B$63)</f>
+        <f>C12*(1-Данные!$B$67)</f>
         <v>42190260</v>
       </c>
       <c r="D39" s="53">
-        <f>Данные!$B$63</f>
+        <f>Данные!$B$67</f>
         <v>0.15</v>
       </c>
     </row>
@@ -1574,11 +1576,11 @@
         <v>2988476.75</v>
       </c>
       <c r="C40" s="11">
-        <f>C12*(1-Данные!$B$63)*(1-Данные!$B$64)</f>
+        <f>C12*(1-Данные!$B$67)*(1-Данные!$B$68)</f>
         <v>35861721</v>
       </c>
       <c r="D40" s="53">
-        <f>Данные!$B$64</f>
+        <f>Данные!$B$68</f>
         <v>0.15</v>
       </c>
     </row>
@@ -1593,11 +1595,11 @@
         <v>2510320.47</v>
       </c>
       <c r="C41" s="11">
-        <f>C12*(1-Данные!$B$63)*(1-Данные!$B$64)*(1-Данные!$B$65)</f>
+        <f>C12*(1-Данные!$B$67)*(1-Данные!$B$68)*(1-Данные!$B$69)</f>
         <v>30123845.64</v>
       </c>
       <c r="D41" s="53">
-        <f>Данные!$B$65</f>
+        <f>Данные!$B$69</f>
         <v>0.16</v>
       </c>
     </row>
@@ -1716,15 +1718,15 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>ЗПП</t>
+          <t>инкубаторий</t>
         </is>
       </c>
       <c r="C48" s="24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="30" t="inlineStr">
         <is>
-          <t>по графику на 2026 год, бригада из трёх человек</t>
+          <t>КП №26/75: ежемесячно 2 раза</t>
         </is>
       </c>
       <c r="E48" s="48" t="n"/>
@@ -1739,15 +1741,15 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>склад ТМЦ</t>
+          <t>ЗПП</t>
         </is>
       </c>
       <c r="C49" s="24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" s="30" t="inlineStr">
         <is>
-          <t>выезд по рекламации за два рабочих дня</t>
+          <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
       <c r="E49" s="48" t="n"/>
@@ -1757,30 +1759,54 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Штат УКПФ</t>
+          <t>Pest Hunters</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>все объекты</t>
+          <t>склад ТМЦ</t>
         </is>
       </c>
       <c r="C50" s="24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D50" s="30" t="inlineStr">
         <is>
-          <t>присутствие 5/2, реакция в тот же день</t>
+          <t>КП №26/75: ежемесячно 2 раза (по договору №921 был 1 обход)</t>
         </is>
       </c>
       <c r="E50" s="48" t="n"/>
       <c r="F50" s="48" t="n"/>
       <c r="G50" s="49" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Штат УКПФ</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>все объекты</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="30" t="inlineStr">
+        <is>
+          <t>присутствие 5/2, реакция в тот же день</t>
+        </is>
+      </c>
+      <c r="E51" s="48" t="n"/>
+      <c r="F51" s="48" t="n"/>
+      <c r="G51" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D51:G51"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D50:G50"/>
     <mergeCell ref="D11:E11"/>
@@ -1793,7 +1819,6 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D49:G49"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="D48:G48"/>
     <mergeCell ref="D47:G47"/>
     <mergeCell ref="A2:G2"/>
@@ -2291,7 +2316,7 @@
         <v>3172000</v>
       </c>
       <c r="C12" s="35">
-        <f>Данные!$B$60</f>
+        <f>Данные!$B$64</f>
         <v>9</v>
       </c>
       <c r="D12" s="11">
@@ -2310,7 +2335,7 @@
         <v>2074000</v>
       </c>
       <c r="C13" s="35">
-        <f>Данные!$B$61</f>
+        <f>Данные!$B$65</f>
         <v>3</v>
       </c>
       <c r="D13" s="11">
@@ -2529,7 +2554,7 @@
         <v>2806000</v>
       </c>
       <c r="C26" s="35">
-        <f>Данные!$B$60</f>
+        <f>Данные!$B$64</f>
         <v>9</v>
       </c>
       <c r="D26" s="10">
@@ -2548,7 +2573,7 @@
         <v>1830000</v>
       </c>
       <c r="C27" s="35">
-        <f>Данные!$B$61</f>
+        <f>Данные!$B$65</f>
         <v>3</v>
       </c>
       <c r="D27" s="10">
@@ -3020,7 +3045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3039,7 +3064,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>У Indigo появился в КП от 19.08.2026: 48 ед. оборудования. У Pest Hunters предложения нет.</t>
+          <t>Indigo — КП от 19.08.2026, 48 ед. оборудования, цена с НДС. Pest Hunters — КП №26/75, 2 обхода в месяц, цена без НДС; по их расчёту 52 приманочных контейнера и 60 живоловок.</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3098,7 @@
       </c>
       <c r="C5" s="33">
         <f>D10</f>
-        <v>0</v>
+        <v>1440000</v>
       </c>
       <c r="D5" s="33">
         <f>D11+D12+D13+D14+D15+D16</f>
@@ -3134,18 +3159,19 @@
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B10" s="35" t="n">
-        <v>0</v>
+          <t>Pest Hunters · КП №26/75, 2 обхода в месяц, без НДС</t>
+        </is>
+      </c>
+      <c r="B10" s="35">
+        <f>Данные!$B$59</f>
+        <v>120000</v>
       </c>
       <c r="C10" s="35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D10" s="11">
         <f>B10*C10</f>
-        <v>0</v>
+        <v>1440000</v>
       </c>
     </row>
     <row r="11">
@@ -3265,7 +3291,7 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>АЛЬТЕРНАТИВНЫЙ ВАРИАНТ INDIGO</t>
+          <t>АЛЬТЕРНАТИВНЫЕ ВАРИАНТЫ И ПРИВЕДЕНИЕ К НДС</t>
         </is>
       </c>
       <c r="B18" s="19" t="n"/>
@@ -3312,68 +3338,112 @@
         <v>1281600</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>Pest Hunters · та же цена, приведённая к НДС для сопоставимости с Indigo</t>
+        </is>
+      </c>
+      <c r="B21" s="35">
+        <f>Данные!$B$59*(1+Данные!$B$63)</f>
+        <v>139200</v>
+      </c>
+      <c r="C21" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" s="10">
+        <f>B21*C21</f>
+        <v>1670400</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B24" s="35">
+      <c r="B25" s="35">
         <f>Данные!$B$50</f>
         <v>100800</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C25" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="D24" s="10">
-        <f>B24*C24</f>
+      <c r="D25" s="10">
+        <f>B25*C25</f>
         <v>1209600</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>Pest Hunters · дезинсекция, КП №26/75, без НДС</t>
+        </is>
+      </c>
+      <c r="B26" s="35">
+        <f>Данные!$B$60</f>
+        <v>100000</v>
+      </c>
+      <c r="C26" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="10">
+        <f>B26*C26</f>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>Внимание: цены несопоставимы напрямую. У Indigo 126 200 ₸ уже с НДС, у Pest Hunters 120 000 ₸ без НДС. С НДС 16 % Pest Hunters даёт 139 200 ₸/мес (1 670 400 ₸/год) — это дороже Indigo. Сравнивать нужно строку «приведённая к НДС».</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A26:D26"/>
+  <mergeCells count="3">
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3665,7 +3735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3684,7 +3754,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>Договор №921 от 01.04.2026, действует с апреля по декабрь. Предложений от Indigo по этому объекту нет.</t>
+          <t>Pest Hunters — КП №26/75 на 2026–2027: дератизация и дезинсекция вынесены отдельными строками, 2 обхода в месяц, цены без НДС. Предложений от Indigo по этому объекту нет.</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3788,7 @@
       </c>
       <c r="C5" s="33">
         <f>D10</f>
-        <v>720000</v>
+        <v>480000</v>
       </c>
       <c r="D5" s="33">
         <f>D11</f>
@@ -3778,20 +3848,19 @@
     <row r="10">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>Pest Hunters · договор №921: дератизация и дезинсекция, выезд по рекламации за 2 рабочих дня</t>
+          <t>Pest Hunters · КП №26/75, только дератизация, 2 обхода в месяц</t>
         </is>
       </c>
       <c r="B10" s="35">
-        <f>Данные!$B$59</f>
-        <v>80000</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Данные!$B$62</f>
-        <v>9</v>
+        <f>Данные!$B$61</f>
+        <v>40000</v>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>12</v>
       </c>
       <c r="D10" s="11">
         <f>B10*C10</f>
-        <v>720000</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="11">
@@ -3812,16 +3881,126 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>С января по март договор не действует, поэтому в году девять оплачиваемых месяцев.</t>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЗИНСЕКЦИЯ — В СРАВНЕНИЕ НЕ ВХОДИТ</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Pest Hunters · дезинсекция, КП №26/75</t>
+        </is>
+      </c>
+      <c r="B15" s="35">
+        <f>Данные!$B$62</f>
+        <v>40000</v>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="10">
+        <f>B15*C15</f>
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>СПРАВОЧНО: ДЕЙСТВУЮЩИЙ ДОГОВОР №921</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Цена в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Месяцев</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>За год, ₸</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>Pest Hunters · договор №921 от 01.04.2026: дератизация и дезинсекция одной суммой, 1 обход в месяц, апрель — декабрь</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C19" s="35">
+        <f>Данные!$B$66</f>
+        <v>9</v>
+      </c>
+      <c r="D19" s="10">
+        <f>B19*C19</f>
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Раньше по складу в сравнение шли 80 000 ₸/мес из договора №921, но эта сумма включает и дезинсекцию. В КП №26/75 услуги разделены: дератизация 40 000 ₸/мес — только она и участвует в сравнении.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>КП №26/75 при той же общей сумме 80 000 ₸/мес даёт 2 обхода в месяц вместо одного по действующему договору.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:D13"/>
+  <mergeCells count="3">
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4869,7 +5048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6071,11 +6250,11 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · склад ТМЦ</t>
+          <t>Pest Hunters · Инкубаторий, дератизация</t>
         </is>
       </c>
       <c r="B59" s="44" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
@@ -6084,78 +6263,78 @@
       </c>
       <c r="H59" s="45" t="inlineStr">
         <is>
-          <t>договор №921 от 01.04.2026; дератизация + дезинсекция, 1 обход в месяц</t>
+          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, с. Акимовка</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
+          <t>Pest Hunters · Инкубаторий, дезинсекция</t>
         </is>
       </c>
       <c r="B60" s="44" t="n">
-        <v>9</v>
+        <v>100000</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>мес.</t>
+          <t>₸/мес</t>
         </is>
       </c>
       <c r="H60" s="45" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
+          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Месяцев низкого тарифа площадок (дек — фев)</t>
+          <t>Pest Hunters · склад ТМЦ, дератизация</t>
         </is>
       </c>
       <c r="B61" s="44" t="n">
-        <v>3</v>
+        <v>40000</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>мес.</t>
+          <t>₸/мес</t>
         </is>
       </c>
       <c r="H61" s="45" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
+          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, пос. К. Кайсенова</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>Месяцев действия договора по складу ТМЦ</t>
+          <t>Pest Hunters · склад ТМЦ, дезинсекция</t>
         </is>
       </c>
       <c r="B62" s="44" t="n">
-        <v>9</v>
+        <v>40000</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>мес.</t>
+          <t>₸/мес</t>
         </is>
       </c>
       <c r="H62" s="45" t="inlineStr">
         <is>
-          <t>апрель — декабрь 2026</t>
+          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>Скидка Indigo за всю территорию фабрики</t>
+          <t>Ставка НДС</t>
         </is>
       </c>
       <c r="B63" s="58" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
@@ -6164,45 +6343,125 @@
       </c>
       <c r="H63" s="45" t="inlineStr">
         <is>
-          <t>КП от 19.08.2026, условия предоставления скидок</t>
+          <t>по КП Pest Hunters №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>Скидка Indigo за 100 % предоплату за год</t>
-        </is>
-      </c>
-      <c r="B64" s="58" t="n">
-        <v>0.15</v>
+          <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
+        </is>
+      </c>
+      <c r="B64" s="44" t="n">
+        <v>9</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>доля</t>
+          <t>мес.</t>
         </is>
       </c>
       <c r="H64" s="45" t="inlineStr">
         <is>
-          <t>КП от 19.08.2026, дополнительно к предыдущей</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
+          <t>Месяцев низкого тарифа площадок (дек — фев)</t>
+        </is>
+      </c>
+      <c r="B65" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>мес.</t>
+        </is>
+      </c>
+      <c r="H65" s="45" t="inlineStr">
+        <is>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Месяцев действия договора по складу ТМЦ</t>
+        </is>
+      </c>
+      <c r="B66" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>мес.</t>
+        </is>
+      </c>
+      <c r="H66" s="45" t="inlineStr">
+        <is>
+          <t>апрель — декабрь 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Скидка Indigo за всю территорию фабрики</t>
+        </is>
+      </c>
+      <c r="B67" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>доля</t>
+        </is>
+      </c>
+      <c r="H67" s="45" t="inlineStr">
+        <is>
+          <t>КП от 19.08.2026, условия предоставления скидок</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>Скидка Indigo за 100 % предоплату за год</t>
+        </is>
+      </c>
+      <c r="B68" s="58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>доля</t>
+        </is>
+      </c>
+      <c r="H68" s="45" t="inlineStr">
+        <is>
+          <t>КП от 19.08.2026, дополнительно к предыдущей</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B65" s="58" t="n">
+      <c r="B69" s="58" t="n">
         <v>0.16</v>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H65" s="45" t="inlineStr">
+      <c r="H69" s="45" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -155,9 +155,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00C8C2AE"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -168,7 +166,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -253,6 +253,15 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -270,9 +279,6 @@
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -307,8 +313,8 @@
     </xf>
     <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -687,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -744,11 +750,11 @@
           <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 5 ДЕРАТИЗАТОРА</t>
         </is>
       </c>
-      <c r="J4" s="48" t="n"/>
-      <c r="K4" s="49" t="n"/>
+      <c r="J4" s="50" t="n"/>
+      <c r="K4" s="51" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="50" t="n"/>
+      <c r="A5" s="52" t="n"/>
       <c r="B5" s="6" t="inlineStr">
         <is>
           <t>месяц</t>
@@ -954,7 +960,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G9" s="49" t="n"/>
+      <c r="G9" s="51" t="n"/>
       <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Материалы, первый год, ₸</t>
@@ -980,7 +986,7 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="49" t="n"/>
+      <c r="C10" s="51" t="n"/>
       <c r="D10" s="10">
         <f>E10/12</f>
         <v>40000</v>
@@ -994,7 +1000,7 @@
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G10" s="49" t="n"/>
+      <c r="G10" s="51" t="n"/>
       <c r="I10" s="14" t="inlineStr">
         <is>
           <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
@@ -1020,13 +1026,13 @@
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C11" s="49" t="n"/>
+      <c r="C11" s="51" t="n"/>
       <c r="D11" s="13" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E11" s="49" t="n"/>
+      <c r="E11" s="51" t="n"/>
       <c r="F11" s="10">
         <f>G11/12</f>
         <v>24062.22917</v>
@@ -1080,361 +1086,303 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
+          <t>ПОДРЯДЧИКИ НА СОПОСТАВИМОЙ БАЗЕ — ЦЕНЫ PEST HUNTERS ПРИВЕДЕНЫ К НДС</t>
         </is>
       </c>
       <c r="B14" s="19" t="n"/>
       <c r="C14" s="19" t="n"/>
       <c r="D14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>во сколько раз</t>
+      <c r="E14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Indigo, ₸/год (с НДС)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Pest Hunters, ₸/год (с НДС 16 %)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Разница, ₸/год</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="B16" s="10">
+        <f>C6</f>
+        <v>1159200</v>
+      </c>
+      <c r="C16" s="10">
+        <f>E6*(1+Данные!$B$63)</f>
+        <v>1044000</v>
+      </c>
+      <c r="D16" s="20" t="str">
+        <f>IF(B16&lt;C16,"Indigo","Pest Hunters")</f>
+        <v>Pest Hunters</v>
+      </c>
+      <c r="E16" s="11">
+        <f>ABS(B16-C16)</f>
+        <v>115200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>C7</f>
+        <v>45447600</v>
+      </c>
+      <c r="C17" s="10">
+        <f>E7*(1+Данные!$B$63)</f>
+        <v>40333200</v>
+      </c>
+      <c r="D17" s="20" t="str">
+        <f>IF(B17&lt;C17,"Indigo","Pest Hunters")</f>
+        <v>Pest Hunters</v>
+      </c>
+      <c r="E17" s="11">
+        <f>ABS(B17-C17)</f>
+        <v>5114400</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Инкубаторий</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>C8</f>
+        <v>1514400</v>
+      </c>
+      <c r="C18" s="10">
+        <f>E8*(1+Данные!$B$63)</f>
+        <v>1670400</v>
+      </c>
+      <c r="D18" s="20" t="str">
+        <f>IF(B18&lt;C18,"Indigo","Pest Hunters")</f>
+        <v>Indigo</v>
+      </c>
+      <c r="E18" s="11">
+        <f>ABS(B18-C18)</f>
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>C9</f>
+        <v>1514400</v>
+      </c>
+      <c r="C19" s="10">
+        <f>E9</f>
+        <v>2160000</v>
+      </c>
+      <c r="D19" s="20" t="str">
+        <f>IF(B19&lt;C19,"Indigo","Pest Hunters")</f>
+        <v>Indigo</v>
+      </c>
+      <c r="E19" s="11">
+        <f>ABS(B19-C19)</f>
+        <v>645600</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C20" s="10">
+        <f>E10*(1+Данные!$B$63)</f>
+        <v>556800</v>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Цены Indigo из КП уже включают НДС, цены Pest Hunters указаны без НДС — здесь к ним добавлены 16 % (ставка из их же КП №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸). Без этого приведения сравнение некорректно: по инкубаторию Pest Hunters в «сырых» цифрах выглядит дешевле, а с НДС оказывается дороже. По ЗПП цена взята из договора №88, ставка НДС в нём не указана, поэтому она показана как есть и включает ещё и дезинсекцию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>во сколько раз</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
           <t>Indigo Solutions дороже штата</t>
         </is>
       </c>
-      <c r="B16" s="10">
-        <f>C16/12</f>
+      <c r="B25" s="10">
+        <f>C25/12</f>
         <v>2003553.062</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C25" s="11">
         <f>C12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
         <v>24042636.75</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D25" s="53">
         <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
         <v>1.93942372</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters дороже штата</t>
         </is>
       </c>
-      <c r="B17" s="10">
-        <f>C17/12</f>
+      <c r="B26" s="10">
+        <f>C26/12</f>
         <v>1179753.062</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C26" s="11">
         <f>E12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
         <v>14157036.75</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D26" s="53">
         <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
         <v>1.553161297</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Штат посчитан вместе с ФОТ (расходники + зарплата), КП подрядчиков — как есть.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
-      <c r="G20" s="19" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Цена за ед., ₸</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>в месяц, ₸</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>за год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B22" s="10">
+      <c r="B31" s="10">
         <f>Данные!$B$13</f>
         <v>5</v>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>чел.</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Оклад одного дератизатора</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>₸/мес</t>
-        </is>
-      </c>
-      <c r="D23" s="10">
-        <f>Данные!$B$12</f>
-        <v>350000</v>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Фонд оплаты труда</t>
-        </is>
-      </c>
-      <c r="B24" s="10">
-        <f>Данные!$B$13</f>
-        <v>5</v>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>чел.</t>
-        </is>
-      </c>
-      <c r="D24" s="10">
-        <f>Данные!$B$12</f>
-        <v>350000</v>
-      </c>
-      <c r="E24" s="10">
-        <f>Данные!$B$13*Данные!$B$12</f>
-        <v>1750000</v>
-      </c>
-      <c r="F24" s="11">
-        <f>Данные!$B$13*Данные!$B$12*12</f>
-        <v>21000000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
-        </is>
-      </c>
-      <c r="B25" s="10">
-        <f>Данные!$B$32+Данные!$C$32</f>
-        <v>1377</v>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D25" s="10">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="11">
-        <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
-        <v>2974320</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
-        </is>
-      </c>
-      <c r="B26" s="10">
-        <f>Данные!$D$32</f>
-        <v>343</v>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>шт/мес</t>
-        </is>
-      </c>
-      <c r="D26" s="10">
-        <f>Данные!$B$8</f>
-        <v>160</v>
-      </c>
-      <c r="E26" s="10">
-        <f>Данные!$D$32*Данные!$B$8</f>
-        <v>54880</v>
-      </c>
-      <c r="F26" s="11">
-        <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
-        <v>384160</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
-        </is>
-      </c>
-      <c r="B27" s="10">
-        <f>Данные!$D$32*2</f>
-        <v>686</v>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>шт/мес</t>
-        </is>
-      </c>
-      <c r="D27" s="10">
-        <f>Данные!$B$8</f>
-        <v>160</v>
-      </c>
-      <c r="E27" s="10">
-        <f>Данные!$D$32*2*Данные!$B$8</f>
-        <v>109760</v>
-      </c>
-      <c r="F27" s="11">
-        <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
-        <v>548800</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Зерноцид · 2-й контур, тёплый сезон</t>
-        </is>
-      </c>
-      <c r="B28" s="10">
-        <f>Данные!$G$32</f>
-        <v>16</v>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D28" s="10">
-        <f>Данные!$B$6</f>
-        <v>740</v>
-      </c>
-      <c r="E28" s="10">
-        <f>Данные!$G$32*Данные!$B$6</f>
-        <v>11840</v>
-      </c>
-      <c r="F28" s="11">
-        <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
-        <v>82880</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
-        </is>
-      </c>
-      <c r="B29" s="10">
-        <f>Данные!$F$32</f>
-        <v>20.3</v>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D29" s="10">
-        <f>Данные!$B$7</f>
-        <v>3642.5</v>
-      </c>
-      <c r="E29" s="10">
-        <f>Данные!$F$32*Данные!$B$7</f>
-        <v>73942.75</v>
-      </c>
-      <c r="F29" s="11">
-        <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
-        <v>517599.25</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
-        </is>
-      </c>
-      <c r="B30" s="10">
-        <f>Данные!$C$32</f>
-        <v>1198</v>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
-        </is>
-      </c>
-      <c r="B31" s="52">
-        <f>Данные!$F$32/Данные!$C$32</f>
-        <v>0.01694490818</v>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
         </is>
       </c>
       <c r="D31" s="5" t="n"/>
@@ -1444,383 +1392,606 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
+          <t>Оклад одного дератизатора</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>₸/мес</t>
+        </is>
+      </c>
+      <c r="D32" s="10">
+        <f>Данные!$B$12</f>
+        <v>350000</v>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Фонд оплаты труда</t>
+        </is>
+      </c>
+      <c r="B33" s="10">
+        <f>Данные!$B$13</f>
+        <v>5</v>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>чел.</t>
+        </is>
+      </c>
+      <c r="D33" s="10">
+        <f>Данные!$B$12</f>
+        <v>350000</v>
+      </c>
+      <c r="E33" s="10">
+        <f>Данные!$B$13*Данные!$B$12</f>
+        <v>1750000</v>
+      </c>
+      <c r="F33" s="11">
+        <f>Данные!$B$13*Данные!$B$12*12</f>
+        <v>21000000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
+        </is>
+      </c>
+      <c r="B34" s="10">
+        <f>Данные!$B$32+Данные!$C$32</f>
+        <v>1377</v>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D34" s="10">
+        <f>Данные!$B$9</f>
+        <v>2160</v>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="11">
+        <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
+        <v>2974320</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
+        </is>
+      </c>
+      <c r="B35" s="10">
+        <f>Данные!$D$32</f>
+        <v>343</v>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D35" s="10">
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E35" s="10">
+        <f>Данные!$D$32*Данные!$B$8</f>
+        <v>54880</v>
+      </c>
+      <c r="F35" s="11">
+        <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
+        <v>384160</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
+        </is>
+      </c>
+      <c r="B36" s="10">
+        <f>Данные!$D$32*2</f>
+        <v>686</v>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D36" s="10">
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E36" s="10">
+        <f>Данные!$D$32*2*Данные!$B$8</f>
+        <v>109760</v>
+      </c>
+      <c r="F36" s="11">
+        <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
+        <v>548800</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Зерноцид · 2-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B37" s="10">
+        <f>Данные!$G$32</f>
+        <v>16</v>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D37" s="10">
+        <f>Данные!$B$6</f>
+        <v>740</v>
+      </c>
+      <c r="E37" s="10">
+        <f>Данные!$G$32*Данные!$B$6</f>
+        <v>11840</v>
+      </c>
+      <c r="F37" s="11">
+        <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
+        <v>82880</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
+        </is>
+      </c>
+      <c r="B38" s="10">
+        <f>Данные!$F$32</f>
+        <v>20.3</v>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D38" s="10">
+        <f>Данные!$B$7</f>
+        <v>3642.5</v>
+      </c>
+      <c r="E38" s="10">
+        <f>Данные!$F$32*Данные!$B$7</f>
+        <v>73942.75</v>
+      </c>
+      <c r="F38" s="11">
+        <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
+        <v>517599.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
+        </is>
+      </c>
+      <c r="B39" s="10">
+        <f>Данные!$C$32</f>
+        <v>1198</v>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
+        </is>
+      </c>
+      <c r="B40" s="54">
+        <f>Данные!$F$32/Данные!$C$32</f>
+        <v>0.01694490818</v>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
           <t>Бутылки, 1-й контур · тёплый сезон</t>
         </is>
       </c>
-      <c r="B32" s="10">
+      <c r="B41" s="10">
         <f>Данные!$B$32</f>
         <v>179</v>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D32" s="10">
+      <c r="D41" s="10">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E41" s="10">
         <f>Данные!$B$32*Данные!$B$10</f>
         <v>12172</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F41" s="11">
         <f>Данные!$B$32*Данные!$B$10*Данные!$B$14</f>
         <v>85204</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="17">
-        <f>F33/12</f>
+      <c r="B42" s="29" t="n"/>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="29" t="n"/>
+      <c r="E42" s="17">
+        <f>F42/12</f>
         <v>2132746.938</v>
       </c>
-      <c r="F33" s="17">
-        <f>F24+F25+F26+F27+F28+F29+F32</f>
+      <c r="F42" s="17">
+        <f>F33+F34+F35+F36+F37+F38+F41</f>
         <v>25592963.25</v>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>Условие</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>Ставка</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Цена КП без скидок</t>
         </is>
       </c>
-      <c r="B38" s="10">
-        <f>C38/12</f>
+      <c r="B47" s="10">
+        <f>C47/12</f>
         <v>4136300</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C47" s="11">
         <f>C12</f>
         <v>49635600</v>
       </c>
-      <c r="D38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B39" s="10">
-        <f>C39/12</f>
+      <c r="B48" s="10">
+        <f>C48/12</f>
         <v>3515855</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C48" s="11">
         <f>C12*(1-Данные!$B$67)</f>
         <v>42190260</v>
       </c>
-      <c r="D39" s="53">
+      <c r="D48" s="55">
         <f>Данные!$B$67</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
-      <c r="B40" s="10">
-        <f>C40/12</f>
+      <c r="B49" s="10">
+        <f>C49/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C49" s="11">
         <f>C12*(1-Данные!$B$67)*(1-Данные!$B$68)</f>
         <v>35861721</v>
       </c>
-      <c r="D40" s="53">
+      <c r="D49" s="55">
         <f>Данные!$B$68</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
-      <c r="B41" s="10">
-        <f>C41/12</f>
+      <c r="B50" s="10">
+        <f>C50/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C50" s="11">
         <f>C12*(1-Данные!$B$67)*(1-Данные!$B$68)*(1-Данные!$B$69)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D41" s="53">
+      <c r="D50" s="55">
         <f>Данные!$B$69</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="B53" s="31" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C53" s="31" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D44" s="29" t="inlineStr">
+      <c r="D53" s="31" t="inlineStr">
         <is>
           <t>Что зафиксировано в документах</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D45" s="30" t="inlineStr">
+      <c r="D54" s="32" t="inlineStr">
         <is>
           <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
         </is>
       </c>
-      <c r="E45" s="48" t="n"/>
-      <c r="F45" s="48" t="n"/>
-      <c r="G45" s="49" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="E54" s="50" t="n"/>
+      <c r="F54" s="50" t="n"/>
+      <c r="G54" s="51" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="C46" s="24" t="n">
+      <c r="C55" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="30" t="inlineStr">
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>выезд по запросу</t>
         </is>
       </c>
-      <c r="E46" s="48" t="n"/>
-      <c r="F46" s="48" t="n"/>
-      <c r="G46" s="49" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="E55" s="50" t="n"/>
+      <c r="F55" s="50" t="n"/>
+      <c r="G55" s="51" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>бройлерные площадки</t>
         </is>
       </c>
-      <c r="C47" s="24" t="n">
+      <c r="C56" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="30" t="inlineStr">
+      <c r="D56" s="32" t="inlineStr">
         <is>
           <t>дополнительные визиты по вызову</t>
         </is>
       </c>
-      <c r="E47" s="48" t="n"/>
-      <c r="F47" s="48" t="n"/>
-      <c r="G47" s="49" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="E56" s="50" t="n"/>
+      <c r="F56" s="50" t="n"/>
+      <c r="G56" s="51" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>инкубаторий</t>
         </is>
       </c>
-      <c r="C48" s="24" t="n">
+      <c r="C57" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="30" t="inlineStr">
+      <c r="D57" s="32" t="inlineStr">
         <is>
           <t>КП №26/75: ежемесячно 2 раза</t>
         </is>
       </c>
-      <c r="E48" s="48" t="n"/>
-      <c r="F48" s="48" t="n"/>
-      <c r="G48" s="49" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="E57" s="50" t="n"/>
+      <c r="F57" s="50" t="n"/>
+      <c r="G57" s="51" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="C49" s="24" t="n">
+      <c r="C58" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D49" s="30" t="inlineStr">
+      <c r="D58" s="32" t="inlineStr">
         <is>
           <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
-      <c r="E49" s="48" t="n"/>
-      <c r="F49" s="48" t="n"/>
-      <c r="G49" s="49" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="E58" s="50" t="n"/>
+      <c r="F58" s="50" t="n"/>
+      <c r="G58" s="51" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>склад ТМЦ</t>
         </is>
       </c>
-      <c r="C50" s="24" t="n">
+      <c r="C59" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="30" t="inlineStr">
+      <c r="D59" s="32" t="inlineStr">
         <is>
           <t>КП №26/75: ежемесячно 2 раза (по договору №921 был 1 обход)</t>
         </is>
       </c>
-      <c r="E50" s="48" t="n"/>
-      <c r="F50" s="48" t="n"/>
-      <c r="G50" s="49" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="E59" s="50" t="n"/>
+      <c r="F59" s="50" t="n"/>
+      <c r="G59" s="51" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C51" s="24" t="n">
+      <c r="C60" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="D51" s="30" t="inlineStr">
+      <c r="D60" s="32" t="inlineStr">
         <is>
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
-      <c r="E51" s="48" t="n"/>
-      <c r="F51" s="48" t="n"/>
-      <c r="G51" s="49" t="n"/>
+      <c r="E60" s="50" t="n"/>
+      <c r="F60" s="50" t="n"/>
+      <c r="G60" s="51" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="D56:G56"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D58:G58"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="D59:G59"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D50:G50"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="D60:G60"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D45:G45"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D57:G57"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
@@ -1851,7 +2022,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/шт разовой закупки, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
         </is>
@@ -1859,37 +2030,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>1159200</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>900000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11+D12+D13+D14+D15+D16</f>
         <v>88137.5</v>
       </c>
@@ -1906,38 +2077,38 @@
       <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$36</f>
         <v>96600</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -1946,16 +2117,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · дератизация</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$52</f>
         <v>75000</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -1964,16 +2135,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>(Данные!$B$19+Данные!$C$19)*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="11">
@@ -1982,16 +2153,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$D$19*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2001,16 +2172,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$D$19*2*Данные!$B$8</f>
         <v>0</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -2020,16 +2191,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>Данные!$G$19*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2039,16 +2210,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$F$19*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2058,16 +2229,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="37">
         <f>Данные!$B$19*Данные!$B$10</f>
         <v>0</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2088,38 +2259,38 @@
       <c r="D18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция</t>
         </is>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="37">
         <f>Данные!$B$53</f>
         <v>70000</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="10">
@@ -2129,14 +2300,14 @@
     </row>
     <row r="21"/>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2175,7 +2346,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2183,37 +2354,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9+D10+D11</f>
         <v>45447600</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D12+D13</f>
         <v>34770000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D14+D15+D16+D17+D18+D19</f>
         <v>4031873.5</v>
       </c>
@@ -2230,38 +2401,38 @@
       <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП (БП-12, БП-13, БП-14) — полная замена, 180 ед.</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$37</f>
         <v>618400</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -2270,16 +2441,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки, площадки Д и Г — полная замена, 166 ед.</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$39</f>
         <v>569800</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -2288,16 +2459,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (рем. молод), В — полная замена, 793 ед.</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>Данные!$B$41</f>
         <v>2599100</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="11">
@@ -2306,16 +2477,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$B$54</f>
         <v>3172000</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$64</f>
         <v>9</v>
       </c>
@@ -2325,16 +2496,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование подрядчика</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$B$55</f>
         <v>2074000</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$65</f>
         <v>3</v>
       </c>
@@ -2344,16 +2515,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>(SUM(Данные!$B$22:$B$29)+SUM(Данные!$C$22:$C$29))*Данные!$B$9</f>
         <v>2715120</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="11">
@@ -2362,16 +2533,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>SUM(Данные!$D$22:$D$29)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2381,16 +2552,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="37">
         <f>SUM(Данные!$D$22:$D$29)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="37">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -2400,16 +2571,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="37">
         <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6</f>
         <v>11100</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2419,16 +2590,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="37">
         <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7</f>
         <v>61922.5</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2438,16 +2609,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="37">
         <f>SUM(Данные!$B$22:$B$29)*Данные!$B$10</f>
         <v>10948</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -2468,38 +2639,38 @@
       <c r="D21" s="19" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП — частичная замена</t>
         </is>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="37">
         <f>Данные!$B$38</f>
         <v>478400</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D23" s="10">
@@ -2508,16 +2679,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г — частичная замена</t>
         </is>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="37">
         <f>Данные!$B$40</f>
         <v>440700</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D24" s="10">
@@ -2526,16 +2697,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В — частичная замена</t>
         </is>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="37">
         <f>Данные!$B$42</f>
         <v>2010300</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="10">
@@ -2544,16 +2715,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, март — ноябрь, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="37">
         <f>Данные!$B$56</f>
         <v>2806000</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="37">
         <f>Данные!$B$64</f>
         <v>9</v>
       </c>
@@ -2563,16 +2734,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · 122 объекта, декабрь — февраль, оборудование заказчика</t>
         </is>
       </c>
-      <c r="B27" s="35">
+      <c r="B27" s="37">
         <f>Данные!$B$57</f>
         <v>1830000</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="37">
         <f>Данные!$B$65</f>
         <v>3</v>
       </c>
@@ -2593,38 +2764,38 @@
       <c r="D29" s="19" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Айыртау БП</t>
         </is>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="37">
         <f>Данные!$B$47</f>
         <v>720000</v>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="10">
@@ -2633,16 +2804,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Многоэтажки Д и Г</t>
         </is>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="37">
         <f>Данные!$B$48</f>
         <v>1080000</v>
       </c>
-      <c r="C32" s="35" t="n">
+      <c r="C32" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D32" s="10">
@@ -2651,16 +2822,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · Площадки А, Б, Е, Ж, В (РМ), В</t>
         </is>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="37">
         <f>Данные!$B$49</f>
         <v>3000000</v>
       </c>
-      <c r="C33" s="35" t="n">
+      <c r="C33" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D33" s="10">
@@ -2670,7 +2841,7 @@
     </row>
     <row r="34"/>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
@@ -2689,17 +2860,17 @@
       <c r="D38" s="19" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>Площадка</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="24" t="inlineStr">
         <is>
           <t>1-й контур</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>2-й контур</t>
         </is>
@@ -2711,11 +2882,11 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B40" s="36">
+      <c r="B40" s="38">
         <f>Данные!$B$22</f>
         <v>13</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="38">
         <f>Данные!$C$22</f>
         <v>147</v>
       </c>
@@ -2726,11 +2897,11 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B41" s="36">
+      <c r="B41" s="38">
         <f>Данные!$B$23</f>
         <v>17</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="38">
         <f>Данные!$C$23</f>
         <v>146</v>
       </c>
@@ -2741,11 +2912,11 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B42" s="36">
+      <c r="B42" s="38">
         <f>Данные!$B$24</f>
         <v>50</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="38">
         <f>Данные!$C$24</f>
         <v>239</v>
       </c>
@@ -2756,11 +2927,11 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B43" s="36">
+      <c r="B43" s="38">
         <f>Данные!$B$25</f>
         <v>17</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="38">
         <f>Данные!$C$25</f>
         <v>88</v>
       </c>
@@ -2771,11 +2942,11 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B44" s="36">
+      <c r="B44" s="38">
         <f>Данные!$B$26</f>
         <v>15</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="38">
         <f>Данные!$C$26</f>
         <v>69</v>
       </c>
@@ -2786,11 +2957,11 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B45" s="36">
+      <c r="B45" s="38">
         <f>Данные!$B$27</f>
         <v>13</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="38">
         <f>Данные!$C$27</f>
         <v>147</v>
       </c>
@@ -2801,11 +2972,11 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B46" s="36">
+      <c r="B46" s="38">
         <f>Данные!$B$28</f>
         <v>17</v>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="38">
         <f>Данные!$C$28</f>
         <v>73</v>
       </c>
@@ -2816,26 +2987,26 @@
           <t>Айыртау</t>
         </is>
       </c>
-      <c r="B47" s="36">
+      <c r="B47" s="38">
         <f>Данные!$B$29</f>
         <v>19</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="38">
         <f>Данные!$C$29</f>
         <v>187</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="37" t="inlineStr">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t>Итого по площадкам</t>
         </is>
       </c>
-      <c r="B48" s="38">
+      <c r="B48" s="40">
         <f>SUM(B40:B47)</f>
         <v>161</v>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="40">
         <f>SUM(C40:C47)</f>
         <v>1096</v>
       </c>
@@ -2852,7 +3023,7 @@
       <c r="D50" s="19" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
@@ -3014,8 +3185,8 @@
           <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
-      <c r="B59" s="26" t="n"/>
-      <c r="C59" s="26" t="n"/>
+      <c r="B59" s="29" t="n"/>
+      <c r="C59" s="29" t="n"/>
       <c r="D59" s="17">
         <f>SUM(D52:D58)</f>
         <v>4031873.5</v>
@@ -3023,7 +3194,7 @@
     </row>
     <row r="60"/>
     <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="27" t="inlineStr">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт, разовая закупка), но количество точек по контурам разное — см. таблицу выше.</t>
         </is>
@@ -3062,7 +3233,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Indigo — КП от 19.08.2026, 48 ед. оборудования, цена с НДС. Pest Hunters — КП №26/75, 2 обхода в месяц, цена без НДС; по их расчёту 52 приманочных контейнера и 60 живоловок.</t>
         </is>
@@ -3070,37 +3241,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>1440000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11+D12+D13+D14+D15+D16</f>
         <v>184205.5</v>
       </c>
@@ -3117,38 +3288,38 @@
       <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования, 48 ед.</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$43</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -3157,16 +3328,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · КП №26/75, 2 обхода в месяц, без НДС</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$59</f>
         <v>120000</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -3175,16 +3346,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>(Данные!$B$20+Данные!$C$20)*Данные!$B$9</f>
         <v>112320</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="11">
@@ -3193,16 +3364,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$D$20*Данные!$B$8</f>
         <v>1920</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3212,16 +3383,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$D$20*2*Данные!$B$8</f>
         <v>3840</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -3231,16 +3402,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>Данные!$G$20*Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3250,16 +3421,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$F$20*Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3269,16 +3440,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="37">
         <f>Данные!$B$20*Данные!$B$10</f>
         <v>1224</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -3299,38 +3470,38 @@
       <c r="D18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="37">
         <f>Данные!$B$44</f>
         <v>106800</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="10">
@@ -3339,16 +3510,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · та же цена, приведённая к НДС для сопоставимости с Indigo</t>
         </is>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="37">
         <f>Данные!$B$59*(1+Данные!$B$63)</f>
         <v>139200</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D21" s="10">
@@ -3368,38 +3539,38 @@
       <c r="D23" s="19" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="37">
         <f>Данные!$B$50</f>
         <v>100800</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="10">
@@ -3408,16 +3579,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция, КП №26/75, без НДС</t>
         </is>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="37">
         <f>Данные!$B$60</f>
         <v>100000</v>
       </c>
-      <c r="C26" s="35" t="n">
+      <c r="C26" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D26" s="10">
@@ -3427,14 +3598,14 @@
     </row>
     <row r="27"/>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>Внимание: цены несопоставимы напрямую. У Indigo 126 200 ₸ уже с НДС, у Pest Hunters 120 000 ₸ без НДС. С НДС 16 % Pest Hunters даёт 139 200 ₸/мес (1 670 400 ₸/год) — это дороже Indigo. Сравнивать нужно строку «приведённая к НДС».</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3473,7 +3644,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3481,37 +3652,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>1514400</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>2160000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3528,38 +3699,38 @@
       <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · полная замена оборудования</t>
         </is>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>Данные!$B$45</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D9" s="11">
@@ -3568,16 +3739,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №88 от 01.01.2026: дератизация и дезинсекция вместе</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$58</f>
         <v>180000</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -3586,15 +3757,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по ЗПП не заданы</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="11">
@@ -3614,38 +3785,38 @@
       <c r="D13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · частичная замена оборудования</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$B$46</f>
         <v>106800</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="10">
@@ -3665,38 +3836,38 @@
       <c r="D17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions · дезинсекция</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="37">
         <f>Данные!$B$51</f>
         <v>160800</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="10">
@@ -3706,14 +3877,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3752,7 +3923,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Pest Hunters — КП №26/75 на 2026–2027: дератизация и дезинсекция вынесены отдельными строками, 2 обхода в месяц, цены без НДС. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -3760,37 +3931,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>480000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11</f>
         <v>0</v>
       </c>
@@ -3807,37 +3978,37 @@
       <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="11">
@@ -3846,16 +4017,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · КП №26/75, только дератизация, 2 обхода в месяц</t>
         </is>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="37">
         <f>Данные!$B$61</f>
         <v>40000</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="11">
@@ -3864,15 +4035,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · нормы расхода по складу не заданы</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="11">
@@ -3892,38 +4063,38 @@
       <c r="D13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · дезинсекция, КП №26/75</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$B$62</f>
         <v>40000</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="37" t="n">
         <v>12</v>
       </c>
       <c r="D15" s="10">
@@ -3943,37 +4114,37 @@
       <c r="D17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters · договор №921 от 01.04.2026: дератизация и дезинсекция одной суммой, 1 обход в месяц, апрель — декабрь</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="37" t="n">
         <v>80000</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="37">
         <f>Данные!$B$66</f>
         <v>9</v>
       </c>
@@ -3984,14 +4155,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Раньше по складу в сравнение шли 80 000 ₸/мес из договора №921, но эта сумма включает и дезинсекцию. В КП №26/75 услуги разделены: дератизация 40 000 ₸/мес — только она и участвует в сравнении.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>КП №26/75 при той же общей сумме 80 000 ₸/мес даёт 2 обхода в месяц вместо одного по действующему договору.</t>
         </is>
@@ -4030,7 +4201,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -4038,37 +4209,37 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>ЗА ГОД, ₸</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>D9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="35">
         <f>D10</f>
         <v>0</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="35">
         <f>D11+D12+D13+D14+D15+D16</f>
         <v>288746.75</v>
       </c>
@@ -4085,37 +4256,37 @@
       <c r="D7" s="19" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Цена в месяц, ₸</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Месяцев</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>За год, ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="11">
@@ -4124,15 +4295,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="37" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="11">
@@ -4141,16 +4312,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>(Данные!$B$21+Данные!$C$21)*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="11">
@@ -4159,16 +4330,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="37">
         <f>Данные!$D$21*Данные!$B$8</f>
         <v>10080</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4178,16 +4349,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>Данные!$D$21*2*Данные!$B$8</f>
         <v>20160</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
@@ -4197,16 +4368,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="37">
         <f>Данные!$G$21*Данные!$B$6</f>
         <v>0</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4216,16 +4387,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <f>Данные!$F$21*Данные!$B$7</f>
         <v>4735.25</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4235,16 +4406,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Штат УКПФ · Бутылки, 1-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="37">
         <f>Данные!$B$21*Данные!$B$10</f>
         <v>0</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="37">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
@@ -4255,14 +4426,14 @@
     </row>
     <row r="17"/>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -4329,17 +4500,17 @@
       <c r="E4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Показатель, ₸</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Оклад 258 488 ₸</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>Оклад 350 000 ₸</t>
         </is>
@@ -4391,7 +4562,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Зарплата за год</t>
         </is>
@@ -4498,7 +4669,7 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B13" s="54">
+      <c r="B13" s="56">
         <f>Данные!$B$19+Данные!$C$19</f>
         <v>29</v>
       </c>
@@ -4506,11 +4677,11 @@
         <f>B13*Данные!$B$9</f>
         <v>62640</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="56">
         <f>Данные!$D$19</f>
         <v>0</v>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="56">
         <f>Данные!$D$19*2</f>
         <v>0</v>
       </c>
@@ -4518,7 +4689,7 @@
         <f>D13*Данные!$B$8*Данные!$B$14+E13*Данные!$B$8*Данные!$B$15</f>
         <v>0</v>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="57">
         <f>Данные!$G$19</f>
         <v>0</v>
       </c>
@@ -4526,7 +4697,7 @@
         <f>G13*Данные!$B$6*Данные!$B$14</f>
         <v>0</v>
       </c>
-      <c r="I13" s="55">
+      <c r="I13" s="57">
         <f>Данные!$F$19</f>
         <v>1</v>
       </c>
@@ -4534,7 +4705,7 @@
         <f>I13*Данные!$B$7*Данные!$B$14</f>
         <v>25497.5</v>
       </c>
-      <c r="K13" s="54">
+      <c r="K13" s="56">
         <f>Данные!$B$19</f>
         <v>0</v>
       </c>
@@ -4553,7 +4724,7 @@
           <t>Бройлерные площадки · 8 шт</t>
         </is>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="56">
         <f>SUM(Данные!$B$22:$B$29)+SUM(Данные!$C$22:$C$29)</f>
         <v>1257</v>
       </c>
@@ -4561,11 +4732,11 @@
         <f>B14*Данные!$B$9</f>
         <v>2715120</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="56">
         <f>SUM(Данные!$D$22:$D$29)</f>
         <v>268</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="56">
         <f>SUM(Данные!$D$22:$D$29)*2</f>
         <v>536</v>
       </c>
@@ -4573,7 +4744,7 @@
         <f>D14*Данные!$B$8*Данные!$B$14+E14*Данные!$B$8*Данные!$B$15</f>
         <v>728960</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="57">
         <f>SUM(Данные!$G$22:$G$29)</f>
         <v>15</v>
       </c>
@@ -4581,7 +4752,7 @@
         <f>G14*Данные!$B$6*Данные!$B$14</f>
         <v>77700</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="57">
         <f>SUM(Данные!$F$22:$F$29)</f>
         <v>17</v>
       </c>
@@ -4589,7 +4760,7 @@
         <f>I14*Данные!$B$7*Данные!$B$14</f>
         <v>433457.5</v>
       </c>
-      <c r="K14" s="54">
+      <c r="K14" s="56">
         <f>SUM(Данные!$B$22:$B$29)</f>
         <v>161</v>
       </c>
@@ -4608,7 +4779,7 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B15" s="54">
+      <c r="B15" s="56">
         <f>Данные!$B$20+Данные!$C$20</f>
         <v>52</v>
       </c>
@@ -4616,11 +4787,11 @@
         <f>B15*Данные!$B$9</f>
         <v>112320</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="56">
         <f>Данные!$D$20</f>
         <v>12</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="56">
         <f>Данные!$D$20*2</f>
         <v>24</v>
       </c>
@@ -4628,7 +4799,7 @@
         <f>D15*Данные!$B$8*Данные!$B$14+E15*Данные!$B$8*Данные!$B$15</f>
         <v>32640</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="57">
         <f>Данные!$G$20</f>
         <v>1</v>
       </c>
@@ -4636,7 +4807,7 @@
         <f>G15*Данные!$B$6*Данные!$B$14</f>
         <v>5180</v>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="57">
         <f>Данные!$F$20</f>
         <v>1</v>
       </c>
@@ -4644,7 +4815,7 @@
         <f>I15*Данные!$B$7*Данные!$B$14</f>
         <v>25497.5</v>
       </c>
-      <c r="K15" s="54">
+      <c r="K15" s="56">
         <f>Данные!$B$20</f>
         <v>18</v>
       </c>
@@ -4663,7 +4834,7 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="56">
         <f>Данные!$B$21+Данные!$C$21</f>
         <v>39</v>
       </c>
@@ -4671,11 +4842,11 @@
         <f>B16*Данные!$B$9</f>
         <v>84240</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="56">
         <f>Данные!$D$21</f>
         <v>63</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="56">
         <f>Данные!$D$21*2</f>
         <v>126</v>
       </c>
@@ -4683,7 +4854,7 @@
         <f>D16*Данные!$B$8*Данные!$B$14+E16*Данные!$B$8*Данные!$B$15</f>
         <v>171360</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="57">
         <f>Данные!$G$21</f>
         <v>0</v>
       </c>
@@ -4691,7 +4862,7 @@
         <f>G16*Данные!$B$6*Данные!$B$14</f>
         <v>0</v>
       </c>
-      <c r="I16" s="55">
+      <c r="I16" s="57">
         <f>Данные!$F$21</f>
         <v>1.3</v>
       </c>
@@ -4699,7 +4870,7 @@
         <f>I16*Данные!$B$7*Данные!$B$14</f>
         <v>33146.75</v>
       </c>
-      <c r="K16" s="54">
+      <c r="K16" s="56">
         <f>Данные!$B$21</f>
         <v>0</v>
       </c>
@@ -4713,44 +4884,44 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>МАТЕРИАЛЫ, ПЕРВЫЙ ГОД ИТОГО (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="42">
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="44">
         <f>SUM(C13:C16)</f>
         <v>2974320</v>
       </c>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="42">
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="44">
         <f>SUM(F13:F16)</f>
         <v>932960</v>
       </c>
-      <c r="G17" s="56">
+      <c r="G17" s="58">
         <f>SUM(G13:G16)</f>
         <v>16</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="44">
         <f>SUM(H13:H16)</f>
         <v>82880</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="58">
         <f>SUM(I13:I16)</f>
         <v>20.3</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="44">
         <f>SUM(J13:J16)</f>
         <v>517599.25</v>
       </c>
-      <c r="K17" s="26" t="n"/>
-      <c r="L17" s="42">
+      <c r="K17" s="29" t="n"/>
+      <c r="L17" s="44">
         <f>SUM(L13:L16)</f>
         <v>85204</v>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="44">
         <f>SUM(M13:M16)</f>
         <v>4592963.25</v>
       </c>
@@ -5027,7 +5198,7 @@
     </row>
     <row r="30"/>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -5091,26 +5262,26 @@
       <c r="H4" s="19" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr"/>
-      <c r="E5" s="29" t="inlineStr"/>
-      <c r="F5" s="29" t="inlineStr"/>
-      <c r="G5" s="29" t="inlineStr"/>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="D5" s="31" t="inlineStr"/>
+      <c r="E5" s="31" t="inlineStr"/>
+      <c r="F5" s="31" t="inlineStr"/>
+      <c r="G5" s="31" t="inlineStr"/>
+      <c r="H5" s="31" t="inlineStr">
         <is>
           <t>Источник / примечание</t>
         </is>
@@ -5122,7 +5293,7 @@
           <t>Зерноцид</t>
         </is>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="46" t="n">
         <v>740</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -5130,7 +5301,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H6" s="45" t="inlineStr">
+      <c r="H6" s="47" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ</t>
         </is>
@@ -5142,7 +5313,7 @@
           <t>Pest Killer, брикеты</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="46" t="n">
         <v>3642.5</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -5150,7 +5321,7 @@
           <t>₸/кг</t>
         </is>
       </c>
-      <c r="H7" s="45" t="inlineStr">
+      <c r="H7" s="47" t="inlineStr">
         <is>
           <t>перенесено из прежнего расчёта по ККЗ; в исходных нормах цены не было</t>
         </is>
@@ -5162,7 +5333,7 @@
           <t>Клеевая станция 3-го контура</t>
         </is>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="46" t="n">
         <v>160</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -5170,7 +5341,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H8" s="45" t="inlineStr">
+      <c r="H8" s="47" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ, расходуется ежемесячно</t>
         </is>
@@ -5182,7 +5353,7 @@
           <t>Приманочная станция 1–2 контура</t>
         </is>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="46" t="n">
         <v>2160</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -5190,7 +5361,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H9" s="45" t="inlineStr">
+      <c r="H9" s="47" t="inlineStr">
         <is>
           <t>разовая закупка оборудования; цена из прежнего расчёта по ККЗ</t>
         </is>
@@ -5202,7 +5373,7 @@
           <t>Бутылка</t>
         </is>
       </c>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="46" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -5210,7 +5381,7 @@
           <t>₸/шт</t>
         </is>
       </c>
-      <c r="H10" s="45" t="inlineStr">
+      <c r="H10" s="47" t="inlineStr">
         <is>
           <t>внутренние данные УКПФ; расход = число точек 1-го контура, тёплый сезон</t>
         </is>
@@ -5222,7 +5393,7 @@
           <t>Оклад дератизатора · вариант 1</t>
         </is>
       </c>
-      <c r="B11" s="44" t="n">
+      <c r="B11" s="46" t="n">
         <v>258488</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -5230,7 +5401,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H11" s="45" t="inlineStr">
+      <c r="H11" s="47" t="inlineStr">
         <is>
           <t>действующий оклад</t>
         </is>
@@ -5242,7 +5413,7 @@
           <t>Оклад дератизатора · вариант 2</t>
         </is>
       </c>
-      <c r="B12" s="44" t="n">
+      <c r="B12" s="46" t="n">
         <v>350000</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5250,7 +5421,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H12" s="45" t="inlineStr">
+      <c r="H12" s="47" t="inlineStr">
         <is>
           <t>альтернативный уровень для сравнения</t>
         </is>
@@ -5262,7 +5433,7 @@
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B13" s="44" t="n">
+      <c r="B13" s="46" t="n">
         <v>5</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -5270,7 +5441,7 @@
           <t>чел.</t>
         </is>
       </c>
-      <c r="H13" s="45" t="inlineStr">
+      <c r="H13" s="47" t="inlineStr">
         <is>
           <t>измените — пересчитаются все листы</t>
         </is>
@@ -5282,7 +5453,7 @@
           <t>Тёплых месяцев (апрель — октябрь)</t>
         </is>
       </c>
-      <c r="B14" s="44" t="n">
+      <c r="B14" s="46" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5290,7 +5461,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H14" s="45" t="inlineStr">
+      <c r="H14" s="47" t="inlineStr">
         <is>
           <t>заряжаются все три контура</t>
         </is>
@@ -5302,7 +5473,7 @@
           <t>Зимних месяцев (ноябрь — март)</t>
         </is>
       </c>
-      <c r="B15" s="44" t="n">
+      <c r="B15" s="46" t="n">
         <v>5</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5310,7 +5481,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H15" s="45" t="inlineStr">
+      <c r="H15" s="47" t="inlineStr">
         <is>
           <t>1-й и 2-й контуры не заряжаются, 3-й обслуживается вдвое</t>
         </is>
@@ -5379,26 +5550,26 @@
           <t>ККЗ · кормоцех</t>
         </is>
       </c>
-      <c r="B19" s="44" t="n">
+      <c r="B19" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="44" t="n">
+      <c r="C19" s="46" t="n">
         <v>29</v>
       </c>
-      <c r="D19" s="44" t="n">
+      <c r="D19" s="46" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(B19:D19)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="57" t="n">
+      <c r="F19" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="57" t="n">
+      <c r="G19" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="45" t="inlineStr">
+      <c r="H19" s="47" t="inlineStr">
         <is>
           <t>29 приманочных станций 2-го контура</t>
         </is>
@@ -5410,26 +5581,26 @@
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B20" s="44" t="n">
+      <c r="B20" s="46" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="44" t="n">
+      <c r="C20" s="46" t="n">
         <v>34</v>
       </c>
-      <c r="D20" s="44" t="n">
+      <c r="D20" s="46" t="n">
         <v>12</v>
       </c>
       <c r="E20" s="10">
         <f>SUM(B20:D20)</f>
         <v>18</v>
       </c>
-      <c r="F20" s="57" t="n">
+      <c r="F20" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="57" t="n">
+      <c r="G20" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="45" t="inlineStr"/>
+      <c r="H20" s="47" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -5437,26 +5608,26 @@
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B21" s="44" t="n">
+      <c r="B21" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="44" t="n">
+      <c r="C21" s="46" t="n">
         <v>39</v>
       </c>
-      <c r="D21" s="44" t="n">
+      <c r="D21" s="46" t="n">
         <v>63</v>
       </c>
       <c r="E21" s="10">
         <f>SUM(B21:D21)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="57" t="n">
+      <c r="F21" s="59" t="n">
         <v>1.3</v>
       </c>
-      <c r="G21" s="57" t="n">
+      <c r="G21" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="45" t="inlineStr">
+      <c r="H21" s="47" t="inlineStr">
         <is>
           <t>1,3 кг — приблизительная оценка, требует подтверждения</t>
         </is>
@@ -5468,26 +5639,26 @@
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B22" s="44" t="n">
+      <c r="B22" s="46" t="n">
         <v>13</v>
       </c>
-      <c r="C22" s="44" t="n">
+      <c r="C22" s="46" t="n">
         <v>147</v>
       </c>
-      <c r="D22" s="44" t="n">
+      <c r="D22" s="46" t="n">
         <v>20</v>
       </c>
       <c r="E22" s="10">
         <f>SUM(B22:D22)</f>
         <v>13</v>
       </c>
-      <c r="F22" s="57" t="n">
+      <c r="F22" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="57" t="n">
+      <c r="G22" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="45" t="inlineStr"/>
+      <c r="H22" s="47" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -5495,26 +5666,26 @@
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B23" s="44" t="n">
+      <c r="B23" s="46" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="46" t="n">
         <v>146</v>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D23" s="46" t="n">
         <v>20</v>
       </c>
       <c r="E23" s="10">
         <f>SUM(B23:D23)</f>
         <v>17</v>
       </c>
-      <c r="F23" s="57" t="n">
+      <c r="F23" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="57" t="n">
+      <c r="G23" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="45" t="inlineStr"/>
+      <c r="H23" s="47" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -5522,26 +5693,26 @@
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B24" s="44" t="n">
+      <c r="B24" s="46" t="n">
         <v>50</v>
       </c>
-      <c r="C24" s="44" t="n">
+      <c r="C24" s="46" t="n">
         <v>239</v>
       </c>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="46" t="n">
         <v>30</v>
       </c>
       <c r="E24" s="10">
         <f>SUM(B24:D24)</f>
         <v>50</v>
       </c>
-      <c r="F24" s="57" t="n">
+      <c r="F24" s="59" t="n">
         <v>3.5</v>
       </c>
-      <c r="G24" s="57" t="n">
+      <c r="G24" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="45" t="inlineStr"/>
+      <c r="H24" s="47" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -5549,26 +5720,26 @@
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B25" s="44" t="n">
+      <c r="B25" s="46" t="n">
         <v>17</v>
       </c>
-      <c r="C25" s="44" t="n">
+      <c r="C25" s="46" t="n">
         <v>88</v>
       </c>
-      <c r="D25" s="44" t="n">
+      <c r="D25" s="46" t="n">
         <v>80</v>
       </c>
       <c r="E25" s="10">
         <f>SUM(B25:D25)</f>
         <v>17</v>
       </c>
-      <c r="F25" s="57" t="n">
+      <c r="F25" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="57" t="n">
+      <c r="G25" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="45" t="inlineStr"/>
+      <c r="H25" s="47" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -5576,26 +5747,26 @@
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B26" s="44" t="n">
+      <c r="B26" s="46" t="n">
         <v>15</v>
       </c>
-      <c r="C26" s="44" t="n">
+      <c r="C26" s="46" t="n">
         <v>69</v>
       </c>
-      <c r="D26" s="44" t="n">
+      <c r="D26" s="46" t="n">
         <v>64</v>
       </c>
       <c r="E26" s="10">
         <f>SUM(B26:D26)</f>
         <v>15</v>
       </c>
-      <c r="F26" s="57" t="n">
+      <c r="F26" s="59" t="n">
         <v>1.5</v>
       </c>
-      <c r="G26" s="57" t="n">
+      <c r="G26" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="45" t="inlineStr"/>
+      <c r="H26" s="47" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -5603,26 +5774,26 @@
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B27" s="44" t="n">
+      <c r="B27" s="46" t="n">
         <v>13</v>
       </c>
-      <c r="C27" s="44" t="n">
+      <c r="C27" s="46" t="n">
         <v>147</v>
       </c>
-      <c r="D27" s="44" t="n">
+      <c r="D27" s="46" t="n">
         <v>20</v>
       </c>
       <c r="E27" s="10">
         <f>SUM(B27:D27)</f>
         <v>13</v>
       </c>
-      <c r="F27" s="57" t="n">
+      <c r="F27" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="57" t="n">
+      <c r="G27" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="45" t="inlineStr"/>
+      <c r="H27" s="47" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -5630,26 +5801,26 @@
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B28" s="44" t="n">
+      <c r="B28" s="46" t="n">
         <v>17</v>
       </c>
-      <c r="C28" s="44" t="n">
+      <c r="C28" s="46" t="n">
         <v>73</v>
       </c>
-      <c r="D28" s="44" t="n">
+      <c r="D28" s="46" t="n">
         <v>10</v>
       </c>
       <c r="E28" s="10">
         <f>SUM(B28:D28)</f>
         <v>17</v>
       </c>
-      <c r="F28" s="57" t="n">
+      <c r="F28" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="57" t="n">
+      <c r="G28" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="45" t="inlineStr"/>
+      <c r="H28" s="47" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -5657,26 +5828,26 @@
           <t>Айыртау (БП)</t>
         </is>
       </c>
-      <c r="B29" s="44" t="n">
+      <c r="B29" s="46" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="44" t="n">
+      <c r="C29" s="46" t="n">
         <v>187</v>
       </c>
-      <c r="D29" s="44" t="n">
+      <c r="D29" s="46" t="n">
         <v>24</v>
       </c>
       <c r="E29" s="10">
         <f>SUM(B29:D29)</f>
         <v>19</v>
       </c>
-      <c r="F29" s="57" t="n">
+      <c r="F29" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="57" t="n">
+      <c r="G29" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="45" t="inlineStr"/>
+      <c r="H29" s="47" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -5688,9 +5859,9 @@
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="n"/>
       <c r="E30" s="10" t="n"/>
-      <c r="F30" s="55" t="n"/>
-      <c r="G30" s="55" t="n"/>
-      <c r="H30" s="45" t="inlineStr">
+      <c r="F30" s="57" t="n"/>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="47" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
@@ -5706,45 +5877,45 @@
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
       <c r="E31" s="10" t="n"/>
-      <c r="F31" s="55" t="n"/>
-      <c r="G31" s="55" t="n"/>
-      <c r="H31" s="45" t="inlineStr">
+      <c r="F31" s="57" t="n"/>
+      <c r="G31" s="57" t="n"/>
+      <c r="H31" s="47" t="inlineStr">
         <is>
           <t>нормы расхода не заданы</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>ИТОГО ПО ФАБРИКЕ</t>
         </is>
       </c>
-      <c r="B32" s="42">
+      <c r="B32" s="44">
         <f>SUM(B19:B31)</f>
         <v>179</v>
       </c>
-      <c r="C32" s="42">
+      <c r="C32" s="44">
         <f>SUM(C19:C31)</f>
         <v>1198</v>
       </c>
-      <c r="D32" s="42">
+      <c r="D32" s="44">
         <f>SUM(D19:D31)</f>
         <v>343</v>
       </c>
-      <c r="E32" s="42">
+      <c r="E32" s="44">
         <f>SUM(E19:E31)</f>
         <v>179</v>
       </c>
-      <c r="F32" s="56">
+      <c r="F32" s="58">
         <f>SUM(F19:F31)</f>
         <v>20.3</v>
       </c>
-      <c r="G32" s="56">
+      <c r="G32" s="58">
         <f>SUM(G19:G31)</f>
         <v>16</v>
       </c>
-      <c r="H32" s="26" t="n"/>
+      <c r="H32" s="29" t="n"/>
     </row>
     <row r="33"/>
     <row r="34">
@@ -5762,26 +5933,26 @@
       <c r="H34" s="19" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr"/>
-      <c r="E35" s="29" t="inlineStr"/>
-      <c r="F35" s="29" t="inlineStr"/>
-      <c r="G35" s="29" t="inlineStr"/>
-      <c r="H35" s="29" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr"/>
+      <c r="E35" s="31" t="inlineStr"/>
+      <c r="F35" s="31" t="inlineStr"/>
+      <c r="G35" s="31" t="inlineStr"/>
+      <c r="H35" s="31" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
@@ -5793,7 +5964,7 @@
           <t>Indigo · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B36" s="44" t="n">
+      <c r="B36" s="46" t="n">
         <v>96600</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -5801,7 +5972,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H36" s="45" t="inlineStr">
+      <c r="H36" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); барьер вокруг периметра кормоцеха и грязный барьер</t>
         </is>
@@ -5813,7 +5984,7 @@
           <t>Indigo · Айыртау БП, полная замена</t>
         </is>
       </c>
-      <c r="B37" s="44" t="n">
+      <c r="B37" s="46" t="n">
         <v>618400</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -5821,7 +5992,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H37" s="45" t="inlineStr">
+      <c r="H37" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 180 ед. оборудования</t>
         </is>
@@ -5833,7 +6004,7 @@
           <t>Indigo · Айыртау БП, частичная замена</t>
         </is>
       </c>
-      <c r="B38" s="44" t="n">
+      <c r="B38" s="46" t="n">
         <v>478400</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -5841,7 +6012,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H38" s="45" t="inlineStr">
+      <c r="H38" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5853,7 +6024,7 @@
           <t>Indigo · Многоэтажки Д и Г, полная замена</t>
         </is>
       </c>
-      <c r="B39" s="44" t="n">
+      <c r="B39" s="46" t="n">
         <v>569800</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -5861,7 +6032,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H39" s="45" t="inlineStr">
+      <c r="H39" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 166 ед. оборудования</t>
         </is>
@@ -5873,7 +6044,7 @@
           <t>Indigo · Многоэтажки Д и Г, частичная замена</t>
         </is>
       </c>
-      <c r="B40" s="44" t="n">
+      <c r="B40" s="46" t="n">
         <v>440700</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -5881,7 +6052,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H40" s="45" t="inlineStr">
+      <c r="H40" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5893,7 +6064,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), полная</t>
         </is>
       </c>
-      <c r="B41" s="44" t="n">
+      <c r="B41" s="46" t="n">
         <v>2599100</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -5901,7 +6072,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H41" s="45" t="inlineStr">
+      <c r="H41" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 793 ед. оборудования</t>
         </is>
@@ -5913,7 +6084,7 @@
           <t>Indigo · Площадки А,Б,Е,Ж,В,В(РМ), частичная</t>
         </is>
       </c>
-      <c r="B42" s="44" t="n">
+      <c r="B42" s="46" t="n">
         <v>2010300</v>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -5921,7 +6092,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H42" s="45" t="inlineStr">
+      <c r="H42" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5933,7 +6104,7 @@
           <t>Indigo · Инкубаторий, полная замена</t>
         </is>
       </c>
-      <c r="B43" s="44" t="n">
+      <c r="B43" s="46" t="n">
         <v>126200</v>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -5941,7 +6112,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H43" s="45" t="inlineStr">
+      <c r="H43" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС); 48 ед. оборудования</t>
         </is>
@@ -5953,7 +6124,7 @@
           <t>Indigo · Инкубаторий, частичная замена</t>
         </is>
       </c>
-      <c r="B44" s="44" t="n">
+      <c r="B44" s="46" t="n">
         <v>106800</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -5961,7 +6132,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H44" s="45" t="inlineStr">
+      <c r="H44" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5973,7 +6144,7 @@
           <t>Indigo · ЗПП, полная замена</t>
         </is>
       </c>
-      <c r="B45" s="44" t="n">
+      <c r="B45" s="46" t="n">
         <v>126200</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -5981,7 +6152,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H45" s="45" t="inlineStr">
+      <c r="H45" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -5993,7 +6164,7 @@
           <t>Indigo · ЗПП, частичная замена</t>
         </is>
       </c>
-      <c r="B46" s="44" t="n">
+      <c r="B46" s="46" t="n">
         <v>106800</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -6001,7 +6172,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H46" s="45" t="inlineStr">
+      <c r="H46" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6013,7 +6184,7 @@
           <t>Indigo · дезинсекция, Айыртау БП</t>
         </is>
       </c>
-      <c r="B47" s="44" t="n">
+      <c r="B47" s="46" t="n">
         <v>720000</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -6021,7 +6192,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H47" s="45" t="inlineStr">
+      <c r="H47" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6033,7 +6204,7 @@
           <t>Indigo · дезинсекция, Многоэтажки</t>
         </is>
       </c>
-      <c r="B48" s="44" t="n">
+      <c r="B48" s="46" t="n">
         <v>1080000</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -6041,7 +6212,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H48" s="45" t="inlineStr">
+      <c r="H48" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6053,7 +6224,7 @@
           <t>Indigo · дезинсекция, Площадки</t>
         </is>
       </c>
-      <c r="B49" s="44" t="n">
+      <c r="B49" s="46" t="n">
         <v>3000000</v>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -6061,7 +6232,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H49" s="45" t="inlineStr">
+      <c r="H49" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6073,7 +6244,7 @@
           <t>Indigo · дезинсекция, Инкубаторий</t>
         </is>
       </c>
-      <c r="B50" s="44" t="n">
+      <c r="B50" s="46" t="n">
         <v>100800</v>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -6081,7 +6252,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H50" s="45" t="inlineStr">
+      <c r="H50" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6093,7 +6264,7 @@
           <t>Indigo · дезинсекция, ЗПП</t>
         </is>
       </c>
-      <c r="B51" s="44" t="n">
+      <c r="B51" s="46" t="n">
         <v>160800</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -6101,7 +6272,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H51" s="45" t="inlineStr">
+      <c r="H51" s="47" t="inlineStr">
         <is>
           <t>Indigo Solutions, КП от 19.08.2026 (цены включают НДС)</t>
         </is>
@@ -6113,7 +6284,7 @@
           <t>Pest Hunters · ККЗ, дератизация</t>
         </is>
       </c>
-      <c r="B52" s="44" t="n">
+      <c r="B52" s="46" t="n">
         <v>75000</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -6121,7 +6292,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H52" s="45" t="inlineStr">
+      <c r="H52" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6133,7 +6304,7 @@
           <t>Pest Hunters · ККЗ, дезинсекция</t>
         </is>
       </c>
-      <c r="B53" s="44" t="n">
+      <c r="B53" s="46" t="n">
         <v>70000</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -6141,7 +6312,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H53" s="45" t="inlineStr">
+      <c r="H53" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6153,7 +6324,7 @@
           <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
-      <c r="B54" s="44" t="n">
+      <c r="B54" s="46" t="n">
         <v>3172000</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -6161,7 +6332,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H54" s="45" t="inlineStr">
+      <c r="H54" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -6173,7 +6344,7 @@
           <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
-      <c r="B55" s="44" t="n">
+      <c r="B55" s="46" t="n">
         <v>2074000</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -6181,7 +6352,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H55" s="45" t="inlineStr">
+      <c r="H55" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
@@ -6193,7 +6364,7 @@
           <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
-      <c r="B56" s="44" t="n">
+      <c r="B56" s="46" t="n">
         <v>2806000</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -6201,7 +6372,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H56" s="45" t="inlineStr">
+      <c r="H56" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -6213,7 +6384,7 @@
           <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
-      <c r="B57" s="44" t="n">
+      <c r="B57" s="46" t="n">
         <v>1830000</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -6221,7 +6392,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H57" s="45" t="inlineStr">
+      <c r="H57" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
@@ -6233,7 +6404,7 @@
           <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
-      <c r="B58" s="44" t="n">
+      <c r="B58" s="46" t="n">
         <v>180000</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
@@ -6241,7 +6412,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H58" s="45" t="inlineStr">
+      <c r="H58" s="47" t="inlineStr">
         <is>
           <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
@@ -6253,7 +6424,7 @@
           <t>Pest Hunters · Инкубаторий, дератизация</t>
         </is>
       </c>
-      <c r="B59" s="44" t="n">
+      <c r="B59" s="46" t="n">
         <v>120000</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -6261,7 +6432,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H59" s="45" t="inlineStr">
+      <c r="H59" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, с. Акимовка</t>
         </is>
@@ -6273,7 +6444,7 @@
           <t>Pest Hunters · Инкубаторий, дезинсекция</t>
         </is>
       </c>
-      <c r="B60" s="44" t="n">
+      <c r="B60" s="46" t="n">
         <v>100000</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -6281,7 +6452,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H60" s="45" t="inlineStr">
+      <c r="H60" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза</t>
         </is>
@@ -6293,7 +6464,7 @@
           <t>Pest Hunters · склад ТМЦ, дератизация</t>
         </is>
       </c>
-      <c r="B61" s="44" t="n">
+      <c r="B61" s="46" t="n">
         <v>40000</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -6301,7 +6472,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H61" s="45" t="inlineStr">
+      <c r="H61" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, пос. К. Кайсенова</t>
         </is>
@@ -6313,7 +6484,7 @@
           <t>Pest Hunters · склад ТМЦ, дезинсекция</t>
         </is>
       </c>
-      <c r="B62" s="44" t="n">
+      <c r="B62" s="46" t="n">
         <v>40000</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -6321,7 +6492,7 @@
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="H62" s="45" t="inlineStr">
+      <c r="H62" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза</t>
         </is>
@@ -6333,7 +6504,7 @@
           <t>Ставка НДС</t>
         </is>
       </c>
-      <c r="B63" s="58" t="n">
+      <c r="B63" s="60" t="n">
         <v>0.16</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -6341,7 +6512,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H63" s="45" t="inlineStr">
+      <c r="H63" s="47" t="inlineStr">
         <is>
           <t>по КП Pest Hunters №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸</t>
         </is>
@@ -6353,7 +6524,7 @@
           <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
-      <c r="B64" s="44" t="n">
+      <c r="B64" s="46" t="n">
         <v>9</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -6361,7 +6532,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H64" s="45" t="inlineStr">
+      <c r="H64" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6373,7 +6544,7 @@
           <t>Месяцев низкого тарифа площадок (дек — фев)</t>
         </is>
       </c>
-      <c r="B65" s="44" t="n">
+      <c r="B65" s="46" t="n">
         <v>3</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -6381,7 +6552,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H65" s="45" t="inlineStr">
+      <c r="H65" s="47" t="inlineStr">
         <is>
           <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
@@ -6393,7 +6564,7 @@
           <t>Месяцев действия договора по складу ТМЦ</t>
         </is>
       </c>
-      <c r="B66" s="44" t="n">
+      <c r="B66" s="46" t="n">
         <v>9</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -6401,7 +6572,7 @@
           <t>мес.</t>
         </is>
       </c>
-      <c r="H66" s="45" t="inlineStr">
+      <c r="H66" s="47" t="inlineStr">
         <is>
           <t>апрель — декабрь 2026</t>
         </is>
@@ -6413,7 +6584,7 @@
           <t>Скидка Indigo за всю территорию фабрики</t>
         </is>
       </c>
-      <c r="B67" s="58" t="n">
+      <c r="B67" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -6421,7 +6592,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H67" s="45" t="inlineStr">
+      <c r="H67" s="47" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, условия предоставления скидок</t>
         </is>
@@ -6433,7 +6604,7 @@
           <t>Скидка Indigo за 100 % предоплату за год</t>
         </is>
       </c>
-      <c r="B68" s="58" t="n">
+      <c r="B68" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -6441,7 +6612,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H68" s="45" t="inlineStr">
+      <c r="H68" s="47" t="inlineStr">
         <is>
           <t>КП от 19.08.2026, дополнительно к предыдущей</t>
         </is>
@@ -6453,7 +6624,7 @@
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B69" s="58" t="n">
+      <c r="B69" s="60" t="n">
         <v>0.16</v>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -6461,7 +6632,7 @@
           <t>доля</t>
         </is>
       </c>
-      <c r="H69" s="45" t="inlineStr">
+      <c r="H69" s="47" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -253,14 +253,14 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1054,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>ВСЕГО ЗА ГОД, РАСХОДНИКИ</t>
+          <t>ВСЕГО ЗА ГОД, ДЕРАТИЗАЦИЯ</t>
         </is>
       </c>
       <c r="B12" s="17">
@@ -1086,15 +1086,17 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ПОДРЯДЧИКИ НА СОПОСТАВИМОЙ БАЗЕ — ЦЕНЫ PEST HUNTERS ПРИВЕДЕНЫ К НДС</t>
+          <t>ДЕЗИНСЕКЦИЯ — ОТДЕЛЬНО ОТ ДЕРАТИЗАЦИИ</t>
         </is>
       </c>
       <c r="B14" s="19" t="n"/>
       <c r="C14" s="19" t="n"/>
       <c r="D14" s="19" t="n"/>
       <c r="E14" s="19" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Объект</t>
@@ -1102,22 +1104,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Indigo, ₸/год (с НДС)</t>
+          <t>Indigo, ₸/мес</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Pest Hunters, ₸/год (с НДС 16 %)</t>
+          <t>Indigo, ₸/год</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Дешевле</t>
+          <t>Pest Hunters, ₸/мес</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Разница, ₸/год</t>
+          <t>Pest Hunters, ₸/год</t>
         </is>
       </c>
     </row>
@@ -1127,873 +1129,1158 @@
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="n"/>
+      <c r="D16" s="10">
+        <f>E16/12</f>
+        <v>70000</v>
+      </c>
+      <c r="E16" s="11">
+        <f>Данные!$B$53*12</f>
+        <v>840000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>C17/12</f>
+        <v>4800000</v>
+      </c>
+      <c r="C17" s="11">
+        <f>(Данные!$B$47+Данные!$B$48+Данные!$B$49)*12</f>
+        <v>57600000</v>
+      </c>
+      <c r="D17" s="10">
+        <f>E17/12</f>
+        <v>1647000</v>
+      </c>
+      <c r="E17" s="11">
+        <f>Данные!$B$54*Данные!$B$55</f>
+        <v>19764000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Инкубаторий</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>C18/12</f>
+        <v>100800</v>
+      </c>
+      <c r="C18" s="11">
+        <f>Данные!$B$50*12</f>
+        <v>1209600</v>
+      </c>
+      <c r="D18" s="10">
+        <f>E18/12</f>
+        <v>100000</v>
+      </c>
+      <c r="E18" s="11">
+        <f>Данные!$B$62*12</f>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>C19/12</f>
+        <v>160800</v>
+      </c>
+      <c r="C19" s="11">
+        <f>Данные!$B$51*12</f>
+        <v>1929600</v>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>входит в договор №88</t>
+        </is>
+      </c>
+      <c r="E19" s="51" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="n"/>
+      <c r="D20" s="10">
+        <f>E20/12</f>
+        <v>40000</v>
+      </c>
+      <c r="E20" s="11">
+        <f>Данные!$B$64*12</f>
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>АБК · 11 корпусов</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="n"/>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>нет в КП</t>
+        </is>
+      </c>
+      <c r="E21" s="51" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>ВСЕГО ЗА ГОД, ДЕЗИНСЕКЦИЯ</t>
+        </is>
+      </c>
+      <c r="B22" s="17">
+        <f>C22/12</f>
+        <v>5061600</v>
+      </c>
+      <c r="C22" s="17">
+        <f>SUM(C16:C21)</f>
+        <v>60739200</v>
+      </c>
+      <c r="D22" s="17">
+        <f>E22/12</f>
+        <v>1857000</v>
+      </c>
+      <c r="E22" s="17">
+        <f>SUM(E16:E21)</f>
+        <v>22284000</v>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Дезинсекцию собственный штат не выполняет — норм расхода по ней нет, поэтому колонки «Штат УКПФ» здесь нет. По ЗПП у Pest Hunters отдельной цены на дезинсекцию не существует: 180 000 ₸/мес по договору №88 покрывают её вместе с дератизацией. По площадкам у Pest Hunters цена задана за обработку (1 раз за 40 дней), число обработок в году принято равным 9 — это допущение, а не цифра из КП.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>ДЕРАТИЗАЦИЯ И ДЕЗИНСЕКЦИЯ ВМЕСТЕ</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Подрядчик</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Дератизация, ₸/год</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Дезинсекция, ₸/год</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Вместе, ₸/год</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B27" s="10">
+        <f>C12</f>
+        <v>49635600</v>
+      </c>
+      <c r="C27" s="10">
+        <f>C22</f>
+        <v>60739200</v>
+      </c>
+      <c r="D27" s="11">
+        <f>B27+C27</f>
+        <v>110374800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B28" s="10">
+        <f>E12</f>
+        <v>39750000</v>
+      </c>
+      <c r="C28" s="10">
+        <f>E22</f>
+        <v>22284000</v>
+      </c>
+      <c r="D28" s="11">
+        <f>B28+C28</f>
+        <v>62034000</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Суммы сложены как есть, без приведения к НДС: у Indigo цены уже с НДС, у Pest Hunters — без. Составы объектов тоже разные, поэтому колонка «Вместе» показывает масштаб, а не готовую цену контракта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>ПОДРЯДЧИКИ НА СОПОСТАВИМОЙ БАЗЕ — ЦЕНЫ PEST HUNTERS ПРИВЕДЕНЫ К НДС</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Indigo, ₸/год (с НДС)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Pest Hunters, ₸/год (с НДС 16 %)</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Дешевле</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Разница, ₸/год</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>ККЗ</t>
+        </is>
+      </c>
+      <c r="B33" s="10">
         <f>C6</f>
         <v>1159200</v>
       </c>
-      <c r="C16" s="10">
-        <f>E6*(1+Данные!$B$63)</f>
+      <c r="C33" s="10">
+        <f>E6*(1+Данные!$B$65)</f>
         <v>1044000</v>
       </c>
-      <c r="D16" s="20" t="str">
-        <f>IF(B16&lt;C16,"Indigo","Pest Hunters")</f>
+      <c r="D33" s="21" t="str">
+        <f>IF(B33&lt;C33,"Indigo","Pest Hunters")</f>
         <v>Pest Hunters</v>
       </c>
-      <c r="E16" s="11">
-        <f>ABS(B16-C16)</f>
+      <c r="E33" s="11">
+        <f>ABS(B33-C33)</f>
         <v>115200</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Бройлерные площадки</t>
         </is>
       </c>
-      <c r="B17" s="10">
+      <c r="B34" s="10">
         <f>C7</f>
         <v>45447600</v>
       </c>
-      <c r="C17" s="10">
-        <f>E7*(1+Данные!$B$63)</f>
+      <c r="C34" s="10">
+        <f>E7*(1+Данные!$B$65)</f>
         <v>40333200</v>
       </c>
-      <c r="D17" s="20" t="str">
-        <f>IF(B17&lt;C17,"Indigo","Pest Hunters")</f>
+      <c r="D34" s="21" t="str">
+        <f>IF(B34&lt;C34,"Indigo","Pest Hunters")</f>
         <v>Pest Hunters</v>
       </c>
-      <c r="E17" s="11">
-        <f>ABS(B17-C17)</f>
+      <c r="E34" s="11">
+        <f>ABS(B34-C34)</f>
         <v>5114400</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B18" s="10">
+      <c r="B35" s="10">
         <f>C8</f>
         <v>1514400</v>
       </c>
-      <c r="C18" s="10">
-        <f>E8*(1+Данные!$B$63)</f>
+      <c r="C35" s="10">
+        <f>E8*(1+Данные!$B$65)</f>
         <v>1670400</v>
       </c>
-      <c r="D18" s="20" t="str">
-        <f>IF(B18&lt;C18,"Indigo","Pest Hunters")</f>
+      <c r="D35" s="21" t="str">
+        <f>IF(B35&lt;C35,"Indigo","Pest Hunters")</f>
         <v>Indigo</v>
       </c>
-      <c r="E18" s="11">
-        <f>ABS(B18-C18)</f>
+      <c r="E35" s="11">
+        <f>ABS(B35-C35)</f>
         <v>156000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="B19" s="10">
+      <c r="B36" s="10">
         <f>C9</f>
         <v>1514400</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C36" s="10">
         <f>E9</f>
         <v>2160000</v>
       </c>
-      <c r="D19" s="20" t="str">
-        <f>IF(B19&lt;C19,"Indigo","Pest Hunters")</f>
+      <c r="D36" s="21" t="str">
+        <f>IF(B36&lt;C36,"Indigo","Pest Hunters")</f>
         <v>Indigo</v>
       </c>
-      <c r="E19" s="11">
-        <f>ABS(B19-C19)</f>
+      <c r="E36" s="11">
+        <f>ABS(B36-C36)</f>
         <v>645600</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Склад ТМЦ</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C20" s="10">
-        <f>E10*(1+Данные!$B$63)</f>
+      <c r="C37" s="10">
+        <f>E10*(1+Данные!$B$65)</f>
         <v>556800</v>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Цены Indigo из КП уже включают НДС, цены Pest Hunters указаны без НДС — здесь к ним добавлены 16 % (ставка из их же КП №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸). Без этого приведения сравнение некорректно: по инкубаторию Pest Hunters в «сырых» цифрах выглядит дешевле, а с НДС оказывается дороже. По ЗПП цена взята из договора №88, ставка НДС в нём не указана, поэтому она показана как есть и включает ещё и дезинсекцию.</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D41" s="24" t="inlineStr">
         <is>
           <t>во сколько раз</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Indigo Solutions дороже штата</t>
         </is>
       </c>
-      <c r="B25" s="10">
-        <f>C25/12</f>
+      <c r="B42" s="10">
+        <f>C42/12</f>
         <v>2003553.062</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C42" s="11">
         <f>C12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
         <v>24042636.75</v>
       </c>
-      <c r="D25" s="53">
+      <c r="D42" s="53">
         <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
         <v>1.93942372</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters дороже штата</t>
         </is>
       </c>
-      <c r="B26" s="10">
-        <f>C26/12</f>
+      <c r="B43" s="10">
+        <f>C43/12</f>
         <v>1179753.062</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C43" s="11">
         <f>E12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
         <v>14157036.75</v>
       </c>
-      <c r="D26" s="53">
+      <c r="D43" s="53">
         <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
         <v>1.553161297</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Штат посчитан вместе с ФОТ (расходники + зарплата), КП подрядчиков — как есть.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Цена за ед., ₸</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>в месяц, ₸</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>за год, ₸</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Численность штата</t>
         </is>
       </c>
-      <c r="B31" s="10">
+      <c r="B48" s="10">
         <f>Данные!$B$13</f>
         <v>5</v>
       </c>
-      <c r="C31" s="27" t="inlineStr">
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Оклад одного дератизатора</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="27" t="inlineStr">
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>₸/мес</t>
         </is>
       </c>
-      <c r="D32" s="10">
+      <c r="D49" s="10">
         <f>Данные!$B$12</f>
         <v>350000</v>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Фонд оплаты труда</t>
         </is>
       </c>
-      <c r="B33" s="10">
+      <c r="B50" s="10">
         <f>Данные!$B$13</f>
         <v>5</v>
       </c>
-      <c r="C33" s="27" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>чел.</t>
         </is>
       </c>
-      <c r="D33" s="10">
+      <c r="D50" s="10">
         <f>Данные!$B$12</f>
         <v>350000</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E50" s="10">
         <f>Данные!$B$13*Данные!$B$12</f>
         <v>1750000</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F50" s="11">
         <f>Данные!$B$13*Данные!$B$12*12</f>
         <v>21000000</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
         </is>
       </c>
-      <c r="B34" s="10">
+      <c r="B51" s="10">
         <f>Данные!$B$32+Данные!$C$32</f>
         <v>1377</v>
       </c>
-      <c r="C34" s="27" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D34" s="10">
+      <c r="D51" s="10">
         <f>Данные!$B$9</f>
         <v>2160</v>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="11">
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="11">
         <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
         <v>2974320</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура · апрель — октябрь</t>
         </is>
       </c>
-      <c r="B35" s="10">
+      <c r="B52" s="10">
         <f>Данные!$D$32</f>
         <v>343</v>
       </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D35" s="10">
+      <c r="D52" s="10">
         <f>Данные!$B$8</f>
         <v>160</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E52" s="10">
         <f>Данные!$D$32*Данные!$B$8</f>
         <v>54880</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F52" s="11">
         <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
         <v>384160</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
         </is>
       </c>
-      <c r="B36" s="10">
+      <c r="B53" s="10">
         <f>Данные!$D$32*2</f>
         <v>686</v>
       </c>
-      <c r="C36" s="27" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D36" s="10">
+      <c r="D53" s="10">
         <f>Данные!$B$8</f>
         <v>160</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E53" s="10">
         <f>Данные!$D$32*2*Данные!$B$8</f>
         <v>109760</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F53" s="11">
         <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
         <v>548800</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Зерноцид · 2-й контур, тёплый сезон</t>
         </is>
       </c>
-      <c r="B37" s="10">
+      <c r="B54" s="10">
         <f>Данные!$G$32</f>
         <v>16</v>
       </c>
-      <c r="C37" s="27" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D37" s="10">
+      <c r="D54" s="10">
         <f>Данные!$B$6</f>
         <v>740</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E54" s="10">
         <f>Данные!$G$32*Данные!$B$6</f>
         <v>11840</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F54" s="11">
         <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
         <v>82880</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
         </is>
       </c>
-      <c r="B38" s="10">
+      <c r="B55" s="10">
         <f>Данные!$F$32</f>
         <v>20.3</v>
       </c>
-      <c r="C38" s="27" t="inlineStr">
+      <c r="C55" s="27" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D38" s="10">
+      <c r="D55" s="10">
         <f>Данные!$B$7</f>
         <v>3642.5</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E55" s="10">
         <f>Данные!$F$32*Данные!$B$7</f>
         <v>73942.75</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F55" s="11">
         <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
         <v>517599.25</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
         </is>
       </c>
-      <c r="B39" s="10">
+      <c r="B56" s="10">
         <f>Данные!$C$32</f>
         <v>1198</v>
       </c>
-      <c r="C39" s="27" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
         </is>
       </c>
-      <c r="B40" s="54">
+      <c r="B57" s="54">
         <f>Данные!$F$32/Данные!$C$32</f>
         <v>0.01694490818</v>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C57" s="27" t="inlineStr">
         <is>
           <t>кг/мес</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Бутылки, 1-й контур · тёплый сезон</t>
         </is>
       </c>
-      <c r="B41" s="10">
+      <c r="B58" s="10">
         <f>Данные!$B$32</f>
         <v>179</v>
       </c>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>шт/мес</t>
         </is>
       </c>
-      <c r="D41" s="10">
+      <c r="D58" s="10">
         <f>Данные!$B$10</f>
         <v>68</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E58" s="10">
         <f>Данные!$B$32*Данные!$B$10</f>
         <v>12172</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F58" s="11">
         <f>Данные!$B$32*Данные!$B$10*Данные!$B$14</f>
         <v>85204</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n"/>
-      <c r="C42" s="29" t="n"/>
-      <c r="D42" s="29" t="n"/>
-      <c r="E42" s="17">
-        <f>F42/12</f>
+      <c r="B59" s="29" t="n"/>
+      <c r="C59" s="29" t="n"/>
+      <c r="D59" s="29" t="n"/>
+      <c r="E59" s="17">
+        <f>F59/12</f>
         <v>2132746.938</v>
       </c>
-      <c r="F42" s="17">
-        <f>F33+F34+F35+F36+F37+F38+F41</f>
+      <c r="F59" s="17">
+        <f>F50+F51+F52+F53+F54+F55+F58</f>
         <v>25592963.25</v>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="22" t="inlineStr">
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="19" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="inlineStr">
         <is>
           <t>Условие</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B63" s="24" t="inlineStr">
         <is>
           <t>в месяц</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C63" s="24" t="inlineStr">
         <is>
           <t>за год</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D63" s="24" t="inlineStr">
         <is>
           <t>Ставка</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>Цена КП без скидок</t>
         </is>
       </c>
-      <c r="B47" s="10">
-        <f>C47/12</f>
+      <c r="B64" s="10">
+        <f>C64/12</f>
         <v>4136300</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C64" s="11">
         <f>C12</f>
         <v>49635600</v>
       </c>
-      <c r="D47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="D64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Вся территория фабрики</t>
         </is>
       </c>
-      <c r="B48" s="10">
-        <f>C48/12</f>
+      <c r="B65" s="10">
+        <f>C65/12</f>
         <v>3515855</v>
       </c>
-      <c r="C48" s="11">
-        <f>C12*(1-Данные!$B$67)</f>
+      <c r="C65" s="11">
+        <f>C12*(1-Данные!$B$69)</f>
         <v>42190260</v>
       </c>
-      <c r="D48" s="55">
-        <f>Данные!$B$67</f>
+      <c r="D65" s="55">
+        <f>Данные!$B$69</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>Вся территория + 100 % предоплата</t>
         </is>
       </c>
-      <c r="B49" s="10">
-        <f>C49/12</f>
+      <c r="B66" s="10">
+        <f>C66/12</f>
         <v>2988476.75</v>
       </c>
-      <c r="C49" s="11">
-        <f>C12*(1-Данные!$B$67)*(1-Данные!$B$68)</f>
+      <c r="C66" s="11">
+        <f>C12*(1-Данные!$B$69)*(1-Данные!$B$70)</f>
         <v>35861721</v>
       </c>
-      <c r="D49" s="55">
-        <f>Данные!$B$68</f>
+      <c r="D66" s="55">
+        <f>Данные!$B$70</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Вся территория + предоплата + неплательщик НДС</t>
         </is>
       </c>
-      <c r="B50" s="10">
-        <f>C50/12</f>
+      <c r="B67" s="10">
+        <f>C67/12</f>
         <v>2510320.47</v>
       </c>
-      <c r="C50" s="11">
-        <f>C12*(1-Данные!$B$67)*(1-Данные!$B$68)*(1-Данные!$B$69)</f>
+      <c r="C67" s="11">
+        <f>C12*(1-Данные!$B$69)*(1-Данные!$B$70)*(1-Данные!$B$71)</f>
         <v>30123845.64</v>
       </c>
-      <c r="D50" s="55">
-        <f>Данные!$B$69</f>
+      <c r="D67" s="55">
+        <f>Данные!$B$71</f>
         <v>0.16</v>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>ПЕРИОДИЧНОСТЬ ОБХОДОВ</t>
         </is>
       </c>
-      <c r="B52" s="19" t="n"/>
-      <c r="C52" s="19" t="n"/>
-      <c r="D52" s="19" t="n"/>
-      <c r="E52" s="19" t="n"/>
-      <c r="F52" s="19" t="n"/>
-      <c r="G52" s="19" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="31" t="inlineStr">
+      <c r="B69" s="19" t="n"/>
+      <c r="C69" s="19" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="19" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B53" s="31" t="inlineStr">
+      <c r="B70" s="31" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C53" s="31" t="inlineStr">
+      <c r="C70" s="31" t="inlineStr">
         <is>
           <t>Обходов в месяц</t>
         </is>
       </c>
-      <c r="D53" s="31" t="inlineStr">
+      <c r="D70" s="31" t="inlineStr">
         <is>
           <t>Что зафиксировано в документах</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C54" s="27" t="inlineStr">
+      <c r="C71" s="27" t="inlineStr">
         <is>
           <t>в КП не указана</t>
         </is>
       </c>
-      <c r="D54" s="32" t="inlineStr">
+      <c r="D71" s="32" t="inlineStr">
         <is>
           <t>ответ по заявке ≤ 2 ч, выезд ≤ 24 ч, вызовы без ограничений</t>
         </is>
       </c>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="50" t="n"/>
-      <c r="G54" s="51" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="E71" s="50" t="n"/>
+      <c r="F71" s="50" t="n"/>
+      <c r="G71" s="51" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="C55" s="27" t="n">
+      <c r="C72" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="D72" s="32" t="inlineStr">
         <is>
           <t>выезд по запросу</t>
         </is>
       </c>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="50" t="n"/>
-      <c r="G55" s="51" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="E72" s="50" t="n"/>
+      <c r="F72" s="50" t="n"/>
+      <c r="G72" s="51" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>бройлерные площадки</t>
         </is>
       </c>
-      <c r="C56" s="27" t="n">
+      <c r="C73" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="32" t="inlineStr">
+      <c r="D73" s="32" t="inlineStr">
         <is>
           <t>дополнительные визиты по вызову</t>
         </is>
       </c>
-      <c r="E56" s="50" t="n"/>
-      <c r="F56" s="50" t="n"/>
-      <c r="G56" s="51" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="E73" s="50" t="n"/>
+      <c r="F73" s="50" t="n"/>
+      <c r="G73" s="51" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>инкубаторий</t>
         </is>
       </c>
-      <c r="C57" s="27" t="n">
+      <c r="C74" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D74" s="32" t="inlineStr">
         <is>
           <t>КП №26/75: ежемесячно 2 раза</t>
         </is>
       </c>
-      <c r="E57" s="50" t="n"/>
-      <c r="F57" s="50" t="n"/>
-      <c r="G57" s="51" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="E74" s="50" t="n"/>
+      <c r="F74" s="50" t="n"/>
+      <c r="G74" s="51" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="C58" s="27" t="n">
+      <c r="C75" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D58" s="32" t="inlineStr">
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>по графику на 2026 год, бригада из трёх человек</t>
         </is>
       </c>
-      <c r="E58" s="50" t="n"/>
-      <c r="F58" s="50" t="n"/>
-      <c r="G58" s="51" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="E75" s="50" t="n"/>
+      <c r="F75" s="50" t="n"/>
+      <c r="G75" s="51" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>склад ТМЦ</t>
         </is>
       </c>
-      <c r="C59" s="27" t="n">
+      <c r="C76" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D59" s="32" t="inlineStr">
+      <c r="D76" s="32" t="inlineStr">
         <is>
           <t>КП №26/75: ежемесячно 2 раза (по договору №921 был 1 обход)</t>
         </is>
       </c>
-      <c r="E59" s="50" t="n"/>
-      <c r="F59" s="50" t="n"/>
-      <c r="G59" s="51" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="E76" s="50" t="n"/>
+      <c r="F76" s="50" t="n"/>
+      <c r="G76" s="51" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>все объекты</t>
         </is>
       </c>
-      <c r="C60" s="27" t="n">
+      <c r="C77" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>присутствие 5/2, реакция в тот же день</t>
         </is>
       </c>
-      <c r="E60" s="50" t="n"/>
-      <c r="F60" s="50" t="n"/>
-      <c r="G60" s="51" t="n"/>
+      <c r="E77" s="50" t="n"/>
+      <c r="F77" s="50" t="n"/>
+      <c r="G77" s="51" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="27">
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="D71:G71"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="D59:G59"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D74:G74"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="D73:G73"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D60:G60"/>
     <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A60:G60"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D77:G77"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D57:G57"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="D76:G76"/>
+    <mergeCell ref="D75:G75"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D72:G72"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2022,7 +2309,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Кормоцех. Indigo — КП от 19.08.2026, цены с НДС. Pest Hunters — КП №26/12, без НДС. Штат УКПФ — 29 приманочных станций 2-го контура по 2 160 ₸/шт разовой закупки, 1 кг брикетов Pest Killer на обработку, только тёплый сезон.</t>
         </is>
@@ -2300,14 +2587,14 @@
     </row>
     <row r="21"/>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Зерноцид по ККЗ в нормах не заявлен, поэтому строка Зерноцида даёт ноль.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Зарплата дератизаторов по объектам не делится — она на листе «Штат УКПФ».</t>
         </is>
@@ -2329,7 +2616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2346,7 +2633,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Восемь площадок: А, Б, В (Восточка), Г, Д, Е, Ж, Айыртау. У Indigo они разбиты на три группы, у Pest Hunters — 122 объекта с сезонным тарифом.</t>
         </is>
@@ -2483,11 +2770,11 @@
         </is>
       </c>
       <c r="B12" s="37">
-        <f>Данные!$B$54</f>
+        <f>Данные!$B$56</f>
         <v>3172000</v>
       </c>
       <c r="C12" s="37">
-        <f>Данные!$B$64</f>
+        <f>Данные!$B$66</f>
         <v>9</v>
       </c>
       <c r="D12" s="11">
@@ -2502,11 +2789,11 @@
         </is>
       </c>
       <c r="B13" s="37">
-        <f>Данные!$B$55</f>
+        <f>Данные!$B$57</f>
         <v>2074000</v>
       </c>
       <c r="C13" s="37">
-        <f>Данные!$B$65</f>
+        <f>Данные!$B$67</f>
         <v>3</v>
       </c>
       <c r="D13" s="11">
@@ -2721,11 +3008,11 @@
         </is>
       </c>
       <c r="B26" s="37">
-        <f>Данные!$B$56</f>
+        <f>Данные!$B$58</f>
         <v>2806000</v>
       </c>
       <c r="C26" s="37">
-        <f>Данные!$B$64</f>
+        <f>Данные!$B$66</f>
         <v>9</v>
       </c>
       <c r="D26" s="10">
@@ -2740,11 +3027,11 @@
         </is>
       </c>
       <c r="B27" s="37">
-        <f>Данные!$B$57</f>
+        <f>Данные!$B$59</f>
         <v>1830000</v>
       </c>
       <c r="C27" s="37">
-        <f>Данные!$B$65</f>
+        <f>Данные!$B$67</f>
         <v>3</v>
       </c>
       <c r="D27" s="10">
@@ -2839,240 +3126,239 @@
         <v>36000000</v>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>Pest Hunters · 122 площадки по 18 000 ₸, 1 раз за 40 дней, без НДС</t>
+        </is>
+      </c>
+      <c r="B34" s="37">
+        <f>Данные!$B$54</f>
+        <v>2196000</v>
+      </c>
+      <c r="C34" s="37">
+        <f>Данные!$B$55</f>
+        <v>9</v>
+      </c>
+      <c r="D34" s="10">
+        <f>B34*C34</f>
+        <v>19764000</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Состав площадок у Indigo и в нашем расчёте описан по-разному: у них шесть напольных площадок плюс «В (рем. молод)», у нас восемь площадок по контурам. Сопоставлять построчно нельзя, только суммарно.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37"/>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>КОНТУР 1 И КОНТУР 2 ПО ПЛОЩАДКАМ, шт</t>
         </is>
       </c>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="19" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Площадка</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>1-й контур</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>2-й контур</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Площадка А</t>
         </is>
       </c>
-      <c r="B40" s="38">
+      <c r="B41" s="38">
         <f>Данные!$B$22</f>
         <v>13</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C41" s="38">
         <f>Данные!$C$22</f>
         <v>147</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Площадка Б</t>
         </is>
       </c>
-      <c r="B41" s="38">
+      <c r="B42" s="38">
         <f>Данные!$B$23</f>
         <v>17</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C42" s="38">
         <f>Данные!$C$23</f>
         <v>146</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>В / Восточка</t>
         </is>
       </c>
-      <c r="B42" s="38">
+      <c r="B43" s="38">
         <f>Данные!$B$24</f>
         <v>50</v>
       </c>
-      <c r="C42" s="38">
+      <c r="C43" s="38">
         <f>Данные!$C$24</f>
         <v>239</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Площадка Г</t>
         </is>
       </c>
-      <c r="B43" s="38">
+      <c r="B44" s="38">
         <f>Данные!$B$25</f>
         <v>17</v>
       </c>
-      <c r="C43" s="38">
+      <c r="C44" s="38">
         <f>Данные!$C$25</f>
         <v>88</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Площадка Д</t>
         </is>
       </c>
-      <c r="B44" s="38">
+      <c r="B45" s="38">
         <f>Данные!$B$26</f>
         <v>15</v>
       </c>
-      <c r="C44" s="38">
+      <c r="C45" s="38">
         <f>Данные!$C$26</f>
         <v>69</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Площадка Е</t>
         </is>
       </c>
-      <c r="B45" s="38">
+      <c r="B46" s="38">
         <f>Данные!$B$27</f>
         <v>13</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C46" s="38">
         <f>Данные!$C$27</f>
         <v>147</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Площадка Ж</t>
         </is>
       </c>
-      <c r="B46" s="38">
+      <c r="B47" s="38">
         <f>Данные!$B$28</f>
         <v>17</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C47" s="38">
         <f>Данные!$C$28</f>
         <v>73</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Айыртау</t>
         </is>
       </c>
-      <c r="B47" s="38">
+      <c r="B48" s="38">
         <f>Данные!$B$29</f>
         <v>19</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C48" s="38">
         <f>Данные!$C$29</f>
         <v>187</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="39" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="39" t="inlineStr">
         <is>
           <t>Итого по площадкам</t>
         </is>
       </c>
-      <c r="B48" s="40">
-        <f>SUM(B40:B47)</f>
+      <c r="B49" s="40">
+        <f>SUM(B41:B48)</f>
         <v>161</v>
       </c>
-      <c r="C48" s="40">
-        <f>SUM(C40:C47)</f>
+      <c r="C49" s="40">
+        <f>SUM(C41:C48)</f>
         <v>1096</v>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>ШТАТ УКПФ ПО БРОЙЛЕРНЫМ ПЛОЩАДКАМ — ДЕТАЛЬНАЯ РАСШИФРОВКА</t>
         </is>
       </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="19" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="B51" s="19" t="n"/>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>₸/мес (разово — цена за шт)</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Мес.</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>За год / разово, ₸</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го контура · разовая закупка</t>
-        </is>
-      </c>
-      <c r="B52" s="10">
-        <f>B48*Данные!$B$9</f>
-        <v>347760</v>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
-        <is>
-          <t>разово</t>
-        </is>
-      </c>
-      <c r="D52" s="10">
-        <f>B48*Данные!$B$9</f>
-        <v>347760</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Приманочные станции 2-го контура · разовая закупка</t>
+          <t>Приманочные станции 1-го контура · разовая закупка</t>
         </is>
       </c>
       <c r="B53" s="10">
-        <f>C48*Данные!$B$9</f>
-        <v>2367360</v>
+        <f>B49*Данные!$B$9</f>
+        <v>347760</v>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
@@ -3080,121 +3366,141 @@
         </is>
       </c>
       <c r="D53" s="10">
-        <f>C48*Данные!$B$9</f>
-        <v>2367360</v>
+        <f>B49*Данные!$B$9</f>
+        <v>347760</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
+          <t>Приманочные станции 2-го контура · разовая закупка</t>
+        </is>
+      </c>
+      <c r="B54" s="10">
+        <f>C49*Данные!$B$9</f>
+        <v>2367360</v>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>разово</t>
+        </is>
+      </c>
+      <c r="D54" s="10">
+        <f>C49*Данные!$B$9</f>
+        <v>2367360</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
           <t>Клеевые станции 3-го контура, тёплый сезон</t>
         </is>
       </c>
-      <c r="B54" s="10">
+      <c r="B55" s="10">
         <f>SUM(Данные!$D$22:$D$29)*Данные!$B$8</f>
         <v>42880</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C55" s="12">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D55" s="10">
         <f>SUM(Данные!$D$22:$D$29)*Данные!$B$8*Данные!$B$14</f>
         <v>300160</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Клеевые станции 3-го контура, зимний сезон — объём вдвое</t>
         </is>
       </c>
-      <c r="B55" s="10">
+      <c r="B56" s="10">
         <f>SUM(Данные!$D$22:$D$29)*2*Данные!$B$8</f>
         <v>85760</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C56" s="12">
         <f>Данные!$B$15</f>
         <v>5</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D56" s="10">
         <f>SUM(Данные!$D$22:$D$29)*2*Данные!$B$8*Данные!$B$15</f>
         <v>428800</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Зерноцид, 2-й контур</t>
         </is>
       </c>
-      <c r="B56" s="10">
+      <c r="B57" s="10">
         <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6</f>
         <v>11100</v>
-      </c>
-      <c r="C56" s="12">
-        <f>Данные!$B$14</f>
-        <v>7</v>
-      </c>
-      <c r="D56" s="10">
-        <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6*Данные!$B$14</f>
-        <v>77700</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты</t>
-        </is>
-      </c>
-      <c r="B57" s="10">
-        <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7</f>
-        <v>61922.5</v>
       </c>
       <c r="C57" s="12">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
       <c r="D57" s="10">
-        <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7*Данные!$B$14</f>
-        <v>433457.5</v>
+        <f>SUM(Данные!$G$22:$G$29)*Данные!$B$6*Данные!$B$14</f>
+        <v>77700</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>Бутылки, 1-й контур, тёплый сезон</t>
+          <t>Pest Killer, брикеты</t>
         </is>
       </c>
       <c r="B58" s="10">
-        <f>B48*Данные!$B$10</f>
-        <v>10948</v>
+        <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7</f>
+        <v>61922.5</v>
       </c>
       <c r="C58" s="12">
         <f>Данные!$B$14</f>
         <v>7</v>
       </c>
       <c r="D58" s="10">
-        <f>B48*Данные!$B$10*Данные!$B$14</f>
+        <f>SUM(Данные!$F$22:$F$29)*Данные!$B$7*Данные!$B$14</f>
+        <v>433457.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Бутылки, 1-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B59" s="10">
+        <f>B49*Данные!$B$10</f>
+        <v>10948</v>
+      </c>
+      <c r="C59" s="12">
+        <f>Данные!$B$14</f>
+        <v>7</v>
+      </c>
+      <c r="D59" s="10">
+        <f>B49*Данные!$B$10*Данные!$B$14</f>
         <v>76636</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>ИТОГО МАТЕРИАЛЫ ПО ПЛОЩАДКАМ, ПЕРВЫЙ ГОД</t>
         </is>
       </c>
-      <c r="B59" s="29" t="n"/>
-      <c r="C59" s="29" t="n"/>
-      <c r="D59" s="17">
-        <f>SUM(D52:D58)</f>
+      <c r="B60" s="29" t="n"/>
+      <c r="C60" s="29" t="n"/>
+      <c r="D60" s="17">
+        <f>SUM(D53:D59)</f>
         <v>4031873.5</v>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="22" t="inlineStr">
+    <row r="61"/>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>Приманочные станции 1-го и 2-го контура показаны раздельно: цена одна и та же (2 160 ₸/шт, разовая закупка), но количество точек по контурам разное — см. таблицу выше.</t>
         </is>
@@ -3202,8 +3508,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3233,7 +3539,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Indigo — КП от 19.08.2026, 48 ед. оборудования, цена с НДС. Pest Hunters — КП №26/75, 2 обхода в месяц, цена без НДС; по их расчёту 52 приманочных контейнера и 60 живоловок.</t>
         </is>
@@ -3334,7 +3640,7 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>Данные!$B$59</f>
+        <f>Данные!$B$61</f>
         <v>120000</v>
       </c>
       <c r="C10" s="37" t="n">
@@ -3516,7 +3822,7 @@
         </is>
       </c>
       <c r="B21" s="37">
-        <f>Данные!$B$59*(1+Данные!$B$63)</f>
+        <f>Данные!$B$61*(1+Данные!$B$65)</f>
         <v>139200</v>
       </c>
       <c r="C21" s="37" t="n">
@@ -3585,7 +3891,7 @@
         </is>
       </c>
       <c r="B26" s="37">
-        <f>Данные!$B$60</f>
+        <f>Данные!$B$62</f>
         <v>100000</v>
       </c>
       <c r="C26" s="37" t="n">
@@ -3598,14 +3904,14 @@
     </row>
     <row r="27"/>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Внимание: цены несопоставимы напрямую. У Indigo 126 200 ₸ уже с НДС, у Pest Hunters 120 000 ₸ без НДС. С НДС 16 % Pest Hunters даёт 139 200 ₸/мес (1 670 400 ₸/год) — это дороже Indigo. Сравнивать нужно строку «приведённая к НДС».</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Нормы штата по инкубаторию: 18 точек 1-го контура, 34 второго, 12 клеевых третьего; 1 кг брикетов Pest Killer и 1 кг Зерноцида на обработку.</t>
         </is>
@@ -3644,7 +3950,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Завод по переработке птицы, 8 309 м². У Pest Hunters — подписанный договор №88, цена включает дезинсекцию. У Indigo — предложение из КП от 19.08.2026.</t>
         </is>
@@ -3745,7 +4051,7 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>Данные!$B$58</f>
+        <f>Данные!$B$60</f>
         <v>180000</v>
       </c>
       <c r="C10" s="37" t="n">
@@ -3877,14 +4183,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Строки не полностью сопоставимы: у Pest Hunters 180 000 ₸ включают и дератизацию, и дезинсекцию, у Indigo эти услуги разделены — 126 200 ₸ дератизация и 160 800 ₸ дезинсекция.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>По штату УКПФ нормы расхода на ЗПП не заданы, поэтому в расчёте ноль.</t>
         </is>
@@ -3923,7 +4229,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Pest Hunters — КП №26/75 на 2026–2027: дератизация и дезинсекция вынесены отдельными строками, 2 обхода в месяц, цены без НДС. Предложений от Indigo по этому объекту нет.</t>
         </is>
@@ -4023,7 +4329,7 @@
         </is>
       </c>
       <c r="B10" s="37">
-        <f>Данные!$B$61</f>
+        <f>Данные!$B$63</f>
         <v>40000</v>
       </c>
       <c r="C10" s="37" t="n">
@@ -4091,7 +4397,7 @@
         </is>
       </c>
       <c r="B15" s="37">
-        <f>Данные!$B$62</f>
+        <f>Данные!$B$64</f>
         <v>40000</v>
       </c>
       <c r="C15" s="37" t="n">
@@ -4145,7 +4451,7 @@
         <v>80000</v>
       </c>
       <c r="C19" s="37">
-        <f>Данные!$B$66</f>
+        <f>Данные!$B$68</f>
         <v>9</v>
       </c>
       <c r="D19" s="10">
@@ -4155,14 +4461,14 @@
     </row>
     <row r="20"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Раньше по складу в сравнение шли 80 000 ₸/мес из договора №921, но эта сумма включает и дезинсекцию. В КП №26/75 услуги разделены: дератизация 40 000 ₸/мес — только она и участвует в сравнении.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>КП №26/75 при той же общей сумме 80 000 ₸/мес даёт 2 обхода в месяц вместо одного по действующему договору.</t>
         </is>
@@ -4201,7 +4507,7 @@
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Административно-бытовые корпуса на одиннадцати площадках. Ни у Indigo, ни у Pest Hunters отдельной строки по АБК нет.</t>
         </is>
@@ -4426,14 +4732,14 @@
     </row>
     <row r="17"/>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Клеевые станции по корпусам: Б — 11, Ж — 5, Е — 6, В — 6, В (РМ) — 6, Д — 3, Г — 3, БП-12 — 6, БП-13 — 6, БП-14 — 6, А — 5. Приманочные: 4, 2, 3, 3, 3, 4, 3, 5, 5, 5, 2.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Норма 1,3 кг брикетов Pest Killer по АБК — приблизительная оценка, требует подтверждения. Зерноцид по АБК не заявлен.</t>
         </is>
@@ -5198,7 +5504,7 @@
     </row>
     <row r="30"/>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Материалы от численности не зависят — норма ядов и станций привязана к точкам, а не к людям. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
         </is>
@@ -5219,7 +5525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6321,51 +6627,51 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки, март — ноябрь</t>
+          <t>Pest Hunters · площадки, дезинсекция</t>
         </is>
       </c>
       <c r="B54" s="46" t="n">
-        <v>3172000</v>
+        <v>2196000</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>₸/мес</t>
+          <t>₸/обраб.</t>
         </is>
       </c>
       <c r="H54" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 площадки по 18 000 ₸, по графику заказчика 1 раз за 40 дней</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки, декабрь — февраль</t>
+          <t>Обработок дезинсекции площадок в год</t>
         </is>
       </c>
       <c r="B55" s="46" t="n">
-        <v>2074000</v>
+        <v>9</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>₸/мес</t>
+          <t>обраб.</t>
         </is>
       </c>
       <c r="H55" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
+          <t>365 ÷ 40 дней ≈ 9,1 — принято 9; периодичность в КП задана в днях, требует подтверждения</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки альт., март — ноябрь</t>
+          <t>Pest Hunters · площадки, март — ноябрь</t>
         </is>
       </c>
       <c r="B56" s="46" t="n">
-        <v>2806000</v>
+        <v>3172000</v>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
@@ -6374,18 +6680,18 @@
       </c>
       <c r="H56" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · площадки альт., дек. — февраль</t>
+          <t>Pest Hunters · площадки, декабрь — февраль</t>
         </is>
       </c>
       <c r="B57" s="46" t="n">
-        <v>1830000</v>
+        <v>2074000</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
@@ -6394,18 +6700,18 @@
       </c>
       <c r="H57" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); 122 объекта, оборудование подрядчика</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · ЗПП</t>
+          <t>Pest Hunters · площадки альт., март — ноябрь</t>
         </is>
       </c>
       <c r="B58" s="46" t="n">
-        <v>180000</v>
+        <v>2806000</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
@@ -6414,18 +6720,18 @@
       </c>
       <c r="H58" s="47" t="inlineStr">
         <is>
-          <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · Инкубаторий, дератизация</t>
+          <t>Pest Hunters · площадки альт., дек. — февраль</t>
         </is>
       </c>
       <c r="B59" s="46" t="n">
-        <v>120000</v>
+        <v>1830000</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
@@ -6434,18 +6740,18 @@
       </c>
       <c r="H59" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, с. Акимовка</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС); оборудование заказчика</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · Инкубаторий, дезинсекция</t>
+          <t>Pest Hunters · ЗПП</t>
         </is>
       </c>
       <c r="B60" s="46" t="n">
-        <v>100000</v>
+        <v>180000</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
@@ -6454,18 +6760,18 @@
       </c>
       <c r="H60" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза</t>
+          <t>договор №88 от 01.01.2026; дератизация + дезинсекция, 8 309 м², 3 обхода в месяц</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · склад ТМЦ, дератизация</t>
+          <t>Pest Hunters · Инкубаторий, дератизация</t>
         </is>
       </c>
       <c r="B61" s="46" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
@@ -6474,18 +6780,18 @@
       </c>
       <c r="H61" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, пос. К. Кайсенова</t>
+          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, с. Акимовка</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>Pest Hunters · склад ТМЦ, дезинсекция</t>
+          <t>Pest Hunters · Инкубаторий, дезинсекция</t>
         </is>
       </c>
       <c r="B62" s="46" t="n">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
@@ -6501,67 +6807,67 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>Ставка НДС</t>
-        </is>
-      </c>
-      <c r="B63" s="60" t="n">
-        <v>0.16</v>
+          <t>Pest Hunters · склад ТМЦ, дератизация</t>
+        </is>
+      </c>
+      <c r="B63" s="46" t="n">
+        <v>40000</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>доля</t>
+          <t>₸/мес</t>
         </is>
       </c>
       <c r="H63" s="47" t="inlineStr">
         <is>
-          <t>по КП Pest Hunters №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸</t>
+          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза, пос. К. Кайсенова</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
+          <t>Pest Hunters · склад ТМЦ, дезинсекция</t>
         </is>
       </c>
       <c r="B64" s="46" t="n">
-        <v>9</v>
+        <v>40000</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>мес.</t>
+          <t>₸/мес</t>
         </is>
       </c>
       <c r="H64" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
+          <t>Pest Hunters, КП №26/75 на 2026–2027 (без НДС); ежемесячно 2 раза</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>Месяцев низкого тарифа площадок (дек — фев)</t>
-        </is>
-      </c>
-      <c r="B65" s="46" t="n">
-        <v>3</v>
+          <t>Ставка НДС</t>
+        </is>
+      </c>
+      <c r="B65" s="60" t="n">
+        <v>0.16</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>мес.</t>
+          <t>доля</t>
         </is>
       </c>
       <c r="H65" s="47" t="inlineStr">
         <is>
-          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
+          <t>по КП Pest Hunters №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>Месяцев действия договора по складу ТМЦ</t>
+          <t>Месяцев высокого тарифа площадок (мар — ноя)</t>
         </is>
       </c>
       <c r="B66" s="46" t="n">
@@ -6574,65 +6880,105 @@
       </c>
       <c r="H66" s="47" t="inlineStr">
         <is>
-          <t>апрель — декабрь 2026</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>Скидка Indigo за всю территорию фабрики</t>
-        </is>
-      </c>
-      <c r="B67" s="60" t="n">
-        <v>0.15</v>
+          <t>Месяцев низкого тарифа площадок (дек — фев)</t>
+        </is>
+      </c>
+      <c r="B67" s="46" t="n">
+        <v>3</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>доля</t>
+          <t>мес.</t>
         </is>
       </c>
       <c r="H67" s="47" t="inlineStr">
         <is>
-          <t>КП от 19.08.2026, условия предоставления скидок</t>
+          <t>Pest Hunters, КП №26/12 на 2026–2027 (без НДС)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>Скидка Indigo за 100 % предоплату за год</t>
-        </is>
-      </c>
-      <c r="B68" s="60" t="n">
-        <v>0.15</v>
+          <t>Месяцев действия договора по складу ТМЦ</t>
+        </is>
+      </c>
+      <c r="B68" s="46" t="n">
+        <v>9</v>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>доля</t>
+          <t>мес.</t>
         </is>
       </c>
       <c r="H68" s="47" t="inlineStr">
         <is>
-          <t>КП от 19.08.2026, дополнительно к предыдущей</t>
+          <t>апрель — декабрь 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
+          <t>Скидка Indigo за всю территорию фабрики</t>
+        </is>
+      </c>
+      <c r="B69" s="60" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>доля</t>
+        </is>
+      </c>
+      <c r="H69" s="47" t="inlineStr">
+        <is>
+          <t>КП от 19.08.2026, условия предоставления скидок</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Скидка Indigo за 100 % предоплату за год</t>
+        </is>
+      </c>
+      <c r="B70" s="60" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>доля</t>
+        </is>
+      </c>
+      <c r="H70" s="47" t="inlineStr">
+        <is>
+          <t>КП от 19.08.2026, дополнительно к предыдущей</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
           <t>Скидка Indigo неплательщику НДС</t>
         </is>
       </c>
-      <c r="B69" s="60" t="n">
+      <c r="B71" s="60" t="n">
         <v>0.16</v>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>доля</t>
         </is>
       </c>
-      <c r="H69" s="47" t="inlineStr">
+      <c r="H71" s="47" t="inlineStr">
         <is>
           <t>КП от 19.08.2026; цены КП уже включают НДС</t>
         </is>

--- a/reports/УКПФ_дератизация_сравнение_КП.xlsx
+++ b/reports/УКПФ_дератизация_сравнение_КП.xlsx
@@ -155,7 +155,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00C8C2AE"/>
+      </right>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -166,9 +168,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00C8C2AE"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="00C8C2AE"/>
       </top>
@@ -214,10 +214,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -251,11 +255,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -284,7 +288,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -313,8 +316,8 @@
     </xf>
     <xf numFmtId="169" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -693,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -723,322 +726,338 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Показывать в таблице:</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Дератизация</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>← выберите из списка</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Indigo Solutions</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Pest Hunters</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Штат УКПФ</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>ЧИСЛЕННОСТЬ ШТАТА: 2 vs 5 ДЕРАТИЗАТОРА</t>
         </is>
       </c>
-      <c r="J4" s="50" t="n"/>
-      <c r="K4" s="51" t="n"/>
+      <c r="J4" s="51" t="n"/>
+      <c r="K4" s="52" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="52" t="n"/>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="53" t="n"/>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>год</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>год</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>месяц (расходники)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>год (расходники)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>2 дератизатора</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>5 дератизаторов</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="12">
         <f>C6/12</f>
         <v>96600</v>
       </c>
-      <c r="C6" s="11">
-        <f>'ККЗ'!B5</f>
+      <c r="C6" s="13">
+        <f>'ККЗ'!B5*($D$3&lt;&gt;"Дезинсекция")+(0)*($D$3&lt;&gt;"Дератизация")</f>
         <v>1159200</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <f>E6/12</f>
         <v>75000</v>
       </c>
-      <c r="E6" s="11">
-        <f>'ККЗ'!C5</f>
+      <c r="E6" s="13">
+        <f>'ККЗ'!C5*($D$3&lt;&gt;"Дезинсекция")+(Данные!$B$53*12)*($D$3&lt;&gt;"Дератизация")</f>
         <v>900000</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="12">
         <f>G6/12</f>
         <v>7344.791667</v>
       </c>
-      <c r="G6" s="11">
-        <f>'ККЗ'!D5</f>
+      <c r="G6" s="13">
+        <f>'ККЗ'!D5*($D$3&lt;&gt;"Дезинсекция")+(0)*($D$3&lt;&gt;"Дератизация")</f>
         <v>88137.5</v>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Оклад одного, ₸/мес</t>
         </is>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="14">
         <f>Данные!$B$11</f>
         <v>258488</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="14">
         <f>Данные!$B$12</f>
         <v>350000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Бройлерные площадки</t>
         </is>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="12">
         <f>C7/12</f>
         <v>3787300</v>
       </c>
-      <c r="C7" s="11">
-        <f>'Бройлерные площадки'!B5</f>
+      <c r="C7" s="13">
+        <f>'Бройлерные площадки'!B5*($D$3&lt;&gt;"Дезинсекция")+((Данные!$B$47+Данные!$B$48+Данные!$B$49)*12)*($D$3&lt;&gt;"Дератизация")</f>
         <v>45447600</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <f>E7/12</f>
         <v>2897500</v>
       </c>
-      <c r="E7" s="11">
-        <f>'Бройлерные площадки'!C5</f>
+      <c r="E7" s="13">
+        <f>'Бройлерные площадки'!C5*($D$3&lt;&gt;"Дезинсекция")+(Данные!$B$54*Данные!$B$55)*($D$3&lt;&gt;"Дератизация")</f>
         <v>34770000</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="12">
         <f>G7/12</f>
         <v>335989.4583</v>
       </c>
-      <c r="G7" s="11">
-        <f>'Бройлерные площадки'!D5</f>
+      <c r="G7" s="13">
+        <f>'Бройлерные площадки'!D5*($D$3&lt;&gt;"Дезинсекция")+(0)*($D$3&lt;&gt;"Дератизация")</f>
         <v>4031873.5</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>ФОТ в месяц, ₸</t>
         </is>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="14">
         <f>2*Данные!$B$11</f>
         <v>516976</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="14">
         <f>5*Данные!$B$12</f>
         <v>1750000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Инкубаторий</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="12">
         <f>C8/12</f>
         <v>126200</v>
       </c>
-      <c r="C8" s="11">
-        <f>'Инкубаторий'!B5</f>
+      <c r="C8" s="13">
+        <f>'Инкубаторий'!B5*($D$3&lt;&gt;"Дезинсекция")+(Данные!$B$50*12)*($D$3&lt;&gt;"Дератизация")</f>
         <v>1514400</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="12">
         <f>E8/12</f>
         <v>120000</v>
       </c>
-      <c r="E8" s="11">
-        <f>'Инкубаторий'!C5</f>
+      <c r="E8" s="13">
+        <f>'Инкубаторий'!C5*($D$3&lt;&gt;"Дезинсекция")+(Данные!$B$62*12)*($D$3&lt;&gt;"Дератизация")</f>
         <v>1440000</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="12">
         <f>G8/12</f>
         <v>15350.45833</v>
       </c>
-      <c r="G8" s="11">
-        <f>'Инкубаторий'!D5</f>
+      <c r="G8" s="13">
+        <f>'Инкубаторий'!D5*($D$3&lt;&gt;"Дезинсекция")+(0)*($D$3&lt;&gt;"Дератизация")</f>
         <v>184205.5</v>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>ФОТ за год, ₸</t>
         </is>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="14">
         <f>2*Данные!$B$11*12</f>
         <v>6203712</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="14">
         <f>5*Данные!$B$12*12</f>
         <v>21000000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>ЗПП</t>
         </is>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="12">
         <f>C9/12</f>
         <v>126200</v>
       </c>
-      <c r="C9" s="11">
-        <f>'ЗПП'!B5</f>
+      <c r="C9" s="13">
+        <f>'ЗПП'!B5*($D$3&lt;&gt;"Дезинсекция")+(Данные!$B$51*12)*($D$3&lt;&gt;"Дератизация")</f>
         <v>1514400</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <f>E9/12</f>
         <v>180000</v>
       </c>
-      <c r="E9" s="11">
-        <f>'ЗПП'!C5</f>
+      <c r="E9" s="13">
+        <f>'ЗПП'!C5*($D$3&lt;&gt;"Дезинсекция")+(0)*($D$3&lt;&gt;"Дератизация")</f>
         <v>2160000</v>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G9" s="51" t="n"/>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="G9" s="52" t="n"/>
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>Материалы, первый год, ₸</t>
         </is>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="14">
         <f>((Данные!$B$32+Данные!$C$32)*Данные!$B$9+Данные!$D$32*Данные!$B$8*Данные!$B$14+Данные!$D$32*2*Данные!$B$8*Данные!$B$15+Данные!$G$32*Данные!$B$6*Данные!$B$14+Данные!$F$32*Данные!$B$7*Данные!$B$14+Данные!$B$32*Данные!$B$10*Данные!$B$14)</f>
         <v>4592963.25</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="14">
         <f>((Данные!$B$32+Данные!$C$32)*Данные!$B$9+Данные!$D$32*Данные!$B$8*Данные!$B$14+Данные!$D$32*2*Данные!$B$8*Данные!$B$15+Данные!$G$32*Данные!$B$6*Данные!$B$14+Данные!$F$32*Данные!$B$7*Данные!$B$14+Данные!$B$32*Данные!$B$10*Данные!$B$14)</f>
         <v>4592963.25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Склад ТМЦ</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C10" s="51" t="n"/>
-      <c r="D10" s="10">
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="12">
         <f>E10/12</f>
         <v>40000</v>
       </c>
-      <c r="E10" s="11">
-        <f>'Склад ТМЦ'!C5</f>
+      <c r="E10" s="13">
+        <f>'Склад ТМЦ'!C5*($D$3&lt;&gt;"Дезинсекция")+(Данные!$B$64*12)*($D$3&lt;&gt;"Дератизация")</f>
         <v>480000</v>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>нормы не заданы</t>
         </is>
       </c>
-      <c r="G10" s="51" t="n"/>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="G10" s="52" t="n"/>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>ИТОГО, ПЕРВЫЙ ГОД, ₸</t>
         </is>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="17">
         <f>J8+J9</f>
         <v>10796675.25</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="17">
         <f>K8+K9</f>
         <v>25592963.25</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>АБК · 11 корпусов</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C11" s="51" t="n"/>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="E11" s="51" t="n"/>
-      <c r="F11" s="10">
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="12">
         <f>G11/12</f>
         <v>24062.22917</v>
       </c>
-      <c r="G11" s="11">
-        <f>'АБК'!D5</f>
+      <c r="G11" s="13">
+        <f>'АБК'!D5*($D$3&lt;&gt;"Дезинсекция")+(0)*($D$3&lt;&gt;"Дератизация")</f>
         <v>288746.75</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1046,1242 +1065,1050 @@
           <t>Разница 5 против 2 чел., ₸/год</t>
         </is>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="18">
         <f>K10-J10</f>
         <v>14796288</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>ВСЕГО ЗА ГОД, ДЕРАТИЗАЦИЯ</t>
-        </is>
-      </c>
-      <c r="B12" s="17">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>ВСЕГО ЗА ГОД</t>
+        </is>
+      </c>
+      <c r="B12" s="19">
         <f>C12/12</f>
         <v>4136300</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="19">
         <f>SUM(C6:C11)</f>
         <v>49635600</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <f>E12/12</f>
         <v>3312500</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="19">
         <f>SUM(E6:E11)</f>
         <v>39750000</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="19">
         <f>G12/12</f>
         <v>382746.9375</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="19">
         <f>SUM(G6:G11)</f>
         <v>4592963.25</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>ДЕЗИНСЕКЦИЯ — ОТДЕЛЬНО ОТ ДЕРАТИЗАЦИИ</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Indigo, ₸/мес</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Indigo, ₸/год</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Pest Hunters, ₸/мес</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Pest Hunters, ₸/год</t>
-        </is>
-      </c>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Прочерк в колонке «Штат УКПФ» при выбранной дезинсекции — норм по ней у собственной службы нет. По ЗПП у Pest Hunters отдельной цены на дезинсекцию не существует: 180 000 ₸/мес по договору №88 покрывают её вместе с дератизацией, поэтому в режиме дезинсекции там ноль, а в режиме дератизации — вся сумма договора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>ДЕРАТИЗАЦИЯ И ДЕЗИНСЕКЦИЯ ВМЕСТЕ</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
+          <t>Подрядчик</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Дератизация, ₸/год</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Дезинсекция, ₸/год</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Вместе, ₸/год</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Indigo Solutions</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>'ККЗ'!B5+'Бройлерные площадки'!B5+'Инкубаторий'!B5+'ЗПП'!B5+'Склад ТМЦ'!B5+'АБК'!B5</f>
+        <v>49635600</v>
+      </c>
+      <c r="C17" s="12">
+        <f>(Данные!$B$47+Данные!$B$48+Данные!$B$49)*12+Данные!$B$50*12+Данные!$B$51*12</f>
+        <v>60739200</v>
+      </c>
+      <c r="D17" s="13">
+        <f>B17+C17</f>
+        <v>110374800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>'ККЗ'!C5+'Бройлерные площадки'!C5+'Инкубаторий'!C5+'ЗПП'!C5+'Склад ТМЦ'!C5+'АБК'!C5</f>
+        <v>39750000</v>
+      </c>
+      <c r="C18" s="12">
+        <f>Данные!$B$53*12+Данные!$B$54*Данные!$B$55+Данные!$B$62*12+Данные!$B$64*12</f>
+        <v>22284000</v>
+      </c>
+      <c r="D18" s="13">
+        <f>B18+C18</f>
+        <v>62034000</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Эта таблица не зависит от переключателя — она всегда показывает обе услуги. Суммы сложены как есть, без приведения к НДС: у Indigo цены уже с НДС, у Pest Hunters — без. Составы объектов тоже разные, поэтому колонка «Вместе» показывает масштаб, а не готовую цену контракта. Дезинсекция площадок у Pest Hunters задана за обработку (1 раз за 40 дней), число обработок в году принято равным 9 — это допущение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>ПОДРЯДЧИКИ НА СОПОСТАВИМОЙ БАЗЕ — ЦЕНЫ PEST HUNTERS ПРИВЕДЕНЫ К НДС</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Indigo, ₸/год (с НДС)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Pest Hunters, ₸/год (с НДС 16 %)</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Дешевле</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Разница, ₸/год</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>ККЗ</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B23" s="12">
+        <f>C6</f>
+        <v>1159200</v>
+      </c>
+      <c r="C23" s="12">
+        <f>E6*(1+Данные!$B$65)</f>
+        <v>1044000</v>
+      </c>
+      <c r="D23" s="23" t="str">
+        <f>IF(B23&lt;C23,"Indigo","Pest Hunters")</f>
+        <v>Pest Hunters</v>
+      </c>
+      <c r="E23" s="13">
+        <f>ABS(B23-C23)</f>
+        <v>115200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Бройлерные площадки</t>
+        </is>
+      </c>
+      <c r="B24" s="12">
+        <f>C7</f>
+        <v>45447600</v>
+      </c>
+      <c r="C24" s="12">
+        <f>E7*(1+Данные!$B$65)</f>
+        <v>40333200</v>
+      </c>
+      <c r="D24" s="23" t="str">
+        <f>IF(B24&lt;C24,"Indigo","Pest Hunters")</f>
+        <v>Pest Hunters</v>
+      </c>
+      <c r="E24" s="13">
+        <f>ABS(B24-C24)</f>
+        <v>5114400</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Инкубаторий</t>
+        </is>
+      </c>
+      <c r="B25" s="12">
+        <f>C8</f>
+        <v>1514400</v>
+      </c>
+      <c r="C25" s="12">
+        <f>E8*(1+Данные!$B$65)</f>
+        <v>1670400</v>
+      </c>
+      <c r="D25" s="23" t="str">
+        <f>IF(B25&lt;C25,"Indigo","Pest Hunters")</f>
+        <v>Indigo</v>
+      </c>
+      <c r="E25" s="13">
+        <f>ABS(B25-C25)</f>
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>ЗПП</t>
+        </is>
+      </c>
+      <c r="B26" s="12">
+        <f>C9</f>
+        <v>1514400</v>
+      </c>
+      <c r="C26" s="12">
+        <f>E9</f>
+        <v>2160000</v>
+      </c>
+      <c r="D26" s="23" t="str">
+        <f>IF(B26&lt;C26,"Indigo","Pest Hunters")</f>
+        <v>Indigo</v>
+      </c>
+      <c r="E26" s="13">
+        <f>ABS(B26-C26)</f>
+        <v>645600</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Склад ТМЦ</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>нет в КП</t>
         </is>
       </c>
-      <c r="C16" s="51" t="n"/>
-      <c r="D16" s="10">
-        <f>E16/12</f>
-        <v>70000</v>
-      </c>
-      <c r="E16" s="11">
-        <f>Данные!$B$53*12</f>
-        <v>840000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Бройлерные площадки</t>
-        </is>
-      </c>
-      <c r="B17" s="10">
-        <f>C17/12</f>
-        <v>4800000</v>
-      </c>
-      <c r="C17" s="11">
-        <f>(Данные!$B$47+Данные!$B$48+Данные!$B$49)*12</f>
-        <v>57600000</v>
-      </c>
-      <c r="D17" s="10">
-        <f>E17/12</f>
-        <v>1647000</v>
-      </c>
-      <c r="E17" s="11">
-        <f>Данные!$B$54*Данные!$B$55</f>
-        <v>19764000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Инкубаторий</t>
-        </is>
-      </c>
-      <c r="B18" s="10">
-        <f>C18/12</f>
-        <v>100800</v>
-      </c>
-      <c r="C18" s="11">
-        <f>Данные!$B$50*12</f>
-        <v>1209600</v>
-      </c>
-      <c r="D18" s="10">
-        <f>E18/12</f>
-        <v>100000</v>
-      </c>
-      <c r="E18" s="11">
-        <f>Данные!$B$62*12</f>
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="B19" s="10">
-        <f>C19/12</f>
-        <v>160800</v>
-      </c>
-      <c r="C19" s="11">
-        <f>Данные!$B$51*12</f>
-        <v>1929600</v>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>входит в договор №88</t>
-        </is>
-      </c>
-      <c r="E19" s="51" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="10">
-        <f>E20/12</f>
-        <v>40000</v>
-      </c>
-      <c r="E20" s="11">
-        <f>Данные!$B$64*12</f>
-        <v>480000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>АБК · 11 корпусов</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="n"/>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="E21" s="51" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>ВСЕГО ЗА ГОД, ДЕЗИНСЕКЦИЯ</t>
-        </is>
-      </c>
-      <c r="B22" s="17">
-        <f>C22/12</f>
-        <v>5061600</v>
-      </c>
-      <c r="C22" s="17">
-        <f>SUM(C16:C21)</f>
-        <v>60739200</v>
-      </c>
-      <c r="D22" s="17">
-        <f>E22/12</f>
-        <v>1857000</v>
-      </c>
-      <c r="E22" s="17">
-        <f>SUM(E16:E21)</f>
-        <v>22284000</v>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Дезинсекцию собственный штат не выполняет — норм расхода по ней нет, поэтому колонки «Штат УКПФ» здесь нет. По ЗПП у Pest Hunters отдельной цены на дезинсекцию не существует: 180 000 ₸/мес по договору №88 покрывают её вместе с дератизацией. По площадкам у Pest Hunters цена задана за обработку (1 раз за 40 дней), число обработок в году принято равным 9 — это допущение, а не цифра из КП.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>ДЕРАТИЗАЦИЯ И ДЕЗИНСЕКЦИЯ ВМЕСТЕ</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
-      <c r="G25" s="19" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Подрядчик</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Дератизация, ₸/год</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Дезинсекция, ₸/год</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Вместе, ₸/год</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Indigo Solutions</t>
-        </is>
-      </c>
-      <c r="B27" s="10">
+      <c r="C27" s="12">
+        <f>E10*(1+Данные!$B$65)</f>
+        <v>556800</v>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Pest Hunters</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Цены Indigo из КП уже включают НДС, цены Pest Hunters указаны без НДС — здесь к ним добавлены 16 % (ставка из их же КП №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸). Без этого приведения сравнение некорректно: по инкубаторию Pest Hunters в «сырых» цифрах выглядит дешевле, а с НДС оказывается дороже. По ЗПП цена взята из договора №88, ставка НДС в нём не указана, поэтому она показана как есть и включает ещё и дезинсекцию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>во сколько раз</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Indigo Solutions дороже штата</t>
+        </is>
+      </c>
+      <c r="B32" s="12">
+        <f>C32/12</f>
+        <v>2003553.062</v>
+      </c>
+      <c r="C32" s="13">
+        <f>C12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
+        <v>24042636.75</v>
+      </c>
+      <c r="D32" s="54">
+        <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
+        <v>1.93942372</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Pest Hunters дороже штата</t>
+        </is>
+      </c>
+      <c r="B33" s="12">
+        <f>C33/12</f>
+        <v>1179753.062</v>
+      </c>
+      <c r="C33" s="13">
+        <f>E12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
+        <v>14157036.75</v>
+      </c>
+      <c r="D33" s="54">
+        <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
+        <v>1.553161297</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Штат посчитан вместе с ФОТ (расходники + зарплата), КП подрядчиков — как есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Количество</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Ед. изм.</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Цена за ед., ₸</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>в месяц, ₸</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>за год, ₸</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Численность штата</t>
+        </is>
+      </c>
+      <c r="B38" s="12">
+        <f>Данные!$B$13</f>
+        <v>5</v>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>чел.</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Оклад одного дератизатора</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>₸/мес</t>
+        </is>
+      </c>
+      <c r="D39" s="12">
+        <f>Данные!$B$12</f>
+        <v>350000</v>
+      </c>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Фонд оплаты труда</t>
+        </is>
+      </c>
+      <c r="B40" s="12">
+        <f>Данные!$B$13</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>чел.</t>
+        </is>
+      </c>
+      <c r="D40" s="12">
+        <f>Данные!$B$12</f>
+        <v>350000</v>
+      </c>
+      <c r="E40" s="12">
+        <f>Данные!$B$13*Данные!$B$12</f>
+        <v>1750000</v>
+      </c>
+      <c r="F40" s="13">
+        <f>Данные!$B$13*Данные!$B$12*12</f>
+        <v>21000000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
+        </is>
+      </c>
+      <c r="B41" s="12">
+        <f>Данные!$B$32+Данные!$C$32</f>
+        <v>1377</v>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D41" s="12">
+        <f>Данные!$B$9</f>
+        <v>2160</v>
+      </c>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="13">
+        <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
+        <v>2974320</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
+        </is>
+      </c>
+      <c r="B42" s="12">
+        <f>Данные!$D$32</f>
+        <v>343</v>
+      </c>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D42" s="12">
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E42" s="12">
+        <f>Данные!$D$32*Данные!$B$8</f>
+        <v>54880</v>
+      </c>
+      <c r="F42" s="13">
+        <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
+        <v>384160</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
+        </is>
+      </c>
+      <c r="B43" s="12">
+        <f>Данные!$D$32*2</f>
+        <v>686</v>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D43" s="12">
+        <f>Данные!$B$8</f>
+        <v>160</v>
+      </c>
+      <c r="E43" s="12">
+        <f>Данные!$D$32*2*Данные!$B$8</f>
+        <v>109760</v>
+      </c>
+      <c r="F43" s="13">
+        <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
+        <v>548800</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Зерноцид · 2-й контур, тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B44" s="12">
+        <f>Данные!$G$32</f>
+        <v>16</v>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D44" s="12">
+        <f>Данные!$B$6</f>
+        <v>740</v>
+      </c>
+      <c r="E44" s="12">
+        <f>Данные!$G$32*Данные!$B$6</f>
+        <v>11840</v>
+      </c>
+      <c r="F44" s="13">
+        <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
+        <v>82880</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
+        </is>
+      </c>
+      <c r="B45" s="12">
+        <f>Данные!$F$32</f>
+        <v>20.3</v>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D45" s="12">
+        <f>Данные!$B$7</f>
+        <v>3642.5</v>
+      </c>
+      <c r="E45" s="12">
+        <f>Данные!$F$32*Данные!$B$7</f>
+        <v>73942.75</v>
+      </c>
+      <c r="F45" s="13">
+        <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
+        <v>517599.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
+        </is>
+      </c>
+      <c r="B46" s="12">
+        <f>Данные!$C$32</f>
+        <v>1198</v>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
+        </is>
+      </c>
+      <c r="B47" s="55">
+        <f>Данные!$F$32/Данные!$C$32</f>
+        <v>0.01694490818</v>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>кг/мес</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Бутылки, 1-й контур · тёплый сезон</t>
+        </is>
+      </c>
+      <c r="B48" s="12">
+        <f>Данные!$B$32</f>
+        <v>179</v>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>шт/мес</t>
+        </is>
+      </c>
+      <c r="D48" s="12">
+        <f>Данные!$B$10</f>
+        <v>68</v>
+      </c>
+      <c r="E48" s="12">
+        <f>Данные!$B$32*Данные!$B$10</f>
+        <v>12172</v>
+      </c>
+      <c r="F48" s="13">
+        <f>Данные!$B$32*Данные!$B$10*Данные!$B$14</f>
+        <v>85204</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>ИТОГО ШТАТ УКПФ, ПЕРВЫЙ ГОД (с разовой закупкой станций)</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="n"/>
+      <c r="C49" s="31" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="19">
+        <f>F49/12</f>
+        <v>2132746.938</v>
+      </c>
+      <c r="F49" s="19">
+        <f>F40+F41+F42+F43+F44+F45+F48</f>
+        <v>25592963.25</v>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Материалы от численности не зависят: норма ядов и станций привязана к точкам, а не к людям. Станции — разовая закупка (входит только в первый год); яды и клей — ежегодно, только тёплый сезон. Каждый дополнительный дератизатор добавляет только фонд оплаты труда.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>СКИДКИ INDIGO ИЗ КП ОТ 19.08.2026</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="22" t="n"/>
+      <c r="G52" s="22" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Условие</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>за год</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>Цена КП без скидок</t>
+        </is>
+      </c>
+      <c r="B54" s="12">
+        <f>C54/12</f>
+        <v>4136300</v>
+      </c>
+      <c r="C54" s="13">
         <f>C12</f>
         <v>49635600</v>
       </c>
-      <c r="C27" s="10">
-        <f>C22</f>
-        <v>60739200</v>
-      </c>
-      <c r="D27" s="11">
-        <f>B27+C27</f>
-        <v>110374800</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="B28" s="10">
-        <f>E12</f>
-        <v>39750000</v>
-      </c>
-      <c r="C28" s="10">
-        <f>E22</f>
-        <v>22284000</v>
-      </c>
-      <c r="D28" s="11">
-        <f>B28+C28</f>
-        <v>62034000</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Суммы сложены как есть, без приведения к НДС: у Indigo цены уже с НДС, у Pest Hunters — без. Составы объектов тоже разные, поэтому колонка «Вместе» показывает масштаб, а не готовую цену контракта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>ПОДРЯДЧИКИ НА СОПОСТАВИМОЙ БАЗЕ — ЦЕНЫ PEST HUNTERS ПРИВЕДЕНЫ К НДС</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Indigo, ₸/год (с НДС)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Pest Hunters, ₸/год (с НДС 16 %)</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Дешевле</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>Разница, ₸/год</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>ККЗ</t>
-        </is>
-      </c>
-      <c r="B33" s="10">
-        <f>C6</f>
-        <v>1159200</v>
-      </c>
-      <c r="C33" s="10">
-        <f>E6*(1+Данные!$B$65)</f>
-        <v>1044000</v>
-      </c>
-      <c r="D33" s="21" t="str">
-        <f>IF(B33&lt;C33,"Indigo","Pest Hunters")</f>
-        <v>Pest Hunters</v>
-      </c>
-      <c r="E33" s="11">
-        <f>ABS(B33-C33)</f>
-        <v>115200</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Бройлерные площадки</t>
-        </is>
-      </c>
-      <c r="B34" s="10">
-        <f>C7</f>
-        <v>45447600</v>
-      </c>
-      <c r="C34" s="10">
-        <f>E7*(1+Данные!$B$65)</f>
-        <v>40333200</v>
-      </c>
-      <c r="D34" s="21" t="str">
-        <f>IF(B34&lt;C34,"Indigo","Pest Hunters")</f>
-        <v>Pest Hunters</v>
-      </c>
-      <c r="E34" s="11">
-        <f>ABS(B34-C34)</f>
-        <v>5114400</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Инкубаторий</t>
-        </is>
-      </c>
-      <c r="B35" s="10">
-        <f>C8</f>
-        <v>1514400</v>
-      </c>
-      <c r="C35" s="10">
-        <f>E8*(1+Данные!$B$65)</f>
-        <v>1670400</v>
-      </c>
-      <c r="D35" s="21" t="str">
-        <f>IF(B35&lt;C35,"Indigo","Pest Hunters")</f>
-        <v>Indigo</v>
-      </c>
-      <c r="E35" s="11">
-        <f>ABS(B35-C35)</f>
-        <v>156000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>ЗПП</t>
-        </is>
-      </c>
-      <c r="B36" s="10">
-        <f>C9</f>
-        <v>1514400</v>
-      </c>
-      <c r="C36" s="10">
-        <f>E9</f>
-        <v>2160000</v>
-      </c>
-      <c r="D36" s="21" t="str">
-        <f>IF(B36&lt;C36,"Indigo","Pest Hunters")</f>
-        <v>Indigo</v>
-      </c>
-      <c r="E36" s="11">
-        <f>ABS(B36-C36)</f>
-        <v>645600</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Склад ТМЦ</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>нет в КП</t>
-        </is>
-      </c>
-      <c r="C37" s="10">
-        <f>E10*(1+Данные!$B$65)</f>
-        <v>556800</v>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>Pest Hunters</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="46" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Цены Indigo из КП уже включают НДС, цены Pest Hunters указаны без НДС — здесь к ним добавлены 16 % (ставка из их же КП №26/12: 2 196 000 ₸ + НДС = 2 547 360 ₸). Без этого приведения сравнение некорректно: по инкубаторию Pest Hunters в «сырых» цифрах выглядит дешевле, а с НДС оказывается дороже. По ЗПП цена взята из договора №88, ставка НДС в нём не указана, поэтому она показана как есть и включает ещё и дезинсекцию.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>РАЗНИЦА С СОБСТВЕННЫМ ШТАТОМ</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>в месяц</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>за год</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>во сколько раз</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Indigo Solutions дороже штата</t>
-        </is>
-      </c>
-      <c r="B42" s="10">
-        <f>C42/12</f>
-        <v>2003553.062</v>
-      </c>
-      <c r="C42" s="11">
-        <f>C12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
-        <v>24042636.75</v>
-      </c>
-      <c r="D42" s="53">
-        <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,C12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
-        <v>1.93942372</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Pest Hunters дороже штата</t>
-        </is>
-      </c>
-      <c r="B43" s="10">
-        <f>C43/12</f>
-        <v>1179753.062</v>
-      </c>
-      <c r="C43" s="11">
-        <f>E12-(G12+Данные!$B$13*Данные!$B$12*12)</f>
-        <v>14157036.75</v>
-      </c>
-      <c r="D43" s="53">
-        <f>IF((G12+Данные!$B$13*Данные!$B$12*12)=0,0,E12/(G12+Данные!$B$13*Данные!$B$12*12))</f>
-        <v>1.553161297</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Штат посчитан вместе с ФОТ (расходники + зарплата), КП подрядчиков — как есть.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>ШТАТ УКПФ · ПОЛНАЯ РАСШИФРОВКА</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="19" t="n"/>
-      <c r="F46" s="19" t="n"/>
-      <c r="G46" s="19" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="26" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Количество</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Ед. изм.</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Цена за ед., ₸</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>в месяц, ₸</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>за год, ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>Численность штата</t>
-        </is>
-      </c>
-      <c r="B48" s="10">
-        <f>Данные!$B$13</f>
-        <v>5</v>
-      </c>
-      <c r="C48" s="27" t="inlineStr">
-        <is>
-          <t>чел.</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>Оклад одного дератизатора</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>₸/мес</t>
-        </is>
-      </c>
-      <c r="D49" s="10">
-        <f>Данные!$B$12</f>
-        <v>350000</v>
-      </c>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Фонд оплаты труда</t>
-        </is>
-      </c>
-      <c r="B50" s="10">
-        <f>Данные!$B$13</f>
-        <v>5</v>
-      </c>
-      <c r="C50" s="27" t="inlineStr">
-        <is>
-          <t>чел.</t>
-        </is>
-      </c>
-      <c r="D50" s="10">
-        <f>Данные!$B$12</f>
-        <v>350000</v>
-      </c>
-      <c r="E50" s="10">
-        <f>Данные!$B$13*Данные!$B$12</f>
-        <v>1750000</v>
-      </c>
-      <c r="F50" s="11">
-        <f>Данные!$B$13*Данные!$B$12*12</f>
-        <v>21000000</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Приманочные станции 1-го и 2-го контура · разовая закупка</t>
-        </is>
-      </c>
-      <c r="B51" s="10">
-        <f>Данные!$B$32+Данные!$C$32</f>
-        <v>1377</v>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D51" s="10">
-        <f>Данные!$B$9</f>
-        <v>2160</v>
-      </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="11">
-        <f>(Данные!$B$32+Данные!$C$32)*Данные!$B$9</f>
-        <v>2974320</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура · апрель — октябрь</t>
-        </is>
-      </c>
-      <c r="B52" s="10">
-        <f>Данные!$D$32</f>
-        <v>343</v>
-      </c>
-      <c r="C52" s="27" t="inlineStr">
-        <is>
-          <t>шт/мес</t>
-        </is>
-      </c>
-      <c r="D52" s="10">
-        <f>Данные!$B$8</f>
-        <v>160</v>
-      </c>
-      <c r="E52" s="10">
-        <f>Данные!$D$32*Данные!$B$8</f>
-        <v>54880</v>
-      </c>
-      <c r="F52" s="11">
-        <f>Данные!$D$32*Данные!$B$8*Данные!$B$14</f>
-        <v>384160</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>Клеевые станции 3-го контура · ноябрь — март, объём вдвое</t>
-        </is>
-      </c>
-      <c r="B53" s="10">
-        <f>Данные!$D$32*2</f>
-        <v>686</v>
-      </c>
-      <c r="C53" s="27" t="inlineStr">
-        <is>
-          <t>шт/мес</t>
-        </is>
-      </c>
-      <c r="D53" s="10">
-        <f>Данные!$B$8</f>
-        <v>160</v>
-      </c>
-      <c r="E53" s="10">
-        <f>Данные!$D$32*2*Данные!$B$8</f>
-        <v>109760</v>
-      </c>
-      <c r="F53" s="11">
-        <f>Данные!$D$32*2*Данные!$B$8*Данные!$B$15</f>
-        <v>548800</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Зерноцид · 2-й контур, тёплый сезон</t>
-        </is>
-      </c>
-      <c r="B54" s="10">
-        <f>Данные!$G$32</f>
-        <v>16</v>
-      </c>
-      <c r="C54" s="27" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D54" s="10">
-        <f>Данные!$B$6</f>
-        <v>740</v>
-      </c>
-      <c r="E54" s="10">
-        <f>Данные!$G$32*Данные!$B$6</f>
-        <v>11840</v>
-      </c>
-      <c r="F54" s="11">
-        <f>Данные!$G$32*Данные!$B$6*Данные!$B$14</f>
-        <v>82880</v>
-      </c>
+      <c r="D54" s="7" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Pest Killer, брикеты · заряжаются в станции 2-го контура</t>
-        </is>
-      </c>
-      <c r="B55" s="10">
-        <f>Данные!$F$32</f>
-        <v>20.3</v>
-      </c>
-      <c r="C55" s="27" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D55" s="10">
-        <f>Данные!$B$7</f>
-        <v>3642.5</v>
-      </c>
-      <c r="E55" s="10">
-        <f>Данные!$F$32*Данные!$B$7</f>
-        <v>73942.75</v>
-      </c>
-      <c r="F55" s="11">
-        <f>Данные!$F$32*Данные!$B$7*Данные!$B$14</f>
-        <v>517599.25</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   в том числе станций 2-го контура, которые заряжаются</t>
-        </is>
-      </c>
-      <c r="B56" s="10">
-        <f>Данные!$C$32</f>
-        <v>1198</v>
-      </c>
-      <c r="C56" s="27" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-      <c r="F56" s="5" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   расход брикетов на одну станцию 2-го контура</t>
-        </is>
-      </c>
-      <c r="B57" s="54">
-        <f>Данные!$F$32/Данные!$C$32</f>
-        <v>0.01694490818</v>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
-        <is>
-          <t>кг/мес</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
-      <c r="F57" s="5" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>Бутылки, 1-й контур · тёплый сезон</t>
-        </is>
-      </c>
-      <c r="B58" s="10">
-        <f>Данные!$B$32</f>
-        <v>179</v>
-      </c>
-      <c r="C58" s="27" t="inlineStr">
-        <is>
-       